--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Strategy" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Positions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Trades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="By Strategy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Open Positions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="README" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1058,7 +1058,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-03T16:30:53.964838 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-03T20:54:02.775861 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -620,8 +620,22 @@
       <c r="T2" t="n">
         <v>0.32</v>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>63775.6</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -649,7 +663,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -658,8 +672,22 @@
       <c r="T3" t="n">
         <v>0.14</v>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1861.73</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -698,6 +726,1428 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>680</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>63541.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L5" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M5" t="n">
+        <v>62200</v>
+      </c>
+      <c r="N5" t="n">
+        <v>65400</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.3121</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-100.57</v>
+      </c>
+      <c r="T5" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>63775.6</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>-104.72</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-10.472</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-04T06:36</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>750</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>63769.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L6" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M6" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.5531</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-99.59999999999999</v>
+      </c>
+      <c r="T6" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>63769.2</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>-103.65</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-10.365</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-04T06:36</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>63769.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L7" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.4251</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-100.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>63769.2</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>-104.21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-10.421</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-04T06:36</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>long_strangle_wk</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>110</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>63769.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>71000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.09760000000000001</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-100.13</v>
+      </c>
+      <c r="T8" t="n">
+        <v>100.13</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-04T06:36</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1863.19</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-100.04</v>
+      </c>
+      <c r="T9" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1863.19</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>-104.16</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-10.416</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-04T06:36</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>long_strangle_wk</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>260</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1863.19</v>
+      </c>
+      <c r="H10" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.0414</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-99.34999999999999</v>
+      </c>
+      <c r="T10" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:47</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>63819</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N11" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.0969</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-99.84</v>
+      </c>
+      <c r="T11" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>63819.0</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>-104.16</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-10.416</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:47</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5330</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>63819</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N12" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.9794</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-100.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>63819.0</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>-104.47</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-10.447</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:47</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>63819</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N13" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-24.32</v>
+      </c>
+      <c r="T13" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>63819.0</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>-18.89</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-1.889</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.3 · 1.2h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:47</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4050</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1870.81</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.3695</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-100.03</v>
+      </c>
+      <c r="T14" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1870.81</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>-104.09</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-10.409</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:47</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1870.81</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.1322</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-100.17</v>
+      </c>
+      <c r="T15" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1870.81</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>-153.41</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-15.341</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 4.2 · 1.2h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2680</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>63773.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L16" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N16" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.5701</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-99.95999999999999</v>
+      </c>
+      <c r="T16" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>63773.7</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>-103.98</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-10.398</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>33830</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>63773.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L17" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M17" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N17" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.4132</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-101.49</v>
+      </c>
+      <c r="T17" t="n">
+        <v>101.49</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>63773.7</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>-104.87</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-10.487</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>16410</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1867.41</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.3283</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1867.41</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>-103.38</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-10.338</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>340</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>63806.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M19" t="n">
+        <v>61400</v>
+      </c>
+      <c r="N19" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.3099</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-100.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>850</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1871.24</v>
+      </c>
+      <c r="H20" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.132</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-100.13</v>
+      </c>
+      <c r="T20" t="n">
+        <v>100.13</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -710,7 +2160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -759,6 +2209,81 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-172.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-86.15000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-17.23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-418.27</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-104.57</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-41.83</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-623.54</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-77.94</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-62.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -770,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -930,22 +2455,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03T12:45</t>
+          <t>2026-08-03T15:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>long_strangle</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -957,10 +2482,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-0.32</v>
+        <v>0.08</v>
       </c>
       <c r="T2" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -968,45 +2493,85 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03T12:45</t>
+          <t>2026-08-04T06:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>long_strangle</t>
+          <t>long_strangle_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>63769.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>71000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.09760000000000001</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.0664</v>
+      </c>
       <c r="S3" t="n">
-        <v>-0.14</v>
+        <v>-100.13</v>
       </c>
       <c r="T3" t="n">
-        <v>0.14</v>
+        <v>100.13</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03T15:33</t>
+          <t>2026-08-04T06:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1016,30 +2581,226 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>long_strangle_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>1863.19</v>
+      </c>
+      <c r="H4" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.0414</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0191</v>
+      </c>
       <c r="S4" t="n">
-        <v>0.08</v>
+        <v>-99.34999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.42</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>340</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>63806.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>28</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L5" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M5" t="n">
+        <v>61400</v>
+      </c>
+      <c r="N5" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.3099</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-100.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>850</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1871.24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.132</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-100.13</v>
+      </c>
+      <c r="T6" t="n">
+        <v>100.13</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1058,7 +2819,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-03T20:54:02.775861 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-04T21:01:23.661117 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2063,8 +2063,22 @@
       <c r="T19" t="n">
         <v>100.5</v>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>64094.7</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>-104.65</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-10.465</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
@@ -2097,7 +2111,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2141,11 +2155,1093 @@
       <c r="T20" t="n">
         <v>100.13</v>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1865.38</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>-104.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-10.43</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-05T03:31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>900</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>64094.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L21" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M21" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N21" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.3714</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-99.98999999999999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>64094.7</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>-104.13</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-10.413</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-05T06:11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>870</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>64326.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L22" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M22" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N22" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.5311</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-100.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>64326.8</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>-104.57</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-10.457</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-05T06:11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>64326.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L23" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M23" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N23" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.4559</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-99.68000000000001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>64326.8</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>-103.78</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-10.378</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-05T06:11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1872.56</v>
+      </c>
+      <c r="H24" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1870</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.201</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-99.90000000000001</v>
+      </c>
+      <c r="T24" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1872.56</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>-104.16</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-10.416</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>64133.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L25" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M25" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N25" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.769</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-99.84</v>
+      </c>
+      <c r="T25" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>64133.8</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>-103.88</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-10.388</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2190</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>64133.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L26" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M26" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N26" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.6067</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-99.86</v>
+      </c>
+      <c r="T26" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>64133.8</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>-104.03</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-10.402</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>410</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>64133.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L27" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M27" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N27" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-17.75</v>
+      </c>
+      <c r="T27" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>64133.8</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>-19.84</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-1.984</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.5 · 2.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5930</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1870.49</v>
+      </c>
+      <c r="H28" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1870</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.1978</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-100.22</v>
+      </c>
+      <c r="T28" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1870.49</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>-104.37</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-10.437</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>710</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1870.49</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1870</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.1255</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-29.04</v>
+      </c>
+      <c r="T29" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1870.49</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>-26.98</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-2.698</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 3.3 · 2.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>400</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>64555.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L30" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M30" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N30" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.2979</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-100.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:27</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>870</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1878.24</v>
+      </c>
+      <c r="H31" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1870</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-0.1317</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-100.05</v>
+      </c>
+      <c r="T31" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:49</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>520</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>64787.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L32" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M32" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N32" t="n">
+        <v>66200</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-0.2782</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-100.88</v>
+      </c>
+      <c r="T32" t="n">
+        <v>100.88</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
         </is>
       </c>
     </row>
@@ -2216,7 +3312,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -2225,13 +3321,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-172.3</v>
+        <v>-219.12</v>
       </c>
       <c r="F2" t="n">
-        <v>-86.15000000000001</v>
+        <v>-54.78</v>
       </c>
       <c r="G2" t="n">
-        <v>-17.23</v>
+        <v>-21.91</v>
       </c>
     </row>
     <row r="3">
@@ -2241,7 +3337,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -2250,13 +3346,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-418.27</v>
+        <v>-730.21</v>
       </c>
       <c r="F3" t="n">
-        <v>-104.57</v>
+        <v>-104.32</v>
       </c>
       <c r="G3" t="n">
-        <v>-41.83</v>
+        <v>-73.02</v>
       </c>
     </row>
     <row r="4">
@@ -2266,22 +3362,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>12.5</v>
+        <v>7.1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-623.54</v>
+        <v>-1249.47</v>
       </c>
       <c r="F4" t="n">
-        <v>-77.94</v>
+        <v>-89.25</v>
       </c>
       <c r="G4" t="n">
-        <v>-62.35</v>
+        <v>-124.95</v>
       </c>
     </row>
   </sheetData>
@@ -2295,7 +3391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2649,7 +3745,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04T12:24</t>
+          <t>2026-08-05T15:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2664,11 +3760,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2676,13 +3772,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>63806.7</v>
+        <v>64555.7</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>22.95</v>
       </c>
       <c r="I5" t="n">
-        <v>0.522</v>
+        <v>0.525</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2690,31 +3786,31 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="L5" t="n">
-        <v>63800</v>
+        <v>64400</v>
       </c>
       <c r="M5" t="n">
-        <v>61400</v>
+        <v>64000</v>
       </c>
       <c r="N5" t="n">
-        <v>65200</v>
+        <v>66000</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3099</v>
+        <v>-0.2979</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0215</v>
+        <v>0.0203</v>
       </c>
       <c r="S5" t="n">
-        <v>-100.5</v>
+        <v>-100.2</v>
       </c>
       <c r="T5" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -2727,7 +3823,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-04T12:24</t>
+          <t>2026-08-05T15:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2742,11 +3838,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2754,51 +3850,129 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1871.24</v>
+        <v>1878.24</v>
       </c>
       <c r="H6" t="n">
-        <v>42.25</v>
+        <v>34.05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.474</v>
+        <v>0.553</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="L6" t="n">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="M6" t="n">
         <v>1800</v>
       </c>
       <c r="N6" t="n">
-        <v>1980</v>
+        <v>1960</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.132</v>
+        <v>-0.1317</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="S6" t="n">
-        <v>-100.13</v>
+        <v>-100.05</v>
       </c>
       <c r="T6" t="n">
-        <v>100.13</v>
+        <v>100.05</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:49</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>520</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>64787.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L7" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M7" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>66200</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.2782</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-100.88</v>
+      </c>
+      <c r="T7" t="n">
+        <v>100.88</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
         </is>
       </c>
     </row>
@@ -2819,7 +3993,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-04T21:01:23.661117 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-05T20:56:29.321865 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -724,8 +724,22 @@
       <c r="T4" t="n">
         <v>0.42</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1901.41</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3037,7 +3051,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3081,8 +3095,22 @@
       <c r="T30" t="n">
         <v>100.2</v>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>64698.6</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>-104.32</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-10.432</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
@@ -3115,7 +3143,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3159,8 +3187,22 @@
       <c r="T31" t="n">
         <v>100.05</v>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1906.15</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>-52.9</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
@@ -3193,7 +3235,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3237,9 +3279,1041 @@
       <c r="T32" t="n">
         <v>100.88</v>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>64698.6</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>-105.09</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-10.509</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>64924.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M33" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N33" t="n">
+        <v>66200</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-0.4414</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-100.15</v>
+      </c>
+      <c r="T33" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>64924.7</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>-104.21</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-10.421</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:19</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2510</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>64924.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L34" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M34" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N34" t="n">
+        <v>66200</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.3388</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-100.15</v>
+      </c>
+      <c r="T34" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>64924.7</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>-104.17</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-10.416</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:19</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2330</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1914.12</v>
+      </c>
+      <c r="H35" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-0.2161</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-100.19</v>
+      </c>
+      <c r="T35" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1914.12</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>-104.38</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-10.438</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1880</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>64635.6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L36" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M36" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N36" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-0.8425</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-100.02</v>
+      </c>
+      <c r="T36" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>64635.6</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>64635.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L37" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M37" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N37" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-0.7534999999999999</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-99.93000000000001</v>
+      </c>
+      <c r="T37" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>64635.6</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>380</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>64635.6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L38" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M38" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N38" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.2431</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
+        <v>-24.21</v>
+      </c>
+      <c r="T38" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>64635.6</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>-13.34</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-1.334</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.3 · 1.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4020</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1904.22</v>
+      </c>
+      <c r="H39" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-0.3209</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1904.22</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>-104.12</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-10.412</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1904.22</v>
+      </c>
+      <c r="H40" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0.1277</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="S40" t="n">
+        <v>-99.88</v>
+      </c>
+      <c r="T40" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1904.22</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>-31.86</v>
+      </c>
+      <c r="W40" t="n">
+        <v>-3.186</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 8.0 · 1.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-06T14:52</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>380</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>64699.9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L41" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M41" t="n">
+        <v>62500</v>
+      </c>
+      <c r="N41" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-0.2998</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-98.98999999999999</v>
+      </c>
+      <c r="T41" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>64271.7</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>-103.09</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-10.309</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-06T14:52</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>890</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1911.09</v>
+      </c>
+      <c r="H42" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-0.1341</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-99.86</v>
+      </c>
+      <c r="T42" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1901.41</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>-103.95</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-10.395</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>920</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>64271.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L43" t="n">
+        <v>64500</v>
+      </c>
+      <c r="M43" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N43" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-0.2734</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>64271.7</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>-104.24</v>
+      </c>
+      <c r="W43" t="n">
+        <v>-10.424</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>cheap strangle: ±400 premiums ≤ 100</t>
         </is>
@@ -3256,7 +4330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3308,36 +4382,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>butterfly</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>-219.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-54.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-21.91</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cheap_strangle</t>
+          <t>butterfly</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -3346,38 +4417,63 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-730.21</v>
+        <v>-264.32</v>
       </c>
       <c r="F3" t="n">
-        <v>-104.32</v>
+        <v>-44.05</v>
       </c>
       <c r="G3" t="n">
-        <v>-73.02</v>
+        <v>-26.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>long_strangle</t>
+          <t>cheap_strangle</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-1249.47</v>
+        <v>-1147.86</v>
       </c>
       <c r="F4" t="n">
-        <v>-89.25</v>
+        <v>-104.35</v>
       </c>
       <c r="G4" t="n">
-        <v>-124.95</v>
+        <v>-114.79</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-2030.59</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-92.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-203.06</v>
       </c>
     </row>
   </sheetData>
@@ -3391,7 +4487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3551,40 +4647,80 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03T15:33</t>
+          <t>2026-08-04T06:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>long_strangle_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>63769.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>71000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.09760000000000001</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0664</v>
+      </c>
       <c r="S2" t="n">
-        <v>0.08</v>
+        <v>-100.13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.42</v>
+        <v>100.13</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3594,7 +4730,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3608,7 +4744,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3616,13 +4752,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>63769.2</v>
+        <v>1863.19</v>
       </c>
       <c r="H3" t="n">
-        <v>29.8</v>
+        <v>43.9</v>
       </c>
       <c r="I3" t="n">
-        <v>0.481</v>
+        <v>0.473</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3630,349 +4766,37 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="L3" t="n">
-        <v>65000</v>
+        <v>1900</v>
       </c>
       <c r="M3" t="n">
-        <v>65000</v>
+        <v>1800</v>
       </c>
       <c r="N3" t="n">
-        <v>71000</v>
+        <v>2200</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0414</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0664</v>
+        <v>0.0191</v>
       </c>
       <c r="S3" t="n">
-        <v>-100.13</v>
+        <v>-99.34999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>100.13</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-04T06:36</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>long_strangle_wk</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>260</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1863.19</v>
-      </c>
-      <c r="H4" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1900</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.0414</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.0191</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-99.34999999999999</v>
-      </c>
-      <c r="T4" t="n">
-        <v>99.34999999999999</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>major event ahead — long vol into the move</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-05T15:27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>long_strangle</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>400</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>64555.7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>22.95</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="L5" t="n">
-        <v>64400</v>
-      </c>
-      <c r="M5" t="n">
-        <v>64000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>66000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.2979</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.0203</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-100.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>major event ahead — long vol into the move</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-05T15:27</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>long_strangle</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>870</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1878.24</v>
-      </c>
-      <c r="H6" t="n">
-        <v>34.05</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1870</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1960</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.1317</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.0061</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-100.05</v>
-      </c>
-      <c r="T6" t="n">
-        <v>100.05</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>major event ahead — long vol into the move</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-05T18:49</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>cheap_strangle</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>520</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>64787.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L7" t="n">
-        <v>64600</v>
-      </c>
-      <c r="M7" t="n">
-        <v>64000</v>
-      </c>
-      <c r="N7" t="n">
-        <v>66200</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.2782</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-100.88</v>
-      </c>
-      <c r="T7" t="n">
-        <v>100.88</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>cheap strangle: ±400 premiums ≤ 100</t>
         </is>
       </c>
     </row>
@@ -3993,7 +4817,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-05T20:56:29.321865 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-07T00:50:02.614860 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4319,6 +4319,2212 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-07T03:26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>64310.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L44" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M44" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N44" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-0.2874</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S44" t="n">
+        <v>-99.81999999999999</v>
+      </c>
+      <c r="T44" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>64310.1</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>-104.01</v>
+      </c>
+      <c r="W44" t="n">
+        <v>-10.401</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-07T05:13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>770</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>64258.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L45" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M45" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N45" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-0.4633</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="S45" t="n">
+        <v>-100.33</v>
+      </c>
+      <c r="T45" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>64258.5</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>-104.49</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-10.449</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-07T05:13</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1640</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>64258.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L46" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M46" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N46" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-0.3188</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-99.70999999999999</v>
+      </c>
+      <c r="T46" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>64258.5</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>-103.81</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-10.381</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-07T05:13</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1898.66</v>
+      </c>
+      <c r="H47" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-0.1697</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1898.66</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>-104.28</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-10.428</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>680</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>64414.6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L48" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M48" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N48" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-0.5708</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-100.5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>64414.6</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>-104.65</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-10.465</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>64414.6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L49" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M49" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N49" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-0.4441</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-100.06</v>
+      </c>
+      <c r="T49" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>64414.6</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W49" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2370</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1904.4</v>
+      </c>
+      <c r="H50" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-0.1757</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="S50" t="n">
+        <v>-99.78</v>
+      </c>
+      <c r="T50" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1904.4</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>-103.81</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-10.381</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-07T07:51</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>64367.9</v>
+      </c>
+      <c r="H51" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L51" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M51" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N51" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-0.5494</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="S51" t="n">
+        <v>-99.68000000000001</v>
+      </c>
+      <c r="T51" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>64367.9</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>-103.79</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-10.379</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-07T07:51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2430</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>64367.9</v>
+      </c>
+      <c r="H52" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L52" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M52" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N52" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-0.3995</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="S52" t="n">
+        <v>-99.87</v>
+      </c>
+      <c r="T52" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>64367.9</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>-104</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-07T07:51</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3660</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1903.11</v>
+      </c>
+      <c r="H53" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-0.184</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="S53" t="n">
+        <v>-99.92</v>
+      </c>
+      <c r="T53" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1903.11</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>-103.94</v>
+      </c>
+      <c r="W53" t="n">
+        <v>-10.394</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-07T08:53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>64588.1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L54" t="n">
+        <v>64500</v>
+      </c>
+      <c r="M54" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N54" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-0.6707</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="S54" t="n">
+        <v>-100.22</v>
+      </c>
+      <c r="T54" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>64588.1</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>-104.32</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-10.432</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-07T08:53</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>64588.1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L55" t="n">
+        <v>64500</v>
+      </c>
+      <c r="M55" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N55" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-0.5241</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-100.25</v>
+      </c>
+      <c r="T55" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>64588.1</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>-104.25</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-10.425</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-07T08:53</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>7010</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1909.99</v>
+      </c>
+      <c r="H56" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0.1678</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="S56" t="n">
+        <v>-100.24</v>
+      </c>
+      <c r="T56" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1909.99</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>-103.75</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-10.375</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:57</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>64838.7</v>
+      </c>
+      <c r="H57" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L57" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M57" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N57" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-0.8344</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-99.87</v>
+      </c>
+      <c r="T57" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>64838.7</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>-104.04</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-10.404</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>64838.7</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L58" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M58" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N58" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0.7221</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-100.22</v>
+      </c>
+      <c r="T58" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>64838.7</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>-104.26</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-10.426</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>390</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>64838.7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L59" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M59" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N59" t="n">
+        <v>72000</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S59" t="n">
+        <v>-22.93</v>
+      </c>
+      <c r="T59" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>64838.7</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>-10.53</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-1.053</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.3 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:57</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1913.67</v>
+      </c>
+      <c r="H60" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-0.1915</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1913.67</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>-103.95</v>
+      </c>
+      <c r="W60" t="n">
+        <v>-10.395</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>610</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1913.67</v>
+      </c>
+      <c r="H61" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S61" t="n">
+        <v>-38.73</v>
+      </c>
+      <c r="T61" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1913.67</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>-71.19</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-7.119</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.1 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-07T10:52</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1530</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>64894.9</v>
+      </c>
+      <c r="H62" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L62" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M62" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N62" t="n">
+        <v>69000</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-1.2901</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="S62" t="n">
+        <v>-99.76000000000001</v>
+      </c>
+      <c r="T62" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>64894.9</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>-103.89</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-10.389</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-07T10:52</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4100</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>64894.9</v>
+      </c>
+      <c r="H63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L63" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M63" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N63" t="n">
+        <v>69000</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-1.053</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="S63" t="n">
+        <v>-100.04</v>
+      </c>
+      <c r="T63" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>64894.9</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>-104.14</v>
+      </c>
+      <c r="W63" t="n">
+        <v>-10.414</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-07T10:52</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>440</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>64894.9</v>
+      </c>
+      <c r="H64" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L64" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M64" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N64" t="n">
+        <v>69000</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-0.422</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S64" t="n">
+        <v>-12.36</v>
+      </c>
+      <c r="T64" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>64894.9</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>-12.98</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-1.298</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.6 · 1.1h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-07T10:52</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1913.22</v>
+      </c>
+      <c r="H65" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-0.7128</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S65" t="n">
+        <v>-99.84</v>
+      </c>
+      <c r="T65" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>1913.22</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>-103.92</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-10.392</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-07T10:52</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>580</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1913.22</v>
+      </c>
+      <c r="H66" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-0.1815</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S66" t="n">
+        <v>-41.88</v>
+      </c>
+      <c r="T66" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>1913.22</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>-69.54000000000001</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-6.954</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.9 · 1.1h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-07T16:49</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>680</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>64920.1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L67" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M67" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N67" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-0.2041</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-99.81999999999999</v>
+      </c>
+      <c r="T67" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4408,7 +6614,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -4417,13 +6623,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-264.32</v>
+        <v>-428.56</v>
       </c>
       <c r="F3" t="n">
-        <v>-44.05</v>
+        <v>-42.86</v>
       </c>
       <c r="G3" t="n">
-        <v>-26.43</v>
+        <v>-42.86</v>
       </c>
     </row>
     <row r="4">
@@ -4433,7 +6639,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -4442,13 +6648,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-1147.86</v>
+        <v>-1876.48</v>
       </c>
       <c r="F4" t="n">
-        <v>-104.35</v>
+        <v>-104.25</v>
       </c>
       <c r="G4" t="n">
-        <v>-114.79</v>
+        <v>-187.65</v>
       </c>
     </row>
     <row r="5">
@@ -4458,22 +6664,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-2030.59</v>
+        <v>-3279.42</v>
       </c>
       <c r="F5" t="n">
-        <v>-92.3</v>
+        <v>-96.45</v>
       </c>
       <c r="G5" t="n">
-        <v>-203.06</v>
+        <v>-327.94</v>
       </c>
     </row>
   </sheetData>
@@ -4487,7 +6693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4800,6 +7006,84 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07T16:49</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>680</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>64920.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L4" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N4" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.2041</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-99.81999999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4817,7 +7101,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-07T00:50:02.614860 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-07T20:28:58.463371 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:Y100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -6517,11 +6517,2991 @@
       <c r="T67" t="n">
         <v>99.81999999999999</v>
       </c>
-      <c r="U67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>64956.2</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>-103.9</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-10.39</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
       <c r="Y67" t="inlineStr">
         <is>
           <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-08T03:01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2710</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>64923.4</v>
+      </c>
+      <c r="H68" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L68" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M68" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N68" t="n">
+        <v>66400</v>
+      </c>
+      <c r="O68" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-0.1626</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="S68" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T68" t="n">
+        <v>100</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>64923.4</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>-104.06</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-10.406</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:20</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2960</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>64983.1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L69" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M69" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N69" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S69" t="n">
+        <v>-100.05</v>
+      </c>
+      <c r="T69" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>64983.1</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>-104.19</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-10.419</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-08T05:15</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3240</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>64993.6</v>
+      </c>
+      <c r="H70" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L70" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M70" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N70" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-0.1992</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="S70" t="n">
+        <v>-100.12</v>
+      </c>
+      <c r="T70" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>64993.6</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>-104</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-08T05:59</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3230</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>64991</v>
+      </c>
+      <c r="H71" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L71" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M71" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N71" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-0.2245</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="S71" t="n">
+        <v>-99.81</v>
+      </c>
+      <c r="T71" t="n">
+        <v>99.81</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>64991.0</t>
+        </is>
+      </c>
+      <c r="V71" t="n">
+        <v>-104.01</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-10.401</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-08T07:04</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2990</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>65005.2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L72" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M72" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N72" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-0.2908</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="S72" t="n">
+        <v>-100.17</v>
+      </c>
+      <c r="T72" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>65005.2</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>-104.05</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-10.405</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:48</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4070</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>64990.1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L73" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M73" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N73" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O73" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-0.2978</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="S73" t="n">
+        <v>-100.12</v>
+      </c>
+      <c r="T73" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>64990.1</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>-104.19</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-10.419</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:48</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>12110</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>64990.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L74" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M74" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N74" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>-0.1766</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="S74" t="n">
+        <v>-100.51</v>
+      </c>
+      <c r="T74" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>64990.1</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:48</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5540</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1916.95</v>
+      </c>
+      <c r="H75" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="P75" t="n">
+        <v>-0.1403</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="S75" t="n">
+        <v>-100.27</v>
+      </c>
+      <c r="T75" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>1916.95</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:32</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>65023.4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L76" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M76" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N76" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P76" t="n">
+        <v>-0.3664</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="S76" t="n">
+        <v>-100.13</v>
+      </c>
+      <c r="T76" t="n">
+        <v>100.13</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>65023.4</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>-104.14</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-10.414</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:32</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>23940</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>65023.4</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L77" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M77" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N77" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>-0.0887</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S77" t="n">
+        <v>-100.55</v>
+      </c>
+      <c r="T77" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>65023.4</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>-102.94</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-10.294</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:32</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>400</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>65023.4</v>
+      </c>
+      <c r="H78" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L78" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M78" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N78" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P78" t="n">
+        <v>-0.0871</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S78" t="n">
+        <v>-21.08</v>
+      </c>
+      <c r="T78" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>65023.4</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.4 · 2.5h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:32</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>43880</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1919.77</v>
+      </c>
+      <c r="H79" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>-0.0531</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="S79" t="n">
+        <v>-100.92</v>
+      </c>
+      <c r="T79" t="n">
+        <v>100.92</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>1919.77</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>-105.31</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-10.531</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:32</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>970</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1919.77</v>
+      </c>
+      <c r="H80" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="P80" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="R80" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="S80" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="T80" t="n">
+        <v>100.39</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>1919.77</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>-128.82</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-12.882</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 3.8 · 2.5h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:07</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>64992.6</v>
+      </c>
+      <c r="H81" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L81" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M81" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N81" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>-0.1487</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="S81" t="n">
+        <v>-99</v>
+      </c>
+      <c r="T81" t="n">
+        <v>99</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>64992.6</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>-103.4</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:07</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>93570</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>64992.6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L82" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M82" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N82" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>-0.0867</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="S82" t="n">
+        <v>-102.93</v>
+      </c>
+      <c r="T82" t="n">
+        <v>102.93</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>64992.6</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>-102.93</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-10.293</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:07</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>480</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>64992.6</v>
+      </c>
+      <c r="H83" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L83" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M83" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N83" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P83" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S83" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="T83" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>64992.6</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>-63.41</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-6.341</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.9 · 1.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:07</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5660</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1919.42</v>
+      </c>
+      <c r="H84" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="P84" t="n">
+        <v>-0.1562</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="S84" t="n">
+        <v>-100.18</v>
+      </c>
+      <c r="T84" t="n">
+        <v>100.18</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>1919.42</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>-104.14</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-10.414</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:07</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>940</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1919.42</v>
+      </c>
+      <c r="H85" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="P85" t="n">
+        <v>-0.0346</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="R85" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="S85" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="T85" t="n">
+        <v>100.39</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>1919.42</t>
+        </is>
+      </c>
+      <c r="V85" t="n">
+        <v>-123.89</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-12.389</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 3.7 · 1.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:50</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>3790</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>65010.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L86" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M86" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N86" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P86" t="n">
+        <v>-0.3949</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="S86" t="n">
+        <v>-100.06</v>
+      </c>
+      <c r="T86" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>65010.5</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>-104.22</v>
+      </c>
+      <c r="W86" t="n">
+        <v>-10.422</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:50</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>147290</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>65010.5</v>
+      </c>
+      <c r="H87" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L87" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M87" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N87" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>-0.0606</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="S87" t="n">
+        <v>-103.1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>65010.5</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>-103.1</v>
+      </c>
+      <c r="W87" t="n">
+        <v>-10.31</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:50</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>430</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>65010.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L88" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M88" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N88" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P88" t="n">
+        <v>-0.2292</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S88" t="n">
+        <v>-14.92</v>
+      </c>
+      <c r="T88" t="n">
+        <v>100.92</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>65010.5</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>-11.27</v>
+      </c>
+      <c r="W88" t="n">
+        <v>-1.127</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.6 · 1.2h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:50</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>8670</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1920.82</v>
+      </c>
+      <c r="H89" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="P89" t="n">
+        <v>-0.182</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S89" t="n">
+        <v>-99.7</v>
+      </c>
+      <c r="T89" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>1920.82</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>-104.04</v>
+      </c>
+      <c r="W89" t="n">
+        <v>-10.404</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:50</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5230</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1920.82</v>
+      </c>
+      <c r="H90" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="P90" t="n">
+        <v>-0.1466</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="R90" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="S90" t="n">
+        <v>-99.89</v>
+      </c>
+      <c r="T90" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>1920.82</t>
+        </is>
+      </c>
+      <c r="V90" t="n">
+        <v>-63.28</v>
+      </c>
+      <c r="W90" t="n">
+        <v>-6.328</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 25.1 · 1.2h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:23</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6880</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>64983.8</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L91" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M91" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N91" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P91" t="n">
+        <v>-0.3831</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="S91" t="n">
+        <v>-99.76000000000001</v>
+      </c>
+      <c r="T91" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>64983.8</t>
+        </is>
+      </c>
+      <c r="V91" t="n">
+        <v>-103.89</v>
+      </c>
+      <c r="W91" t="n">
+        <v>-10.389</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:23</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>64983.8</v>
+      </c>
+      <c r="H92" t="n">
+        <v>5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L92" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M92" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N92" t="n">
+        <v>65800</v>
+      </c>
+      <c r="O92" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T92" t="n">
+        <v>100</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>64983.8</t>
+        </is>
+      </c>
+      <c r="V92" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W92" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:23</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>166610</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1920.03</v>
+      </c>
+      <c r="H93" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N93" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>-0.08160000000000001</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S93" t="n">
+        <v>-99.97</v>
+      </c>
+      <c r="T93" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>1920.03</t>
+        </is>
+      </c>
+      <c r="V93" t="n">
+        <v>-99.97</v>
+      </c>
+      <c r="W93" t="n">
+        <v>-9.997</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:24</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>4329.96</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>10</v>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:52</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>106100</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>64956.9</v>
+      </c>
+      <c r="H95" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L95" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M95" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N95" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>-0.1359</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S95" t="n">
+        <v>-95.48999999999999</v>
+      </c>
+      <c r="T95" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>64956.9</t>
+        </is>
+      </c>
+      <c r="V95" t="n">
+        <v>-106.1</v>
+      </c>
+      <c r="W95" t="n">
+        <v>-10.61</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:52</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>64956.9</v>
+      </c>
+      <c r="H96" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L96" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M96" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N96" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T96" t="n">
+        <v>100</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>64956.9</t>
+        </is>
+      </c>
+      <c r="V96" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W96" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:52</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1919.99</v>
+      </c>
+      <c r="H97" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T97" t="n">
+        <v>100</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>1919.99</t>
+        </is>
+      </c>
+      <c r="V97" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W97" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:37</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>750</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H98" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M98" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N98" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O98" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P98" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="S98" t="n">
+        <v>-99.45</v>
+      </c>
+      <c r="T98" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:37</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1110</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H99" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M99" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N99" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>-0.122</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="S99" t="n">
+        <v>-99.90000000000001</v>
+      </c>
+      <c r="T99" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:37</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1919.95</v>
+      </c>
+      <c r="H100" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P100" t="n">
+        <v>-0.0703</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S100" t="n">
+        <v>-100.32</v>
+      </c>
+      <c r="T100" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
         </is>
       </c>
     </row>
@@ -6614,7 +9594,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -6623,13 +9603,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-428.56</v>
+        <v>-832.4299999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-42.86</v>
+        <v>-52.03</v>
       </c>
       <c r="G3" t="n">
-        <v>-42.86</v>
+        <v>-83.23999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -6639,7 +9619,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -6648,13 +9628,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-1876.48</v>
+        <v>-3113.81</v>
       </c>
       <c r="F4" t="n">
-        <v>-104.25</v>
+        <v>-103.79</v>
       </c>
       <c r="G4" t="n">
-        <v>-187.65</v>
+        <v>-311.38</v>
       </c>
     </row>
     <row r="5">
@@ -6664,22 +9644,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-3279.42</v>
+        <v>-4522.97</v>
       </c>
       <c r="F5" t="n">
-        <v>-96.45</v>
+        <v>-98.33</v>
       </c>
       <c r="G5" t="n">
-        <v>-327.94</v>
+        <v>-452.3</v>
       </c>
     </row>
   </sheetData>
@@ -6693,7 +9673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7009,26 +9989,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07T16:49</t>
+          <t>2026-08-08T11:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>XAUTUSD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cheap_strangle</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>perpetual</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>680</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -7036,51 +10016,253 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>64920.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="L4" t="n">
-        <v>65000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>64600</v>
-      </c>
-      <c r="N4" t="n">
-        <v>66800</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-0.0001</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.2041</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.0184</v>
+        <v>4329.96</v>
       </c>
       <c r="S4" t="n">
-        <v>-99.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>99.81999999999999</v>
+        <v>10</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:37</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>750</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N5" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-99.45</v>
+      </c>
+      <c r="T5" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:37</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1110</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N6" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.122</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-99.90000000000001</v>
+      </c>
+      <c r="T6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:37</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1919.95</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.0703</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-100.32</v>
+      </c>
+      <c r="T7" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>major event ahead — long vol into the move</t>
         </is>
       </c>
     </row>
@@ -7101,7 +10283,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-07T20:28:58.463371 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-08T20:16:47.818371 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y100"/>
+  <dimension ref="A1:Y117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -9341,8 +9341,22 @@
       <c r="T98" t="n">
         <v>99.45</v>
       </c>
-      <c r="U98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>64981.4</t>
+        </is>
+      </c>
+      <c r="V98" t="n">
+        <v>-103.58</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-10.357</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
       <c r="Y98" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
@@ -9375,7 +9389,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -9419,8 +9433,22 @@
       <c r="T99" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="U99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>64981.4</t>
+        </is>
+      </c>
+      <c r="V99" t="n">
+        <v>-104.01</v>
+      </c>
+      <c r="W99" t="n">
+        <v>-10.401</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
       <c r="Y99" t="inlineStr">
         <is>
           <t>cheap strangle: ±400 premiums ≤ 100</t>
@@ -9453,7 +9481,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -9497,11 +9525,1607 @@
       <c r="T100" t="n">
         <v>100.32</v>
       </c>
-      <c r="U100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>1918.83</t>
+        </is>
+      </c>
+      <c r="V100" t="n">
+        <v>-104.41</v>
+      </c>
+      <c r="W100" t="n">
+        <v>-10.441</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
       <c r="Y100" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-09T03:13</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>3490</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>64761.4</v>
+      </c>
+      <c r="H101" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L101" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M101" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N101" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O101" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>-0.144</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="S101" t="n">
+        <v>-99.81</v>
+      </c>
+      <c r="T101" t="n">
+        <v>99.81</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>64761.4</t>
+        </is>
+      </c>
+      <c r="V101" t="n">
+        <v>-104</v>
+      </c>
+      <c r="W101" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-09T04:38</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>4830</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>64813.3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L102" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M102" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N102" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>-0.1366</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="S102" t="n">
+        <v>-99.98</v>
+      </c>
+      <c r="T102" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>64813.3</t>
+        </is>
+      </c>
+      <c r="V102" t="n">
+        <v>-103.84</v>
+      </c>
+      <c r="W102" t="n">
+        <v>-10.384</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:34</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4150</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>64788.5</v>
+      </c>
+      <c r="H103" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L103" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M103" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N103" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O103" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>-0.1719</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="S103" t="n">
+        <v>-100.02</v>
+      </c>
+      <c r="T103" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>64788.5</t>
+        </is>
+      </c>
+      <c r="V103" t="n">
+        <v>-104.17</v>
+      </c>
+      <c r="W103" t="n">
+        <v>-10.416</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-09T06:28</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>5560</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>64843.2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L104" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M104" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N104" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>-0.1497</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="S104" t="n">
+        <v>-100.08</v>
+      </c>
+      <c r="T104" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>64843.2</t>
+        </is>
+      </c>
+      <c r="V104" t="n">
+        <v>-103.97</v>
+      </c>
+      <c r="W104" t="n">
+        <v>-10.397</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-09T07:34</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>16380</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>64844.3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L105" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M105" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N105" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>-0.0886</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="S105" t="n">
+        <v>-99.92</v>
+      </c>
+      <c r="T105" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>64844.3</t>
+        </is>
+      </c>
+      <c r="V105" t="n">
+        <v>-104.83</v>
+      </c>
+      <c r="W105" t="n">
+        <v>-10.483</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-09T08:22</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>11340</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>64911.5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L106" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M106" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N106" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>-0.1608</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S106" t="n">
+        <v>-99.79000000000001</v>
+      </c>
+      <c r="T106" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>64911.5</t>
+        </is>
+      </c>
+      <c r="V106" t="n">
+        <v>-104.33</v>
+      </c>
+      <c r="W106" t="n">
+        <v>-10.433</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>54120</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>64830.1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L107" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M107" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N107" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>-0.0501</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="S107" t="n">
+        <v>-97.42</v>
+      </c>
+      <c r="T107" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>64830.1</t>
+        </is>
+      </c>
+      <c r="V107" t="n">
+        <v>-102.83</v>
+      </c>
+      <c r="W107" t="n">
+        <v>-10.283</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:10</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>360</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>64830.1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L108" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M108" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N108" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P108" t="n">
+        <v>-0.1847</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S108" t="n">
+        <v>-28.01</v>
+      </c>
+      <c r="T108" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>64830.1</t>
+        </is>
+      </c>
+      <c r="V108" t="n">
+        <v>-18.86</v>
+      </c>
+      <c r="W108" t="n">
+        <v>-1.886</v>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.2 · 2.8h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:10</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>710</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1916.02</v>
+      </c>
+      <c r="H109" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O109" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="P109" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="S109" t="n">
+        <v>-28.54</v>
+      </c>
+      <c r="T109" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>1916.02</t>
+        </is>
+      </c>
+      <c r="V109" t="n">
+        <v>-87.12</v>
+      </c>
+      <c r="W109" t="n">
+        <v>-8.712</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.6 · 2.8h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:55</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>29740</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>64851.5</v>
+      </c>
+      <c r="H110" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L110" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M110" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N110" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>-0.1064</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="S110" t="n">
+        <v>-101.12</v>
+      </c>
+      <c r="T110" t="n">
+        <v>101.12</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>64851.5</t>
+        </is>
+      </c>
+      <c r="V110" t="n">
+        <v>-104.09</v>
+      </c>
+      <c r="W110" t="n">
+        <v>-10.409</v>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:55</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>370</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>64851.5</v>
+      </c>
+      <c r="H111" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L111" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M111" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N111" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P111" t="n">
+        <v>-0.0463</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R111" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S111" t="n">
+        <v>-24.86</v>
+      </c>
+      <c r="T111" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>64851.5</t>
+        </is>
+      </c>
+      <c r="V111" t="n">
+        <v>-7.81</v>
+      </c>
+      <c r="W111" t="n">
+        <v>-0.781</v>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.2 · 2.1h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:55</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>4190</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1920.57</v>
+      </c>
+      <c r="H112" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="P112" t="n">
+        <v>-0.1161</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="R112" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="S112" t="n">
+        <v>-100.14</v>
+      </c>
+      <c r="T112" t="n">
+        <v>100.14</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>1920.57</t>
+        </is>
+      </c>
+      <c r="V112" t="n">
+        <v>-81.29000000000001</v>
+      </c>
+      <c r="W112" t="n">
+        <v>-8.129</v>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 19.9 · 2.1h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-09T10:30</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>8850</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>64970.2</v>
+      </c>
+      <c r="H113" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L113" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M113" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N113" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O113" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>-0.5161</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="S113" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T113" t="n">
+        <v>100</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>64970.2</t>
+        </is>
+      </c>
+      <c r="V113" t="n">
+        <v>-104.43</v>
+      </c>
+      <c r="W113" t="n">
+        <v>-10.443</v>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-09T10:30</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>390</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>64970.2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L114" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M114" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N114" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O114" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="P114" t="n">
+        <v>-0.5373</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S114" t="n">
+        <v>-21.02</v>
+      </c>
+      <c r="T114" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>64970.2</t>
+        </is>
+      </c>
+      <c r="V114" t="n">
+        <v>-58.5</v>
+      </c>
+      <c r="W114" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.4 · 1.5h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-09T10:30</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>4860</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>1920.61</v>
+      </c>
+      <c r="H115" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="P115" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R115" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="S115" t="n">
+        <v>-100.12</v>
+      </c>
+      <c r="T115" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>1920.61</t>
+        </is>
+      </c>
+      <c r="V115" t="n">
+        <v>-75.81999999999999</v>
+      </c>
+      <c r="W115" t="n">
+        <v>-7.582</v>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 23.3 · 1.5h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-09T11:06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>26270</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>64980.3</v>
+      </c>
+      <c r="H116" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L116" t="n">
+        <v>64800</v>
+      </c>
+      <c r="M116" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N116" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O116" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>-0.3134</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="S116" t="n">
+        <v>-99.83</v>
+      </c>
+      <c r="T116" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>64980.3</t>
+        </is>
+      </c>
+      <c r="V116" t="n">
+        <v>-105.08</v>
+      </c>
+      <c r="W116" t="n">
+        <v>-10.508</v>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-09T11:43</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>64990</v>
+      </c>
+      <c r="H117" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L117" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M117" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N117" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T117" t="n">
+        <v>100</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>64990.0</t>
+        </is>
+      </c>
+      <c r="V117" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W117" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
         </is>
       </c>
     </row>
@@ -9594,7 +11218,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -9603,13 +11227,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-832.4299999999999</v>
+        <v>-1161.83</v>
       </c>
       <c r="F3" t="n">
-        <v>-52.03</v>
+        <v>-52.81</v>
       </c>
       <c r="G3" t="n">
-        <v>-83.23999999999999</v>
+        <v>-116.18</v>
       </c>
     </row>
     <row r="4">
@@ -9619,7 +11243,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -9628,13 +11252,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-3113.81</v>
+        <v>-4359.39</v>
       </c>
       <c r="F4" t="n">
-        <v>-103.79</v>
+        <v>-103.8</v>
       </c>
       <c r="G4" t="n">
-        <v>-311.38</v>
+        <v>-435.94</v>
       </c>
     </row>
     <row r="5">
@@ -9644,22 +11268,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-4522.97</v>
+        <v>-4730.96</v>
       </c>
       <c r="F5" t="n">
-        <v>-98.33</v>
+        <v>-98.56</v>
       </c>
       <c r="G5" t="n">
-        <v>-452.3</v>
+        <v>-473.1</v>
       </c>
     </row>
   </sheetData>
@@ -9673,7 +11297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10032,240 +11656,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-08T12:37</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>long_strangle</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>750</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>65000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>65000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>64800</v>
-      </c>
-      <c r="N5" t="n">
-        <v>66800</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.0001</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.0211</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-99.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>99.45</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>major event ahead — long vol into the move</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-08T12:37</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>cheap_strangle</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1110</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>65000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>65000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>64800</v>
-      </c>
-      <c r="N6" t="n">
-        <v>66800</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.122</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-99.90000000000001</v>
-      </c>
-      <c r="T6" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>cheap strangle: ±400 premiums ≤ 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-08T12:37</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>long_strangle</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1919.95</v>
-      </c>
-      <c r="H7" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1920</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1880</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2040</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.0703</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-100.32</v>
-      </c>
-      <c r="T7" t="n">
-        <v>100.32</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>major event ahead — long vol into the move</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10283,7 +11673,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-08T20:16:47.818371 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-09T20:19:13.337124 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y117"/>
+  <dimension ref="A1:Y133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1088,7 +1088,17 @@
         <v>100.13</v>
       </c>
       <c r="U8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-55.04</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-5.504</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
@@ -1213,7 +1223,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1258,7 +1268,17 @@
         <v>99.34999999999999</v>
       </c>
       <c r="U10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-52.26</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-5.226</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>major event ahead — long vol into the move</t>
@@ -8975,7 +8995,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -8987,8 +9007,22 @@
       <c r="T94" t="n">
         <v>10</v>
       </c>
-      <c r="U94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>4322.23</t>
+        </is>
+      </c>
+      <c r="V94" t="n">
+        <v>-16.61</v>
+      </c>
+      <c r="W94" t="n">
+        <v>-1.661</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="Y94" t="inlineStr">
         <is>
           <t>20/50 EMA 3rd retest</t>
@@ -11126,6 +11160,1418 @@
       <c r="Y117" t="inlineStr">
         <is>
           <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-09T21:03</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>560</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>65138.5</v>
+      </c>
+      <c r="H118" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L118" t="n">
+        <v>65200</v>
+      </c>
+      <c r="M118" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N118" t="n">
+        <v>67200</v>
+      </c>
+      <c r="O118" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>-0.3018</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="S118" t="n">
+        <v>-99.40000000000001</v>
+      </c>
+      <c r="T118" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>64905.3</t>
+        </is>
+      </c>
+      <c r="V118" t="n">
+        <v>-103.54</v>
+      </c>
+      <c r="W118" t="n">
+        <v>-10.354</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-10T00:04</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>280</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1910.79</v>
+      </c>
+      <c r="H119" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N119" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="T119" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>1910.79</t>
+        </is>
+      </c>
+      <c r="V119" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="W119" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>neutral / mid IV — default condor</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-10T02:33</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>850</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>64970.4</v>
+      </c>
+      <c r="H120" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L120" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M120" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N120" t="n">
+        <v>67200</v>
+      </c>
+      <c r="O120" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-0.365</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="S120" t="n">
+        <v>-100.38</v>
+      </c>
+      <c r="T120" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>64970.4</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>-104.55</v>
+      </c>
+      <c r="W120" t="n">
+        <v>-10.455</v>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-10T04:17</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>990</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>65071.7</v>
+      </c>
+      <c r="H121" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L121" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M121" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N121" t="n">
+        <v>67200</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-0.3902</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="S121" t="n">
+        <v>-100.49</v>
+      </c>
+      <c r="T121" t="n">
+        <v>100.49</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>65071.7</t>
+        </is>
+      </c>
+      <c r="V121" t="n">
+        <v>-104.64</v>
+      </c>
+      <c r="W121" t="n">
+        <v>-10.464</v>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:54</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>65103</v>
+      </c>
+      <c r="H122" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L122" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M122" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N122" t="n">
+        <v>67200</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P122" t="n">
+        <v>-0.3919</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-100.31</v>
+      </c>
+      <c r="T122" t="n">
+        <v>100.31</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>65103.0</t>
+        </is>
+      </c>
+      <c r="V122" t="n">
+        <v>-104.49</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-10.449</v>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-10T07:22</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>65286.7</v>
+      </c>
+      <c r="H123" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L123" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M123" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N123" t="n">
+        <v>67200</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P123" t="n">
+        <v>-0.3898</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="S123" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T123" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>65286.7</t>
+        </is>
+      </c>
+      <c r="V123" t="n">
+        <v>-104.28</v>
+      </c>
+      <c r="W123" t="n">
+        <v>-10.428</v>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:56</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6210</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>65238.2</v>
+      </c>
+      <c r="H124" t="n">
+        <v>15</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L124" t="n">
+        <v>65200</v>
+      </c>
+      <c r="M124" t="n">
+        <v>64600</v>
+      </c>
+      <c r="N124" t="n">
+        <v>67200</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>-0.2684</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="S124" t="n">
+        <v>-99.98</v>
+      </c>
+      <c r="T124" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>65238.2</t>
+        </is>
+      </c>
+      <c r="V124" t="n">
+        <v>-104.33</v>
+      </c>
+      <c r="W124" t="n">
+        <v>-10.433</v>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-10T10:15</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>50</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>65039.5</v>
+      </c>
+      <c r="H125" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L125" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M125" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N125" t="n">
+        <v>71000</v>
+      </c>
+      <c r="O125" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="S125" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="T125" t="n">
+        <v>106.16</v>
+      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-10T10:15</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>250</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1919.25</v>
+      </c>
+      <c r="H126" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N126" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T126" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>1919.25</t>
+        </is>
+      </c>
+      <c r="V126" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>IV rank 38% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-10T10:15</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>240</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1919.25</v>
+      </c>
+      <c r="H127" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1850</v>
+      </c>
+      <c r="N127" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S127" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="T127" t="n">
+        <v>98.11</v>
+      </c>
+      <c r="U127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-10T11:29</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>10210</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>65080.7</v>
+      </c>
+      <c r="H128" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L128" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M128" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N128" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O128" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P128" t="n">
+        <v>-0.7862</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S128" t="n">
+        <v>-100.06</v>
+      </c>
+      <c r="T128" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>65080.7</t>
+        </is>
+      </c>
+      <c r="V128" t="n">
+        <v>-104.14</v>
+      </c>
+      <c r="W128" t="n">
+        <v>-10.414</v>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>IV rank 12% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-10T11:29</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>176600</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>65080.7</v>
+      </c>
+      <c r="H129" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L129" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M129" t="n">
+        <v>64800</v>
+      </c>
+      <c r="N129" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>-0.107</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S129" t="n">
+        <v>-105.96</v>
+      </c>
+      <c r="T129" t="n">
+        <v>105.96</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>65080.7</t>
+        </is>
+      </c>
+      <c r="V129" t="n">
+        <v>-105.96</v>
+      </c>
+      <c r="W129" t="n">
+        <v>-10.596</v>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-10T11:29</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>10460</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1919.24</v>
+      </c>
+      <c r="H130" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N130" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="P130" t="n">
+        <v>-0.3484</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="S130" t="n">
+        <v>-100.42</v>
+      </c>
+      <c r="T130" t="n">
+        <v>100.42</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>1919.24</t>
+        </is>
+      </c>
+      <c r="V130" t="n">
+        <v>-104.6</v>
+      </c>
+      <c r="W130" t="n">
+        <v>-10.46</v>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>IV rank 12% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-10T12:10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>70</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>65194.9</v>
+      </c>
+      <c r="H131" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L131" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M131" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N131" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="S131" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="T131" t="n">
+        <v>104.91</v>
+      </c>
+      <c r="U131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-10T12:10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>290</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1922.47</v>
+      </c>
+      <c r="H132" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S132" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="T132" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="n">
+        <v>-29.06</v>
+      </c>
+      <c r="W132" t="n">
+        <v>-2.906</v>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-10T15:41</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>290</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1879.12</v>
+      </c>
+      <c r="H133" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N133" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O133" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S133" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="T133" t="n">
+        <v>98.98</v>
+      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -11140,7 +12586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11214,11 +12660,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>butterfly</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -11227,63 +12673,138 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-1161.83</v>
+        <v>-16.61</v>
       </c>
       <c r="F3" t="n">
-        <v>-52.81</v>
+        <v>-16.61</v>
       </c>
       <c r="G3" t="n">
-        <v>-116.18</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cheap_strangle</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="E4" t="n">
-        <v>-4359.39</v>
+        <v>-17.24</v>
       </c>
       <c r="F4" t="n">
-        <v>-103.8</v>
+        <v>-5.75</v>
       </c>
       <c r="G4" t="n">
-        <v>-435.94</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>long_strangle</t>
+          <t>long_strangle_wk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-4730.96</v>
+        <v>-107.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-98.56</v>
+        <v>-53.65</v>
       </c>
       <c r="G5" t="n">
-        <v>-473.1</v>
+        <v>-10.73</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1161.83</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-52.81</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-116.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-4939.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-98.79000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-493.97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>49</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-5091.18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-103.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-509.12</v>
       </c>
     </row>
   </sheetData>
@@ -11297,7 +12818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11457,7 +12978,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04T06:36</t>
+          <t>2026-08-10T10:15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11467,7 +12988,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>long_strangle_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -11476,7 +12997,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11484,13 +13005,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>63769.2</v>
+        <v>65039.5</v>
       </c>
       <c r="H2" t="n">
-        <v>29.8</v>
+        <v>26.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.481</v>
+        <v>0.412</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -11498,44 +13019,44 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.77</v>
+        <v>0.97</v>
       </c>
       <c r="L2" t="n">
         <v>65000</v>
       </c>
       <c r="M2" t="n">
-        <v>65000</v>
+        <v>60000</v>
       </c>
       <c r="N2" t="n">
         <v>71000</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0664</v>
+        <v>-0.03</v>
       </c>
       <c r="S2" t="n">
-        <v>-100.13</v>
+        <v>9.24</v>
       </c>
       <c r="T2" t="n">
-        <v>100.13</v>
+        <v>106.16</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>major event ahead — long vol into the move</t>
+          <t>IV rank 100% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04T06:36</t>
+          <t>2026-08-10T10:15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11545,7 +13066,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>long_strangle_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11554,7 +13075,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11562,77 +13083,77 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1863.19</v>
+        <v>1919.25</v>
       </c>
       <c r="H3" t="n">
-        <v>43.9</v>
+        <v>38.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.473</v>
+        <v>0.649</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.15</v>
+        <v>0.96</v>
       </c>
       <c r="L3" t="n">
         <v>1900</v>
       </c>
       <c r="M3" t="n">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="N3" t="n">
         <v>2200</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0007</v>
+        <v>0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0414</v>
+        <v>0.0199</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0191</v>
+        <v>-0.0046</v>
       </c>
       <c r="S3" t="n">
-        <v>-99.34999999999999</v>
+        <v>21.89</v>
       </c>
       <c r="T3" t="n">
-        <v>99.34999999999999</v>
+        <v>98.11</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>major event ahead — long vol into the move</t>
+          <t>IV rank 100% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-08T11:24</t>
+          <t>2026-08-10T12:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XAUTUSD</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gold_ema</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>perpetual</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -11640,19 +13161,129 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4329.96</v>
+        <v>65194.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L4" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.0136</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>7.44</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>104.91</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>20/50 EMA 3rd retest</t>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10T15:41</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1879.12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>98.98</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -11673,7 +13304,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-09T20:19:13.337124 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-10T20:30:35.929415 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y133"/>
+  <dimension ref="A1:Y150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -12401,8 +12401,22 @@
       <c r="T131" t="n">
         <v>104.91</v>
       </c>
-      <c r="U131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>64081.6</t>
+        </is>
+      </c>
+      <c r="V131" t="n">
+        <v>-45.79</v>
+      </c>
+      <c r="W131" t="n">
+        <v>-4.579</v>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="Y131" t="inlineStr">
         <is>
           <t>IV rank 88% rich — sell premium</t>
@@ -12523,7 +12537,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -12568,10 +12582,1528 @@
         <v>98.98</v>
       </c>
       <c r="U133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
+      <c r="V133" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="Y133" t="inlineStr">
         <is>
           <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-11T02:12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>60</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>64081.6</v>
+      </c>
+      <c r="H134" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L134" t="n">
+        <v>65000</v>
+      </c>
+      <c r="M134" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N134" t="n">
+        <v>69000</v>
+      </c>
+      <c r="O134" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>-0.0297</v>
+      </c>
+      <c r="S134" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="T134" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="U134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-11T02:12</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>260</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1878.17</v>
+      </c>
+      <c r="H135" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.0766</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="T135" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>1878.17</t>
+        </is>
+      </c>
+      <c r="V135" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-11T02:12</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>250</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1878.17</v>
+      </c>
+      <c r="H136" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1850</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="S136" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="T136" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="U136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-11T03:55</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>90</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>64128.1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L137" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M137" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N137" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="S137" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="T137" t="n">
+        <v>101.42</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>64128.1</t>
+        </is>
+      </c>
+      <c r="V137" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-11T03:55</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>270</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>1880.88</v>
+      </c>
+      <c r="H138" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S138" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="T138" t="n">
+        <v>101.36</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>1880.88</t>
+        </is>
+      </c>
+      <c r="V138" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-11T05:03</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>90</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>64037.7</v>
+      </c>
+      <c r="H139" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L139" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M139" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N139" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="S139" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T139" t="n">
+        <v>105.02</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>64037.7</t>
+        </is>
+      </c>
+      <c r="V139" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-11T05:03</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>260</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1876.45</v>
+      </c>
+      <c r="H140" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N140" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O140" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S140" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T140" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>1876.45</t>
+        </is>
+      </c>
+      <c r="V140" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>IV rank 78% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-11T06:03</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>90</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>63987.7</v>
+      </c>
+      <c r="H141" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L141" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M141" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N141" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O141" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T141" t="n">
+        <v>103.59</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>63987.7</t>
+        </is>
+      </c>
+      <c r="V141" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-11T06:03</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>260</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1872.85</v>
+      </c>
+      <c r="H142" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N142" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="S142" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T142" t="n">
+        <v>100.83</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>1872.85</t>
+        </is>
+      </c>
+      <c r="V142" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-11T07:35</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>90</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>64020</v>
+      </c>
+      <c r="H143" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L143" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M143" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N143" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="S143" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T143" t="n">
+        <v>103.74</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>64020.0</t>
+        </is>
+      </c>
+      <c r="V143" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>IV rank 44% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-11T07:35</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>260</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1876.82</v>
+      </c>
+      <c r="H144" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N144" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S144" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="T144" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>1876.82</t>
+        </is>
+      </c>
+      <c r="V144" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>IV rank 44% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-11T08:36</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>90</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>64075.5</v>
+      </c>
+      <c r="H145" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L145" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M145" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N145" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0.8222</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="S145" t="n">
+        <v>6</v>
+      </c>
+      <c r="T145" t="n">
+        <v>102.72</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>64075.5</t>
+        </is>
+      </c>
+      <c r="V145" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>IV rank 78% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-11T08:36</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>260</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>1877.37</v>
+      </c>
+      <c r="H146" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S146" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T146" t="n">
+        <v>100.88</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>1877.37</t>
+        </is>
+      </c>
+      <c r="V146" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-11T09:41</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>80</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>64188.4</v>
+      </c>
+      <c r="H147" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L147" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M147" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N147" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O147" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0.2229</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T147" t="n">
+        <v>94.27</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>64188.4</t>
+        </is>
+      </c>
+      <c r="V147" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-11T11:29</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>90</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>64337.8</v>
+      </c>
+      <c r="H148" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L148" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M148" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N148" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O148" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>1.2519</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S148" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T148" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>64337.8</t>
+        </is>
+      </c>
+      <c r="V148" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-11T12:24</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>80</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>64316.5</v>
+      </c>
+      <c r="H149" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L149" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M149" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N149" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="S149" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="T149" t="n">
+        <v>102.97</v>
+      </c>
+      <c r="U149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>IV rank 78% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-11T12:24</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>280</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1891.13</v>
+      </c>
+      <c r="H150" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S150" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="T150" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="U150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -12638,73 +14170,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.04</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.34</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gold_ema</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>-16.61</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-16.61</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.66</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-17.24</v>
+        <v>-16.61</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.75</v>
+        <v>-16.61</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.72</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="5">
@@ -12818,7 +14350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13134,7 +14666,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10T12:10</t>
+          <t>2026-08-11T02:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13144,16 +14676,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -13161,21 +14693,21 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>65194.9</v>
+        <v>64081.6</v>
       </c>
       <c r="H4" t="n">
-        <v>24.25</v>
+        <v>28.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.551</v>
+        <v>0.487</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.96</v>
+        <v>1.39</v>
       </c>
       <c r="L4" t="n">
         <v>65000</v>
@@ -13184,35 +14716,35 @@
         <v>65000</v>
       </c>
       <c r="N4" t="n">
-        <v>66800</v>
+        <v>69000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1569</v>
+        <v>0.0366</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0136</v>
+        <v>-0.0297</v>
       </c>
       <c r="S4" t="n">
-        <v>7.44</v>
+        <v>13.96</v>
       </c>
       <c r="T4" t="n">
-        <v>104.91</v>
+        <v>94.88</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 88% rich — sell premium</t>
+          <t>IV rank 100% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10T15:41</t>
+          <t>2026-08-11T02:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -13222,16 +14754,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -13239,13 +14771,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1879.12</v>
+        <v>1878.17</v>
       </c>
       <c r="H5" t="n">
-        <v>33.85</v>
+        <v>39.85</v>
       </c>
       <c r="I5" t="n">
-        <v>0.626</v>
+        <v>0.66</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -13253,37 +14785,193 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="M5" t="n">
-        <v>1840</v>
+        <v>1850</v>
       </c>
       <c r="N5" t="n">
-        <v>2020</v>
+        <v>2200</v>
       </c>
       <c r="O5" t="n">
         <v>-0.0001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0721</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0048</v>
       </c>
       <c r="S5" t="n">
-        <v>17.02</v>
+        <v>26.35</v>
       </c>
       <c r="T5" t="n">
-        <v>98.98</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 75% rich — sell premium</t>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11T12:24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>64316.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M6" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N6" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="T6" t="n">
+        <v>102.97</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>IV rank 78% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-11T12:24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1891.13</v>
+      </c>
+      <c r="H7" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -13304,7 +14992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-10T20:30:35.929415 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-11T20:33:17.813687 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y150"/>
+  <dimension ref="A1:Y173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -12048,7 +12048,17 @@
         <v>98.11</v>
       </c>
       <c r="U127" t="inlineStr"/>
-      <c r="X127" t="inlineStr"/>
+      <c r="V127" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="Y127" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -13977,7 +13987,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -14021,8 +14031,22 @@
       <c r="T149" t="n">
         <v>102.97</v>
       </c>
-      <c r="U149" t="inlineStr"/>
-      <c r="X149" t="inlineStr"/>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>63808.7</t>
+        </is>
+      </c>
+      <c r="V149" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="W149" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="Y149" t="inlineStr">
         <is>
           <t>IV rank 78% rich — sell premium</t>
@@ -14055,7 +14079,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -14100,10 +14124,2068 @@
         <v>99.2</v>
       </c>
       <c r="U150" t="inlineStr"/>
-      <c r="X150" t="inlineStr"/>
+      <c r="V150" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="Y150" t="inlineStr">
         <is>
           <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-11T22:03</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>270</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1886.12</v>
+      </c>
+      <c r="H151" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L151" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N151" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S151" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="T151" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>1884.8</t>
+        </is>
+      </c>
+      <c r="V151" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-12T04:20</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>90</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>63826.3</v>
+      </c>
+      <c r="H152" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L152" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M152" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N152" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O152" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0.2417</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="S152" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="T152" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>63826.3</t>
+        </is>
+      </c>
+      <c r="V152" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-12T04:20</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>270</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1889.88</v>
+      </c>
+      <c r="H153" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S153" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="T153" t="n">
+        <v>101.79</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>1889.88</t>
+        </is>
+      </c>
+      <c r="V153" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:53</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>90</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>63830.3</v>
+      </c>
+      <c r="H154" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L154" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M154" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N154" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O154" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S154" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T154" t="n">
+        <v>105.17</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>63830.3</t>
+        </is>
+      </c>
+      <c r="V154" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>IV rank 80% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:53</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>2480</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>63830.3</v>
+      </c>
+      <c r="H155" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L155" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M155" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N155" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>-0.2667</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="S155" t="n">
+        <v>-100.19</v>
+      </c>
+      <c r="T155" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>63830.3</t>
+        </is>
+      </c>
+      <c r="V155" t="n">
+        <v>-104.41</v>
+      </c>
+      <c r="W155" t="n">
+        <v>-10.441</v>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:53</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>260</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1891.51</v>
+      </c>
+      <c r="H156" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M156" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S156" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="T156" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>1891.51</t>
+        </is>
+      </c>
+      <c r="V156" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>IV rank 70% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-12T07:17</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>90</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>63751.2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L157" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M157" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N157" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="S157" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="T157" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>63751.2</t>
+        </is>
+      </c>
+      <c r="V157" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W157" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>IV rank 80% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-12T07:17</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>2870</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>63751.2</v>
+      </c>
+      <c r="H158" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L158" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M158" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N158" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O158" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>-0.3171</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="S158" t="n">
+        <v>-99.88</v>
+      </c>
+      <c r="T158" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>63751.2</t>
+        </is>
+      </c>
+      <c r="V158" t="n">
+        <v>-104.18</v>
+      </c>
+      <c r="W158" t="n">
+        <v>-10.418</v>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-12T07:17</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>260</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1889.77</v>
+      </c>
+      <c r="H159" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O159" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="T159" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>1889.77</t>
+        </is>
+      </c>
+      <c r="V159" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:46</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>90</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>63779.1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>13</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L160" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M160" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N160" t="n">
+        <v>64600</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="T160" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>63779.1</t>
+        </is>
+      </c>
+      <c r="V160" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>IV rank 40% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:46</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>11410</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>63779.1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>13</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L161" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M161" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N161" t="n">
+        <v>64600</v>
+      </c>
+      <c r="O161" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>-0.1619</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="S161" t="n">
+        <v>-100.41</v>
+      </c>
+      <c r="T161" t="n">
+        <v>100.41</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>63779.1</t>
+        </is>
+      </c>
+      <c r="V161" t="n">
+        <v>-103.83</v>
+      </c>
+      <c r="W161" t="n">
+        <v>-10.383</v>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:46</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>260</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>1891.07</v>
+      </c>
+      <c r="H162" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O162" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S162" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T162" t="n">
+        <v>100.54</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>1891.07</t>
+        </is>
+      </c>
+      <c r="V162" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>IV rank 40% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:57</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>70</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>64083</v>
+      </c>
+      <c r="H163" t="n">
+        <v>15</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L163" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M163" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N163" t="n">
+        <v>64600</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>1.3692</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="S163" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T163" t="n">
+        <v>95.02</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>64083.0</t>
+        </is>
+      </c>
+      <c r="V163" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>IV rank 40% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:57</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1970</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>64083</v>
+      </c>
+      <c r="H164" t="n">
+        <v>15</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L164" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M164" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N164" t="n">
+        <v>64600</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P164" t="n">
+        <v>-1.1077</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="S164" t="n">
+        <v>-100.08</v>
+      </c>
+      <c r="T164" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>64083.0</t>
+        </is>
+      </c>
+      <c r="V164" t="n">
+        <v>-104.21</v>
+      </c>
+      <c r="W164" t="n">
+        <v>-10.421</v>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:57</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>390</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>64083</v>
+      </c>
+      <c r="H165" t="n">
+        <v>15</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L165" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M165" t="n">
+        <v>63800</v>
+      </c>
+      <c r="N165" t="n">
+        <v>64600</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0.8633</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="R165" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S165" t="n">
+        <v>-21.84</v>
+      </c>
+      <c r="T165" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>64083.0</t>
+        </is>
+      </c>
+      <c r="V165" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W165" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.3 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:57</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>260</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>1904.61</v>
+      </c>
+      <c r="H166" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L166" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M166" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O166" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0.2254</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="S166" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T166" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>1904.61</t>
+        </is>
+      </c>
+      <c r="V166" t="n">
+        <v>2</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>IV rank 30% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:57</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>1904.61</v>
+      </c>
+      <c r="H167" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="P167" t="n">
+        <v>-0.105</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="S167" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T167" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>1904.61</t>
+        </is>
+      </c>
+      <c r="V167" t="n">
+        <v>-26.95</v>
+      </c>
+      <c r="W167" t="n">
+        <v>-2.695</v>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 7.7 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:00</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>80</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>64200</v>
+      </c>
+      <c r="H168" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L168" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M168" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N168" t="n">
+        <v>64600</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>1.2307</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="T168" t="n">
+        <v>96.42</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>64200.0</t>
+        </is>
+      </c>
+      <c r="V168" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="W168" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>IV rank 30% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:00</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>34480</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>64200</v>
+      </c>
+      <c r="H169" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L169" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M169" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N169" t="n">
+        <v>64600</v>
+      </c>
+      <c r="O169" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>-1.2307</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="S169" t="n">
+        <v>-99.98999999999999</v>
+      </c>
+      <c r="T169" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>64200.0</t>
+        </is>
+      </c>
+      <c r="V169" t="n">
+        <v>-103.44</v>
+      </c>
+      <c r="W169" t="n">
+        <v>-10.344</v>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:00</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>5950</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>1911.18</v>
+      </c>
+      <c r="H170" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M170" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N170" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O170" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="P170" t="n">
+        <v>-0.3366</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="S170" t="n">
+        <v>-99.95999999999999</v>
+      </c>
+      <c r="T170" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>1911.18</t>
+        </is>
+      </c>
+      <c r="V170" t="n">
+        <v>-104.13</v>
+      </c>
+      <c r="W170" t="n">
+        <v>-10.413</v>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>IV rank 10% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-12T13:09</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>60</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>64091.2</v>
+      </c>
+      <c r="H171" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L171" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M171" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N171" t="n">
+        <v>66800</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="S171" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="T171" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="U171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-12T13:09</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>410</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>1910.17</v>
+      </c>
+      <c r="H172" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M172" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N172" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O172" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S172" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="T172" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="U172" t="inlineStr"/>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-12T18:36</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>4395.42</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>10</v>
+      </c>
+      <c r="U173" t="inlineStr"/>
+      <c r="X173" t="inlineStr"/>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
         </is>
       </c>
     </row>
@@ -14174,22 +16256,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>88.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="E2" t="n">
-        <v>3.34</v>
+        <v>69.02</v>
       </c>
       <c r="F2" t="n">
-        <v>0.19</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.33</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3">
@@ -14199,19 +16281,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07000000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07000000000000001</v>
+        <v>5.08</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="4">
@@ -14271,22 +16353,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>-1161.83</v>
+        <v>-1182.58</v>
       </c>
       <c r="F6" t="n">
-        <v>-52.81</v>
+        <v>-49.27</v>
       </c>
       <c r="G6" t="n">
-        <v>-116.18</v>
+        <v>-118.26</v>
       </c>
     </row>
     <row r="7">
@@ -14296,7 +16378,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -14305,13 +16387,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-4939.7</v>
+        <v>-5043.83</v>
       </c>
       <c r="F7" t="n">
-        <v>-98.79000000000001</v>
+        <v>-98.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-493.97</v>
+        <v>-504.38</v>
       </c>
     </row>
     <row r="8">
@@ -14321,7 +16403,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -14330,13 +16412,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-5091.18</v>
+        <v>-5611.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-103.9</v>
+        <v>-103.91</v>
       </c>
       <c r="G8" t="n">
-        <v>-509.12</v>
+        <v>-561.12</v>
       </c>
     </row>
   </sheetData>
@@ -14588,12 +16670,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10T10:15</t>
+          <t>2026-08-11T02:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14603,11 +16685,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14615,13 +16697,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1919.25</v>
+        <v>64081.6</v>
       </c>
       <c r="H3" t="n">
-        <v>38.3</v>
+        <v>28.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.649</v>
+        <v>0.487</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -14629,31 +16711,31 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.96</v>
+        <v>1.39</v>
       </c>
       <c r="L3" t="n">
-        <v>1900</v>
+        <v>65000</v>
       </c>
       <c r="M3" t="n">
-        <v>1850</v>
+        <v>65000</v>
       </c>
       <c r="N3" t="n">
-        <v>2200</v>
+        <v>69000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0199</v>
+        <v>0.0366</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="S3" t="n">
-        <v>21.89</v>
+        <v>13.96</v>
       </c>
       <c r="T3" t="n">
-        <v>98.11</v>
+        <v>94.88</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -14671,7 +16753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14685,7 +16767,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14693,45 +16775,45 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>64081.6</v>
+        <v>1878.17</v>
       </c>
       <c r="H4" t="n">
-        <v>28.5</v>
+        <v>39.85</v>
       </c>
       <c r="I4" t="n">
-        <v>0.487</v>
+        <v>0.66</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.39</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>65000</v>
+        <v>1900</v>
       </c>
       <c r="M4" t="n">
-        <v>65000</v>
+        <v>1850</v>
       </c>
       <c r="N4" t="n">
-        <v>69000</v>
+        <v>2200</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>-0.0001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0366</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0297</v>
+        <v>-0.0048</v>
       </c>
       <c r="S4" t="n">
-        <v>13.96</v>
+        <v>26.35</v>
       </c>
       <c r="T4" t="n">
-        <v>94.88</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -14744,26 +16826,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11T02:12</t>
+          <t>2026-08-12T13:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -14771,13 +16853,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1878.17</v>
+        <v>64091.2</v>
       </c>
       <c r="H5" t="n">
-        <v>39.85</v>
+        <v>28.55</v>
       </c>
       <c r="I5" t="n">
-        <v>0.66</v>
+        <v>0.488</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -14785,49 +16867,49 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="L5" t="n">
-        <v>1900</v>
+        <v>64000</v>
       </c>
       <c r="M5" t="n">
-        <v>1850</v>
+        <v>63000</v>
       </c>
       <c r="N5" t="n">
-        <v>2200</v>
+        <v>66800</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.2295</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0155</v>
       </c>
       <c r="S5" t="n">
-        <v>26.35</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>98.65000000000001</v>
+        <v>98.52</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
+          <t>IV rank 90% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11T12:24</t>
+          <t>2026-08-12T13:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14837,11 +16919,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -14849,77 +16931,77 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>64316.5</v>
+        <v>1910.17</v>
       </c>
       <c r="H6" t="n">
-        <v>21.65</v>
+        <v>41.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.641</v>
+        <v>0.658</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="L6" t="n">
-        <v>64200</v>
+        <v>1900</v>
       </c>
       <c r="M6" t="n">
-        <v>63800</v>
+        <v>1840</v>
       </c>
       <c r="N6" t="n">
-        <v>66800</v>
+        <v>2040</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1258</v>
+        <v>0.0592</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0125</v>
+        <v>-0.0027</v>
       </c>
       <c r="S6" t="n">
-        <v>9.67</v>
+        <v>22.88</v>
       </c>
       <c r="T6" t="n">
-        <v>102.97</v>
+        <v>100.12</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 78% rich — sell premium</t>
+          <t>IV rank 100% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11T12:24</t>
+          <t>2026-08-12T18:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>XAUTUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>perpetual</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>280</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -14927,51 +17009,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1891.13</v>
-      </c>
-      <c r="H7" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1890</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1820</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2020</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.0542</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.0032</v>
+        <v>4395.42</v>
       </c>
       <c r="S7" t="n">
-        <v>12.8</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>99.2</v>
+        <v>10</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 89% rich — sell premium</t>
+          <t>20/50 EMA 3rd retest</t>
         </is>
       </c>
     </row>
@@ -14992,7 +17042,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-11T20:33:17.813687 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-12T20:31:50.601283 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y173"/>
+  <dimension ref="A1:Y196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -16057,8 +16057,22 @@
       <c r="T171" t="n">
         <v>98.52</v>
       </c>
-      <c r="U171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>63485.7</t>
+        </is>
+      </c>
+      <c r="V171" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="W171" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="Y171" t="inlineStr">
         <is>
           <t>IV rank 90% rich — sell premium</t>
@@ -16091,7 +16105,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -16136,7 +16150,17 @@
         <v>100.12</v>
       </c>
       <c r="U172" t="inlineStr"/>
-      <c r="X172" t="inlineStr"/>
+      <c r="V172" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="Y172" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -16169,7 +16193,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -16181,11 +16205,2115 @@
       <c r="T173" t="n">
         <v>10</v>
       </c>
-      <c r="U173" t="inlineStr"/>
-      <c r="X173" t="inlineStr"/>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>4374.98</t>
+        </is>
+      </c>
+      <c r="V173" t="n">
+        <v>-12.53</v>
+      </c>
+      <c r="W173" t="n">
+        <v>-1.253</v>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="Y173" t="inlineStr">
         <is>
           <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:27</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>280</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>1879.93</v>
+      </c>
+      <c r="H174" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M174" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N174" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O174" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S174" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="T174" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>1879.0</t>
+        </is>
+      </c>
+      <c r="V174" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>IV rank 40% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-13T04:12</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>90</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>63626.1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L175" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M175" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N175" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0.1581</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="S175" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="T175" t="n">
+        <v>103.42</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>63626.1</t>
+        </is>
+      </c>
+      <c r="V175" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="W175" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-13T04:12</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>270</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>1886.18</v>
+      </c>
+      <c r="H176" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M176" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N176" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O176" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S176" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="T176" t="n">
+        <v>101.63</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>1886.18</t>
+        </is>
+      </c>
+      <c r="V176" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="W176" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:48</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>90</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>63888.8</v>
+      </c>
+      <c r="H177" t="n">
+        <v>18</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L177" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M177" t="n">
+        <v>63400</v>
+      </c>
+      <c r="N177" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O177" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="S177" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T177" t="n">
+        <v>103.97</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>63888.8</t>
+        </is>
+      </c>
+      <c r="V177" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="W177" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:49</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>2770</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>63888.8</v>
+      </c>
+      <c r="H178" t="n">
+        <v>18</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L178" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M178" t="n">
+        <v>63400</v>
+      </c>
+      <c r="N178" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P178" t="n">
+        <v>-0.2243</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="S178" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T178" t="n">
+        <v>100</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>63888.8</t>
+        </is>
+      </c>
+      <c r="V178" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W178" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:49</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>260</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>1896.84</v>
+      </c>
+      <c r="H179" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M179" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N179" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O179" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S179" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="T179" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>1896.84</t>
+        </is>
+      </c>
+      <c r="V179" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="W179" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:20</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>90</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>63872.4</v>
+      </c>
+      <c r="H180" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L180" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M180" t="n">
+        <v>63400</v>
+      </c>
+      <c r="N180" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O180" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="S180" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T180" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>63872.4</t>
+        </is>
+      </c>
+      <c r="V180" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W180" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>IV rank 55% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:20</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>3250</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>63872.4</v>
+      </c>
+      <c r="H181" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L181" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M181" t="n">
+        <v>63400</v>
+      </c>
+      <c r="N181" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P181" t="n">
+        <v>-0.2603</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="S181" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T181" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>63872.4</t>
+        </is>
+      </c>
+      <c r="V181" t="n">
+        <v>-104</v>
+      </c>
+      <c r="W181" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:20</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>260</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>1896.88</v>
+      </c>
+      <c r="H182" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M182" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N182" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O182" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S182" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T182" t="n">
+        <v>101.09</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>1896.88</t>
+        </is>
+      </c>
+      <c r="V182" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W182" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>IV rank 55% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:50</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>90</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>63768.7</v>
+      </c>
+      <c r="H183" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L183" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M183" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N183" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S183" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="T183" t="n">
+        <v>104.09</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>63768.7</t>
+        </is>
+      </c>
+      <c r="V183" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W183" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>IV rank 45% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:50</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>5040</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>63768.7</v>
+      </c>
+      <c r="H184" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L184" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M184" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N184" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O184" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>-0.3151</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="S184" t="n">
+        <v>-99.79000000000001</v>
+      </c>
+      <c r="T184" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>63768.7</t>
+        </is>
+      </c>
+      <c r="V184" t="n">
+        <v>-104.33</v>
+      </c>
+      <c r="W184" t="n">
+        <v>-10.433</v>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:50</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>260</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>1889.99</v>
+      </c>
+      <c r="H185" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M185" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O185" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S185" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="T185" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>1889.99</t>
+        </is>
+      </c>
+      <c r="V185" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W185" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>IV rank 36% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:59</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>80</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>63780.2</v>
+      </c>
+      <c r="H186" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L186" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M186" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N186" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S186" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T186" t="n">
+        <v>94.68000000000001</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>63780.2</t>
+        </is>
+      </c>
+      <c r="V186" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W186" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>IV rank 27% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:59</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>49890</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>63780.2</v>
+      </c>
+      <c r="H187" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L187" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M187" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N187" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>-0.1105</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="S187" t="n">
+        <v>-99.78</v>
+      </c>
+      <c r="T187" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>63780.2</t>
+        </is>
+      </c>
+      <c r="V187" t="n">
+        <v>-104.77</v>
+      </c>
+      <c r="W187" t="n">
+        <v>-10.477</v>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:59</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>450</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>63780.2</v>
+      </c>
+      <c r="H188" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L188" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M188" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N188" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O188" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P188" t="n">
+        <v>-0.0878</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="R188" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S188" t="n">
+        <v>-11.03</v>
+      </c>
+      <c r="T188" t="n">
+        <v>101.03</v>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>63780.2</t>
+        </is>
+      </c>
+      <c r="V188" t="n">
+        <v>-59.54</v>
+      </c>
+      <c r="W188" t="n">
+        <v>-5.954</v>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.7 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:59</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>20120</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>1889.7</v>
+      </c>
+      <c r="H189" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M189" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N189" t="n">
+        <v>1920</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P189" t="n">
+        <v>-0.1406</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="S189" t="n">
+        <v>-100.6</v>
+      </c>
+      <c r="T189" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>1889.7</t>
+        </is>
+      </c>
+      <c r="V189" t="n">
+        <v>-104.62</v>
+      </c>
+      <c r="W189" t="n">
+        <v>-10.462</v>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>IV rank 18% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:59</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>1889.7</v>
+      </c>
+      <c r="H190" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M190" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N190" t="n">
+        <v>1920</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="P190" t="n">
+        <v>-0.0368</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="R190" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="S190" t="n">
+        <v>-100.19</v>
+      </c>
+      <c r="T190" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>1889.7</t>
+        </is>
+      </c>
+      <c r="V190" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="W190" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 4.0 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-13T11:04</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>3830</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>63654.4</v>
+      </c>
+      <c r="H191" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L191" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M191" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N191" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O191" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P191" t="n">
+        <v>-0.6693</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S191" t="n">
+        <v>-99.95999999999999</v>
+      </c>
+      <c r="T191" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>63654.4</t>
+        </is>
+      </c>
+      <c r="V191" t="n">
+        <v>-104.18</v>
+      </c>
+      <c r="W191" t="n">
+        <v>-10.418</v>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>IV rank 0% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-13T11:04</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>273310</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>63654.4</v>
+      </c>
+      <c r="H192" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L192" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M192" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N192" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O192" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>-0.0359</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S192" t="n">
+        <v>-109.32</v>
+      </c>
+      <c r="T192" t="n">
+        <v>109.32</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>63654.4</t>
+        </is>
+      </c>
+      <c r="V192" t="n">
+        <v>-109.32</v>
+      </c>
+      <c r="W192" t="n">
+        <v>-10.932</v>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-13T11:04</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>3050</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>1883.08</v>
+      </c>
+      <c r="H193" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M193" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N193" t="n">
+        <v>1920</v>
+      </c>
+      <c r="O193" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="P193" t="n">
+        <v>-0.8411999999999999</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S193" t="n">
+        <v>-100.04</v>
+      </c>
+      <c r="T193" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>1883.08</t>
+        </is>
+      </c>
+      <c r="V193" t="n">
+        <v>-104</v>
+      </c>
+      <c r="W193" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>IV rank 0% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:21</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>60</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>63706.2</v>
+      </c>
+      <c r="H194" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L194" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M194" t="n">
+        <v>61500</v>
+      </c>
+      <c r="N194" t="n">
+        <v>66500</v>
+      </c>
+      <c r="O194" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>-0.0147</v>
+      </c>
+      <c r="S194" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="T194" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="U194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:21</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>290</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>1889.97</v>
+      </c>
+      <c r="H195" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L195" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M195" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S195" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="T195" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>IV rank 82% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-13T19:43</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>270</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>1886.57</v>
+      </c>
+      <c r="H196" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M196" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N196" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O196" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="S196" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="T196" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="U196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>IV rank 45% — default sell</t>
         </is>
       </c>
     </row>
@@ -16256,22 +18384,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>93.8</v>
+        <v>93.3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="E2" t="n">
-        <v>69.02</v>
+        <v>124.22</v>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.76</v>
       </c>
       <c r="G2" t="n">
-        <v>6.9</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="3">
@@ -16303,7 +18431,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -16312,13 +18440,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-16.61</v>
+        <v>-29.14</v>
       </c>
       <c r="F4" t="n">
-        <v>-16.61</v>
+        <v>-14.57</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.66</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="5">
@@ -16353,22 +18481,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-1182.58</v>
+        <v>-1252.62</v>
       </c>
       <c r="F6" t="n">
-        <v>-49.27</v>
+        <v>-48.18</v>
       </c>
       <c r="G6" t="n">
-        <v>-118.26</v>
+        <v>-125.26</v>
       </c>
     </row>
     <row r="7">
@@ -16378,22 +18506,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-5043.83</v>
+        <v>-5356.63</v>
       </c>
       <c r="F7" t="n">
-        <v>-98.90000000000001</v>
+        <v>-99.2</v>
       </c>
       <c r="G7" t="n">
-        <v>-504.38</v>
+        <v>-535.66</v>
       </c>
     </row>
     <row r="8">
@@ -16403,7 +18531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -16412,13 +18540,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-5611.25</v>
+        <v>-6137.82</v>
       </c>
       <c r="F8" t="n">
-        <v>-103.91</v>
+        <v>-104.03</v>
       </c>
       <c r="G8" t="n">
-        <v>-561.12</v>
+        <v>-613.78</v>
       </c>
     </row>
   </sheetData>
@@ -16432,7 +18560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16826,7 +18954,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12T13:09</t>
+          <t>2026-08-13T13:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -16841,7 +18969,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -16853,58 +18981,58 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>64091.2</v>
+        <v>63706.2</v>
       </c>
       <c r="H5" t="n">
-        <v>28.55</v>
+        <v>24.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.488</v>
+        <v>0.587</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="L5" t="n">
-        <v>64000</v>
+        <v>63600</v>
       </c>
       <c r="M5" t="n">
-        <v>63000</v>
+        <v>61500</v>
       </c>
       <c r="N5" t="n">
-        <v>66800</v>
+        <v>66500</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2295</v>
+        <v>0.1831</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0147</v>
       </c>
       <c r="S5" t="n">
-        <v>9.960000000000001</v>
+        <v>7.03</v>
       </c>
       <c r="T5" t="n">
-        <v>98.52</v>
+        <v>101.45</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 90% rich — sell premium</t>
+          <t>IV rank 91% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12T13:09</t>
+          <t>2026-08-13T19:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -16919,11 +19047,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>410</v>
+        <v>270</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -16931,97 +19059,51 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1910.17</v>
+        <v>1886.57</v>
       </c>
       <c r="H6" t="n">
-        <v>41.1</v>
+        <v>22.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.658</v>
+        <v>0.727</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
-        <v>1900</v>
+        <v>1880</v>
       </c>
       <c r="M6" t="n">
-        <v>1840</v>
+        <v>1800</v>
       </c>
       <c r="N6" t="n">
-        <v>2040</v>
+        <v>2000</v>
       </c>
       <c r="O6" t="n">
-        <v>-0</v>
+        <v>-0.0003</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0592</v>
+        <v>0.0612</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0027</v>
+        <v>-0.0031</v>
       </c>
       <c r="S6" t="n">
-        <v>22.88</v>
+        <v>7.99</v>
       </c>
       <c r="T6" t="n">
-        <v>100.12</v>
+        <v>100.01</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-12T18:36</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>XAUTUSD</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>gold_ema</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>perpetual</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4395.42</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>10</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>20/50 EMA 3rd retest</t>
+          <t>IV rank 45% — default sell</t>
         </is>
       </c>
     </row>
@@ -17042,7 +19124,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-12T20:31:50.601283 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-13T20:29:34.425160 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y196"/>
+  <dimension ref="A1:Y210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -11877,8 +11877,22 @@
       <c r="T125" t="n">
         <v>106.16</v>
       </c>
-      <c r="U125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>63574.7</t>
+        </is>
+      </c>
+      <c r="V125" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="W125" t="n">
+        <v>-0.378</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="Y125" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -12805,7 +12819,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -12850,7 +12864,17 @@
         <v>98.65000000000001</v>
       </c>
       <c r="U136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
+      <c r="V136" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="Y136" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -18099,7 +18123,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -18143,8 +18167,22 @@
       <c r="T194" t="n">
         <v>101.45</v>
       </c>
-      <c r="U194" t="inlineStr"/>
-      <c r="X194" t="inlineStr"/>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>63574.7</t>
+        </is>
+      </c>
+      <c r="V194" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W194" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="Y194" t="inlineStr">
         <is>
           <t>IV rank 91% rich — sell premium</t>
@@ -18265,7 +18303,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -18310,10 +18348,1272 @@
         <v>100.01</v>
       </c>
       <c r="U196" t="inlineStr"/>
-      <c r="X196" t="inlineStr"/>
+      <c r="V196" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="W196" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="Y196" t="inlineStr">
         <is>
           <t>IV rank 45% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-13T23:57</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>280</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>1885.75</v>
+      </c>
+      <c r="H197" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M197" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N197" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O197" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S197" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="T197" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>1889.66</t>
+        </is>
+      </c>
+      <c r="V197" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="W197" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>IV rank 27% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-14T04:17</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>90</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>63456.2</v>
+      </c>
+      <c r="H198" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L198" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M198" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N198" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="S198" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="T198" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>63456.2</t>
+        </is>
+      </c>
+      <c r="V198" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="W198" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-14T04:17</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>260</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>1887.66</v>
+      </c>
+      <c r="H199" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K199" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1850</v>
+      </c>
+      <c r="N199" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O199" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0.0806</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S199" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="T199" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>1887.66</t>
+        </is>
+      </c>
+      <c r="V199" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="W199" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-14T05:53</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>90</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>63368.3</v>
+      </c>
+      <c r="H200" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L200" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M200" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N200" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O200" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="S200" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T200" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>63368.3</t>
+        </is>
+      </c>
+      <c r="V200" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="W200" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-14T05:53</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>260</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>1884.19</v>
+      </c>
+      <c r="H201" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L201" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M201" t="n">
+        <v>1850</v>
+      </c>
+      <c r="N201" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S201" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T201" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>1884.19</t>
+        </is>
+      </c>
+      <c r="V201" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="W201" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-14T07:17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>90</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>63096.8</v>
+      </c>
+      <c r="H202" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L202" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M202" t="n">
+        <v>62000</v>
+      </c>
+      <c r="N202" t="n">
+        <v>71000</v>
+      </c>
+      <c r="O202" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S202" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="T202" t="n">
+        <v>103.64</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>63096.8</t>
+        </is>
+      </c>
+      <c r="V202" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="W202" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-14T07:17</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>260</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>1876.77</v>
+      </c>
+      <c r="H203" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M203" t="n">
+        <v>1850</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O203" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="S203" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="T203" t="n">
+        <v>100.23</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>1876.77</t>
+        </is>
+      </c>
+      <c r="V203" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="W203" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>IV rank 58% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-14T08:43</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>70</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>62826.7</v>
+      </c>
+      <c r="H204" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L204" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M204" t="n">
+        <v>62000</v>
+      </c>
+      <c r="N204" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="S204" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T204" t="n">
+        <v>102.93</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>62826.7</t>
+        </is>
+      </c>
+      <c r="V204" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W204" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-14T08:43</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>260</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>1873.46</v>
+      </c>
+      <c r="H205" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M205" t="n">
+        <v>1850</v>
+      </c>
+      <c r="N205" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O205" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="S205" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T205" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>1873.46</t>
+        </is>
+      </c>
+      <c r="V205" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W205" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-14T09:44</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>260</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>1872.35</v>
+      </c>
+      <c r="H206" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M206" t="n">
+        <v>1850</v>
+      </c>
+      <c r="N206" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O206" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S206" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="T206" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="U206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-14T10:41</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>80</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>62889.2</v>
+      </c>
+      <c r="H207" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L207" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M207" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N207" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>1.0395</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S207" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T207" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>62889.2</t>
+        </is>
+      </c>
+      <c r="V207" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W207" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>IV rank 42% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-14T12:10</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>90</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>62801.2</v>
+      </c>
+      <c r="H208" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L208" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M208" t="n">
+        <v>62400</v>
+      </c>
+      <c r="N208" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O208" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="S208" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="T208" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="U208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-14T12:10</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>280</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>1876.06</v>
+      </c>
+      <c r="H209" t="n">
+        <v>31</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M209" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N209" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S209" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="T209" t="n">
+        <v>101.02</v>
+      </c>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="W209" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-14T17:37</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>270</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>1885.07</v>
+      </c>
+      <c r="H210" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L210" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M210" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N210" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O210" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S210" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="T210" t="n">
+        <v>101.82</v>
+      </c>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="W210" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>IV rank 58% — default sell</t>
         </is>
       </c>
     </row>
@@ -18384,22 +19684,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>93.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>2.45</v>
+        <v>3.22</v>
       </c>
       <c r="E2" t="n">
-        <v>124.22</v>
+        <v>190.04</v>
       </c>
       <c r="F2" t="n">
-        <v>2.76</v>
+        <v>3.22</v>
       </c>
       <c r="G2" t="n">
-        <v>12.42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -18409,19 +19709,22 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.01</v>
       </c>
     </row>
     <row r="4">
@@ -18560,7 +19863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18720,7 +20023,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10T10:15</t>
+          <t>2026-08-11T02:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18735,11 +20038,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18747,45 +20050,45 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>65039.5</v>
+        <v>64081.6</v>
       </c>
       <c r="H2" t="n">
-        <v>26.8</v>
+        <v>28.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.412</v>
+        <v>0.487</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.97</v>
+        <v>1.39</v>
       </c>
       <c r="L2" t="n">
         <v>65000</v>
       </c>
       <c r="M2" t="n">
-        <v>60000</v>
+        <v>65000</v>
       </c>
       <c r="N2" t="n">
-        <v>71000</v>
+        <v>69000</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0907</v>
+        <v>0.0366</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.03</v>
+        <v>-0.0297</v>
       </c>
       <c r="S2" t="n">
-        <v>9.24</v>
+        <v>13.96</v>
       </c>
       <c r="T2" t="n">
-        <v>106.16</v>
+        <v>94.88</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -18798,12 +20101,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11T02:12</t>
+          <t>2026-08-14T09:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18817,7 +20120,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18825,77 +20128,77 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>64081.6</v>
+        <v>1872.35</v>
       </c>
       <c r="H3" t="n">
-        <v>28.5</v>
+        <v>33.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.487</v>
+        <v>0.605</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="L3" t="n">
-        <v>65000</v>
+        <v>1900</v>
       </c>
       <c r="M3" t="n">
-        <v>65000</v>
+        <v>1850</v>
       </c>
       <c r="N3" t="n">
-        <v>69000</v>
+        <v>2200</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>-0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0366</v>
+        <v>0.0127</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0297</v>
+        <v>-0.0059</v>
       </c>
       <c r="S3" t="n">
-        <v>13.96</v>
+        <v>29.43</v>
       </c>
       <c r="T3" t="n">
-        <v>94.88</v>
+        <v>100.57</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
+          <t>IV rank 92% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11T02:12</t>
+          <t>2026-08-14T12:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -18903,13 +20206,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1878.17</v>
+        <v>62801.2</v>
       </c>
       <c r="H4" t="n">
-        <v>39.85</v>
+        <v>23.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66</v>
+        <v>0.716</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -18917,193 +20220,37 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="L4" t="n">
-        <v>1900</v>
+        <v>63000</v>
       </c>
       <c r="M4" t="n">
-        <v>1850</v>
+        <v>62400</v>
       </c>
       <c r="N4" t="n">
-        <v>2200</v>
+        <v>66000</v>
       </c>
       <c r="O4" t="n">
         <v>-0.0001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0048</v>
+        <v>-0.0074</v>
       </c>
       <c r="S4" t="n">
-        <v>26.35</v>
+        <v>7.88</v>
       </c>
       <c r="T4" t="n">
-        <v>98.65000000000001</v>
+        <v>100.12</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-13T13:21</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>60</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>63706.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L5" t="n">
-        <v>63600</v>
-      </c>
-      <c r="M5" t="n">
-        <v>61500</v>
-      </c>
-      <c r="N5" t="n">
-        <v>66500</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.0001</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.1831</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.0147</v>
-      </c>
-      <c r="S5" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="T5" t="n">
-        <v>101.45</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>IV rank 91% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-13T19:43</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>270</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1886.57</v>
-      </c>
-      <c r="H6" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1880</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0612</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.0031</v>
-      </c>
-      <c r="S6" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="T6" t="n">
-        <v>100.01</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>IV rank 45% — default sell</t>
+          <t>IV rank 83% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -19124,7 +20271,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-13T20:29:34.425160 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-14T20:20:56.419963 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y210"/>
+  <dimension ref="A1:Y230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -19433,8 +19433,22 @@
       <c r="T208" t="n">
         <v>100.12</v>
       </c>
-      <c r="U208" t="inlineStr"/>
-      <c r="X208" t="inlineStr"/>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>63022.5</t>
+        </is>
+      </c>
+      <c r="V208" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="W208" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
       <c r="Y208" t="inlineStr">
         <is>
           <t>IV rank 83% rich — sell premium</t>
@@ -19614,6 +19628,1772 @@
       <c r="Y210" t="inlineStr">
         <is>
           <t>IV rank 58% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-15T00:58</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>260</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>1882.67</v>
+      </c>
+      <c r="H211" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L211" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M211" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N211" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O211" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S211" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="T211" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>1882.67</t>
+        </is>
+      </c>
+      <c r="V211" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>IV rank 54% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-15T02:14</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>90</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>63045.7</v>
+      </c>
+      <c r="H212" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L212" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M212" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N212" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O212" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0.1066</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="S212" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T212" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>63045.7</t>
+        </is>
+      </c>
+      <c r="V212" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-15T02:14</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>250</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>1884.83</v>
+      </c>
+      <c r="H213" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N213" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="T213" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>1884.83</t>
+        </is>
+      </c>
+      <c r="V213" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="W213" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>IV rank 46% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:06</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>90</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>63148.4</v>
+      </c>
+      <c r="H214" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L214" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M214" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N214" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O214" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="S214" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T214" t="n">
+        <v>104.24</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>63148.4</t>
+        </is>
+      </c>
+      <c r="V214" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W214" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>IV rank 62% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:06</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>260</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>1885.97</v>
+      </c>
+      <c r="H215" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S215" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T215" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>1885.97</t>
+        </is>
+      </c>
+      <c r="V215" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W215" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>IV rank 46% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:52</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>80</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>63074.7</v>
+      </c>
+      <c r="H216" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K216" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L216" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M216" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N216" t="n">
+        <v>66400</v>
+      </c>
+      <c r="O216" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S216" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T216" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>63074.7</t>
+        </is>
+      </c>
+      <c r="V216" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W216" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>IV rank 38% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:53</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>260</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>1883.5</v>
+      </c>
+      <c r="H217" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M217" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N217" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O217" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S217" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T217" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>1883.5</t>
+        </is>
+      </c>
+      <c r="V217" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="W217" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-15T04:24</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>80</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>63122.8</v>
+      </c>
+      <c r="H218" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L218" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M218" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N218" t="n">
+        <v>66400</v>
+      </c>
+      <c r="O218" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="S218" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T218" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>63122.8</t>
+        </is>
+      </c>
+      <c r="V218" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W218" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-15T04:24</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>260</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>1884.04</v>
+      </c>
+      <c r="H219" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L219" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N219" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O219" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S219" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T219" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>1884.04</t>
+        </is>
+      </c>
+      <c r="V219" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="W219" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-15T04:26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>4366.86</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>10</v>
+      </c>
+      <c r="U220" t="inlineStr"/>
+      <c r="X220" t="inlineStr"/>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-15T04:55</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>80</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>63121</v>
+      </c>
+      <c r="H221" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L221" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M221" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N221" t="n">
+        <v>66400</v>
+      </c>
+      <c r="O221" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="S221" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T221" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>63121.0</t>
+        </is>
+      </c>
+      <c r="V221" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W221" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-15T04:56</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>260</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>1884.38</v>
+      </c>
+      <c r="H222" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M222" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N222" t="n">
+        <v>1980</v>
+      </c>
+      <c r="O222" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S222" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T222" t="n">
+        <v>100.91</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>1884.38</t>
+        </is>
+      </c>
+      <c r="V222" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="W222" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:22</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>80</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>63136.2</v>
+      </c>
+      <c r="H223" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L223" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M223" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N223" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O223" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="S223" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T223" t="n">
+        <v>94.53</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>63136.2</t>
+        </is>
+      </c>
+      <c r="V223" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W223" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>IV rank 38% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:22</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>270</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>1884.25</v>
+      </c>
+      <c r="H224" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M224" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N224" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="S224" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="T224" t="n">
+        <v>101.82</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>1884.25</t>
+        </is>
+      </c>
+      <c r="V224" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="W224" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:50</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>80</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>63061.2</v>
+      </c>
+      <c r="H225" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L225" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M225" t="n">
+        <v>62800</v>
+      </c>
+      <c r="N225" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O225" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0.1446</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="S225" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T225" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>63061.2</t>
+        </is>
+      </c>
+      <c r="V225" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W225" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:50</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>250</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>1880.47</v>
+      </c>
+      <c r="H226" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L226" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M226" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N226" t="n">
+        <v>2040</v>
+      </c>
+      <c r="O226" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S226" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T226" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>1880.47</t>
+        </is>
+      </c>
+      <c r="V226" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W226" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-15T07:43</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>90</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>63084.3</v>
+      </c>
+      <c r="H227" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L227" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M227" t="n">
+        <v>62800</v>
+      </c>
+      <c r="N227" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="S227" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T227" t="n">
+        <v>104.67</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>63084.3</t>
+        </is>
+      </c>
+      <c r="V227" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="W227" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-15T08:43</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>80</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>63019.4</v>
+      </c>
+      <c r="H228" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L228" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M228" t="n">
+        <v>62800</v>
+      </c>
+      <c r="N228" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O228" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0.2739</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="S228" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T228" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>63019.4</t>
+        </is>
+      </c>
+      <c r="V228" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W228" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:38</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>80</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>62983.5</v>
+      </c>
+      <c r="H229" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K229" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L229" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M229" t="n">
+        <v>62800</v>
+      </c>
+      <c r="N229" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="S229" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="T229" t="n">
+        <v>106.64</v>
+      </c>
+      <c r="U229" t="inlineStr"/>
+      <c r="X229" t="inlineStr"/>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:38</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>270</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>1879.02</v>
+      </c>
+      <c r="H230" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M230" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N230" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S230" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="T230" t="n">
+        <v>101.09</v>
+      </c>
+      <c r="U230" t="inlineStr"/>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>IV rank 46% — default sell</t>
         </is>
       </c>
     </row>
@@ -19684,22 +21464,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
-        <v>94.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>3.22</v>
+        <v>3.82</v>
       </c>
       <c r="E2" t="n">
-        <v>190.04</v>
+        <v>240.99</v>
       </c>
       <c r="F2" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="3">
@@ -19863,7 +21643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20179,26 +21959,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14T12:10</t>
+          <t>2026-08-15T04:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>XAUTUSD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>perpetual</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -20206,51 +21986,175 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>62801.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L4" t="n">
-        <v>63000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>62400</v>
-      </c>
-      <c r="N4" t="n">
-        <v>66000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-0.0001</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.08169999999999999</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.0074</v>
+        <v>4366.86</v>
       </c>
       <c r="S4" t="n">
-        <v>7.88</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>100.12</v>
+        <v>10</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 83% rich — sell premium</t>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:38</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>62983.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L5" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>62800</v>
+      </c>
+      <c r="N5" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="T5" t="n">
+        <v>106.64</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>270</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1879.02</v>
+      </c>
+      <c r="H6" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="T6" t="n">
+        <v>101.09</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>IV rank 46% — default sell</t>
         </is>
       </c>
     </row>
@@ -20271,7 +22175,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-14T20:20:56.419963 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-15T20:10:43.947988 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y230"/>
+  <dimension ref="A1:Y254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -21312,7 +21312,17 @@
         <v>106.64</v>
       </c>
       <c r="U229" t="inlineStr"/>
-      <c r="X229" t="inlineStr"/>
+      <c r="V229" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W229" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
       <c r="Y229" t="inlineStr">
         <is>
           <t>IV rank 31% — default sell</t>
@@ -21345,7 +21355,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -21390,10 +21400,2200 @@
         <v>101.09</v>
       </c>
       <c r="U230" t="inlineStr"/>
-      <c r="X230" t="inlineStr"/>
+      <c r="V230" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W230" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
       <c r="Y230" t="inlineStr">
         <is>
           <t>IV rank 46% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:24</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>90</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>63077.7</v>
+      </c>
+      <c r="H231" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L231" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M231" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N231" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="S231" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T231" t="n">
+        <v>105.31</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>63077.7</t>
+        </is>
+      </c>
+      <c r="V231" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W231" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>IV rank 57% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:24</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>260</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>1881.99</v>
+      </c>
+      <c r="H232" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L232" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M232" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N232" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S232" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T232" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>1881.99</t>
+        </is>
+      </c>
+      <c r="V232" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="W232" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>IV rank 64% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-16T02:39</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>80</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>63120.5</v>
+      </c>
+      <c r="H233" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L233" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M233" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N233" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O233" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="S233" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="T233" t="n">
+        <v>94.34</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>63120.5</t>
+        </is>
+      </c>
+      <c r="V233" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W233" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>IV rank 36% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-16T02:39</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>260</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>1883.75</v>
+      </c>
+      <c r="H234" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M234" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S234" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T234" t="n">
+        <v>101.87</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>1883.75</t>
+        </is>
+      </c>
+      <c r="V234" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="W234" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>IV rank 64% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-16T03:32</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>80</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>63120</v>
+      </c>
+      <c r="H235" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K235" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L235" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M235" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N235" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O235" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="S235" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T235" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>63120.0</t>
+        </is>
+      </c>
+      <c r="V235" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W235" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>IV rank 36% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-16T03:32</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>250</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>1883.79</v>
+      </c>
+      <c r="H236" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K236" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L236" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M236" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N236" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S236" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T236" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>1883.79</t>
+        </is>
+      </c>
+      <c r="V236" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W236" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>IV rank 64% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-16T04:20</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>90</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>63156.6</v>
+      </c>
+      <c r="H237" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K237" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L237" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M237" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N237" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O237" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0.2306</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="S237" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T237" t="n">
+        <v>104.72</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>63156.6</t>
+        </is>
+      </c>
+      <c r="V237" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="W237" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-16T04:20</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>260</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>1883.84</v>
+      </c>
+      <c r="H238" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K238" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L238" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M238" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N238" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O238" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S238" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="T238" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>1883.84</t>
+        </is>
+      </c>
+      <c r="V238" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="W238" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-16T04:59</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>90</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>63086.7</v>
+      </c>
+      <c r="H239" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K239" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L239" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M239" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N239" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O239" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="S239" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="T239" t="n">
+        <v>103.91</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>63086.7</t>
+        </is>
+      </c>
+      <c r="V239" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="W239" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-16T04:59</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>260</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>1881.82</v>
+      </c>
+      <c r="H240" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M240" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N240" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O240" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S240" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T240" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>1881.82</t>
+        </is>
+      </c>
+      <c r="V240" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W240" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-16T05:34</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>90</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>63069.2</v>
+      </c>
+      <c r="H241" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K241" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L241" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M241" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N241" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="S241" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T241" t="n">
+        <v>103.94</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>63069.2</t>
+        </is>
+      </c>
+      <c r="V241" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="W241" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>IV rank 57% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-16T05:34</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>260</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>1880.98</v>
+      </c>
+      <c r="H242" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M242" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N242" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O242" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S242" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T242" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>1880.98</t>
+        </is>
+      </c>
+      <c r="V242" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W242" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>IV rank 36% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-16T06:00</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>90</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>63063.3</v>
+      </c>
+      <c r="H243" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L243" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M243" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N243" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="S243" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="T243" t="n">
+        <v>104.17</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>63063.3</t>
+        </is>
+      </c>
+      <c r="V243" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="W243" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-16T06:00</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>260</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>1879.87</v>
+      </c>
+      <c r="H244" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L244" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M244" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N244" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S244" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T244" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>1879.87</t>
+        </is>
+      </c>
+      <c r="V244" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W244" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>IV rank 36% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-16T06:53</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>90</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>63071.7</v>
+      </c>
+      <c r="H245" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L245" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M245" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N245" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S245" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T245" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>63071.7</t>
+        </is>
+      </c>
+      <c r="V245" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W245" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-16T06:53</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>250</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>1880.63</v>
+      </c>
+      <c r="H246" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K246" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L246" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M246" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N246" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O246" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P246" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S246" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T246" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>1880.63</t>
+        </is>
+      </c>
+      <c r="V246" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W246" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>IV rank 36% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-16T07:26</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>90</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>63061</v>
+      </c>
+      <c r="H247" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K247" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L247" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M247" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N247" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="S247" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T247" t="n">
+        <v>105.53</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>63061.0</t>
+        </is>
+      </c>
+      <c r="V247" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W247" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>IV rank 36% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-16T07:26</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>250</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>1881.74</v>
+      </c>
+      <c r="H248" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L248" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M248" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N248" t="n">
+        <v>1940</v>
+      </c>
+      <c r="O248" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="S248" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T248" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>1881.74</t>
+        </is>
+      </c>
+      <c r="V248" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W248" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-16T07:54</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>90</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>63058.7</v>
+      </c>
+      <c r="H249" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L249" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M249" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N249" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P249" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="S249" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T249" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>63058.7</t>
+        </is>
+      </c>
+      <c r="V249" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="W249" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-16T08:23</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>80</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>63062.1</v>
+      </c>
+      <c r="H250" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L250" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M250" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N250" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O250" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="S250" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T250" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>63062.1</t>
+        </is>
+      </c>
+      <c r="V250" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W250" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-16T08:55</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>90</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>63069.6</v>
+      </c>
+      <c r="H251" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L251" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M251" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N251" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O251" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="S251" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T251" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>63069.6</t>
+        </is>
+      </c>
+      <c r="V251" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="W251" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-16T09:24</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>90</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>63068.9</v>
+      </c>
+      <c r="H252" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L252" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M252" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N252" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O252" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S252" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T252" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>63068.9</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W252" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-16T12:49</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>90</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>63007.1</v>
+      </c>
+      <c r="H253" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L253" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M253" t="n">
+        <v>61600</v>
+      </c>
+      <c r="N253" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="S253" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="T253" t="n">
+        <v>100.54</v>
+      </c>
+      <c r="U253" t="inlineStr"/>
+      <c r="X253" t="inlineStr"/>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-16T12:49</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>370</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>1879.7</v>
+      </c>
+      <c r="H254" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L254" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M254" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N254" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S254" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T254" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="U254" t="inlineStr"/>
+      <c r="X254" t="inlineStr"/>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -21464,22 +23664,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C2" t="n">
-        <v>96.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="D2" t="n">
-        <v>3.82</v>
+        <v>4.53</v>
       </c>
       <c r="E2" t="n">
-        <v>240.99</v>
+        <v>301.61</v>
       </c>
       <c r="F2" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="G2" t="n">
-        <v>24.1</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="3">
@@ -22005,7 +24205,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15T12:38</t>
+          <t>2026-08-16T12:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -22020,11 +24220,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -22032,58 +24232,58 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>62983.5</v>
+        <v>63007.1</v>
       </c>
       <c r="H5" t="n">
-        <v>12.2</v>
+        <v>18.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.655</v>
+        <v>0.697</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="L5" t="n">
         <v>63000</v>
       </c>
       <c r="M5" t="n">
-        <v>62800</v>
+        <v>61600</v>
       </c>
       <c r="N5" t="n">
-        <v>64000</v>
+        <v>64800</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0712</v>
+        <v>0.1092</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0135</v>
+        <v>-0.0128</v>
       </c>
       <c r="S5" t="n">
-        <v>5.36</v>
+        <v>7.46</v>
       </c>
       <c r="T5" t="n">
-        <v>106.64</v>
+        <v>100.54</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 31% — default sell</t>
+          <t>IV rank 86% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-15T12:38</t>
+          <t>2026-08-16T12:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -22098,11 +24298,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -22110,13 +24310,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1879.02</v>
+        <v>1879.7</v>
       </c>
       <c r="H6" t="n">
-        <v>18.25</v>
+        <v>27.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.716</v>
+        <v>0.735</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -22124,37 +24324,37 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="L6" t="n">
         <v>1880</v>
       </c>
       <c r="M6" t="n">
-        <v>1860</v>
+        <v>1840</v>
       </c>
       <c r="N6" t="n">
-        <v>1940</v>
+        <v>2000</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0381</v>
+        <v>0.0408</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="S6" t="n">
-        <v>6.91</v>
+        <v>11.1</v>
       </c>
       <c r="T6" t="n">
-        <v>101.09</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 46% — default sell</t>
+          <t>IV rank 86% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -22175,7 +24375,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15T20:10:43.947988 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-16T20:09:43.583339 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y254"/>
+  <dimension ref="A1:Y299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20485,7 +20485,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -20497,8 +20497,22 @@
       <c r="T220" t="n">
         <v>10</v>
       </c>
-      <c r="U220" t="inlineStr"/>
-      <c r="X220" t="inlineStr"/>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>4358.46</t>
+        </is>
+      </c>
+      <c r="V220" t="n">
+        <v>-16.12</v>
+      </c>
+      <c r="W220" t="n">
+        <v>-1.612</v>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
       <c r="Y220" t="inlineStr">
         <is>
           <t>20/50 EMA 3rd retest</t>
@@ -23467,7 +23481,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -23511,8 +23525,22 @@
       <c r="T253" t="n">
         <v>100.54</v>
       </c>
-      <c r="U253" t="inlineStr"/>
-      <c r="X253" t="inlineStr"/>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>63138.6</t>
+        </is>
+      </c>
+      <c r="V253" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="W253" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="Y253" t="inlineStr">
         <is>
           <t>IV rank 86% rich — sell premium</t>
@@ -23545,7 +23573,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -23589,11 +23617,4125 @@
       <c r="T254" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="U254" t="inlineStr"/>
-      <c r="X254" t="inlineStr"/>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>1891.03</t>
+        </is>
+      </c>
+      <c r="V254" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="W254" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="Y254" t="inlineStr">
         <is>
           <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-17T02:33</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>90</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>63320</v>
+      </c>
+      <c r="H255" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L255" t="n">
+        <v>63000</v>
+      </c>
+      <c r="M255" t="n">
+        <v>62000</v>
+      </c>
+      <c r="N255" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="S255" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="T255" t="n">
+        <v>103.37</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>63320.0</t>
+        </is>
+      </c>
+      <c r="V255" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="W255" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-17T02:33</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>280</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>1895.12</v>
+      </c>
+      <c r="H256" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L256" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M256" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N256" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O256" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S256" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="T256" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>1895.12</t>
+        </is>
+      </c>
+      <c r="V256" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="W256" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-17T03:32</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>90</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>63347.2</v>
+      </c>
+      <c r="H257" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L257" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M257" t="n">
+        <v>61600</v>
+      </c>
+      <c r="N257" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="S257" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="T257" t="n">
+        <v>102.62</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>63347.2</t>
+        </is>
+      </c>
+      <c r="V257" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="W257" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-17T03:32</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>260</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>1898.12</v>
+      </c>
+      <c r="H258" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L258" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M258" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N258" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S258" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T258" t="n">
+        <v>98.72</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>1898.12</t>
+        </is>
+      </c>
+      <c r="V258" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="W258" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-17T04:25</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>90</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>63493.1</v>
+      </c>
+      <c r="H259" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L259" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M259" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N259" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="S259" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="T259" t="n">
+        <v>100.53</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>63493.1</t>
+        </is>
+      </c>
+      <c r="V259" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="W259" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-17T04:25</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>270</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>1903.15</v>
+      </c>
+      <c r="H260" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L260" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M260" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N260" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S260" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="T260" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>1903.15</t>
+        </is>
+      </c>
+      <c r="V260" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="W260" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:06</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>90</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>63509.2</v>
+      </c>
+      <c r="H261" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L261" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M261" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N261" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O261" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="S261" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="T261" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>63509.2</t>
+        </is>
+      </c>
+      <c r="V261" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="W261" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:06</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>63509.2</v>
+      </c>
+      <c r="H262" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L262" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M262" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N262" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O262" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P262" t="n">
+        <v>-0.2392</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="S262" t="n">
+        <v>-99.90000000000001</v>
+      </c>
+      <c r="T262" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>63509.2</t>
+        </is>
+      </c>
+      <c r="V262" t="n">
+        <v>-103.92</v>
+      </c>
+      <c r="W262" t="n">
+        <v>-10.392</v>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:06</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>270</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>1902.21</v>
+      </c>
+      <c r="H263" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L263" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M263" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N263" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="P263" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S263" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="T263" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>1902.21</t>
+        </is>
+      </c>
+      <c r="V263" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W263" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:49</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>90</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>63474.7</v>
+      </c>
+      <c r="H264" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K264" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L264" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M264" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N264" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="S264" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="T264" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>63474.7</t>
+        </is>
+      </c>
+      <c r="V264" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="W264" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:49</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>2570</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>63474.7</v>
+      </c>
+      <c r="H265" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K265" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L265" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M265" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N265" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P265" t="n">
+        <v>-0.2486</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="S265" t="n">
+        <v>-99.97</v>
+      </c>
+      <c r="T265" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>63474.7</t>
+        </is>
+      </c>
+      <c r="V265" t="n">
+        <v>-104.09</v>
+      </c>
+      <c r="W265" t="n">
+        <v>-10.409</v>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:49</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>260</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>1899.61</v>
+      </c>
+      <c r="H266" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L266" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M266" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N266" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S266" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T266" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>1899.61</t>
+        </is>
+      </c>
+      <c r="V266" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W266" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-17T06:44</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>90</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>63600.1</v>
+      </c>
+      <c r="H267" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K267" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L267" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M267" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N267" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S267" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T267" t="n">
+        <v>105.72</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>63600.1</t>
+        </is>
+      </c>
+      <c r="V267" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W267" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-17T06:44</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>3790</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>63600.1</v>
+      </c>
+      <c r="H268" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K268" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L268" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M268" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N268" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O268" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>-0.2335</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="S268" t="n">
+        <v>-100.06</v>
+      </c>
+      <c r="T268" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>63600.1</t>
+        </is>
+      </c>
+      <c r="V268" t="n">
+        <v>-104.22</v>
+      </c>
+      <c r="W268" t="n">
+        <v>-10.422</v>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-17T06:44</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>260</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>1903.24</v>
+      </c>
+      <c r="H269" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K269" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M269" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N269" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0.1116</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S269" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="T269" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>1903.24</t>
+        </is>
+      </c>
+      <c r="V269" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="W269" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:39</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>90</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>63558.2</v>
+      </c>
+      <c r="H270" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K270" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L270" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M270" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N270" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O270" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="S270" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T270" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>63558.2</t>
+        </is>
+      </c>
+      <c r="V270" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W270" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>IV rank 73% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:39</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>4210</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>63558.2</v>
+      </c>
+      <c r="H271" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K271" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L271" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M271" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N271" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O271" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>-0.254</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="S271" t="n">
+        <v>-99.78</v>
+      </c>
+      <c r="T271" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>63558.2</t>
+        </is>
+      </c>
+      <c r="V271" t="n">
+        <v>-103.99</v>
+      </c>
+      <c r="W271" t="n">
+        <v>-10.399</v>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:39</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>260</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>1903.39</v>
+      </c>
+      <c r="H272" t="n">
+        <v>24</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K272" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L272" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M272" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N272" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P272" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S272" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="T272" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>1903.39</t>
+        </is>
+      </c>
+      <c r="V272" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W272" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-17T08:23</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>90</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>63411.5</v>
+      </c>
+      <c r="H273" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K273" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L273" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M273" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N273" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O273" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0.4309</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="S273" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T273" t="n">
+        <v>103.06</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>63411.5</t>
+        </is>
+      </c>
+      <c r="V273" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="W273" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>IV rank 60% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-17T08:23</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>8370</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>63411.5</v>
+      </c>
+      <c r="H274" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K274" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L274" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M274" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N274" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>-0.1892</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="S274" t="n">
+        <v>-99.59999999999999</v>
+      </c>
+      <c r="T274" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>63411.5</t>
+        </is>
+      </c>
+      <c r="V274" t="n">
+        <v>-103.79</v>
+      </c>
+      <c r="W274" t="n">
+        <v>-10.379</v>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-17T08:24</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>260</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>1892.64</v>
+      </c>
+      <c r="H275" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K275" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L275" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M275" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N275" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O275" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="P275" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S275" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="T275" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>1892.64</t>
+        </is>
+      </c>
+      <c r="V275" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W275" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>IV rank 60% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:08</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>90</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>63394.5</v>
+      </c>
+      <c r="H276" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K276" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L276" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M276" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N276" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="S276" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T276" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>63394.5</t>
+        </is>
+      </c>
+      <c r="V276" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="W276" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>IV rank 27% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:08</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>18150</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>63394.5</v>
+      </c>
+      <c r="H277" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K277" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L277" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M277" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N277" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O277" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>-0.1357</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="S277" t="n">
+        <v>-99.81999999999999</v>
+      </c>
+      <c r="T277" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>63394.5</t>
+        </is>
+      </c>
+      <c r="V277" t="n">
+        <v>-103.45</v>
+      </c>
+      <c r="W277" t="n">
+        <v>-10.345</v>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:08</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>470</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>63394.5</v>
+      </c>
+      <c r="H278" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K278" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L278" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M278" t="n">
+        <v>63000</v>
+      </c>
+      <c r="N278" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O278" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="P278" t="n">
+        <v>-0.0521</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="R278" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S278" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="T278" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>63394.5</t>
+        </is>
+      </c>
+      <c r="V278" t="n">
+        <v>-66.18000000000001</v>
+      </c>
+      <c r="W278" t="n">
+        <v>-6.618</v>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.8 · 2.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:08</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>260</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>1896.26</v>
+      </c>
+      <c r="H279" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K279" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L279" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M279" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N279" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S279" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T279" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>1896.26</t>
+        </is>
+      </c>
+      <c r="V279" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="W279" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:08</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>720</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>1896.26</v>
+      </c>
+      <c r="H280" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="I280" t="n">
+        <v>1</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K280" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L280" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M280" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N280" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O280" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="P280" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="R280" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="S280" t="n">
+        <v>-28.37</v>
+      </c>
+      <c r="T280" t="n">
+        <v>100.37</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>1896.26</t>
+        </is>
+      </c>
+      <c r="V280" t="n">
+        <v>-90</v>
+      </c>
+      <c r="W280" t="n">
+        <v>-9</v>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.6 · 2.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:56</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>90</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>63321.8</v>
+      </c>
+      <c r="H281" t="n">
+        <v>10</v>
+      </c>
+      <c r="I281" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K281" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L281" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M281" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N281" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0.4589</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S281" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T281" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>63321.8</t>
+        </is>
+      </c>
+      <c r="V281" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W281" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:56</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>5990</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>63321.8</v>
+      </c>
+      <c r="H282" t="n">
+        <v>10</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K282" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L282" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M282" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N282" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O282" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>-0.3885</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S282" t="n">
+        <v>-100.03</v>
+      </c>
+      <c r="T282" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>63321.8</t>
+        </is>
+      </c>
+      <c r="V282" t="n">
+        <v>-104.23</v>
+      </c>
+      <c r="W282" t="n">
+        <v>-10.423</v>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:56</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>360</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>63321.8</v>
+      </c>
+      <c r="H283" t="n">
+        <v>10</v>
+      </c>
+      <c r="I283" t="n">
+        <v>1</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K283" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L283" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M283" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N283" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O283" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="R283" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S283" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="T283" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>63321.8</t>
+        </is>
+      </c>
+      <c r="V283" t="n">
+        <v>-40.46</v>
+      </c>
+      <c r="W283" t="n">
+        <v>-4.046</v>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.2 · 2.1h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:56</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>4980</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>1893.93</v>
+      </c>
+      <c r="H284" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K284" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L284" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M284" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N284" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O284" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P284" t="n">
+        <v>-0.2498</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="S284" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T284" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>1893.93</t>
+        </is>
+      </c>
+      <c r="V284" t="n">
+        <v>-104.08</v>
+      </c>
+      <c r="W284" t="n">
+        <v>-10.408</v>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>IV rank 20% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:56</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>620</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>1893.93</v>
+      </c>
+      <c r="H285" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="I285" t="n">
+        <v>1</v>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K285" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L285" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M285" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N285" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O285" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="P285" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="R285" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S285" t="n">
+        <v>-38.32</v>
+      </c>
+      <c r="T285" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>1893.93</t>
+        </is>
+      </c>
+      <c r="V285" t="n">
+        <v>-73.28</v>
+      </c>
+      <c r="W285" t="n">
+        <v>-7.328</v>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.1 · 2.1h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:29</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>7510</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>63411.1</v>
+      </c>
+      <c r="H286" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K286" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L286" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M286" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N286" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>-0.2774</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="S286" t="n">
+        <v>-99.88</v>
+      </c>
+      <c r="T286" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>63411.1</t>
+        </is>
+      </c>
+      <c r="V286" t="n">
+        <v>-104.39</v>
+      </c>
+      <c r="W286" t="n">
+        <v>-10.439</v>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>IV rank 20% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:29</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>37230</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>63411.1</v>
+      </c>
+      <c r="H287" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K287" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L287" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M287" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N287" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>-0.1241</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="S287" t="n">
+        <v>-100.52</v>
+      </c>
+      <c r="T287" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>63411.1</t>
+        </is>
+      </c>
+      <c r="V287" t="n">
+        <v>-104.24</v>
+      </c>
+      <c r="W287" t="n">
+        <v>-10.424</v>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:29</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>390</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>63411.1</v>
+      </c>
+      <c r="H288" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K288" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L288" t="n">
+        <v>63200</v>
+      </c>
+      <c r="M288" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N288" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P288" t="n">
+        <v>-0.2331</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="R288" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S288" t="n">
+        <v>-21.18</v>
+      </c>
+      <c r="T288" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>63411.1</t>
+        </is>
+      </c>
+      <c r="V288" t="n">
+        <v>-18.02</v>
+      </c>
+      <c r="W288" t="n">
+        <v>-1.802</v>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.4 · 1.5h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:29</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>6990</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>1896.8</v>
+      </c>
+      <c r="H289" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K289" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L289" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M289" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N289" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P289" t="n">
+        <v>-0.3148</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S289" t="n">
+        <v>-99.95999999999999</v>
+      </c>
+      <c r="T289" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>1896.8</t>
+        </is>
+      </c>
+      <c r="V289" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W289" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>IV rank 13% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:29</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>750</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>1896.8</v>
+      </c>
+      <c r="H290" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K290" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L290" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M290" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N290" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O290" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="P290" t="n">
+        <v>-0.0463</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="R290" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S290" t="n">
+        <v>-24.98</v>
+      </c>
+      <c r="T290" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>1896.8</t>
+        </is>
+      </c>
+      <c r="V290" t="n">
+        <v>-94.12</v>
+      </c>
+      <c r="W290" t="n">
+        <v>-9.412000000000001</v>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.8 · 1.5h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:58</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>3460</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>63665.7</v>
+      </c>
+      <c r="H291" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K291" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L291" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M291" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N291" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O291" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P291" t="n">
+        <v>-0.9973</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="S291" t="n">
+        <v>-99.98999999999999</v>
+      </c>
+      <c r="T291" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>63665.7</t>
+        </is>
+      </c>
+      <c r="V291" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W291" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>IV rank 0% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:58</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>311310</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>63665.7</v>
+      </c>
+      <c r="H292" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K292" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L292" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M292" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N292" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>-0.0403</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S292" t="n">
+        <v>-93.39</v>
+      </c>
+      <c r="T292" t="n">
+        <v>93.39</v>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>63665.7</t>
+        </is>
+      </c>
+      <c r="V292" t="n">
+        <v>-93.39</v>
+      </c>
+      <c r="W292" t="n">
+        <v>-9.339</v>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:58</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>480</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>63665.7</v>
+      </c>
+      <c r="H293" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K293" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L293" t="n">
+        <v>63400</v>
+      </c>
+      <c r="M293" t="n">
+        <v>63200</v>
+      </c>
+      <c r="N293" t="n">
+        <v>64800</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P293" t="n">
+        <v>-0.3271</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="R293" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S293" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="T293" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>63665.7</t>
+        </is>
+      </c>
+      <c r="V293" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="W293" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.9 · 1.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:58</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>10900</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>1906.33</v>
+      </c>
+      <c r="H294" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K294" t="n">
+        <v>1</v>
+      </c>
+      <c r="L294" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M294" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N294" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="P294" t="n">
+        <v>-0.2781</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S294" t="n">
+        <v>-100.28</v>
+      </c>
+      <c r="T294" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>1906.33</t>
+        </is>
+      </c>
+      <c r="V294" t="n">
+        <v>-104.64</v>
+      </c>
+      <c r="W294" t="n">
+        <v>-10.464</v>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>IV rank 0% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:58</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>1906.33</v>
+      </c>
+      <c r="H295" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K295" t="n">
+        <v>1</v>
+      </c>
+      <c r="L295" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M295" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N295" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="P295" t="n">
+        <v>-0.1168</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="R295" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="S295" t="n">
+        <v>-100.17</v>
+      </c>
+      <c r="T295" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>1906.33</t>
+        </is>
+      </c>
+      <c r="V295" t="n">
+        <v>-12.01</v>
+      </c>
+      <c r="W295" t="n">
+        <v>-1.201</v>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 6.6 · 1.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:21</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>1</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>4388.56</v>
+      </c>
+      <c r="S296" t="n">
+        <v>0</v>
+      </c>
+      <c r="T296" t="n">
+        <v>10</v>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>4372.63</t>
+        </is>
+      </c>
+      <c r="V296" t="n">
+        <v>-13.25</v>
+      </c>
+      <c r="W296" t="n">
+        <v>-1.325</v>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:35</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>90</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>63714.6</v>
+      </c>
+      <c r="H297" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K297" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L297" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M297" t="n">
+        <v>61800</v>
+      </c>
+      <c r="N297" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O297" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P297" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="S297" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="T297" t="n">
+        <v>98.37</v>
+      </c>
+      <c r="U297" t="inlineStr"/>
+      <c r="X297" t="inlineStr"/>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:35</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>280</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>1905.7</v>
+      </c>
+      <c r="H298" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K298" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L298" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M298" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N298" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O298" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P298" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S298" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="T298" t="n">
+        <v>100.74</v>
+      </c>
+      <c r="U298" t="inlineStr"/>
+      <c r="V298" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W298" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-17T17:43</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>270</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>1908.92</v>
+      </c>
+      <c r="H299" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K299" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L299" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M299" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N299" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O299" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P299" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S299" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="T299" t="n">
+        <v>100.87</v>
+      </c>
+      <c r="U299" t="inlineStr"/>
+      <c r="X299" t="inlineStr"/>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>IV rank 60% — default sell</t>
         </is>
       </c>
     </row>
@@ -23664,22 +27806,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C2" t="n">
-        <v>97</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>4.53</v>
+        <v>5.9</v>
       </c>
       <c r="E2" t="n">
-        <v>301.61</v>
+        <v>419.28</v>
       </c>
       <c r="F2" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="G2" t="n">
-        <v>30.16</v>
+        <v>41.93</v>
       </c>
     </row>
     <row r="3">
@@ -23714,7 +27856,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -23723,13 +27865,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-29.14</v>
+        <v>-58.51</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.57</v>
+        <v>-14.63</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.91</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="5">
@@ -23764,22 +27906,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-1252.62</v>
+        <v>-1650.39</v>
       </c>
       <c r="F6" t="n">
-        <v>-48.18</v>
+        <v>-48.54</v>
       </c>
       <c r="G6" t="n">
-        <v>-125.26</v>
+        <v>-165.04</v>
       </c>
     </row>
     <row r="7">
@@ -23789,22 +27931,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-5356.63</v>
+        <v>-5878.04</v>
       </c>
       <c r="F7" t="n">
-        <v>-99.2</v>
+        <v>-99.63</v>
       </c>
       <c r="G7" t="n">
-        <v>-535.66</v>
+        <v>-587.8</v>
       </c>
     </row>
     <row r="8">
@@ -23814,7 +27956,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -23823,13 +27965,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-6137.82</v>
+        <v>-7063.14</v>
       </c>
       <c r="F8" t="n">
-        <v>-104.03</v>
+        <v>-103.87</v>
       </c>
       <c r="G8" t="n">
-        <v>-613.78</v>
+        <v>-706.3099999999999</v>
       </c>
     </row>
   </sheetData>
@@ -23843,7 +27985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24159,26 +28301,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-15T04:26</t>
+          <t>2026-08-17T13:35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XAUTUSD</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gold_ema</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>perpetual</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -24186,31 +28328,63 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4366.86</v>
+        <v>63714.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>63600</v>
+      </c>
+      <c r="M4" t="n">
+        <v>61800</v>
+      </c>
+      <c r="N4" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.0136</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>98.37</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>20/50 EMA 3rd retest</t>
+          <t>IV rank 93% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16T12:49</t>
+          <t>2026-08-17T17:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -24220,11 +28394,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -24232,13 +28406,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>63007.1</v>
+        <v>1908.92</v>
       </c>
       <c r="H5" t="n">
-        <v>18.6</v>
+        <v>24.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.697</v>
+        <v>0.767</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -24246,115 +28420,37 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L5" t="n">
-        <v>63000</v>
+        <v>1900</v>
       </c>
       <c r="M5" t="n">
-        <v>61600</v>
+        <v>1820</v>
       </c>
       <c r="N5" t="n">
-        <v>64800</v>
+        <v>2000</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1092</v>
+        <v>0.0536</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0128</v>
+        <v>-0.0029</v>
       </c>
       <c r="S5" t="n">
-        <v>7.46</v>
+        <v>7.13</v>
       </c>
       <c r="T5" t="n">
-        <v>100.54</v>
+        <v>100.87</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 86% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-16T12:49</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>370</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1879.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1880</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1840</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="S6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>IV rank 86% rich — sell premium</t>
+          <t>IV rank 60% — default sell</t>
         </is>
       </c>
     </row>
@@ -24375,7 +28471,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-16T20:09:43.583339 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-17T20:14:26.350556 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y299"/>
+  <dimension ref="A1:Y327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -19264,7 +19264,17 @@
         <v>100.57</v>
       </c>
       <c r="U206" t="inlineStr"/>
-      <c r="X206" t="inlineStr"/>
+      <c r="V206" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="Y206" t="inlineStr">
         <is>
           <t>IV rank 92% rich — sell premium</t>
@@ -27521,7 +27531,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -27565,8 +27575,22 @@
       <c r="T297" t="n">
         <v>98.37</v>
       </c>
-      <c r="U297" t="inlineStr"/>
-      <c r="X297" t="inlineStr"/>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>64381.7</t>
+        </is>
+      </c>
+      <c r="V297" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="W297" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="Y297" t="inlineStr">
         <is>
           <t>IV rank 93% rich — sell premium</t>
@@ -27687,7 +27711,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -27732,10 +27756,2536 @@
         <v>100.87</v>
       </c>
       <c r="U299" t="inlineStr"/>
-      <c r="X299" t="inlineStr"/>
+      <c r="V299" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="W299" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="Y299" t="inlineStr">
         <is>
           <t>IV rank 60% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-17T21:49</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>270</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>1906.19</v>
+      </c>
+      <c r="H300" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K300" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L300" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M300" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N300" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O300" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="P300" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S300" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="T300" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>1909.46</t>
+        </is>
+      </c>
+      <c r="V300" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="W300" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>IV rank 40% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-18T00:57</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>60</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>64381.7</v>
+      </c>
+      <c r="H301" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K301" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L301" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M301" t="n">
+        <v>58000</v>
+      </c>
+      <c r="N301" t="n">
+        <v>75000</v>
+      </c>
+      <c r="O301" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P301" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>-0.0316</v>
+      </c>
+      <c r="S301" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="T301" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="U301" t="inlineStr"/>
+      <c r="X301" t="inlineStr"/>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-18T00:57</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>240</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>1909.46</v>
+      </c>
+      <c r="H302" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K302" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L302" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M302" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N302" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="S302" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="T302" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="U302" t="inlineStr"/>
+      <c r="X302" t="inlineStr"/>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-18T02:16</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>90</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>64170.1</v>
+      </c>
+      <c r="H303" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K303" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L303" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M303" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N303" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
+      <c r="P303" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="S303" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T303" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>64170.1</t>
+        </is>
+      </c>
+      <c r="V303" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="W303" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-18T02:16</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>260</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>1899.1</v>
+      </c>
+      <c r="H304" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K304" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L304" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M304" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N304" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P304" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S304" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T304" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>1899.1</t>
+        </is>
+      </c>
+      <c r="V304" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W304" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-18T03:21</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>90</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>64107.2</v>
+      </c>
+      <c r="H305" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K305" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L305" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M305" t="n">
+        <v>63400</v>
+      </c>
+      <c r="N305" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O305" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P305" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="S305" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="T305" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>64107.2</t>
+        </is>
+      </c>
+      <c r="V305" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="W305" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-18T03:21</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>260</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>1890.34</v>
+      </c>
+      <c r="H306" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="K306" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L306" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M306" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N306" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O306" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P306" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S306" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T306" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>1890.34</t>
+        </is>
+      </c>
+      <c r="V306" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="W306" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-18T04:06</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>90</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>64123.7</v>
+      </c>
+      <c r="H307" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K307" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L307" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M307" t="n">
+        <v>63400</v>
+      </c>
+      <c r="N307" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P307" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="S307" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="T307" t="n">
+        <v>104.03</v>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>64123.7</t>
+        </is>
+      </c>
+      <c r="V307" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="W307" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-18T04:06</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>260</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>1893.81</v>
+      </c>
+      <c r="H308" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K308" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L308" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M308" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N308" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P308" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S308" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="T308" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>1893.81</t>
+        </is>
+      </c>
+      <c r="V308" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="W308" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-18T04:50</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>90</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>64196.2</v>
+      </c>
+      <c r="H309" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K309" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L309" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M309" t="n">
+        <v>63400</v>
+      </c>
+      <c r="N309" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" t="n">
+        <v>0.2245</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="S309" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T309" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>64196.2</t>
+        </is>
+      </c>
+      <c r="V309" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W309" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-18T04:50</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>260</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>1895.98</v>
+      </c>
+      <c r="H310" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K310" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L310" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M310" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N310" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O310" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P310" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S310" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="T310" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>1895.98</t>
+        </is>
+      </c>
+      <c r="V310" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W310" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-18T05:23</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>90</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>64213.5</v>
+      </c>
+      <c r="H311" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I311" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K311" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L311" t="n">
+        <v>64000</v>
+      </c>
+      <c r="M311" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N311" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O311" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P311" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="S311" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="T311" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>64213.5</t>
+        </is>
+      </c>
+      <c r="V311" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="W311" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-18T05:23</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>260</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>1896.15</v>
+      </c>
+      <c r="H312" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I312" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K312" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L312" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M312" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N312" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O312" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P312" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S312" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T312" t="n">
+        <v>100.41</v>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>1896.15</t>
+        </is>
+      </c>
+      <c r="V312" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="W312" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-18T05:53</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>90</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>64219.4</v>
+      </c>
+      <c r="H313" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K313" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L313" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M313" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N313" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O313" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P313" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="S313" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T313" t="n">
+        <v>105.58</v>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>64219.4</t>
+        </is>
+      </c>
+      <c r="V313" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="W313" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-18T05:53</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>260</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>1896.1</v>
+      </c>
+      <c r="H314" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I314" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K314" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L314" t="n">
+        <v>1890</v>
+      </c>
+      <c r="M314" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N314" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O314" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P314" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S314" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T314" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>1896.1</t>
+        </is>
+      </c>
+      <c r="V314" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W314" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>IV rank 69% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-18T06:34</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>90</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>64382.5</v>
+      </c>
+      <c r="H315" t="n">
+        <v>17</v>
+      </c>
+      <c r="I315" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K315" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L315" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M315" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N315" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O315" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P315" t="n">
+        <v>0.2364</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="S315" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="T315" t="n">
+        <v>103.27</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>64382.5</t>
+        </is>
+      </c>
+      <c r="V315" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="W315" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-18T06:34</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>270</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>1901.38</v>
+      </c>
+      <c r="H316" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="I316" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K316" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L316" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M316" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N316" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O316" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="P316" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S316" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="T316" t="n">
+        <v>101.84</v>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>1901.38</t>
+        </is>
+      </c>
+      <c r="V316" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="W316" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>IV rank 69% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-18T07:24</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>90</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>64311.5</v>
+      </c>
+      <c r="H317" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K317" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L317" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M317" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N317" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O317" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P317" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="S317" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="T317" t="n">
+        <v>104.63</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>64311.5</t>
+        </is>
+      </c>
+      <c r="V317" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="W317" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>IV rank 69% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-18T07:24</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>260</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>1901.08</v>
+      </c>
+      <c r="H318" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K318" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L318" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M318" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N318" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O318" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P318" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S318" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T318" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>1901.08</t>
+        </is>
+      </c>
+      <c r="V318" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="W318" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>IV rank 62% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-18T08:02</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>90</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>64211.9</v>
+      </c>
+      <c r="H319" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K319" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L319" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M319" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N319" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O319" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P319" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="S319" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="T319" t="n">
+        <v>102.23</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>64211.9</t>
+        </is>
+      </c>
+      <c r="V319" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="W319" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>IV rank 62% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-18T08:02</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>260</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>1898.91</v>
+      </c>
+      <c r="H320" t="n">
+        <v>19</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K320" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L320" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M320" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N320" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P320" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S320" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T320" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>1898.91</t>
+        </is>
+      </c>
+      <c r="V320" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="W320" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-18T08:52</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>80</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>64281.8</v>
+      </c>
+      <c r="H321" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K321" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L321" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M321" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N321" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O321" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P321" t="n">
+        <v>0.1967</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S321" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T321" t="n">
+        <v>94.48</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>64281.8</t>
+        </is>
+      </c>
+      <c r="V321" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W321" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-18T08:52</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>260</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>1899.93</v>
+      </c>
+      <c r="H322" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="I322" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K322" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L322" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M322" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N322" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O322" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P322" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="S322" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T322" t="n">
+        <v>101.87</v>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>1899.93</t>
+        </is>
+      </c>
+      <c r="V322" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="W322" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-18T09:58</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>80</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>64181.8</v>
+      </c>
+      <c r="H323" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K323" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L323" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M323" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N323" t="n">
+        <v>65200</v>
+      </c>
+      <c r="O323" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P323" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S323" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T323" t="n">
+        <v>94.37</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>64181.8</t>
+        </is>
+      </c>
+      <c r="V323" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W323" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-18T11:01</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>250</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>1899.13</v>
+      </c>
+      <c r="H324" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I324" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K324" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L324" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M324" t="n">
+        <v>1880</v>
+      </c>
+      <c r="N324" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P324" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="S324" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T324" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>1899.13</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W324" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-18T12:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>80</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>64341.4</v>
+      </c>
+      <c r="H325" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K325" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L325" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M325" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N325" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P325" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="S325" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="T325" t="n">
+        <v>104.56</v>
+      </c>
+      <c r="U325" t="inlineStr"/>
+      <c r="X325" t="inlineStr"/>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-18T12:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>290</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>1902.93</v>
+      </c>
+      <c r="H326" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K326" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L326" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M326" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N326" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O326" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="P326" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S326" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="T326" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="U326" t="inlineStr"/>
+      <c r="V326" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W326" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-18T19:48</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>270</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>1915.07</v>
+      </c>
+      <c r="H327" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I327" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K327" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L327" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M327" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N327" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O327" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P327" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="S327" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="T327" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U327" t="inlineStr"/>
+      <c r="X327" t="inlineStr"/>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>IV rank 62% — default sell</t>
         </is>
       </c>
     </row>
@@ -27806,22 +30356,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>97.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9</v>
+        <v>6.43</v>
       </c>
       <c r="E2" t="n">
-        <v>419.28</v>
+        <v>512.0599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="G2" t="n">
-        <v>41.93</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="3">
@@ -27831,22 +30381,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D3" t="n">
-        <v>6.28</v>
+        <v>10.26</v>
       </c>
       <c r="E3" t="n">
-        <v>19.95</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>4.99</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
@@ -27985,7 +30535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28223,12 +30773,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14T09:44</t>
+          <t>2026-08-18T00:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -28238,11 +30788,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -28250,77 +30800,77 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1872.35</v>
+        <v>64381.7</v>
       </c>
       <c r="H3" t="n">
-        <v>33.1</v>
+        <v>25.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.605</v>
+        <v>0.522</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1900</v>
+        <v>64000</v>
       </c>
       <c r="M3" t="n">
-        <v>1850</v>
+        <v>58000</v>
       </c>
       <c r="N3" t="n">
-        <v>2200</v>
+        <v>75000</v>
       </c>
       <c r="O3" t="n">
         <v>-0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0127</v>
+        <v>0.0357</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0059</v>
+        <v>-0.0316</v>
       </c>
       <c r="S3" t="n">
-        <v>29.43</v>
+        <v>14.73</v>
       </c>
       <c r="T3" t="n">
-        <v>100.57</v>
+        <v>94.11</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>IV rank 92% rich — sell premium</t>
+          <t>IV rank 100% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:35</t>
+          <t>2026-08-18T00:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -28328,63 +30878,63 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>63714.6</v>
+        <v>1909.46</v>
       </c>
       <c r="H4" t="n">
-        <v>20.7</v>
+        <v>34.15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.594</v>
+        <v>0.711</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>63600</v>
+        <v>1900</v>
       </c>
       <c r="M4" t="n">
-        <v>61800</v>
+        <v>1700</v>
       </c>
       <c r="N4" t="n">
-        <v>65200</v>
+        <v>2200</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1475</v>
+        <v>0.0074</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0136</v>
+        <v>-0.0049</v>
       </c>
       <c r="S4" t="n">
-        <v>9.630000000000001</v>
+        <v>19.56</v>
       </c>
       <c r="T4" t="n">
-        <v>98.37</v>
+        <v>100.44</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 93% rich — sell premium</t>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17T17:43</t>
+          <t>2026-08-18T12:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -28394,11 +30944,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -28406,51 +30956,129 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1908.92</v>
+        <v>64341.4</v>
       </c>
       <c r="H5" t="n">
-        <v>24.2</v>
+        <v>19.95</v>
       </c>
       <c r="I5" t="n">
-        <v>0.767</v>
+        <v>0.654</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.75</v>
+        <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>1900</v>
+        <v>64200</v>
       </c>
       <c r="M5" t="n">
-        <v>1820</v>
+        <v>62600</v>
       </c>
       <c r="N5" t="n">
-        <v>2000</v>
+        <v>65600</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0.0001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0536</v>
+        <v>0.1129</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0114</v>
       </c>
       <c r="S5" t="n">
-        <v>7.13</v>
+        <v>8.08</v>
       </c>
       <c r="T5" t="n">
-        <v>100.87</v>
+        <v>104.56</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 60% — default sell</t>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-18T19:48</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>270</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1915.07</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="T6" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>IV rank 62% — default sell</t>
         </is>
       </c>
     </row>
@@ -28471,7 +31099,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-17T20:14:26.350556 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-18T20:11:19.624594 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y327"/>
+  <dimension ref="A1:Y375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27969,7 +27969,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -28014,7 +28014,17 @@
         <v>100.44</v>
       </c>
       <c r="U302" t="inlineStr"/>
-      <c r="X302" t="inlineStr"/>
+      <c r="V302" t="n">
+        <v>-57.67</v>
+      </c>
+      <c r="W302" t="n">
+        <v>-5.767</v>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="Y302" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
@@ -30071,7 +30081,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -30115,8 +30125,22 @@
       <c r="T325" t="n">
         <v>104.56</v>
       </c>
-      <c r="U325" t="inlineStr"/>
-      <c r="X325" t="inlineStr"/>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>64519.9</t>
+        </is>
+      </c>
+      <c r="V325" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="W325" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="Y325" t="inlineStr">
         <is>
           <t>IV rank 88% rich — sell premium</t>
@@ -30237,7 +30261,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -30282,10 +30306,4328 @@
         <v>100.28</v>
       </c>
       <c r="U327" t="inlineStr"/>
-      <c r="X327" t="inlineStr"/>
+      <c r="V327" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="W327" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="Y327" t="inlineStr">
         <is>
           <t>IV rank 62% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-18T22:18</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>1210</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>64575.5</v>
+      </c>
+      <c r="H328" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I328" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K328" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L328" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M328" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N328" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O328" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P328" t="n">
+        <v>-0.1946</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="S328" t="n">
+        <v>-99.58</v>
+      </c>
+      <c r="T328" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>64519.9</t>
+        </is>
+      </c>
+      <c r="V328" t="n">
+        <v>-103.7</v>
+      </c>
+      <c r="W328" t="n">
+        <v>-10.37</v>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:58</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>270</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>1914.06</v>
+      </c>
+      <c r="H329" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="I329" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K329" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L329" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M329" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N329" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O329" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P329" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S329" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="T329" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>1914.06</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="W329" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:19</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>90</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G330" t="n">
+        <v>64361.8</v>
+      </c>
+      <c r="H330" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="I330" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K330" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L330" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M330" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N330" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O330" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P330" t="n">
+        <v>0.1805</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="S330" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="T330" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>64361.8</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="W330" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:19</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>64361.8</v>
+      </c>
+      <c r="H331" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="I331" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K331" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L331" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M331" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N331" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O331" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P331" t="n">
+        <v>-0.2439</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="S331" t="n">
+        <v>-99.76000000000001</v>
+      </c>
+      <c r="T331" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>64361.8</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>-103.82</v>
+      </c>
+      <c r="W331" t="n">
+        <v>-10.382</v>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:19</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>260</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>1909.52</v>
+      </c>
+      <c r="H332" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I332" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K332" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L332" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M332" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N332" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
+      <c r="P332" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S332" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="T332" t="n">
+        <v>100.13</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>1909.52</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="W332" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:24</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>90</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>64375.6</v>
+      </c>
+      <c r="H333" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="I333" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K333" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L333" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M333" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N333" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O333" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P333" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="S333" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T333" t="n">
+        <v>103.03</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>64375.6</t>
+        </is>
+      </c>
+      <c r="V333" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W333" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:24</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>64375.6</v>
+      </c>
+      <c r="H334" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="I334" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K334" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L334" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M334" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N334" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O334" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P334" t="n">
+        <v>-0.2409</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="S334" t="n">
+        <v>-100.21</v>
+      </c>
+      <c r="T334" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>64375.6</t>
+        </is>
+      </c>
+      <c r="V334" t="n">
+        <v>-104.31</v>
+      </c>
+      <c r="W334" t="n">
+        <v>-10.431</v>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:24</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>260</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>1913.35</v>
+      </c>
+      <c r="H335" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="I335" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K335" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L335" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M335" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N335" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P335" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S335" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="T335" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>1913.35</t>
+        </is>
+      </c>
+      <c r="V335" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="W335" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:06</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>90</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>64303</v>
+      </c>
+      <c r="H336" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I336" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K336" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L336" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M336" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N336" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O336" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P336" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="S336" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="T336" t="n">
+        <v>102.12</v>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>64303.0</t>
+        </is>
+      </c>
+      <c r="V336" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="W336" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:06</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>2080</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G337" t="n">
+        <v>64303</v>
+      </c>
+      <c r="H337" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I337" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K337" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L337" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M337" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N337" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O337" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P337" t="n">
+        <v>-0.2268</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="S337" t="n">
+        <v>-100.26</v>
+      </c>
+      <c r="T337" t="n">
+        <v>100.26</v>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>64303.0</t>
+        </is>
+      </c>
+      <c r="V337" t="n">
+        <v>-104.42</v>
+      </c>
+      <c r="W337" t="n">
+        <v>-10.442</v>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:06</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>260</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>1910.9</v>
+      </c>
+      <c r="H338" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="I338" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K338" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L338" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M338" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N338" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O338" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="P338" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S338" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T338" t="n">
+        <v>98.98</v>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>1910.9</t>
+        </is>
+      </c>
+      <c r="V338" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="W338" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:50</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>90</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>64349.7</v>
+      </c>
+      <c r="H339" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I339" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K339" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L339" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M339" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N339" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O339" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P339" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="S339" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T339" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>64349.7</t>
+        </is>
+      </c>
+      <c r="V339" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="W339" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:50</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>2360</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>64349.7</v>
+      </c>
+      <c r="H340" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I340" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K340" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L340" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M340" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N340" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O340" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P340" t="n">
+        <v>-0.2353</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="S340" t="n">
+        <v>-100.06</v>
+      </c>
+      <c r="T340" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>64349.7</t>
+        </is>
+      </c>
+      <c r="V340" t="n">
+        <v>-104.08</v>
+      </c>
+      <c r="W340" t="n">
+        <v>-10.408</v>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:50</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>260</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>1911.36</v>
+      </c>
+      <c r="H341" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K341" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L341" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M341" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N341" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O341" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P341" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S341" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="T341" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>1911.36</t>
+        </is>
+      </c>
+      <c r="V341" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="W341" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>IV rank 82% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-19T06:36</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>90</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>64273.9</v>
+      </c>
+      <c r="H342" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="I342" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K342" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L342" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M342" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N342" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O342" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P342" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="S342" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="T342" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>64273.9</t>
+        </is>
+      </c>
+      <c r="V342" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="W342" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>IV rank 76% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-19T06:36</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>260</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>1910.83</v>
+      </c>
+      <c r="H343" t="n">
+        <v>22</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K343" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L343" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M343" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N343" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O343" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P343" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S343" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="T343" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>1910.83</t>
+        </is>
+      </c>
+      <c r="V343" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W343" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>IV rank 71% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-19T07:24</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>90</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>64339.9</v>
+      </c>
+      <c r="H344" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I344" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K344" t="n">
+        <v>1</v>
+      </c>
+      <c r="L344" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M344" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N344" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O344" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P344" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="S344" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T344" t="n">
+        <v>105.18</v>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>64339.9</t>
+        </is>
+      </c>
+      <c r="V344" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W344" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>IV rank 65% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-19T07:24</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>260</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>1918.86</v>
+      </c>
+      <c r="H345" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I345" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K345" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L345" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M345" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N345" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O345" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P345" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S345" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="T345" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>1918.86</t>
+        </is>
+      </c>
+      <c r="V345" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="W345" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>IV rank 59% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-19T08:02</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>90</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>64293</v>
+      </c>
+      <c r="H346" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="I346" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K346" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L346" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M346" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N346" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O346" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P346" t="n">
+        <v>0.2121</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="S346" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T346" t="n">
+        <v>104.56</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>64293.0</t>
+        </is>
+      </c>
+      <c r="V346" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W346" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>IV rank 59% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-19T08:02</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>270</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>1915.89</v>
+      </c>
+      <c r="H347" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="I347" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K347" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L347" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M347" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N347" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="P347" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S347" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="T347" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>1915.89</t>
+        </is>
+      </c>
+      <c r="V347" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="W347" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>IV rank 53% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-19T08:53</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>90</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>64459.5</v>
+      </c>
+      <c r="H348" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I348" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K348" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L348" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M348" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N348" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O348" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P348" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S348" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T348" t="n">
+        <v>105.57</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>64459.5</t>
+        </is>
+      </c>
+      <c r="V348" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W348" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>IV rank 53% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:28</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>90</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>64385.5</v>
+      </c>
+      <c r="H349" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I349" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K349" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L349" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M349" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N349" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0</v>
+      </c>
+      <c r="P349" t="n">
+        <v>0.5738</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S349" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="T349" t="n">
+        <v>103.86</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>64385.5</t>
+        </is>
+      </c>
+      <c r="V349" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="W349" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>IV rank 53% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:59</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>90</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>64427.5</v>
+      </c>
+      <c r="H350" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="I350" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K350" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L350" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M350" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N350" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O350" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P350" t="n">
+        <v>0.5745</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="S350" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T350" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>64427.5</t>
+        </is>
+      </c>
+      <c r="V350" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="W350" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>IV rank 35% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:36</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>4550</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>64403.3</v>
+      </c>
+      <c r="H351" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I351" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K351" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L351" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M351" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N351" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O351" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P351" t="n">
+        <v>-0.6208</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="S351" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T351" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>64403.3</t>
+        </is>
+      </c>
+      <c r="V351" t="n">
+        <v>-104.2</v>
+      </c>
+      <c r="W351" t="n">
+        <v>-10.419</v>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>IV rank 18% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:36</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>30860</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>64403.3</v>
+      </c>
+      <c r="H352" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I352" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K352" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L352" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M352" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N352" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O352" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P352" t="n">
+        <v>-0.1716</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="S352" t="n">
+        <v>-98.75</v>
+      </c>
+      <c r="T352" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>64403.3</t>
+        </is>
+      </c>
+      <c r="V352" t="n">
+        <v>-104.92</v>
+      </c>
+      <c r="W352" t="n">
+        <v>-10.492</v>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:36</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>390</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>64403.3</v>
+      </c>
+      <c r="H353" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I353" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K353" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L353" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M353" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N353" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P353" t="n">
+        <v>-0.4095</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="R353" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S353" t="n">
+        <v>-22.46</v>
+      </c>
+      <c r="T353" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>64403.3</t>
+        </is>
+      </c>
+      <c r="V353" t="n">
+        <v>-22.19</v>
+      </c>
+      <c r="W353" t="n">
+        <v>-2.219</v>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.3 · 1.4h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:36</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>260</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>1918.34</v>
+      </c>
+      <c r="H354" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K354" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L354" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M354" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N354" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="P354" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="S354" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="T354" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>1918.34</t>
+        </is>
+      </c>
+      <c r="V354" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W354" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>IV rank 47% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:36</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>810</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>1918.34</v>
+      </c>
+      <c r="H355" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="I355" t="n">
+        <v>1</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K355" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L355" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M355" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N355" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O355" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="P355" t="n">
+        <v>-0.2156</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="R355" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S355" t="n">
+        <v>-18.63</v>
+      </c>
+      <c r="T355" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>1918.34</t>
+        </is>
+      </c>
+      <c r="V355" t="n">
+        <v>-109.11</v>
+      </c>
+      <c r="W355" t="n">
+        <v>-10.911</v>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 3.1 · 1.4h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:01</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>5050</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>64456.2</v>
+      </c>
+      <c r="H356" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I356" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K356" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L356" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M356" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N356" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O356" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P356" t="n">
+        <v>-0.5780999999999999</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="S356" t="n">
+        <v>-99.98999999999999</v>
+      </c>
+      <c r="T356" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>64456.2</t>
+        </is>
+      </c>
+      <c r="V356" t="n">
+        <v>-104.03</v>
+      </c>
+      <c r="W356" t="n">
+        <v>-10.403</v>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>IV rank 6% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:01</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>138220</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>64456.2</v>
+      </c>
+      <c r="H357" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I357" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K357" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L357" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M357" t="n">
+        <v>64200</v>
+      </c>
+      <c r="N357" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O357" t="n">
+        <v>0</v>
+      </c>
+      <c r="P357" t="n">
+        <v>-0.07679999999999999</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="S357" t="n">
+        <v>-96.75</v>
+      </c>
+      <c r="T357" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>64456.2</t>
+        </is>
+      </c>
+      <c r="V357" t="n">
+        <v>-110.58</v>
+      </c>
+      <c r="W357" t="n">
+        <v>-11.058</v>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:01</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>1920.12</v>
+      </c>
+      <c r="H358" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I358" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K358" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L358" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M358" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N358" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O358" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="P358" t="n">
+        <v>-0.2041</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="S358" t="n">
+        <v>-99.95999999999999</v>
+      </c>
+      <c r="T358" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>1920.12</t>
+        </is>
+      </c>
+      <c r="V358" t="n">
+        <v>-104.04</v>
+      </c>
+      <c r="W358" t="n">
+        <v>-10.404</v>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>IV rank 6% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:38</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>63770</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>64517.7</v>
+      </c>
+      <c r="H359" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I359" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K359" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L359" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M359" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N359" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
+      <c r="P359" t="n">
+        <v>-0.2888</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="S359" t="n">
+        <v>-102.03</v>
+      </c>
+      <c r="T359" t="n">
+        <v>102.03</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>64517.7</t>
+        </is>
+      </c>
+      <c r="V359" t="n">
+        <v>-102.03</v>
+      </c>
+      <c r="W359" t="n">
+        <v>-10.203</v>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>IV rank 6% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:38</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>171700</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>64517.7</v>
+      </c>
+      <c r="H360" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I360" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K360" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L360" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M360" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N360" t="n">
+        <v>65000</v>
+      </c>
+      <c r="O360" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P360" t="n">
+        <v>-0.1445</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S360" t="n">
+        <v>-103.02</v>
+      </c>
+      <c r="T360" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>64517.7</t>
+        </is>
+      </c>
+      <c r="V360" t="n">
+        <v>-103.02</v>
+      </c>
+      <c r="W360" t="n">
+        <v>-10.302</v>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:38</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>79070</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>1924.08</v>
+      </c>
+      <c r="H361" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I361" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K361" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L361" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M361" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N361" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
+      <c r="P361" t="n">
+        <v>-0.1843</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S361" t="n">
+        <v>-102.79</v>
+      </c>
+      <c r="T361" t="n">
+        <v>102.79</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>1924.08</t>
+        </is>
+      </c>
+      <c r="V361" t="n">
+        <v>-102.79</v>
+      </c>
+      <c r="W361" t="n">
+        <v>-10.279</v>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>IV rank 12% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:59</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>64515.5</v>
+      </c>
+      <c r="H362" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="I362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K362" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L362" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M362" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N362" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0</v>
+      </c>
+      <c r="P362" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>0</v>
+      </c>
+      <c r="S362" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T362" t="n">
+        <v>100</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>64515.5</t>
+        </is>
+      </c>
+      <c r="V362" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W362" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>IV rank 0% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:59</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>64515.5</v>
+      </c>
+      <c r="H363" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K363" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L363" t="n">
+        <v>64400</v>
+      </c>
+      <c r="M363" t="n">
+        <v>64400</v>
+      </c>
+      <c r="N363" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O363" t="n">
+        <v>0</v>
+      </c>
+      <c r="P363" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>0</v>
+      </c>
+      <c r="S363" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T363" t="n">
+        <v>100</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>64515.5</t>
+        </is>
+      </c>
+      <c r="V363" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W363" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:59</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>1923.06</v>
+      </c>
+      <c r="H364" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K364" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L364" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M364" t="n">
+        <v>1920</v>
+      </c>
+      <c r="N364" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
+      <c r="P364" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T364" t="n">
+        <v>100</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>1923.06</t>
+        </is>
+      </c>
+      <c r="V364" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W364" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>IV rank 6% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-19T13:01</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>110</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>64799.1</v>
+      </c>
+      <c r="H365" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I365" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K365" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L365" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M365" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N365" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O365" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="S365" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="T365" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="U365" t="inlineStr"/>
+      <c r="X365" t="inlineStr"/>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-19T13:01</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>290</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>1934.82</v>
+      </c>
+      <c r="H366" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="I366" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K366" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L366" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M366" t="n">
+        <v>1920</v>
+      </c>
+      <c r="N366" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O366" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P366" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S366" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="T366" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="U366" t="inlineStr"/>
+      <c r="V366" t="n">
+        <v>-58.17</v>
+      </c>
+      <c r="W366" t="n">
+        <v>-5.817</v>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:06</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>150</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>66456.7</v>
+      </c>
+      <c r="H367" t="n">
+        <v>26</v>
+      </c>
+      <c r="I367" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K367" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L367" t="n">
+        <v>65600</v>
+      </c>
+      <c r="M367" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N367" t="n">
+        <v>66600</v>
+      </c>
+      <c r="O367" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P367" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S367" t="n">
+        <v>-100.72</v>
+      </c>
+      <c r="T367" t="n">
+        <v>100.72</v>
+      </c>
+      <c r="U367" t="inlineStr"/>
+      <c r="X367" t="inlineStr"/>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>trending up +5.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:06</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>190</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>66456.7</v>
+      </c>
+      <c r="H368" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="I368" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K368" t="n">
+        <v>1</v>
+      </c>
+      <c r="L368" t="n">
+        <v>64500</v>
+      </c>
+      <c r="M368" t="n">
+        <v>58000</v>
+      </c>
+      <c r="N368" t="n">
+        <v>75000</v>
+      </c>
+      <c r="O368" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P368" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="S368" t="n">
+        <v>-97.55</v>
+      </c>
+      <c r="T368" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="U368" t="inlineStr"/>
+      <c r="X368" t="inlineStr"/>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>trending up +5.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:06</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>320</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>2005.71</v>
+      </c>
+      <c r="H369" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="I369" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K369" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L369" t="n">
+        <v>1940</v>
+      </c>
+      <c r="M369" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N369" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O369" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="P369" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S369" t="n">
+        <v>-101.57</v>
+      </c>
+      <c r="T369" t="n">
+        <v>101.57</v>
+      </c>
+      <c r="U369" t="inlineStr"/>
+      <c r="V369" t="n">
+        <v>-74.69</v>
+      </c>
+      <c r="W369" t="n">
+        <v>-7.469</v>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>trending up +6.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:06</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>2005.71</v>
+      </c>
+      <c r="H370" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="I370" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K370" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L370" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M370" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N370" t="n">
+        <v>2300</v>
+      </c>
+      <c r="O370" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P370" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S370" t="n">
+        <v>-99.64</v>
+      </c>
+      <c r="T370" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="U370" t="inlineStr"/>
+      <c r="V370" t="n">
+        <v>-77.95</v>
+      </c>
+      <c r="W370" t="n">
+        <v>-7.795</v>
+      </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>trending up +6.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:45</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>280</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>2087.16</v>
+      </c>
+      <c r="H371" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="I371" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K371" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L371" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M371" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N371" t="n">
+        <v>2160</v>
+      </c>
+      <c r="O371" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="P371" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="S371" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="T371" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="U371" t="inlineStr"/>
+      <c r="V371" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="W371" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:11</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>480</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>2090.18</v>
+      </c>
+      <c r="H372" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="I372" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K372" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="L372" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M372" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N372" t="n">
+        <v>2160</v>
+      </c>
+      <c r="O372" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="P372" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="S372" t="n">
+        <v>-100.56</v>
+      </c>
+      <c r="T372" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="U372" t="inlineStr"/>
+      <c r="X372" t="inlineStr"/>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>trending up +11.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:11</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>230</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>2090.18</v>
+      </c>
+      <c r="H373" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="I373" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K373" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L373" t="n">
+        <v>1950</v>
+      </c>
+      <c r="M373" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N373" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P373" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S373" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="T373" t="n">
+        <v>100.42</v>
+      </c>
+      <c r="U373" t="inlineStr"/>
+      <c r="X373" t="inlineStr"/>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-19T19:03</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>190</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>2093.54</v>
+      </c>
+      <c r="H374" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I374" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K374" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L374" t="n">
+        <v>2080</v>
+      </c>
+      <c r="M374" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N374" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O374" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P374" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S374" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="T374" t="n">
+        <v>102.11</v>
+      </c>
+      <c r="U374" t="inlineStr"/>
+      <c r="X374" t="inlineStr"/>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-19T19:03</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>2093.54</v>
+      </c>
+      <c r="H375" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="I375" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K375" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L375" t="n">
+        <v>1950</v>
+      </c>
+      <c r="M375" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N375" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O375" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P375" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="S375" t="n">
+        <v>-100.2</v>
+      </c>
+      <c r="T375" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U375" t="inlineStr"/>
+      <c r="X375" t="inlineStr"/>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>trending up +11.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -30300,7 +34642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30356,22 +34698,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C2" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>6.43</v>
+        <v>4.65</v>
       </c>
       <c r="E2" t="n">
-        <v>512.0599999999999</v>
+        <v>556.73</v>
       </c>
       <c r="F2" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="G2" t="n">
-        <v>51.21</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="3">
@@ -30381,22 +34723,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="D3" t="n">
-        <v>10.26</v>
+        <v>0.63</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>-22.67</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>-3.78</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="4">
@@ -30427,11 +34769,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>long_strangle_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -30440,88 +34782,138 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-107.3</v>
+        <v>-74.69</v>
       </c>
       <c r="F5" t="n">
-        <v>-53.65</v>
+        <v>-74.69</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.73</v>
+        <v>-7.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-1650.39</v>
+        <v>-77.95</v>
       </c>
       <c r="F6" t="n">
-        <v>-48.54</v>
+        <v>-77.95</v>
       </c>
       <c r="G6" t="n">
-        <v>-165.04</v>
+        <v>-7.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>long_strangle</t>
+          <t>long_strangle_wk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-5878.04</v>
+        <v>-107.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-99.63</v>
+        <v>-53.65</v>
       </c>
       <c r="G7" t="n">
-        <v>-587.8</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cheap_strangle</t>
+          <t>butterfly</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-7063.14</v>
+        <v>-1781.69</v>
       </c>
       <c r="F8" t="n">
-        <v>-103.87</v>
+        <v>-49.49</v>
       </c>
       <c r="G8" t="n">
-        <v>-706.3099999999999</v>
+        <v>-178.17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-6595.13</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-99.93000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-659.51</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>77</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-8001.99</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-103.92</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-800.2</v>
       </c>
     </row>
   </sheetData>
@@ -30535,7 +34927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30851,26 +35243,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18T00:57</t>
+          <t>2026-08-19T13:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -30878,45 +35270,45 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1909.46</v>
+        <v>64799.1</v>
       </c>
       <c r="H4" t="n">
-        <v>34.15</v>
+        <v>23.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.711</v>
+        <v>0.573</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1900</v>
+        <v>64600</v>
       </c>
       <c r="M4" t="n">
-        <v>1700</v>
+        <v>62600</v>
       </c>
       <c r="N4" t="n">
-        <v>2200</v>
+        <v>66000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0074</v>
+        <v>0.1344</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0049</v>
+        <v>-0.0117</v>
       </c>
       <c r="S4" t="n">
-        <v>19.56</v>
+        <v>11.62</v>
       </c>
       <c r="T4" t="n">
-        <v>100.44</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -30929,7 +35321,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18T12:00</t>
+          <t>2026-08-19T15:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -30939,16 +35331,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -30956,77 +35348,77 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>64341.4</v>
+        <v>66456.7</v>
       </c>
       <c r="H5" t="n">
-        <v>19.95</v>
+        <v>26</v>
       </c>
       <c r="I5" t="n">
-        <v>0.654</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="L5" t="n">
-        <v>64200</v>
+        <v>65600</v>
       </c>
       <c r="M5" t="n">
-        <v>62600</v>
+        <v>65000</v>
       </c>
       <c r="N5" t="n">
-        <v>65600</v>
+        <v>66600</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001</v>
+        <v>-0.0004</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1129</v>
+        <v>0.0716</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0064</v>
       </c>
       <c r="S5" t="n">
-        <v>8.08</v>
+        <v>-100.72</v>
       </c>
       <c r="T5" t="n">
-        <v>104.56</v>
+        <v>100.72</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 88% rich — sell premium</t>
+          <t>trending up +5.5% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18T19:48</t>
+          <t>2026-08-19T15:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -31034,51 +35426,363 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1915.07</v>
+        <v>66456.7</v>
       </c>
       <c r="H6" t="n">
-        <v>21.8</v>
+        <v>25.65</v>
       </c>
       <c r="I6" t="n">
-        <v>0.73</v>
+        <v>0.645</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1920</v>
+        <v>64500</v>
       </c>
       <c r="M6" t="n">
-        <v>1900</v>
+        <v>58000</v>
       </c>
       <c r="N6" t="n">
-        <v>2000</v>
+        <v>75000</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0609</v>
+        <v>0.0086</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0031</v>
+        <v>-0.0055</v>
       </c>
       <c r="S6" t="n">
-        <v>7.72</v>
+        <v>-97.55</v>
       </c>
       <c r="T6" t="n">
-        <v>100.28</v>
+        <v>97.55</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 62% — default sell</t>
+          <t>trending up +5.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>480</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2090.18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2160</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-100.56</v>
+      </c>
+      <c r="T7" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>trending up +11.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>230</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2090.18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1950</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="T8" t="n">
+        <v>100.42</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-19T19:03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>190</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2093.54</v>
+      </c>
+      <c r="H9" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="T9" t="n">
+        <v>102.11</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-19T19:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2093.54</v>
+      </c>
+      <c r="H10" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1950</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-100.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>trending up +11.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -31099,7 +35803,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18T20:11:19.624594 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-19T20:14:52.536244 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y375"/>
+  <dimension ref="A1:Y443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -33759,7 +33759,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G365" t="n">
@@ -33803,8 +33803,22 @@
       <c r="T365" t="n">
         <v>99.26000000000001</v>
       </c>
-      <c r="U365" t="inlineStr"/>
-      <c r="X365" t="inlineStr"/>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>69396.6</t>
+        </is>
+      </c>
+      <c r="V365" t="n">
+        <v>-133.39</v>
+      </c>
+      <c r="W365" t="n">
+        <v>-13.339</v>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="Y365" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
@@ -33925,7 +33939,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -33969,8 +33983,22 @@
       <c r="T367" t="n">
         <v>100.72</v>
       </c>
-      <c r="U367" t="inlineStr"/>
-      <c r="X367" t="inlineStr"/>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>69396.6</t>
+        </is>
+      </c>
+      <c r="V367" t="n">
+        <v>-107.64</v>
+      </c>
+      <c r="W367" t="n">
+        <v>-10.764</v>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="Y367" t="inlineStr">
         <is>
           <t>trending up +5.5% — skewed fly</t>
@@ -34345,7 +34373,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -34390,7 +34418,17 @@
         <v>100.56</v>
       </c>
       <c r="U372" t="inlineStr"/>
-      <c r="X372" t="inlineStr"/>
+      <c r="V372" t="n">
+        <v>-55.01</v>
+      </c>
+      <c r="W372" t="n">
+        <v>-5.501</v>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="Y372" t="inlineStr">
         <is>
           <t>trending up +11.1% — skewed fly</t>
@@ -34423,7 +34461,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -34468,7 +34506,17 @@
         <v>100.42</v>
       </c>
       <c r="U373" t="inlineStr"/>
-      <c r="X373" t="inlineStr"/>
+      <c r="V373" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="W373" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="Y373" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
@@ -34501,7 +34549,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -34546,7 +34594,17 @@
         <v>102.11</v>
       </c>
       <c r="U374" t="inlineStr"/>
-      <c r="X374" t="inlineStr"/>
+      <c r="V374" t="n">
+        <v>-86.36</v>
+      </c>
+      <c r="W374" t="n">
+        <v>-8.635999999999999</v>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="Y374" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
@@ -34579,7 +34637,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G375" t="n">
@@ -34624,10 +34682,6152 @@
         <v>100.2</v>
       </c>
       <c r="U375" t="inlineStr"/>
-      <c r="X375" t="inlineStr"/>
+      <c r="V375" t="n">
+        <v>-92.34999999999999</v>
+      </c>
+      <c r="W375" t="n">
+        <v>-9.234999999999999</v>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="Y375" t="inlineStr">
         <is>
           <t>trending up +11.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-19T21:01</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>280</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>2224.85</v>
+      </c>
+      <c r="H376" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="I376" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K376" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="L376" t="n">
+        <v>2120</v>
+      </c>
+      <c r="M376" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N376" t="n">
+        <v>2240</v>
+      </c>
+      <c r="O376" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P376" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="S376" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="T376" t="n">
+        <v>101.39</v>
+      </c>
+      <c r="U376" t="inlineStr"/>
+      <c r="V376" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="W376" t="n">
+        <v>-0.456</v>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-19T21:01</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>510</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G377" t="n">
+        <v>2224.85</v>
+      </c>
+      <c r="H377" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="I377" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K377" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="L377" t="n">
+        <v>2120</v>
+      </c>
+      <c r="M377" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N377" t="n">
+        <v>2240</v>
+      </c>
+      <c r="O377" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="P377" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="S377" t="n">
+        <v>-100.93</v>
+      </c>
+      <c r="T377" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="U377" t="inlineStr"/>
+      <c r="V377" t="n">
+        <v>-57.48</v>
+      </c>
+      <c r="W377" t="n">
+        <v>-5.748</v>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>trending up +18.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-19T21:02</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>220</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>2224.85</v>
+      </c>
+      <c r="H378" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I378" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K378" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L378" t="n">
+        <v>1950</v>
+      </c>
+      <c r="M378" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N378" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P378" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S378" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="T378" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="U378" t="inlineStr"/>
+      <c r="V378" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="W378" t="n">
+        <v>-0.178</v>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-19T21:02</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G379" t="n">
+        <v>2224.85</v>
+      </c>
+      <c r="H379" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I379" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K379" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L379" t="n">
+        <v>1950</v>
+      </c>
+      <c r="M379" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N379" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O379" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P379" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="S379" t="n">
+        <v>-100.21</v>
+      </c>
+      <c r="T379" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="U379" t="inlineStr"/>
+      <c r="V379" t="n">
+        <v>-91.67</v>
+      </c>
+      <c r="W379" t="n">
+        <v>-9.167</v>
+      </c>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>trending up +18.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-19T21:39</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>430</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>2272.62</v>
+      </c>
+      <c r="H380" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="I380" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K380" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="L380" t="n">
+        <v>2140</v>
+      </c>
+      <c r="M380" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N380" t="n">
+        <v>2360</v>
+      </c>
+      <c r="O380" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="P380" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="S380" t="n">
+        <v>-99.55</v>
+      </c>
+      <c r="T380" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>2257.93</t>
+        </is>
+      </c>
+      <c r="V380" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="W380" t="n">
+        <v>1.883</v>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>trending up +20.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-19T21:59</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>220</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G381" t="n">
+        <v>2284.6</v>
+      </c>
+      <c r="H381" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="I381" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K381" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="L381" t="n">
+        <v>2150</v>
+      </c>
+      <c r="M381" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N381" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O381" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P381" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="S381" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="T381" t="n">
+        <v>98.19</v>
+      </c>
+      <c r="U381" t="inlineStr"/>
+      <c r="V381" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="W381" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-20T02:35</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>190</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G382" t="n">
+        <v>2257.93</v>
+      </c>
+      <c r="H382" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="I382" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K382" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L382" t="n">
+        <v>2220</v>
+      </c>
+      <c r="M382" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N382" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
+      <c r="P382" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S382" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="T382" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>2257.93</t>
+        </is>
+      </c>
+      <c r="V382" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="W382" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-20T03:28</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>80</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G383" t="n">
+        <v>68974.7</v>
+      </c>
+      <c r="H383" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="I383" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K383" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L383" t="n">
+        <v>68800</v>
+      </c>
+      <c r="M383" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N383" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
+      <c r="P383" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="S383" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="T383" t="n">
+        <v>102.16</v>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>68974.7</t>
+        </is>
+      </c>
+      <c r="V383" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="W383" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-20T03:28</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>70</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G384" t="n">
+        <v>68974.7</v>
+      </c>
+      <c r="H384" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="I384" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K384" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L384" t="n">
+        <v>68800</v>
+      </c>
+      <c r="M384" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N384" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O384" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P384" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="S384" t="n">
+        <v>-99.2</v>
+      </c>
+      <c r="T384" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>68974.7</t>
+        </is>
+      </c>
+      <c r="V384" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="W384" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>trending up +9.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-20T03:28</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>290</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G385" t="n">
+        <v>2235.68</v>
+      </c>
+      <c r="H385" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="I385" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K385" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L385" t="n">
+        <v>2200</v>
+      </c>
+      <c r="M385" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N385" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P385" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S385" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="T385" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>2235.68</t>
+        </is>
+      </c>
+      <c r="V385" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="W385" t="n">
+        <v>1.502</v>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-20T03:28</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>270</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G386" t="n">
+        <v>2235.68</v>
+      </c>
+      <c r="H386" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="I386" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K386" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L386" t="n">
+        <v>2200</v>
+      </c>
+      <c r="M386" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N386" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O386" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="P386" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S386" t="n">
+        <v>-98.95</v>
+      </c>
+      <c r="T386" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>2235.68</t>
+        </is>
+      </c>
+      <c r="V386" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="W386" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>trending up +18.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:09</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>80</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G387" t="n">
+        <v>69307.5</v>
+      </c>
+      <c r="H387" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="I387" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K387" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L387" t="n">
+        <v>69000</v>
+      </c>
+      <c r="M387" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N387" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O387" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P387" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="S387" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="T387" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>69307.5</t>
+        </is>
+      </c>
+      <c r="V387" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W387" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:09</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>70</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G388" t="n">
+        <v>69307.5</v>
+      </c>
+      <c r="H388" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K388" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L388" t="n">
+        <v>69000</v>
+      </c>
+      <c r="M388" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N388" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O388" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P388" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="S388" t="n">
+        <v>-95.81999999999999</v>
+      </c>
+      <c r="T388" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>69307.5</t>
+        </is>
+      </c>
+      <c r="V388" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="W388" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>trending up +9.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:09</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>230</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G389" t="n">
+        <v>2255.31</v>
+      </c>
+      <c r="H389" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="I389" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K389" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L389" t="n">
+        <v>2220</v>
+      </c>
+      <c r="M389" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N389" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O389" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P389" t="n">
+        <v>0.2216</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S389" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="T389" t="n">
+        <v>101.57</v>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>2255.31</t>
+        </is>
+      </c>
+      <c r="V389" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="W389" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:09</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>270</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>2255.31</v>
+      </c>
+      <c r="H390" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="I390" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K390" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L390" t="n">
+        <v>2220</v>
+      </c>
+      <c r="M390" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N390" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O390" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="P390" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S390" t="n">
+        <v>-101.66</v>
+      </c>
+      <c r="T390" t="n">
+        <v>101.66</v>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>2255.31</t>
+        </is>
+      </c>
+      <c r="V390" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="W390" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>trending up +19.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:51</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>80</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>69439</v>
+      </c>
+      <c r="H391" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I391" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K391" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L391" t="n">
+        <v>69000</v>
+      </c>
+      <c r="M391" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N391" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P391" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="S391" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="T391" t="n">
+        <v>105.42</v>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>69439.0</t>
+        </is>
+      </c>
+      <c r="V391" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="W391" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:51</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>70</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>69439</v>
+      </c>
+      <c r="H392" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I392" t="n">
+        <v>1</v>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K392" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L392" t="n">
+        <v>69000</v>
+      </c>
+      <c r="M392" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N392" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O392" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P392" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="S392" t="n">
+        <v>-99.58</v>
+      </c>
+      <c r="T392" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>69439.0</t>
+        </is>
+      </c>
+      <c r="V392" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W392" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>trending up +10.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:51</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>220</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>2252.88</v>
+      </c>
+      <c r="H393" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="I393" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K393" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L393" t="n">
+        <v>2240</v>
+      </c>
+      <c r="M393" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N393" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O393" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P393" t="n">
+        <v>0.2245</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S393" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="T393" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>2252.88</t>
+        </is>
+      </c>
+      <c r="V393" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W393" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:51</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>250</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>2252.88</v>
+      </c>
+      <c r="H394" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="I394" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K394" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L394" t="n">
+        <v>2240</v>
+      </c>
+      <c r="M394" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N394" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O394" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="P394" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S394" t="n">
+        <v>-99.03</v>
+      </c>
+      <c r="T394" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>2252.88</t>
+        </is>
+      </c>
+      <c r="V394" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="W394" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>trending up +19.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:25</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>80</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>69651.5</v>
+      </c>
+      <c r="H395" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="I395" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K395" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L395" t="n">
+        <v>69200</v>
+      </c>
+      <c r="M395" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N395" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0</v>
+      </c>
+      <c r="P395" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="S395" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="T395" t="n">
+        <v>106.09</v>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>69651.5</t>
+        </is>
+      </c>
+      <c r="V395" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="W395" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:25</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>70</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>69651.5</v>
+      </c>
+      <c r="H396" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="I396" t="n">
+        <v>1</v>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K396" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L396" t="n">
+        <v>69200</v>
+      </c>
+      <c r="M396" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N396" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O396" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P396" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="S396" t="n">
+        <v>-100.34</v>
+      </c>
+      <c r="T396" t="n">
+        <v>100.34</v>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>69651.5</t>
+        </is>
+      </c>
+      <c r="V396" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="W396" t="n">
+        <v>-0.137</v>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>trending up +10.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:25</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>220</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>2256.03</v>
+      </c>
+      <c r="H397" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K397" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L397" t="n">
+        <v>2240</v>
+      </c>
+      <c r="M397" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N397" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O397" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P397" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S397" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="T397" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>2256.03</t>
+        </is>
+      </c>
+      <c r="V397" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="W397" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:25</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>260</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>2256.03</v>
+      </c>
+      <c r="H398" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K398" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L398" t="n">
+        <v>2240</v>
+      </c>
+      <c r="M398" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N398" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O398" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="P398" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S398" t="n">
+        <v>-100.44</v>
+      </c>
+      <c r="T398" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>2256.03</t>
+        </is>
+      </c>
+      <c r="V398" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="W398" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>trending up +19.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:56</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>80</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>69377.7</v>
+      </c>
+      <c r="H399" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="I399" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K399" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L399" t="n">
+        <v>69400</v>
+      </c>
+      <c r="M399" t="n">
+        <v>68600</v>
+      </c>
+      <c r="N399" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O399" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P399" t="n">
+        <v>0.4582</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="S399" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="T399" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>69377.7</t>
+        </is>
+      </c>
+      <c r="V399" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W399" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:56</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>70</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>69377.7</v>
+      </c>
+      <c r="H400" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="I400" t="n">
+        <v>1</v>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K400" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L400" t="n">
+        <v>69400</v>
+      </c>
+      <c r="M400" t="n">
+        <v>68600</v>
+      </c>
+      <c r="N400" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O400" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P400" t="n">
+        <v>0.5873</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="S400" t="n">
+        <v>-102.64</v>
+      </c>
+      <c r="T400" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>69377.7</t>
+        </is>
+      </c>
+      <c r="V400" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W400" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="X400" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y400" t="inlineStr">
+        <is>
+          <t>trending up +10.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:56</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>280</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>2245.91</v>
+      </c>
+      <c r="H401" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="I401" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K401" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L401" t="n">
+        <v>2240</v>
+      </c>
+      <c r="M401" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N401" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P401" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S401" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="T401" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>2245.91</t>
+        </is>
+      </c>
+      <c r="V401" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="W401" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:56</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>220</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>2245.91</v>
+      </c>
+      <c r="H402" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="I402" t="n">
+        <v>1</v>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K402" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L402" t="n">
+        <v>2240</v>
+      </c>
+      <c r="M402" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N402" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O402" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="P402" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S402" t="n">
+        <v>-98.03</v>
+      </c>
+      <c r="T402" t="n">
+        <v>98.03</v>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>2245.91</t>
+        </is>
+      </c>
+      <c r="V402" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="W402" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>trending up +19.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-20T06:42</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>80</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>69744.10000000001</v>
+      </c>
+      <c r="H403" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="I403" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K403" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L403" t="n">
+        <v>69400</v>
+      </c>
+      <c r="M403" t="n">
+        <v>68600</v>
+      </c>
+      <c r="N403" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O403" t="n">
+        <v>0</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S403" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T403" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>69744.1</t>
+        </is>
+      </c>
+      <c r="V403" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="W403" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="X403" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y403" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-20T06:42</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>60</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>69744.10000000001</v>
+      </c>
+      <c r="H404" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="I404" t="n">
+        <v>1</v>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K404" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L404" t="n">
+        <v>69400</v>
+      </c>
+      <c r="M404" t="n">
+        <v>68600</v>
+      </c>
+      <c r="N404" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O404" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="S404" t="n">
+        <v>-102.71</v>
+      </c>
+      <c r="T404" t="n">
+        <v>102.71</v>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>69744.1</t>
+        </is>
+      </c>
+      <c r="V404" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="W404" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>trending up +10.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-20T06:42</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>220</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>2260.45</v>
+      </c>
+      <c r="H405" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="I405" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K405" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L405" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M405" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N405" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O405" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0.2296</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S405" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="T405" t="n">
+        <v>102.08</v>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>2260.45</t>
+        </is>
+      </c>
+      <c r="V405" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="W405" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-20T06:42</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>230</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>2260.45</v>
+      </c>
+      <c r="H406" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="I406" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K406" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L406" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M406" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N406" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O406" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="P406" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S406" t="n">
+        <v>-99.77</v>
+      </c>
+      <c r="T406" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>2260.45</t>
+        </is>
+      </c>
+      <c r="V406" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W406" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="X406" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y406" t="inlineStr">
+        <is>
+          <t>trending up +20.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:27</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>80</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>69680.89999999999</v>
+      </c>
+      <c r="H407" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="I407" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K407" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L407" t="n">
+        <v>69600</v>
+      </c>
+      <c r="M407" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N407" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O407" t="n">
+        <v>0</v>
+      </c>
+      <c r="P407" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="S407" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="T407" t="n">
+        <v>104.79</v>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>69680.9</t>
+        </is>
+      </c>
+      <c r="V407" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="W407" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:27</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>60</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>69680.89999999999</v>
+      </c>
+      <c r="H408" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="I408" t="n">
+        <v>1</v>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K408" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L408" t="n">
+        <v>69600</v>
+      </c>
+      <c r="M408" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N408" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O408" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="S408" t="n">
+        <v>-92.93000000000001</v>
+      </c>
+      <c r="T408" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>69680.9</t>
+        </is>
+      </c>
+      <c r="V408" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W408" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>trending up +10.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:27</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>220</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>2252.1</v>
+      </c>
+      <c r="H409" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I409" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K409" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L409" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M409" t="n">
+        <v>2210</v>
+      </c>
+      <c r="N409" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S409" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="T409" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>2252.1</t>
+        </is>
+      </c>
+      <c r="V409" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="W409" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:27</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>210</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>2252.1</v>
+      </c>
+      <c r="H410" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I410" t="n">
+        <v>1</v>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K410" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L410" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M410" t="n">
+        <v>2210</v>
+      </c>
+      <c r="N410" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O410" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S410" t="n">
+        <v>-101.77</v>
+      </c>
+      <c r="T410" t="n">
+        <v>101.77</v>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>2252.1</t>
+        </is>
+      </c>
+      <c r="V410" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="W410" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="X410" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y410" t="inlineStr">
+        <is>
+          <t>trending up +19.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:06</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>80</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>69882</v>
+      </c>
+      <c r="H411" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I411" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K411" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L411" t="n">
+        <v>69600</v>
+      </c>
+      <c r="M411" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N411" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0.5491</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="S411" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="T411" t="n">
+        <v>106.62</v>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>69882.0</t>
+        </is>
+      </c>
+      <c r="V411" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="W411" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y411" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:06</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>60</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>69882</v>
+      </c>
+      <c r="H412" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I412" t="n">
+        <v>1</v>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K412" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L412" t="n">
+        <v>69600</v>
+      </c>
+      <c r="M412" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N412" t="n">
+        <v>71200</v>
+      </c>
+      <c r="O412" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P412" t="n">
+        <v>0.7402</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="S412" t="n">
+        <v>-94.39</v>
+      </c>
+      <c r="T412" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>69882.0</t>
+        </is>
+      </c>
+      <c r="V412" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="W412" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y412" t="inlineStr">
+        <is>
+          <t>trending up +10.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:06</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>210</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>2252.19</v>
+      </c>
+      <c r="H413" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I413" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K413" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L413" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M413" t="n">
+        <v>2210</v>
+      </c>
+      <c r="N413" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S413" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="T413" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>2252.19</t>
+        </is>
+      </c>
+      <c r="V413" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="W413" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y413" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:06</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>200</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>2252.19</v>
+      </c>
+      <c r="H414" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1</v>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K414" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L414" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M414" t="n">
+        <v>2210</v>
+      </c>
+      <c r="N414" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O414" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S414" t="n">
+        <v>-99.54000000000001</v>
+      </c>
+      <c r="T414" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>2252.19</t>
+        </is>
+      </c>
+      <c r="V414" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W414" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>trending up +19.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:55</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>80</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>71797.7</v>
+      </c>
+      <c r="H415" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="I415" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K415" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="L415" t="n">
+        <v>71000</v>
+      </c>
+      <c r="M415" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N415" t="n">
+        <v>72800</v>
+      </c>
+      <c r="O415" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0.7288</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="S415" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T415" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>71797.7</t>
+        </is>
+      </c>
+      <c r="V415" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="W415" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="X415" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y415" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:55</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>100</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>71797.7</v>
+      </c>
+      <c r="H416" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="I416" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K416" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="L416" t="n">
+        <v>71000</v>
+      </c>
+      <c r="M416" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N416" t="n">
+        <v>72800</v>
+      </c>
+      <c r="O416" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P416" t="n">
+        <v>0.8572</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="S416" t="n">
+        <v>-104.68</v>
+      </c>
+      <c r="T416" t="n">
+        <v>104.68</v>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>71797.7</t>
+        </is>
+      </c>
+      <c r="V416" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="W416" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>trending up +13.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:55</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>220</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>2282.99</v>
+      </c>
+      <c r="H417" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="I417" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K417" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L417" t="n">
+        <v>2260</v>
+      </c>
+      <c r="M417" t="n">
+        <v>2210</v>
+      </c>
+      <c r="N417" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O417" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P417" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S417" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="T417" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>2282.99</t>
+        </is>
+      </c>
+      <c r="V417" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="W417" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y417" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:55</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>260</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>2282.99</v>
+      </c>
+      <c r="H418" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="I418" t="n">
+        <v>1</v>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K418" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L418" t="n">
+        <v>2260</v>
+      </c>
+      <c r="M418" t="n">
+        <v>2210</v>
+      </c>
+      <c r="N418" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O418" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="P418" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S418" t="n">
+        <v>-101.53</v>
+      </c>
+      <c r="T418" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>2282.99</t>
+        </is>
+      </c>
+      <c r="V418" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="W418" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="X418" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y418" t="inlineStr">
+        <is>
+          <t>trending up +21.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-20T09:30</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>80</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>71832.7</v>
+      </c>
+      <c r="H419" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I419" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K419" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="L419" t="n">
+        <v>71200</v>
+      </c>
+      <c r="M419" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N419" t="n">
+        <v>73000</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+      <c r="P419" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S419" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T419" t="n">
+        <v>106.66</v>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>71832.7</t>
+        </is>
+      </c>
+      <c r="V419" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="W419" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="X419" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y419" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-20T09:30</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>80</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G420" t="n">
+        <v>71832.7</v>
+      </c>
+      <c r="H420" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I420" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K420" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="L420" t="n">
+        <v>71200</v>
+      </c>
+      <c r="M420" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N420" t="n">
+        <v>73000</v>
+      </c>
+      <c r="O420" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P420" t="n">
+        <v>1.1845</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="S420" t="n">
+        <v>-98.52</v>
+      </c>
+      <c r="T420" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>71832.7</t>
+        </is>
+      </c>
+      <c r="V420" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W420" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="X420" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>trending up +13.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-20T09:30</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>210</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>2285.02</v>
+      </c>
+      <c r="H421" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="I421" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K421" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L421" t="n">
+        <v>2270</v>
+      </c>
+      <c r="M421" t="n">
+        <v>2210</v>
+      </c>
+      <c r="N421" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O421" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P421" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="S421" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="T421" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>2285.02</t>
+        </is>
+      </c>
+      <c r="V421" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="W421" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-20T09:30</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>250</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G422" t="n">
+        <v>2285.02</v>
+      </c>
+      <c r="H422" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="I422" t="n">
+        <v>1</v>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K422" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L422" t="n">
+        <v>2270</v>
+      </c>
+      <c r="M422" t="n">
+        <v>2210</v>
+      </c>
+      <c r="N422" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O422" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="P422" t="n">
+        <v>0.5644</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S422" t="n">
+        <v>-98.09999999999999</v>
+      </c>
+      <c r="T422" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>2285.02</t>
+        </is>
+      </c>
+      <c r="V422" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W422" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>trending up +21.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:02</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>80</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G423" t="n">
+        <v>71852.39999999999</v>
+      </c>
+      <c r="H423" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I423" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K423" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="L423" t="n">
+        <v>71400</v>
+      </c>
+      <c r="M423" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N423" t="n">
+        <v>73200</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
+      <c r="P423" t="n">
+        <v>1.5124</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="S423" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="T423" t="n">
+        <v>103.77</v>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>71852.4</t>
+        </is>
+      </c>
+      <c r="V423" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="W423" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="X423" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y423" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:02</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>70</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G424" t="n">
+        <v>71852.39999999999</v>
+      </c>
+      <c r="H424" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I424" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K424" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="L424" t="n">
+        <v>71400</v>
+      </c>
+      <c r="M424" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N424" t="n">
+        <v>73200</v>
+      </c>
+      <c r="O424" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P424" t="n">
+        <v>1.3496</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="S424" t="n">
+        <v>-101.28</v>
+      </c>
+      <c r="T424" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>71852.4</t>
+        </is>
+      </c>
+      <c r="V424" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="W424" t="n">
+        <v>-0.221</v>
+      </c>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y424" t="inlineStr">
+        <is>
+          <t>trending up +13.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:02</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>210</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G425" t="n">
+        <v>2280.8</v>
+      </c>
+      <c r="H425" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="I425" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K425" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L425" t="n">
+        <v>2270</v>
+      </c>
+      <c r="M425" t="n">
+        <v>2250</v>
+      </c>
+      <c r="N425" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O425" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P425" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S425" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="T425" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>2280.8</t>
+        </is>
+      </c>
+      <c r="V425" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="W425" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:02</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>190</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G426" t="n">
+        <v>2280.8</v>
+      </c>
+      <c r="H426" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="I426" t="n">
+        <v>1</v>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K426" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L426" t="n">
+        <v>2270</v>
+      </c>
+      <c r="M426" t="n">
+        <v>2250</v>
+      </c>
+      <c r="N426" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O426" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="P426" t="n">
+        <v>0.7366</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S426" t="n">
+        <v>-99.69</v>
+      </c>
+      <c r="T426" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>2280.8</t>
+        </is>
+      </c>
+      <c r="V426" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="W426" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>trending up +21.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:46</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>80</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G427" t="n">
+        <v>71849</v>
+      </c>
+      <c r="H427" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I427" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K427" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L427" t="n">
+        <v>71600</v>
+      </c>
+      <c r="M427" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N427" t="n">
+        <v>73000</v>
+      </c>
+      <c r="O427" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P427" t="n">
+        <v>1.8338</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="S427" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="T427" t="n">
+        <v>106.57</v>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>71849.0</t>
+        </is>
+      </c>
+      <c r="V427" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W427" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>IV rank 72% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:46</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>60</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G428" t="n">
+        <v>71849</v>
+      </c>
+      <c r="H428" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I428" t="n">
+        <v>1</v>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K428" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L428" t="n">
+        <v>71600</v>
+      </c>
+      <c r="M428" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N428" t="n">
+        <v>73000</v>
+      </c>
+      <c r="O428" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P428" t="n">
+        <v>2.5597</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="S428" t="n">
+        <v>-96.73</v>
+      </c>
+      <c r="T428" t="n">
+        <v>96.73</v>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>71849.0</t>
+        </is>
+      </c>
+      <c r="V428" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="W428" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y428" t="inlineStr">
+        <is>
+          <t>trending up +13.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:46</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>210</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>2282.21</v>
+      </c>
+      <c r="H429" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="I429" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K429" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L429" t="n">
+        <v>2270</v>
+      </c>
+      <c r="M429" t="n">
+        <v>2250</v>
+      </c>
+      <c r="N429" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="S429" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="T429" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>2282.21</t>
+        </is>
+      </c>
+      <c r="V429" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="W429" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y429" t="inlineStr">
+        <is>
+          <t>IV rank 61% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:46</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>180</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>2282.21</v>
+      </c>
+      <c r="H430" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="I430" t="n">
+        <v>1</v>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K430" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L430" t="n">
+        <v>2270</v>
+      </c>
+      <c r="M430" t="n">
+        <v>2250</v>
+      </c>
+      <c r="N430" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O430" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0.6718</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S430" t="n">
+        <v>-98.98</v>
+      </c>
+      <c r="T430" t="n">
+        <v>98.98</v>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>2282.21</t>
+        </is>
+      </c>
+      <c r="V430" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="W430" t="n">
+        <v>-0.376</v>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y430" t="inlineStr">
+        <is>
+          <t>trending up +21.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-20T11:21</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>70</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>71913.60000000001</v>
+      </c>
+      <c r="H431" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I431" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K431" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L431" t="n">
+        <v>71600</v>
+      </c>
+      <c r="M431" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N431" t="n">
+        <v>73000</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+      <c r="P431" t="n">
+        <v>2.4315</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S431" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T431" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>71913.6</t>
+        </is>
+      </c>
+      <c r="V431" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="W431" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y431" t="inlineStr">
+        <is>
+          <t>IV rank 44% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-20T11:22</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>60</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>71913.60000000001</v>
+      </c>
+      <c r="H432" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I432" t="n">
+        <v>1</v>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K432" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L432" t="n">
+        <v>71600</v>
+      </c>
+      <c r="M432" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N432" t="n">
+        <v>73000</v>
+      </c>
+      <c r="O432" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P432" t="n">
+        <v>3.1285</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="S432" t="n">
+        <v>-95.5</v>
+      </c>
+      <c r="T432" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>71913.6</t>
+        </is>
+      </c>
+      <c r="V432" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="W432" t="n">
+        <v>-0.291</v>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>trending up +14.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-20T11:52</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>2311.68</v>
+      </c>
+      <c r="H433" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="I433" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K433" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L433" t="n">
+        <v>2150</v>
+      </c>
+      <c r="M433" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N433" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O433" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="S433" t="n">
+        <v>-99.75</v>
+      </c>
+      <c r="T433" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="U433" t="inlineStr"/>
+      <c r="X433" t="inlineStr"/>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>trending up +22.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-20T12:38</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>80</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G434" t="n">
+        <v>71819.5</v>
+      </c>
+      <c r="H434" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K434" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="L434" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M434" t="n">
+        <v>66000</v>
+      </c>
+      <c r="N434" t="n">
+        <v>74800</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P434" t="n">
+        <v>0.1138</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="S434" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="T434" t="n">
+        <v>103.46</v>
+      </c>
+      <c r="U434" t="inlineStr"/>
+      <c r="V434" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W434" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y434" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-20T12:38</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>100</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G435" t="n">
+        <v>71819.5</v>
+      </c>
+      <c r="H435" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K435" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="L435" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M435" t="n">
+        <v>66000</v>
+      </c>
+      <c r="N435" t="n">
+        <v>74800</v>
+      </c>
+      <c r="O435" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S435" t="n">
+        <v>-97.28</v>
+      </c>
+      <c r="T435" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="U435" t="inlineStr"/>
+      <c r="V435" t="n">
+        <v>-52.08</v>
+      </c>
+      <c r="W435" t="n">
+        <v>-5.208</v>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>trending up +13.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-20T12:38</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>200</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G436" t="n">
+        <v>2278.96</v>
+      </c>
+      <c r="H436" t="n">
+        <v>73</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K436" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L436" t="n">
+        <v>2260</v>
+      </c>
+      <c r="M436" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N436" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S436" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="T436" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="U436" t="inlineStr"/>
+      <c r="V436" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="W436" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-20T12:38</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>460</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G437" t="n">
+        <v>2278.96</v>
+      </c>
+      <c r="H437" t="n">
+        <v>73</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K437" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L437" t="n">
+        <v>2260</v>
+      </c>
+      <c r="M437" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N437" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O437" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="S437" t="n">
+        <v>-99.13</v>
+      </c>
+      <c r="T437" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="U437" t="inlineStr"/>
+      <c r="V437" t="n">
+        <v>-67.84999999999999</v>
+      </c>
+      <c r="W437" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>trending up +21.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-20T15:03</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>80</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G438" t="n">
+        <v>72283.3</v>
+      </c>
+      <c r="H438" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K438" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="L438" t="n">
+        <v>70600</v>
+      </c>
+      <c r="M438" t="n">
+        <v>67000</v>
+      </c>
+      <c r="N438" t="n">
+        <v>74800</v>
+      </c>
+      <c r="O438" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="S438" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="T438" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="U438" t="inlineStr"/>
+      <c r="V438" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="W438" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Y438" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-20T17:02</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>420</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G439" t="n">
+        <v>2342.18</v>
+      </c>
+      <c r="H439" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K439" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L439" t="n">
+        <v>2290</v>
+      </c>
+      <c r="M439" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N439" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O439" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="P439" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="S439" t="n">
+        <v>-98.87</v>
+      </c>
+      <c r="T439" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="U439" t="inlineStr"/>
+      <c r="X439" t="inlineStr"/>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>trending up +24.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-20T17:02</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>230</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G440" t="n">
+        <v>2342.18</v>
+      </c>
+      <c r="H440" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K440" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L440" t="n">
+        <v>2200</v>
+      </c>
+      <c r="M440" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N440" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S440" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="T440" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="U440" t="inlineStr"/>
+      <c r="X440" t="inlineStr"/>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-20T18:13</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>80</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G441" t="n">
+        <v>72494.3</v>
+      </c>
+      <c r="H441" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="I441" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K441" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L441" t="n">
+        <v>71600</v>
+      </c>
+      <c r="M441" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N441" t="n">
+        <v>74800</v>
+      </c>
+      <c r="O441" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P441" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="S441" t="n">
+        <v>-94.43000000000001</v>
+      </c>
+      <c r="T441" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="U441" t="inlineStr"/>
+      <c r="X441" t="inlineStr"/>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>trending up +14.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-20T19:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>80</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G442" t="n">
+        <v>72404.60000000001</v>
+      </c>
+      <c r="H442" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I442" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K442" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="L442" t="n">
+        <v>72000</v>
+      </c>
+      <c r="M442" t="n">
+        <v>69000</v>
+      </c>
+      <c r="N442" t="n">
+        <v>74800</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0.1844</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="S442" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="T442" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="U442" t="inlineStr"/>
+      <c r="X442" t="inlineStr"/>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-20T20:04</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>230</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G443" t="n">
+        <v>2323.56</v>
+      </c>
+      <c r="H443" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="I443" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K443" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L443" t="n">
+        <v>2300</v>
+      </c>
+      <c r="M443" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N443" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O443" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P443" t="n">
+        <v>0.1141</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S443" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="T443" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="U443" t="inlineStr"/>
+      <c r="X443" t="inlineStr"/>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -34698,22 +40898,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="C2" t="n">
-        <v>97.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>4.65</v>
+        <v>2.48</v>
       </c>
       <c r="E2" t="n">
-        <v>556.73</v>
+        <v>557.62</v>
       </c>
       <c r="F2" t="n">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
-        <v>55.67</v>
+        <v>55.76</v>
       </c>
     </row>
     <row r="3">
@@ -34723,22 +40923,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="E3" t="n">
-        <v>-22.67</v>
+        <v>-22.38</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.78</v>
+        <v>-2.8</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.27</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="4">
@@ -34769,11 +40969,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>long_strangle_wk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -34782,13 +40982,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-74.69</v>
+        <v>-107.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-74.69</v>
+        <v>-53.65</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.47</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="6">
@@ -34798,7 +40998,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -34807,38 +41007,38 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-77.95</v>
+        <v>-261.97</v>
       </c>
       <c r="F6" t="n">
-        <v>-77.95</v>
+        <v>-87.31999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.79</v>
+        <v>-26.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>long_strangle_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>56.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E7" t="n">
-        <v>-107.3</v>
+        <v>-321.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-53.65</v>
+        <v>-10.06</v>
       </c>
       <c r="G7" t="n">
-        <v>-10.73</v>
+        <v>-32.18</v>
       </c>
     </row>
     <row r="8">
@@ -35243,7 +41443,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19T13:01</t>
+          <t>2026-08-19T15:06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -35253,16 +41453,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -35270,13 +41470,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>64799.1</v>
+        <v>66456.7</v>
       </c>
       <c r="H4" t="n">
-        <v>23.1</v>
+        <v>25.65</v>
       </c>
       <c r="I4" t="n">
-        <v>0.573</v>
+        <v>0.645</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -35284,63 +41484,63 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.65</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>64600</v>
+        <v>64500</v>
       </c>
       <c r="M4" t="n">
-        <v>62600</v>
+        <v>58000</v>
       </c>
       <c r="N4" t="n">
-        <v>66000</v>
+        <v>75000</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1344</v>
+        <v>0.0086</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0117</v>
+        <v>-0.0055</v>
       </c>
       <c r="S4" t="n">
-        <v>11.62</v>
+        <v>-97.55</v>
       </c>
       <c r="T4" t="n">
-        <v>99.26000000000001</v>
+        <v>97.55</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 94% rich — sell premium</t>
+          <t>trending up +5.5% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19T15:06</t>
+          <t>2026-08-20T11:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>1900</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -35348,13 +41548,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>66456.7</v>
+        <v>2311.68</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>58.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.546</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -35362,63 +41562,63 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="L5" t="n">
-        <v>65600</v>
+        <v>2150</v>
       </c>
       <c r="M5" t="n">
-        <v>65000</v>
+        <v>1700</v>
       </c>
       <c r="N5" t="n">
-        <v>66600</v>
+        <v>2700</v>
       </c>
       <c r="O5" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.0004</v>
       </c>
-      <c r="P5" t="n">
-        <v>0.0716</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.0064</v>
-      </c>
       <c r="S5" t="n">
-        <v>-100.72</v>
+        <v>-99.75</v>
       </c>
       <c r="T5" t="n">
-        <v>100.72</v>
+        <v>99.75</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>trending up +5.5% — skewed fly</t>
+          <t>trending up +22.8% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19T15:06</t>
+          <t>2026-08-20T17:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>190</v>
+        <v>420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -35426,58 +41626,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>66456.7</v>
+        <v>2342.18</v>
       </c>
       <c r="H6" t="n">
-        <v>25.65</v>
+        <v>62.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.645</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>1.79</v>
       </c>
       <c r="L6" t="n">
-        <v>64500</v>
+        <v>2290</v>
       </c>
       <c r="M6" t="n">
-        <v>58000</v>
+        <v>2100</v>
       </c>
       <c r="N6" t="n">
-        <v>75000</v>
+        <v>2440</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0001</v>
+        <v>-0.0021</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0086</v>
+        <v>0.0165</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0055</v>
+        <v>-0.0005</v>
       </c>
       <c r="S6" t="n">
-        <v>-97.55</v>
+        <v>-98.87</v>
       </c>
       <c r="T6" t="n">
-        <v>97.55</v>
+        <v>98.87</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +5.5% — skewed fly</t>
+          <t>trending up +24.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19T16:11</t>
+          <t>2026-08-20T17:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -35487,16 +41687,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>480</v>
+        <v>230</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -35504,13 +41704,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2090.18</v>
+        <v>2342.18</v>
       </c>
       <c r="H7" t="n">
-        <v>61.9</v>
+        <v>59.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.743</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -35518,63 +41718,63 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="L7" t="n">
-        <v>2020</v>
+        <v>2200</v>
       </c>
       <c r="M7" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="N7" t="n">
-        <v>2160</v>
+        <v>2700</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0022</v>
+        <v>0.0005</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0131</v>
+        <v>0.0065</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0004</v>
+        <v>-0.0019</v>
       </c>
       <c r="S7" t="n">
-        <v>-100.56</v>
+        <v>13.66</v>
       </c>
       <c r="T7" t="n">
-        <v>100.56</v>
+        <v>101.34</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>trending up +11.1% — skewed fly</t>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19T16:11</t>
+          <t>2026-08-20T18:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -35582,63 +41782,63 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2090.18</v>
+        <v>72494.3</v>
       </c>
       <c r="H8" t="n">
-        <v>49.35</v>
+        <v>34.35</v>
       </c>
       <c r="I8" t="n">
-        <v>0.668</v>
+        <v>0.87</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1950</v>
+        <v>71600</v>
       </c>
       <c r="M8" t="n">
-        <v>1700</v>
+        <v>69000</v>
       </c>
       <c r="N8" t="n">
-        <v>2700</v>
+        <v>74800</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0004</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0052</v>
+        <v>0.0978</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0021</v>
+        <v>-0.0062</v>
       </c>
       <c r="S8" t="n">
-        <v>14.58</v>
+        <v>-94.43000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>100.42</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>IV rank 94% rich — sell premium</t>
+          <t>trending up +14.9% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19T19:03</t>
+          <t>2026-08-20T19:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -35648,11 +41848,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -35660,13 +41860,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2093.54</v>
+        <v>72404.60000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>40.5</v>
+        <v>32.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.673</v>
+        <v>0.703</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -35674,31 +41874,31 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.83</v>
+        <v>4.72</v>
       </c>
       <c r="L9" t="n">
-        <v>2080</v>
+        <v>72000</v>
       </c>
       <c r="M9" t="n">
-        <v>2000</v>
+        <v>69000</v>
       </c>
       <c r="N9" t="n">
-        <v>2200</v>
+        <v>74800</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0988</v>
+        <v>0.1844</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.003</v>
+        <v>-0.0076</v>
       </c>
       <c r="S9" t="n">
-        <v>11.89</v>
+        <v>10.09</v>
       </c>
       <c r="T9" t="n">
-        <v>102.11</v>
+        <v>101.91</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -35711,7 +41911,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19T19:03</t>
+          <t>2026-08-20T20:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -35721,16 +41921,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1670</v>
+        <v>230</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -35738,51 +41938,51 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2093.54</v>
+        <v>2323.56</v>
       </c>
       <c r="H10" t="n">
-        <v>44.2</v>
+        <v>46.55</v>
       </c>
       <c r="I10" t="n">
-        <v>0.519</v>
+        <v>0.695</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="L10" t="n">
-        <v>1950</v>
+        <v>2300</v>
       </c>
       <c r="M10" t="n">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="N10" t="n">
-        <v>2700</v>
+        <v>2440</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0011</v>
+        <v>0.1141</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0005</v>
+        <v>-0.0028</v>
       </c>
       <c r="S10" t="n">
-        <v>-100.2</v>
+        <v>15.66</v>
       </c>
       <c r="T10" t="n">
-        <v>100.2</v>
+        <v>99.34</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>trending up +11.3% — skewed fly</t>
+          <t>IV rank 89% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -35803,7 +42003,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-19T20:14:52.536244 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-20T20:16:41.273258 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y443"/>
+  <dimension ref="A1:Y507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -12693,8 +12693,22 @@
       <c r="T134" t="n">
         <v>94.88</v>
       </c>
-      <c r="U134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>73713.9</t>
+        </is>
+      </c>
+      <c r="V134" t="n">
+        <v>-129.2</v>
+      </c>
+      <c r="W134" t="n">
+        <v>-12.92</v>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y134" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -39949,7 +39963,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G433" t="n">
@@ -39994,7 +40008,17 @@
         <v>99.75</v>
       </c>
       <c r="U433" t="inlineStr"/>
-      <c r="X433" t="inlineStr"/>
+      <c r="V433" t="n">
+        <v>-93.09999999999999</v>
+      </c>
+      <c r="W433" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y433" t="inlineStr">
         <is>
           <t>trending up +22.8% — skewed fly</t>
@@ -40467,7 +40491,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G439" t="n">
@@ -40511,8 +40535,22 @@
       <c r="T439" t="n">
         <v>98.87</v>
       </c>
-      <c r="U439" t="inlineStr"/>
-      <c r="X439" t="inlineStr"/>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>2339.23</t>
+        </is>
+      </c>
+      <c r="V439" t="n">
+        <v>-26.59</v>
+      </c>
+      <c r="W439" t="n">
+        <v>-2.659</v>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y439" t="inlineStr">
         <is>
           <t>trending up +24.4% — skewed fly</t>
@@ -40545,7 +40583,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G440" t="n">
@@ -40590,7 +40628,17 @@
         <v>101.34</v>
       </c>
       <c r="U440" t="inlineStr"/>
-      <c r="X440" t="inlineStr"/>
+      <c r="V440" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W440" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y440" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
@@ -40623,7 +40671,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G441" t="n">
@@ -40668,7 +40716,17 @@
         <v>94.43000000000001</v>
       </c>
       <c r="U441" t="inlineStr"/>
-      <c r="X441" t="inlineStr"/>
+      <c r="V441" t="n">
+        <v>-63.2</v>
+      </c>
+      <c r="W441" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y441" t="inlineStr">
         <is>
           <t>trending up +14.9% — skewed fly</t>
@@ -40701,7 +40759,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G442" t="n">
@@ -40745,8 +40803,22 @@
       <c r="T442" t="n">
         <v>101.91</v>
       </c>
-      <c r="U442" t="inlineStr"/>
-      <c r="X442" t="inlineStr"/>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>73713.9</t>
+        </is>
+      </c>
+      <c r="V442" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="W442" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y442" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
@@ -40779,7 +40851,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G443" t="n">
@@ -40824,10 +40896,5780 @@
         <v>99.34</v>
       </c>
       <c r="U443" t="inlineStr"/>
-      <c r="X443" t="inlineStr"/>
+      <c r="V443" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="W443" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="Y443" t="inlineStr">
         <is>
           <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-20T22:23</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>1</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G444" t="n">
+        <v>4500.27</v>
+      </c>
+      <c r="S444" t="n">
+        <v>0</v>
+      </c>
+      <c r="T444" t="n">
+        <v>10</v>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>4531.66</t>
+        </is>
+      </c>
+      <c r="V444" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="W444" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-20T22:53</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>220</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G445" t="n">
+        <v>2318.11</v>
+      </c>
+      <c r="H445" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K445" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L445" t="n">
+        <v>2300</v>
+      </c>
+      <c r="M445" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N445" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O445" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S445" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="T445" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>2339.23</t>
+        </is>
+      </c>
+      <c r="V445" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="W445" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:01</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>90</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G446" t="n">
+        <v>73713.89999999999</v>
+      </c>
+      <c r="H446" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K446" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="L446" t="n">
+        <v>72200</v>
+      </c>
+      <c r="M446" t="n">
+        <v>69400</v>
+      </c>
+      <c r="N446" t="n">
+        <v>74800</v>
+      </c>
+      <c r="O446" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="S446" t="n">
+        <v>-99.77</v>
+      </c>
+      <c r="T446" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>73713.9</t>
+        </is>
+      </c>
+      <c r="V446" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="W446" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y446" t="inlineStr">
+        <is>
+          <t>trending up +17.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:36</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>80</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>74732.60000000001</v>
+      </c>
+      <c r="H447" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="I447" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K447" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="L447" t="n">
+        <v>72800</v>
+      </c>
+      <c r="M447" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N447" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="S447" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="T447" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>74732.6</t>
+        </is>
+      </c>
+      <c r="V447" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="W447" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:36</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>90</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>74732.60000000001</v>
+      </c>
+      <c r="H448" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K448" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="L448" t="n">
+        <v>72800</v>
+      </c>
+      <c r="M448" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N448" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O448" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P448" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="S448" t="n">
+        <v>-95.76000000000001</v>
+      </c>
+      <c r="T448" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>74732.6</t>
+        </is>
+      </c>
+      <c r="V448" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="W448" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>trending up +18.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:36</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>220</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>2358.56</v>
+      </c>
+      <c r="H449" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K449" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L449" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M449" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N449" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O449" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P449" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S449" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="T449" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>2358.56</t>
+        </is>
+      </c>
+      <c r="V449" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="W449" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:36</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>300</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>2358.56</v>
+      </c>
+      <c r="H450" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I450" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K450" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L450" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M450" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N450" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O450" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="P450" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S450" t="n">
+        <v>-100.95</v>
+      </c>
+      <c r="T450" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>2358.56</t>
+        </is>
+      </c>
+      <c r="V450" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="W450" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y450" t="inlineStr">
+        <is>
+          <t>trending up +25.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:35</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>80</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>74587.10000000001</v>
+      </c>
+      <c r="H451" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="I451" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K451" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="L451" t="n">
+        <v>73000</v>
+      </c>
+      <c r="M451" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N451" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O451" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P451" t="n">
+        <v>0.5592</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="S451" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="T451" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>74587.1</t>
+        </is>
+      </c>
+      <c r="V451" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W451" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:35</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>80</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>74587.10000000001</v>
+      </c>
+      <c r="H452" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="I452" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K452" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="L452" t="n">
+        <v>73000</v>
+      </c>
+      <c r="M452" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N452" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O452" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P452" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="S452" t="n">
+        <v>-94.63</v>
+      </c>
+      <c r="T452" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>74587.1</t>
+        </is>
+      </c>
+      <c r="V452" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="W452" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y452" t="inlineStr">
+        <is>
+          <t>trending up +18.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:35</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>220</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>2350.79</v>
+      </c>
+      <c r="H453" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="I453" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K453" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L453" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M453" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N453" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P453" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S453" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="T453" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>2350.79</t>
+        </is>
+      </c>
+      <c r="V453" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="W453" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:35</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>300</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>2350.79</v>
+      </c>
+      <c r="H454" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="I454" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K454" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L454" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M454" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N454" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O454" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="P454" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S454" t="n">
+        <v>-101.61</v>
+      </c>
+      <c r="T454" t="n">
+        <v>101.61</v>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>2350.79</t>
+        </is>
+      </c>
+      <c r="V454" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="W454" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y454" t="inlineStr">
+        <is>
+          <t>trending up +25.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-21T04:22</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>80</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>74909.8</v>
+      </c>
+      <c r="H455" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I455" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K455" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="L455" t="n">
+        <v>73800</v>
+      </c>
+      <c r="M455" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N455" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
+      <c r="P455" t="n">
+        <v>0.5538</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="S455" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="T455" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>74909.8</t>
+        </is>
+      </c>
+      <c r="V455" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="W455" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y455" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-21T04:22</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>80</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>74909.8</v>
+      </c>
+      <c r="H456" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I456" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K456" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="L456" t="n">
+        <v>73800</v>
+      </c>
+      <c r="M456" t="n">
+        <v>71000</v>
+      </c>
+      <c r="N456" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O456" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P456" t="n">
+        <v>0.5286</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="S456" t="n">
+        <v>-98.62</v>
+      </c>
+      <c r="T456" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>74909.8</t>
+        </is>
+      </c>
+      <c r="V456" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="W456" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y456" t="inlineStr">
+        <is>
+          <t>trending up +19.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-21T04:22</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>220</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>2348.86</v>
+      </c>
+      <c r="H457" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="I457" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K457" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L457" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M457" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N457" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O457" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P457" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S457" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="T457" t="n">
+        <v>100.91</v>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>2348.86</t>
+        </is>
+      </c>
+      <c r="V457" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="W457" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-21T04:22</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>250</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>2348.86</v>
+      </c>
+      <c r="H458" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="I458" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K458" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L458" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M458" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N458" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O458" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="P458" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S458" t="n">
+        <v>-99.8</v>
+      </c>
+      <c r="T458" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>2348.86</t>
+        </is>
+      </c>
+      <c r="V458" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W458" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y458" t="inlineStr">
+        <is>
+          <t>trending up +25.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-21T05:03</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>70</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>75044.8</v>
+      </c>
+      <c r="H459" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K459" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L459" t="n">
+        <v>73800</v>
+      </c>
+      <c r="M459" t="n">
+        <v>71400</v>
+      </c>
+      <c r="N459" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" t="n">
+        <v>0.5805</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="S459" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="T459" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>75044.8</t>
+        </is>
+      </c>
+      <c r="V459" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="W459" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y459" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-21T05:03</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>90</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>75044.8</v>
+      </c>
+      <c r="H460" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K460" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L460" t="n">
+        <v>73800</v>
+      </c>
+      <c r="M460" t="n">
+        <v>71400</v>
+      </c>
+      <c r="N460" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O460" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P460" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="S460" t="n">
+        <v>-104.01</v>
+      </c>
+      <c r="T460" t="n">
+        <v>104.01</v>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>75044.8</t>
+        </is>
+      </c>
+      <c r="V460" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="W460" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y460" t="inlineStr">
+        <is>
+          <t>trending up +19.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-21T05:03</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>220</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>2355.07</v>
+      </c>
+      <c r="H461" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="I461" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K461" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L461" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M461" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N461" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P461" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S461" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="T461" t="n">
+        <v>98.19</v>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>2355.07</t>
+        </is>
+      </c>
+      <c r="V461" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="W461" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y461" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-21T05:03</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>270</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G462" t="n">
+        <v>2355.07</v>
+      </c>
+      <c r="H462" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="I462" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K462" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L462" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M462" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N462" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O462" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="P462" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S462" t="n">
+        <v>-101.79</v>
+      </c>
+      <c r="T462" t="n">
+        <v>101.79</v>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>2355.07</t>
+        </is>
+      </c>
+      <c r="V462" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="W462" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y462" t="inlineStr">
+        <is>
+          <t>trending up +25.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-21T05:47</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>70</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G463" t="n">
+        <v>75216.89999999999</v>
+      </c>
+      <c r="H463" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="I463" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K463" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L463" t="n">
+        <v>74000</v>
+      </c>
+      <c r="M463" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N463" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O463" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P463" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="S463" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="T463" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>75216.9</t>
+        </is>
+      </c>
+      <c r="V463" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="W463" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y463" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-21T05:47</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>90</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G464" t="n">
+        <v>75216.89999999999</v>
+      </c>
+      <c r="H464" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="I464" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K464" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L464" t="n">
+        <v>74000</v>
+      </c>
+      <c r="M464" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N464" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O464" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P464" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="S464" t="n">
+        <v>-104.81</v>
+      </c>
+      <c r="T464" t="n">
+        <v>104.81</v>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>75216.9</t>
+        </is>
+      </c>
+      <c r="V464" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="W464" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y464" t="inlineStr">
+        <is>
+          <t>trending up +19.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-21T05:47</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>220</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G465" t="n">
+        <v>2353.02</v>
+      </c>
+      <c r="H465" t="n">
+        <v>55</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K465" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L465" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M465" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N465" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O465" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P465" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S465" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="T465" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>2353.02</t>
+        </is>
+      </c>
+      <c r="V465" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="W465" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="X465" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y465" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-21T05:47</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>260</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G466" t="n">
+        <v>2353.02</v>
+      </c>
+      <c r="H466" t="n">
+        <v>55</v>
+      </c>
+      <c r="I466" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K466" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L466" t="n">
+        <v>2330</v>
+      </c>
+      <c r="M466" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N466" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O466" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="P466" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S466" t="n">
+        <v>-101.74</v>
+      </c>
+      <c r="T466" t="n">
+        <v>101.74</v>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>2353.02</t>
+        </is>
+      </c>
+      <c r="V466" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="W466" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="X466" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y466" t="inlineStr">
+        <is>
+          <t>trending up +25.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-21T06:38</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>70</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G467" t="n">
+        <v>75573.5</v>
+      </c>
+      <c r="H467" t="n">
+        <v>56</v>
+      </c>
+      <c r="I467" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K467" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="L467" t="n">
+        <v>74400</v>
+      </c>
+      <c r="M467" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N467" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P467" t="n">
+        <v>0.6534</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="S467" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="T467" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>75573.5</t>
+        </is>
+      </c>
+      <c r="V467" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="W467" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="X467" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y467" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-21T06:38</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>70</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G468" t="n">
+        <v>75573.5</v>
+      </c>
+      <c r="H468" t="n">
+        <v>56</v>
+      </c>
+      <c r="I468" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K468" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="L468" t="n">
+        <v>74400</v>
+      </c>
+      <c r="M468" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N468" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O468" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0.8504</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="S468" t="n">
+        <v>-96.12</v>
+      </c>
+      <c r="T468" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>75573.5</t>
+        </is>
+      </c>
+      <c r="V468" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="W468" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="X468" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y468" t="inlineStr">
+        <is>
+          <t>trending up +20.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-21T06:38</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>220</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G469" t="n">
+        <v>2369.39</v>
+      </c>
+      <c r="H469" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="I469" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K469" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L469" t="n">
+        <v>2340</v>
+      </c>
+      <c r="M469" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N469" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O469" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S469" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="T469" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>2369.39</t>
+        </is>
+      </c>
+      <c r="V469" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="W469" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="X469" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y469" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-21T06:38</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>320</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G470" t="n">
+        <v>2369.39</v>
+      </c>
+      <c r="H470" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K470" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L470" t="n">
+        <v>2340</v>
+      </c>
+      <c r="M470" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N470" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O470" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="P470" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S470" t="n">
+        <v>-101.34</v>
+      </c>
+      <c r="T470" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>2369.39</t>
+        </is>
+      </c>
+      <c r="V470" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="W470" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="X470" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y470" t="inlineStr">
+        <is>
+          <t>trending up +26.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-21T07:28</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>70</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G471" t="n">
+        <v>76255.3</v>
+      </c>
+      <c r="H471" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K471" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L471" t="n">
+        <v>74800</v>
+      </c>
+      <c r="M471" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N471" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O471" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P471" t="n">
+        <v>0.6343</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="S471" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="T471" t="n">
+        <v>104.01</v>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>76255.3</t>
+        </is>
+      </c>
+      <c r="V471" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="W471" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="X471" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y471" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-21T07:28</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>90</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G472" t="n">
+        <v>76255.3</v>
+      </c>
+      <c r="H472" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K472" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L472" t="n">
+        <v>74800</v>
+      </c>
+      <c r="M472" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N472" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O472" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P472" t="n">
+        <v>0.8473000000000001</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="S472" t="n">
+        <v>-101.01</v>
+      </c>
+      <c r="T472" t="n">
+        <v>101.01</v>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>76255.3</t>
+        </is>
+      </c>
+      <c r="V472" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="W472" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="X472" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y472" t="inlineStr">
+        <is>
+          <t>trending up +21.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-21T07:28</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>220</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G473" t="n">
+        <v>2378.17</v>
+      </c>
+      <c r="H473" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K473" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L473" t="n">
+        <v>2360</v>
+      </c>
+      <c r="M473" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N473" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P473" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="S473" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="T473" t="n">
+        <v>101.93</v>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>2378.17</t>
+        </is>
+      </c>
+      <c r="V473" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="W473" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y473" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-21T07:28</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>200</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G474" t="n">
+        <v>2378.17</v>
+      </c>
+      <c r="H474" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="I474" t="n">
+        <v>1</v>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K474" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L474" t="n">
+        <v>2360</v>
+      </c>
+      <c r="M474" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N474" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O474" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="P474" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S474" t="n">
+        <v>-100.72</v>
+      </c>
+      <c r="T474" t="n">
+        <v>100.72</v>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>2378.17</t>
+        </is>
+      </c>
+      <c r="V474" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="W474" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="X474" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y474" t="inlineStr">
+        <is>
+          <t>trending up +26.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:06</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>70</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G475" t="n">
+        <v>76553.8</v>
+      </c>
+      <c r="H475" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K475" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="L475" t="n">
+        <v>74800</v>
+      </c>
+      <c r="M475" t="n">
+        <v>73000</v>
+      </c>
+      <c r="N475" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P475" t="n">
+        <v>0.8944</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="S475" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="T475" t="n">
+        <v>102.63</v>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>76553.8</t>
+        </is>
+      </c>
+      <c r="V475" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="W475" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="X475" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y475" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:06</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>80</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G476" t="n">
+        <v>76553.8</v>
+      </c>
+      <c r="H476" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K476" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="L476" t="n">
+        <v>74800</v>
+      </c>
+      <c r="M476" t="n">
+        <v>73000</v>
+      </c>
+      <c r="N476" t="n">
+        <v>77200</v>
+      </c>
+      <c r="O476" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P476" t="n">
+        <v>1.2016</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="S476" t="n">
+        <v>-95.43000000000001</v>
+      </c>
+      <c r="T476" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>76553.8</t>
+        </is>
+      </c>
+      <c r="V476" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="W476" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y476" t="inlineStr">
+        <is>
+          <t>trending up +21.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:06</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>220</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G477" t="n">
+        <v>2378.11</v>
+      </c>
+      <c r="H477" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="I477" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K477" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L477" t="n">
+        <v>2360</v>
+      </c>
+      <c r="M477" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N477" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P477" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S477" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="T477" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>2378.11</t>
+        </is>
+      </c>
+      <c r="V477" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="W477" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="X477" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y477" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:06</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>240</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G478" t="n">
+        <v>2378.11</v>
+      </c>
+      <c r="H478" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="I478" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K478" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L478" t="n">
+        <v>2360</v>
+      </c>
+      <c r="M478" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N478" t="n">
+        <v>2440</v>
+      </c>
+      <c r="O478" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="P478" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S478" t="n">
+        <v>-100.51</v>
+      </c>
+      <c r="T478" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>2378.11</t>
+        </is>
+      </c>
+      <c r="V478" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="W478" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X478" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y478" t="inlineStr">
+        <is>
+          <t>trending up +26.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:57</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>70</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G479" t="n">
+        <v>78776.89999999999</v>
+      </c>
+      <c r="H479" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K479" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="L479" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M479" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N479" t="n">
+        <v>78800</v>
+      </c>
+      <c r="O479" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P479" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="S479" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="T479" t="n">
+        <v>105.56</v>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>78776.9</t>
+        </is>
+      </c>
+      <c r="V479" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="W479" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="X479" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y479" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:57</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>100</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G480" t="n">
+        <v>78776.89999999999</v>
+      </c>
+      <c r="H480" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I480" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K480" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="L480" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M480" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N480" t="n">
+        <v>78800</v>
+      </c>
+      <c r="O480" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P480" t="n">
+        <v>1.4308</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="S480" t="n">
+        <v>-98.09999999999999</v>
+      </c>
+      <c r="T480" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>78776.9</t>
+        </is>
+      </c>
+      <c r="V480" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="W480" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="X480" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y480" t="inlineStr">
+        <is>
+          <t>trending up +25.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:57</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>210</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G481" t="n">
+        <v>2438.71</v>
+      </c>
+      <c r="H481" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="I481" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K481" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L481" t="n">
+        <v>2390</v>
+      </c>
+      <c r="M481" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N481" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O481" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="P481" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S481" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="T481" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>2438.71</t>
+        </is>
+      </c>
+      <c r="V481" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W481" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y481" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:57</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>290</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G482" t="n">
+        <v>2438.71</v>
+      </c>
+      <c r="H482" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K482" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L482" t="n">
+        <v>2390</v>
+      </c>
+      <c r="M482" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N482" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O482" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="P482" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="S482" t="n">
+        <v>-101.01</v>
+      </c>
+      <c r="T482" t="n">
+        <v>101.01</v>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>2438.71</t>
+        </is>
+      </c>
+      <c r="V482" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="W482" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y482" t="inlineStr">
+        <is>
+          <t>trending up +30.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:57</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>230</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G483" t="n">
+        <v>2438.71</v>
+      </c>
+      <c r="H483" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="I483" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K483" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="L483" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M483" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N483" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O483" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P483" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S483" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="T483" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="U483" t="inlineStr"/>
+      <c r="X483" t="inlineStr"/>
+      <c r="Y483" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-21T09:36</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>70</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G484" t="n">
+        <v>77830.3</v>
+      </c>
+      <c r="H484" t="n">
+        <v>45</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K484" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L484" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M484" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N484" t="n">
+        <v>80400</v>
+      </c>
+      <c r="O484" t="n">
+        <v>0</v>
+      </c>
+      <c r="P484" t="n">
+        <v>2.0465</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="S484" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="T484" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>77830.3</t>
+        </is>
+      </c>
+      <c r="V484" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="W484" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="X484" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y484" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-21T09:36</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>70</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G485" t="n">
+        <v>77830.3</v>
+      </c>
+      <c r="H485" t="n">
+        <v>45</v>
+      </c>
+      <c r="I485" t="n">
+        <v>1</v>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K485" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L485" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M485" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N485" t="n">
+        <v>80400</v>
+      </c>
+      <c r="O485" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P485" t="n">
+        <v>2.373</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="S485" t="n">
+        <v>-106.76</v>
+      </c>
+      <c r="T485" t="n">
+        <v>106.76</v>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>77830.3</t>
+        </is>
+      </c>
+      <c r="V485" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="W485" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y485" t="inlineStr">
+        <is>
+          <t>trending up +23.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-21T09:36</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>220</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G486" t="n">
+        <v>2394.73</v>
+      </c>
+      <c r="H486" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="I486" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K486" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L486" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M486" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N486" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O486" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P486" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S486" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="T486" t="n">
+        <v>98.14</v>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>2394.73</t>
+        </is>
+      </c>
+      <c r="V486" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="W486" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y486" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-21T09:36</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>220</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G487" t="n">
+        <v>2394.73</v>
+      </c>
+      <c r="H487" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K487" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L487" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M487" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N487" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O487" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="P487" t="n">
+        <v>0.7892</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S487" t="n">
+        <v>-100.03</v>
+      </c>
+      <c r="T487" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>2394.73</t>
+        </is>
+      </c>
+      <c r="V487" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="W487" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y487" t="inlineStr">
+        <is>
+          <t>trending up +27.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:05</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>70</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G488" t="n">
+        <v>77753.5</v>
+      </c>
+      <c r="H488" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="I488" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K488" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L488" t="n">
+        <v>76800</v>
+      </c>
+      <c r="M488" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N488" t="n">
+        <v>80400</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>2.1737</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="S488" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="T488" t="n">
+        <v>103.59</v>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>77753.5</t>
+        </is>
+      </c>
+      <c r="V488" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="W488" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y488" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:05</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>60</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G489" t="n">
+        <v>77753.5</v>
+      </c>
+      <c r="H489" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="I489" t="n">
+        <v>1</v>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K489" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L489" t="n">
+        <v>76800</v>
+      </c>
+      <c r="M489" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N489" t="n">
+        <v>80400</v>
+      </c>
+      <c r="O489" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P489" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S489" t="n">
+        <v>-98.17</v>
+      </c>
+      <c r="T489" t="n">
+        <v>98.17</v>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>77753.5</t>
+        </is>
+      </c>
+      <c r="V489" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W489" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y489" t="inlineStr">
+        <is>
+          <t>trending up +23.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:05</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>220</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G490" t="n">
+        <v>2399.76</v>
+      </c>
+      <c r="H490" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I490" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K490" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L490" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M490" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N490" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O490" t="n">
+        <v>0</v>
+      </c>
+      <c r="P490" t="n">
+        <v>0.7271</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S490" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="T490" t="n">
+        <v>98.73999999999999</v>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>2399.76</t>
+        </is>
+      </c>
+      <c r="V490" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="W490" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y490" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:05</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>220</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G491" t="n">
+        <v>2399.76</v>
+      </c>
+      <c r="H491" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I491" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K491" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L491" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M491" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N491" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O491" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="P491" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S491" t="n">
+        <v>-99.68000000000001</v>
+      </c>
+      <c r="T491" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>2399.76</t>
+        </is>
+      </c>
+      <c r="V491" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W491" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y491" t="inlineStr">
+        <is>
+          <t>trending up +27.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:46</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>70</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G492" t="n">
+        <v>77936.7</v>
+      </c>
+      <c r="H492" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="I492" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K492" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L492" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M492" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N492" t="n">
+        <v>80400</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="P492" t="n">
+        <v>2.8499</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="S492" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="T492" t="n">
+        <v>104.38</v>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>77936.7</t>
+        </is>
+      </c>
+      <c r="V492" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="W492" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y492" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:46</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>50</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G493" t="n">
+        <v>77936.7</v>
+      </c>
+      <c r="H493" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="I493" t="n">
+        <v>1</v>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K493" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L493" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M493" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N493" t="n">
+        <v>80400</v>
+      </c>
+      <c r="O493" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P493" t="n">
+        <v>3.9943</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="S493" t="n">
+        <v>-91.94</v>
+      </c>
+      <c r="T493" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>77936.7</t>
+        </is>
+      </c>
+      <c r="V493" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="W493" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y493" t="inlineStr">
+        <is>
+          <t>trending up +23.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:46</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>210</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G494" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H494" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I494" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K494" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L494" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M494" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N494" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O494" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P494" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="S494" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="T494" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>2400.0</t>
+        </is>
+      </c>
+      <c r="V494" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="W494" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y494" t="inlineStr">
+        <is>
+          <t>IV rank 79% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:46</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>190</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G495" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H495" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I495" t="n">
+        <v>1</v>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K495" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L495" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M495" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N495" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O495" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="P495" t="n">
+        <v>1.1887</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S495" t="n">
+        <v>-100.95</v>
+      </c>
+      <c r="T495" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>2400.0</t>
+        </is>
+      </c>
+      <c r="V495" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="W495" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y495" t="inlineStr">
+        <is>
+          <t>trending up +27.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-21T11:21</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>70</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G496" t="n">
+        <v>77495.7</v>
+      </c>
+      <c r="H496" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="I496" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K496" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L496" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M496" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N496" t="n">
+        <v>80400</v>
+      </c>
+      <c r="O496" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P496" t="n">
+        <v>3.0118</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S496" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="T496" t="n">
+        <v>107.62</v>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>77495.7</t>
+        </is>
+      </c>
+      <c r="V496" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="W496" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y496" t="inlineStr">
+        <is>
+          <t>IV rank 79% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-21T11:21</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>50</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G497" t="n">
+        <v>77495.7</v>
+      </c>
+      <c r="H497" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="I497" t="n">
+        <v>1</v>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K497" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L497" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M497" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N497" t="n">
+        <v>80400</v>
+      </c>
+      <c r="O497" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P497" t="n">
+        <v>4.0629</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S497" t="n">
+        <v>-100.47</v>
+      </c>
+      <c r="T497" t="n">
+        <v>100.47</v>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>77495.7</t>
+        </is>
+      </c>
+      <c r="V497" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="W497" t="n">
+        <v>-0.413</v>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y497" t="inlineStr">
+        <is>
+          <t>trending up +23.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-21T11:21</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>210</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G498" t="n">
+        <v>2380.72</v>
+      </c>
+      <c r="H498" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K498" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L498" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M498" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N498" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O498" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P498" t="n">
+        <v>1.3691</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S498" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T498" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>2380.72</t>
+        </is>
+      </c>
+      <c r="V498" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="W498" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y498" t="inlineStr">
+        <is>
+          <t>IV rank 42% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-21T11:21</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>180</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G499" t="n">
+        <v>2380.72</v>
+      </c>
+      <c r="H499" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="I499" t="n">
+        <v>1</v>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K499" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L499" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M499" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N499" t="n">
+        <v>2480</v>
+      </c>
+      <c r="O499" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="P499" t="n">
+        <v>1.1493</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="S499" t="n">
+        <v>-102.67</v>
+      </c>
+      <c r="T499" t="n">
+        <v>102.67</v>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>2380.72</t>
+        </is>
+      </c>
+      <c r="V499" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="W499" t="n">
+        <v>-0.495</v>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y499" t="inlineStr">
+        <is>
+          <t>trending up +26.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-21T12:37</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>70</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G500" t="n">
+        <v>76950.8</v>
+      </c>
+      <c r="H500" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K500" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="L500" t="n">
+        <v>76800</v>
+      </c>
+      <c r="M500" t="n">
+        <v>70000</v>
+      </c>
+      <c r="N500" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
+      <c r="P500" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="S500" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="T500" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="U500" t="inlineStr"/>
+      <c r="V500" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W500" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y500" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-21T12:37</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>90</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G501" t="n">
+        <v>76950.8</v>
+      </c>
+      <c r="H501" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="I501" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K501" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="L501" t="n">
+        <v>76800</v>
+      </c>
+      <c r="M501" t="n">
+        <v>70000</v>
+      </c>
+      <c r="N501" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O501" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P501" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S501" t="n">
+        <v>-95.92</v>
+      </c>
+      <c r="T501" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="U501" t="inlineStr"/>
+      <c r="X501" t="inlineStr"/>
+      <c r="Y501" t="inlineStr">
+        <is>
+          <t>trending up +22.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-21T12:37</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>320</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G502" t="n">
+        <v>2384.39</v>
+      </c>
+      <c r="H502" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="I502" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K502" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L502" t="n">
+        <v>2360</v>
+      </c>
+      <c r="M502" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N502" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S502" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="T502" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="U502" t="inlineStr"/>
+      <c r="V502" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="W502" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y502" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-21T12:37</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>410</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G503" t="n">
+        <v>2384.39</v>
+      </c>
+      <c r="H503" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="I503" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K503" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L503" t="n">
+        <v>2360</v>
+      </c>
+      <c r="M503" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N503" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O503" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="P503" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="S503" t="n">
+        <v>-100.25</v>
+      </c>
+      <c r="T503" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="U503" t="inlineStr"/>
+      <c r="V503" t="n">
+        <v>-55.8</v>
+      </c>
+      <c r="W503" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y503" t="inlineStr">
+        <is>
+          <t>trending up +27.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:27</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>70</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G504" t="n">
+        <v>77130</v>
+      </c>
+      <c r="H504" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K504" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L504" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M504" t="n">
+        <v>72600</v>
+      </c>
+      <c r="N504" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="S504" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="T504" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="U504" t="inlineStr"/>
+      <c r="X504" t="inlineStr"/>
+      <c r="Y504" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:27</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>320</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G505" t="n">
+        <v>2396.15</v>
+      </c>
+      <c r="H505" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K505" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L505" t="n">
+        <v>2380</v>
+      </c>
+      <c r="M505" t="n">
+        <v>2280</v>
+      </c>
+      <c r="N505" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S505" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="T505" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="U505" t="inlineStr"/>
+      <c r="X505" t="inlineStr"/>
+      <c r="Y505" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-21T17:01</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>1640</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G506" t="n">
+        <v>2405.4</v>
+      </c>
+      <c r="H506" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="I506" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K506" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L506" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M506" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N506" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O506" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P506" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="S506" t="n">
+        <v>-100.37</v>
+      </c>
+      <c r="T506" t="n">
+        <v>100.37</v>
+      </c>
+      <c r="U506" t="inlineStr"/>
+      <c r="X506" t="inlineStr"/>
+      <c r="Y506" t="inlineStr">
+        <is>
+          <t>trending up +28.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-21T18:04</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>340</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G507" t="n">
+        <v>2425.53</v>
+      </c>
+      <c r="H507" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K507" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L507" t="n">
+        <v>2390</v>
+      </c>
+      <c r="M507" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N507" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O507" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="P507" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S507" t="n">
+        <v>-99.76000000000001</v>
+      </c>
+      <c r="T507" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="U507" t="inlineStr"/>
+      <c r="X507" t="inlineStr"/>
+      <c r="Y507" t="inlineStr">
+        <is>
+          <t>trending up +29.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -40898,57 +46740,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="C2" t="n">
-        <v>96.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.48</v>
+        <v>3.23</v>
       </c>
       <c r="E2" t="n">
-        <v>557.62</v>
+        <v>841.76</v>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>3.57</v>
       </c>
       <c r="G2" t="n">
-        <v>55.76</v>
+        <v>84.18000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>62.5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="E3" t="n">
-        <v>-22.38</v>
+        <v>-37.76</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8</v>
+        <v>-7.55</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.24</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gold_ema</t>
+          <t>long_strangle_wk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -40957,88 +46799,88 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-58.51</v>
+        <v>-107.3</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.63</v>
+        <v>-53.65</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.85</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>long_strangle_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>-107.3</v>
+        <v>-150.41</v>
       </c>
       <c r="F5" t="n">
-        <v>-53.65</v>
+        <v>-15.04</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.73</v>
+        <v>-15.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="E6" t="n">
-        <v>-261.97</v>
+        <v>-276.31</v>
       </c>
       <c r="F6" t="n">
-        <v>-87.31999999999999</v>
+        <v>-4.46</v>
       </c>
       <c r="G6" t="n">
-        <v>-26.2</v>
+        <v>-27.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>56.2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-321.8</v>
+        <v>-355.07</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.06</v>
+        <v>-88.77</v>
       </c>
       <c r="G7" t="n">
-        <v>-32.18</v>
+        <v>-35.51</v>
       </c>
     </row>
     <row r="8">
@@ -41127,7 +46969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -41287,7 +47129,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11T02:12</t>
+          <t>2026-08-18T00:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -41302,7 +47144,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -41314,13 +47156,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>64081.6</v>
+        <v>64381.7</v>
       </c>
       <c r="H2" t="n">
-        <v>28.5</v>
+        <v>25.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.487</v>
+        <v>0.522</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -41328,31 +47170,31 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.39</v>
+        <v>0.85</v>
       </c>
       <c r="L2" t="n">
-        <v>65000</v>
+        <v>64000</v>
       </c>
       <c r="M2" t="n">
-        <v>65000</v>
+        <v>58000</v>
       </c>
       <c r="N2" t="n">
-        <v>69000</v>
+        <v>75000</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>-0.0001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0366</v>
+        <v>0.0357</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0297</v>
+        <v>-0.0316</v>
       </c>
       <c r="S2" t="n">
-        <v>13.96</v>
+        <v>14.73</v>
       </c>
       <c r="T2" t="n">
-        <v>94.88</v>
+        <v>94.11</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -41365,7 +47207,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18T00:57</t>
+          <t>2026-08-19T15:06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -41375,7 +47217,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -41384,7 +47226,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -41392,13 +47234,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>64381.7</v>
+        <v>66456.7</v>
       </c>
       <c r="H3" t="n">
-        <v>25.35</v>
+        <v>25.65</v>
       </c>
       <c r="I3" t="n">
-        <v>0.522</v>
+        <v>0.645</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -41406,10 +47248,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>64000</v>
+        <v>64500</v>
       </c>
       <c r="M3" t="n">
         <v>58000</v>
@@ -41421,39 +47263,39 @@
         <v>-0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0357</v>
+        <v>0.0086</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0316</v>
+        <v>-0.0055</v>
       </c>
       <c r="S3" t="n">
-        <v>14.73</v>
+        <v>-97.55</v>
       </c>
       <c r="T3" t="n">
-        <v>94.11</v>
+        <v>97.55</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
+          <t>trending up +5.5% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19T15:06</t>
+          <t>2026-08-21T08:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -41462,7 +47304,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -41470,77 +47312,77 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>66456.7</v>
+        <v>2438.71</v>
       </c>
       <c r="H4" t="n">
-        <v>25.65</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.645</v>
+        <v>0.647</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3.42</v>
       </c>
       <c r="L4" t="n">
-        <v>64500</v>
+        <v>2250</v>
       </c>
       <c r="M4" t="n">
-        <v>58000</v>
+        <v>1700</v>
       </c>
       <c r="N4" t="n">
-        <v>75000</v>
+        <v>2700</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0086</v>
+        <v>0.007</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0055</v>
+        <v>-0.0018</v>
       </c>
       <c r="S4" t="n">
-        <v>-97.55</v>
+        <v>15.09</v>
       </c>
       <c r="T4" t="n">
-        <v>97.55</v>
+        <v>99.91</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>trending up +5.5% — skewed fly</t>
+          <t>IV rank 100% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20T11:52</t>
+          <t>2026-08-21T12:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1900</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -41548,77 +47390,77 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2311.68</v>
+        <v>76950.8</v>
       </c>
       <c r="H5" t="n">
-        <v>58.2</v>
+        <v>57.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.546</v>
+        <v>0.763</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.29</v>
+        <v>6.35</v>
       </c>
       <c r="L5" t="n">
-        <v>2150</v>
+        <v>76800</v>
       </c>
       <c r="M5" t="n">
-        <v>1700</v>
+        <v>70000</v>
       </c>
       <c r="N5" t="n">
-        <v>2700</v>
+        <v>83200</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001</v>
+        <v>0.0175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0034</v>
       </c>
       <c r="S5" t="n">
-        <v>-99.75</v>
+        <v>-95.92</v>
       </c>
       <c r="T5" t="n">
-        <v>99.75</v>
+        <v>95.92</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>trending up +22.8% — skewed fly</t>
+          <t>trending up +22.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20T17:02</t>
+          <t>2026-08-21T16:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -41626,58 +47468,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2342.18</v>
+        <v>77130</v>
       </c>
       <c r="H6" t="n">
-        <v>62.4</v>
+        <v>36.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.79</v>
+        <v>2.91</v>
       </c>
       <c r="L6" t="n">
-        <v>2290</v>
+        <v>77000</v>
       </c>
       <c r="M6" t="n">
-        <v>2100</v>
+        <v>72600</v>
       </c>
       <c r="N6" t="n">
-        <v>2440</v>
+        <v>83200</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0021</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0165</v>
+        <v>0.2409</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0005</v>
+        <v>-0.0105</v>
       </c>
       <c r="S6" t="n">
-        <v>-98.87</v>
+        <v>13.4</v>
       </c>
       <c r="T6" t="n">
-        <v>98.87</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +24.4% — skewed fly</t>
+          <t>IV rank 95% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20T17:02</t>
+          <t>2026-08-21T16:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -41687,16 +47529,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -41704,77 +47546,77 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2342.18</v>
+        <v>2396.15</v>
       </c>
       <c r="H7" t="n">
-        <v>59.1</v>
+        <v>50.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.646</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>0.75</v>
       </c>
       <c r="L7" t="n">
-        <v>2200</v>
+        <v>2380</v>
       </c>
       <c r="M7" t="n">
-        <v>1700</v>
+        <v>2280</v>
       </c>
       <c r="N7" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0005</v>
+        <v>0.0001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0065</v>
+        <v>0.0977</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0019</v>
+        <v>-0.0029</v>
       </c>
       <c r="S7" t="n">
-        <v>13.66</v>
+        <v>26.62</v>
       </c>
       <c r="T7" t="n">
-        <v>101.34</v>
+        <v>101.38</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 94% rich — sell premium</t>
+          <t>IV rank 89% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20T18:13</t>
+          <t>2026-08-21T17:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>1640</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -41782,13 +47624,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>72494.3</v>
+        <v>2405.4</v>
       </c>
       <c r="H8" t="n">
-        <v>34.35</v>
+        <v>58.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.87</v>
+        <v>0.554</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -41796,63 +47638,63 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>71600</v>
+        <v>2250</v>
       </c>
       <c r="M8" t="n">
-        <v>69000</v>
+        <v>2200</v>
       </c>
       <c r="N8" t="n">
-        <v>74800</v>
+        <v>2700</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0978</v>
+        <v>0.001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0062</v>
+        <v>-0.0005</v>
       </c>
       <c r="S8" t="n">
-        <v>-94.43000000000001</v>
+        <v>-100.37</v>
       </c>
       <c r="T8" t="n">
-        <v>94.43000000000001</v>
+        <v>100.37</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>trending up +14.9% — skewed fly</t>
+          <t>trending up +28.2% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20T19:00</t>
+          <t>2026-08-21T18:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -41860,129 +47702,51 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>72404.60000000001</v>
+        <v>2425.53</v>
       </c>
       <c r="H9" t="n">
-        <v>32.5</v>
+        <v>49.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.703</v>
+        <v>0.798</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4.72</v>
+        <v>0.77</v>
       </c>
       <c r="L9" t="n">
-        <v>72000</v>
+        <v>2390</v>
       </c>
       <c r="M9" t="n">
-        <v>69000</v>
+        <v>2300</v>
       </c>
       <c r="N9" t="n">
-        <v>74800</v>
+        <v>2600</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.0026</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1844</v>
+        <v>0.0453</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0076</v>
+        <v>-0.0015</v>
       </c>
       <c r="S9" t="n">
-        <v>10.09</v>
+        <v>-99.76000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>101.91</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>IV rank 94% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-20T20:04</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>230</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2323.56</v>
-      </c>
-      <c r="H10" t="n">
-        <v>46.55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Bearish</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2300</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2200</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2440</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1141</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.0028</v>
-      </c>
-      <c r="S10" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="T10" t="n">
-        <v>99.34</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>IV rank 89% rich — sell premium</t>
+          <t>trending up +29.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -42003,7 +47767,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-20T20:16:41.273258 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-21T20:13:32.366391 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y507"/>
+  <dimension ref="A1:Y587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -44495,7 +44495,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G483" t="n">
@@ -44540,7 +44540,17 @@
         <v>99.91</v>
       </c>
       <c r="U483" t="inlineStr"/>
-      <c r="X483" t="inlineStr"/>
+      <c r="V483" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="W483" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="X483" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y483" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -46133,7 +46143,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G501" t="n">
@@ -46178,7 +46188,17 @@
         <v>95.92</v>
       </c>
       <c r="U501" t="inlineStr"/>
-      <c r="X501" t="inlineStr"/>
+      <c r="V501" t="n">
+        <v>-66.68000000000001</v>
+      </c>
+      <c r="W501" t="n">
+        <v>-6.668</v>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y501" t="inlineStr">
         <is>
           <t>trending up +22.4% — skewed fly</t>
@@ -46387,7 +46407,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G504" t="n">
@@ -46432,7 +46452,17 @@
         <v>98.59999999999999</v>
       </c>
       <c r="U504" t="inlineStr"/>
-      <c r="X504" t="inlineStr"/>
+      <c r="V504" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="W504" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
       <c r="Y504" t="inlineStr">
         <is>
           <t>IV rank 95% rich — sell premium</t>
@@ -46465,7 +46495,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G505" t="n">
@@ -46510,7 +46540,17 @@
         <v>101.38</v>
       </c>
       <c r="U505" t="inlineStr"/>
-      <c r="X505" t="inlineStr"/>
+      <c r="V505" t="n">
+        <v>-44.7</v>
+      </c>
+      <c r="W505" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y505" t="inlineStr">
         <is>
           <t>IV rank 89% rich — sell premium</t>
@@ -46543,7 +46583,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G506" t="n">
@@ -46588,7 +46628,17 @@
         <v>100.37</v>
       </c>
       <c r="U506" t="inlineStr"/>
-      <c r="X506" t="inlineStr"/>
+      <c r="V506" t="n">
+        <v>-94.79000000000001</v>
+      </c>
+      <c r="W506" t="n">
+        <v>-9.478999999999999</v>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y506" t="inlineStr">
         <is>
           <t>trending up +28.2% — skewed fly</t>
@@ -46621,7 +46671,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G507" t="n">
@@ -46666,10 +46716,7230 @@
         <v>99.76000000000001</v>
       </c>
       <c r="U507" t="inlineStr"/>
-      <c r="X507" t="inlineStr"/>
+      <c r="V507" t="n">
+        <v>-61.03</v>
+      </c>
+      <c r="W507" t="n">
+        <v>-6.103</v>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="Y507" t="inlineStr">
         <is>
           <t>trending up +29.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-21T21:47</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>80</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G508" t="n">
+        <v>78255.7</v>
+      </c>
+      <c r="H508" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K508" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L508" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M508" t="n">
+        <v>74000</v>
+      </c>
+      <c r="N508" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O508" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P508" t="n">
+        <v>0.1937</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="S508" t="n">
+        <v>-94.76000000000001</v>
+      </c>
+      <c r="T508" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>77970.6</t>
+        </is>
+      </c>
+      <c r="V508" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="W508" t="n">
+        <v>2.426</v>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y508" t="inlineStr">
+        <is>
+          <t>trending up +24.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-21T21:47</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>220</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G509" t="n">
+        <v>2485.59</v>
+      </c>
+      <c r="H509" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="I509" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K509" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L509" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M509" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N509" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="P509" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="S509" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="T509" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="U509" t="inlineStr"/>
+      <c r="V509" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W509" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y509" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-21T21:47</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>390</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G510" t="n">
+        <v>2485.59</v>
+      </c>
+      <c r="H510" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="I510" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K510" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L510" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M510" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N510" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O510" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="P510" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="S510" t="n">
+        <v>-99.95999999999999</v>
+      </c>
+      <c r="T510" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>2520.57</t>
+        </is>
+      </c>
+      <c r="V510" t="n">
+        <v>-109.82</v>
+      </c>
+      <c r="W510" t="n">
+        <v>-10.982</v>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y510" t="inlineStr">
+        <is>
+          <t>trending up +32.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-21T22:18</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>240</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G511" t="n">
+        <v>2540.48</v>
+      </c>
+      <c r="H511" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I511" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K511" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="L511" t="n">
+        <v>2300</v>
+      </c>
+      <c r="M511" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N511" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O511" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P511" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S511" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="T511" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="U511" t="inlineStr"/>
+      <c r="V511" t="n">
+        <v>-30.72</v>
+      </c>
+      <c r="W511" t="n">
+        <v>-3.072</v>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y511" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-21T22:18</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>400</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G512" t="n">
+        <v>2540.48</v>
+      </c>
+      <c r="H512" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K512" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="L512" t="n">
+        <v>2300</v>
+      </c>
+      <c r="M512" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N512" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O512" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="P512" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="S512" t="n">
+        <v>-100.68</v>
+      </c>
+      <c r="T512" t="n">
+        <v>100.68</v>
+      </c>
+      <c r="U512" t="inlineStr"/>
+      <c r="X512" t="inlineStr"/>
+      <c r="Y512" t="inlineStr">
+        <is>
+          <t>trending up +35.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-21T23:19</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>250</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G513" t="n">
+        <v>2534.59</v>
+      </c>
+      <c r="H513" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K513" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L513" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M513" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N513" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O513" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P513" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S513" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="T513" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="U513" t="inlineStr"/>
+      <c r="V513" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="W513" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y513" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-21T23:20</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>1</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G514" t="n">
+        <v>4590.36</v>
+      </c>
+      <c r="S514" t="n">
+        <v>0</v>
+      </c>
+      <c r="T514" t="n">
+        <v>10</v>
+      </c>
+      <c r="U514" t="inlineStr"/>
+      <c r="X514" t="inlineStr"/>
+      <c r="Y514" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-22T00:58</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>70</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G515" t="n">
+        <v>77970.60000000001</v>
+      </c>
+      <c r="H515" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="I515" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K515" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L515" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M515" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N515" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O515" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P515" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="S515" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="T515" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>77970.6</t>
+        </is>
+      </c>
+      <c r="V515" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W515" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y515" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-22T00:58</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>190</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G516" t="n">
+        <v>2520.57</v>
+      </c>
+      <c r="H516" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K516" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L516" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M516" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N516" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O516" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P516" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S516" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="T516" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>2520.57</t>
+        </is>
+      </c>
+      <c r="V516" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="W516" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y516" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-22T02:17</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>70</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G517" t="n">
+        <v>78160.39999999999</v>
+      </c>
+      <c r="H517" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K517" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L517" t="n">
+        <v>77800</v>
+      </c>
+      <c r="M517" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N517" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O517" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="S517" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="T517" t="n">
+        <v>101.99</v>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>78160.4</t>
+        </is>
+      </c>
+      <c r="V517" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="W517" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-22T02:17</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>60</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G518" t="n">
+        <v>78160.39999999999</v>
+      </c>
+      <c r="H518" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K518" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L518" t="n">
+        <v>77800</v>
+      </c>
+      <c r="M518" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N518" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O518" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P518" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="S518" t="n">
+        <v>-97.59999999999999</v>
+      </c>
+      <c r="T518" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>78160.4</t>
+        </is>
+      </c>
+      <c r="V518" t="n">
+        <v>3</v>
+      </c>
+      <c r="W518" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>trending up +21.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-22T02:17</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>230</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G519" t="n">
+        <v>2512.65</v>
+      </c>
+      <c r="H519" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I519" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K519" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L519" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M519" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N519" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O519" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P519" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S519" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="T519" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>2512.65</t>
+        </is>
+      </c>
+      <c r="V519" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="W519" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-22T02:17</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>250</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G520" t="n">
+        <v>2512.65</v>
+      </c>
+      <c r="H520" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I520" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K520" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L520" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M520" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N520" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O520" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="P520" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S520" t="n">
+        <v>-100.28</v>
+      </c>
+      <c r="T520" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>2512.65</t>
+        </is>
+      </c>
+      <c r="V520" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="W520" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y520" t="inlineStr">
+        <is>
+          <t>trending up +31.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-22T03:13</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>70</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G521" t="n">
+        <v>78401</v>
+      </c>
+      <c r="H521" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K521" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L521" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M521" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N521" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O521" t="n">
+        <v>0</v>
+      </c>
+      <c r="P521" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="S521" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="T521" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>78401.0</t>
+        </is>
+      </c>
+      <c r="V521" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="W521" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y521" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-22T03:13</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>70</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G522" t="n">
+        <v>78401</v>
+      </c>
+      <c r="H522" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K522" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L522" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M522" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N522" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O522" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P522" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="S522" t="n">
+        <v>-98.78</v>
+      </c>
+      <c r="T522" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>78401.0</t>
+        </is>
+      </c>
+      <c r="V522" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="W522" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y522" t="inlineStr">
+        <is>
+          <t>trending up +21.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-22T03:13</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>230</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G523" t="n">
+        <v>2513.71</v>
+      </c>
+      <c r="H523" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K523" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L523" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M523" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N523" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O523" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P523" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S523" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="T523" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>2513.71</t>
+        </is>
+      </c>
+      <c r="V523" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="W523" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y523" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-22T03:13</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>250</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G524" t="n">
+        <v>2513.71</v>
+      </c>
+      <c r="H524" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K524" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L524" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M524" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N524" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O524" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="P524" t="n">
+        <v>0.1407</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S524" t="n">
+        <v>-99.55</v>
+      </c>
+      <c r="T524" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>2513.71</t>
+        </is>
+      </c>
+      <c r="V524" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W524" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y524" t="inlineStr">
+        <is>
+          <t>trending up +31.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-22T03:57</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>70</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G525" t="n">
+        <v>78491.39999999999</v>
+      </c>
+      <c r="H525" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K525" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L525" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M525" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N525" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O525" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P525" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="S525" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="T525" t="n">
+        <v>102.43</v>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>78491.4</t>
+        </is>
+      </c>
+      <c r="V525" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="W525" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y525" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-22T03:57</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>60</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G526" t="n">
+        <v>78491.39999999999</v>
+      </c>
+      <c r="H526" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K526" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L526" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M526" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N526" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O526" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P526" t="n">
+        <v>0.6073</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="S526" t="n">
+        <v>-99.18000000000001</v>
+      </c>
+      <c r="T526" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>78491.4</t>
+        </is>
+      </c>
+      <c r="V526" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="W526" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y526" t="inlineStr">
+        <is>
+          <t>trending up +21.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-22T03:57</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>150</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G527" t="n">
+        <v>2519.42</v>
+      </c>
+      <c r="H527" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K527" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L527" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M527" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N527" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O527" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="P527" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S527" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T527" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>2519.42</t>
+        </is>
+      </c>
+      <c r="V527" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="W527" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y527" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-22T03:57</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>240</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G528" t="n">
+        <v>2519.42</v>
+      </c>
+      <c r="H528" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K528" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L528" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M528" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N528" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O528" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="P528" t="n">
+        <v>0.1934</v>
+      </c>
+      <c r="Q528" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S528" t="n">
+        <v>-100.78</v>
+      </c>
+      <c r="T528" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>2519.42</t>
+        </is>
+      </c>
+      <c r="V528" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="W528" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y528" t="inlineStr">
+        <is>
+          <t>trending up +31.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-22T04:35</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>70</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G529" t="n">
+        <v>78692.89999999999</v>
+      </c>
+      <c r="H529" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="I529" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K529" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L529" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M529" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N529" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O529" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P529" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="Q529" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="S529" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="T529" t="n">
+        <v>103.84</v>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>78692.9</t>
+        </is>
+      </c>
+      <c r="V529" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="W529" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y529" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-22T04:35</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>70</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G530" t="n">
+        <v>78692.89999999999</v>
+      </c>
+      <c r="H530" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K530" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L530" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M530" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N530" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O530" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P530" t="n">
+        <v>0.6145</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="S530" t="n">
+        <v>-102.75</v>
+      </c>
+      <c r="T530" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>78692.9</t>
+        </is>
+      </c>
+      <c r="V530" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="W530" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y530" t="inlineStr">
+        <is>
+          <t>trending up +22.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-22T04:35</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>240</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G531" t="n">
+        <v>2521.78</v>
+      </c>
+      <c r="H531" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="I531" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K531" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L531" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M531" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N531" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P531" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S531" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="T531" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>2521.78</t>
+        </is>
+      </c>
+      <c r="V531" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="W531" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y531" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-22T04:35</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>240</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G532" t="n">
+        <v>2521.78</v>
+      </c>
+      <c r="H532" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K532" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L532" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M532" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N532" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O532" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="P532" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="Q532" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S532" t="n">
+        <v>-99.06999999999999</v>
+      </c>
+      <c r="T532" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>2521.78</t>
+        </is>
+      </c>
+      <c r="V532" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="W532" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y532" t="inlineStr">
+        <is>
+          <t>trending up +31.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:04</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>70</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G533" t="n">
+        <v>78541</v>
+      </c>
+      <c r="H533" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K533" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L533" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M533" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N533" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O533" t="n">
+        <v>0</v>
+      </c>
+      <c r="P533" t="n">
+        <v>0.5978</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="S533" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="T533" t="n">
+        <v>101.94</v>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>78541.0</t>
+        </is>
+      </c>
+      <c r="V533" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="W533" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y533" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:04</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>60</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G534" t="n">
+        <v>78541</v>
+      </c>
+      <c r="H534" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="I534" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K534" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L534" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M534" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N534" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O534" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P534" t="n">
+        <v>0.6434</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="S534" t="n">
+        <v>-99.29000000000001</v>
+      </c>
+      <c r="T534" t="n">
+        <v>99.29000000000001</v>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>78541.0</t>
+        </is>
+      </c>
+      <c r="V534" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W534" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y534" t="inlineStr">
+        <is>
+          <t>trending up +21.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:04</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>220</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G535" t="n">
+        <v>2516.89</v>
+      </c>
+      <c r="H535" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K535" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L535" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M535" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N535" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O535" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P535" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S535" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="T535" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>2516.89</t>
+        </is>
+      </c>
+      <c r="V535" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="W535" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y535" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:04</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>230</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G536" t="n">
+        <v>2516.89</v>
+      </c>
+      <c r="H536" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K536" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L536" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M536" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N536" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O536" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="P536" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="Q536" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S536" t="n">
+        <v>-100.58</v>
+      </c>
+      <c r="T536" t="n">
+        <v>100.58</v>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>2516.89</t>
+        </is>
+      </c>
+      <c r="V536" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="W536" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y536" t="inlineStr">
+        <is>
+          <t>trending up +31.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:41</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>70</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G537" t="n">
+        <v>77117.2</v>
+      </c>
+      <c r="H537" t="n">
+        <v>41</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K537" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L537" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M537" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N537" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O537" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P537" t="n">
+        <v>0.5852000000000001</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="S537" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="T537" t="n">
+        <v>102.12</v>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>77117.2</t>
+        </is>
+      </c>
+      <c r="V537" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="W537" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y537" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:41</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>60</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G538" t="n">
+        <v>77117.2</v>
+      </c>
+      <c r="H538" t="n">
+        <v>41</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K538" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L538" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M538" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N538" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O538" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P538" t="n">
+        <v>0.7272</v>
+      </c>
+      <c r="Q538" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="S538" t="n">
+        <v>-99.89</v>
+      </c>
+      <c r="T538" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>77117.2</t>
+        </is>
+      </c>
+      <c r="V538" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W538" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y538" t="inlineStr">
+        <is>
+          <t>trending up +19.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:41</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>230</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G539" t="n">
+        <v>2431.22</v>
+      </c>
+      <c r="H539" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="I539" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K539" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L539" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M539" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N539" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O539" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P539" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="Q539" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S539" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="T539" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>2431.22</t>
+        </is>
+      </c>
+      <c r="V539" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="W539" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y539" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:41</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>300</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G540" t="n">
+        <v>2431.22</v>
+      </c>
+      <c r="H540" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K540" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L540" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M540" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N540" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O540" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="P540" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="S540" t="n">
+        <v>-98.79000000000001</v>
+      </c>
+      <c r="T540" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>2431.22</t>
+        </is>
+      </c>
+      <c r="V540" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="W540" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y540" t="inlineStr">
+        <is>
+          <t>trending up +27.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:01</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>70</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G541" t="n">
+        <v>77436.7</v>
+      </c>
+      <c r="H541" t="n">
+        <v>40</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K541" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L541" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M541" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N541" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O541" t="n">
+        <v>0</v>
+      </c>
+      <c r="P541" t="n">
+        <v>0.6239</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="S541" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="T541" t="n">
+        <v>104.03</v>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>77436.7</t>
+        </is>
+      </c>
+      <c r="V541" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="W541" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y541" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:01</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>60</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G542" t="n">
+        <v>77436.7</v>
+      </c>
+      <c r="H542" t="n">
+        <v>40</v>
+      </c>
+      <c r="I542" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K542" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L542" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M542" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N542" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O542" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P542" t="n">
+        <v>0.8167</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="S542" t="n">
+        <v>-102.59</v>
+      </c>
+      <c r="T542" t="n">
+        <v>102.59</v>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>77436.7</t>
+        </is>
+      </c>
+      <c r="V542" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W542" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y542" t="inlineStr">
+        <is>
+          <t>trending up +20.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:01</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>230</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G543" t="n">
+        <v>2443.63</v>
+      </c>
+      <c r="H543" t="n">
+        <v>64</v>
+      </c>
+      <c r="I543" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K543" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L543" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M543" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N543" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O543" t="n">
+        <v>0</v>
+      </c>
+      <c r="P543" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S543" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="T543" t="n">
+        <v>102.21</v>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>2443.63</t>
+        </is>
+      </c>
+      <c r="V543" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="W543" t="n">
+        <v>1.217</v>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y543" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:01</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>280</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G544" t="n">
+        <v>2443.63</v>
+      </c>
+      <c r="H544" t="n">
+        <v>64</v>
+      </c>
+      <c r="I544" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K544" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L544" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M544" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N544" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O544" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="P544" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S544" t="n">
+        <v>-101.39</v>
+      </c>
+      <c r="T544" t="n">
+        <v>101.39</v>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>2443.63</t>
+        </is>
+      </c>
+      <c r="V544" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="W544" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y544" t="inlineStr">
+        <is>
+          <t>trending up +27.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:01</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>250</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G545" t="n">
+        <v>2443.63</v>
+      </c>
+      <c r="H545" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="I545" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K545" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="L545" t="n">
+        <v>2300</v>
+      </c>
+      <c r="M545" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N545" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O545" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P545" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S545" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="T545" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="U545" t="inlineStr"/>
+      <c r="X545" t="inlineStr"/>
+      <c r="Y545" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:58</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>70</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G546" t="n">
+        <v>77449.10000000001</v>
+      </c>
+      <c r="H546" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I546" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K546" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L546" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M546" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N546" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O546" t="n">
+        <v>0</v>
+      </c>
+      <c r="P546" t="n">
+        <v>0.8250999999999999</v>
+      </c>
+      <c r="Q546" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="S546" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="T546" t="n">
+        <v>102.49</v>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>77449.1</t>
+        </is>
+      </c>
+      <c r="V546" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="W546" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y546" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:58</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>60</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G547" t="n">
+        <v>77449.10000000001</v>
+      </c>
+      <c r="H547" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I547" t="n">
+        <v>1</v>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K547" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L547" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M547" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N547" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O547" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P547" t="n">
+        <v>0.8808</v>
+      </c>
+      <c r="Q547" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="S547" t="n">
+        <v>-104.68</v>
+      </c>
+      <c r="T547" t="n">
+        <v>104.68</v>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>77449.1</t>
+        </is>
+      </c>
+      <c r="V547" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W547" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y547" t="inlineStr">
+        <is>
+          <t>trending up +20.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:58</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>230</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G548" t="n">
+        <v>2436.4</v>
+      </c>
+      <c r="H548" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K548" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L548" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M548" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N548" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O548" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P548" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="Q548" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S548" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="T548" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>2436.4</t>
+        </is>
+      </c>
+      <c r="V548" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="W548" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y548" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:58</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>270</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G549" t="n">
+        <v>2436.4</v>
+      </c>
+      <c r="H549" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I549" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K549" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L549" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M549" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N549" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O549" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="P549" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S549" t="n">
+        <v>-99.68000000000001</v>
+      </c>
+      <c r="T549" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>2436.4</t>
+        </is>
+      </c>
+      <c r="V549" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="W549" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y549" t="inlineStr">
+        <is>
+          <t>trending up +27.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:34</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>70</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G550" t="n">
+        <v>77447.60000000001</v>
+      </c>
+      <c r="H550" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I550" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K550" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L550" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M550" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N550" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O550" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P550" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="Q550" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="S550" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T550" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>77447.6</t>
+        </is>
+      </c>
+      <c r="V550" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="W550" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y550" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:34</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>60</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G551" t="n">
+        <v>77447.60000000001</v>
+      </c>
+      <c r="H551" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I551" t="n">
+        <v>1</v>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K551" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L551" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M551" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N551" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O551" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P551" t="n">
+        <v>0.9508</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="S551" t="n">
+        <v>-106.41</v>
+      </c>
+      <c r="T551" t="n">
+        <v>106.41</v>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>77447.6</t>
+        </is>
+      </c>
+      <c r="V551" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="W551" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y551" t="inlineStr">
+        <is>
+          <t>trending up +20.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:34</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>220</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G552" t="n">
+        <v>2439.49</v>
+      </c>
+      <c r="H552" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="I552" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K552" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L552" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M552" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N552" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O552" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P552" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="Q552" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S552" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="T552" t="n">
+        <v>100.54</v>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>2439.49</t>
+        </is>
+      </c>
+      <c r="V552" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W552" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y552" t="inlineStr">
+        <is>
+          <t>IV rank 85% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:34</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>240</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G553" t="n">
+        <v>2439.49</v>
+      </c>
+      <c r="H553" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K553" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L553" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M553" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N553" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O553" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="P553" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S553" t="n">
+        <v>-99.79000000000001</v>
+      </c>
+      <c r="T553" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>2439.49</t>
+        </is>
+      </c>
+      <c r="V553" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="W553" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y553" t="inlineStr">
+        <is>
+          <t>trending up +27.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:59</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>220</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G554" t="n">
+        <v>2431.81</v>
+      </c>
+      <c r="H554" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K554" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L554" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M554" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N554" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O554" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P554" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="Q554" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S554" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="T554" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>2431.81</t>
+        </is>
+      </c>
+      <c r="V554" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W554" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y554" t="inlineStr">
+        <is>
+          <t>IV rank 85% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>240</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G555" t="n">
+        <v>2431.81</v>
+      </c>
+      <c r="H555" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="I555" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K555" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L555" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M555" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N555" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O555" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="P555" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S555" t="n">
+        <v>-100.06</v>
+      </c>
+      <c r="T555" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>2431.81</t>
+        </is>
+      </c>
+      <c r="V555" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="W555" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y555" t="inlineStr">
+        <is>
+          <t>trending up +27.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:39</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>70</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G556" t="n">
+        <v>77119.7</v>
+      </c>
+      <c r="H556" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K556" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L556" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M556" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N556" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O556" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P556" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="Q556" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="S556" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="T556" t="n">
+        <v>105.22</v>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>77119.7</t>
+        </is>
+      </c>
+      <c r="V556" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W556" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y556" t="inlineStr">
+        <is>
+          <t>IV rank 85% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:39</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>50</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G557" t="n">
+        <v>77119.7</v>
+      </c>
+      <c r="H557" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I557" t="n">
+        <v>1</v>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K557" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L557" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M557" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N557" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O557" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P557" t="n">
+        <v>1.0858</v>
+      </c>
+      <c r="Q557" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="S557" t="n">
+        <v>-96.98999999999999</v>
+      </c>
+      <c r="T557" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>77119.7</t>
+        </is>
+      </c>
+      <c r="V557" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="W557" t="n">
+        <v>-0.186</v>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y557" t="inlineStr">
+        <is>
+          <t>trending up +19.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:39</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>220</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G558" t="n">
+        <v>2419.22</v>
+      </c>
+      <c r="H558" t="n">
+        <v>39</v>
+      </c>
+      <c r="I558" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K558" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L558" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M558" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N558" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O558" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="P558" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="Q558" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S558" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="T558" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>2419.22</t>
+        </is>
+      </c>
+      <c r="V558" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="W558" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y558" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:39</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>220</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G559" t="n">
+        <v>2419.22</v>
+      </c>
+      <c r="H559" t="n">
+        <v>39</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K559" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L559" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M559" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N559" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O559" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="P559" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="Q559" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S559" t="n">
+        <v>-98.65000000000001</v>
+      </c>
+      <c r="T559" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>2419.22</t>
+        </is>
+      </c>
+      <c r="V559" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W559" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y559" t="inlineStr">
+        <is>
+          <t>trending up +26.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:02</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>70</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G560" t="n">
+        <v>77137</v>
+      </c>
+      <c r="H560" t="n">
+        <v>23</v>
+      </c>
+      <c r="I560" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K560" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L560" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M560" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N560" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O560" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P560" t="n">
+        <v>0.8801</v>
+      </c>
+      <c r="Q560" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="S560" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T560" t="n">
+        <v>106.96</v>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>77137.0</t>
+        </is>
+      </c>
+      <c r="V560" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="W560" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y560" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:02</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>50</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G561" t="n">
+        <v>77137</v>
+      </c>
+      <c r="H561" t="n">
+        <v>23</v>
+      </c>
+      <c r="I561" t="n">
+        <v>1</v>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K561" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L561" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M561" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N561" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O561" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P561" t="n">
+        <v>1.1737</v>
+      </c>
+      <c r="Q561" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="S561" t="n">
+        <v>-96.56</v>
+      </c>
+      <c r="T561" t="n">
+        <v>96.56</v>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>77137.0</t>
+        </is>
+      </c>
+      <c r="V561" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="W561" t="n">
+        <v>-0.221</v>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y561" t="inlineStr">
+        <is>
+          <t>trending up +19.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:02</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>220</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G562" t="n">
+        <v>2419.61</v>
+      </c>
+      <c r="H562" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="I562" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K562" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L562" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M562" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N562" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O562" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P562" t="n">
+        <v>0.4623</v>
+      </c>
+      <c r="Q562" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S562" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="T562" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>2419.61</t>
+        </is>
+      </c>
+      <c r="V562" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="W562" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y562" t="inlineStr">
+        <is>
+          <t>IV rank 80% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:03</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>220</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G563" t="n">
+        <v>2419.61</v>
+      </c>
+      <c r="H563" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="I563" t="n">
+        <v>1</v>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K563" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L563" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M563" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N563" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O563" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="P563" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="Q563" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S563" t="n">
+        <v>-100.28</v>
+      </c>
+      <c r="T563" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>2419.61</t>
+        </is>
+      </c>
+      <c r="V563" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W563" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y563" t="inlineStr">
+        <is>
+          <t>trending up +26.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:40</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>70</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G564" t="n">
+        <v>77188.39999999999</v>
+      </c>
+      <c r="H564" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="I564" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K564" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L564" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M564" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N564" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O564" t="n">
+        <v>0</v>
+      </c>
+      <c r="P564" t="n">
+        <v>1.1372</v>
+      </c>
+      <c r="Q564" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S564" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="T564" t="n">
+        <v>106.18</v>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>77188.4</t>
+        </is>
+      </c>
+      <c r="V564" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="W564" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y564" t="inlineStr">
+        <is>
+          <t>IV rank 80% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:41</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>50</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G565" t="n">
+        <v>77188.39999999999</v>
+      </c>
+      <c r="H565" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="I565" t="n">
+        <v>1</v>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K565" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L565" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M565" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N565" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O565" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P565" t="n">
+        <v>1.6025</v>
+      </c>
+      <c r="Q565" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="S565" t="n">
+        <v>-101.14</v>
+      </c>
+      <c r="T565" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>77188.4</t>
+        </is>
+      </c>
+      <c r="V565" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="W565" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y565" t="inlineStr">
+        <is>
+          <t>trending up +19.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:41</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>210</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G566" t="n">
+        <v>2422.48</v>
+      </c>
+      <c r="H566" t="n">
+        <v>32</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K566" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L566" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M566" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N566" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O566" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="P566" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="Q566" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S566" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T566" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>2422.48</t>
+        </is>
+      </c>
+      <c r="V566" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="W566" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y566" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:41</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>190</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G567" t="n">
+        <v>2422.48</v>
+      </c>
+      <c r="H567" t="n">
+        <v>32</v>
+      </c>
+      <c r="I567" t="n">
+        <v>1</v>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K567" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L567" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M567" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N567" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O567" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="P567" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="Q567" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S567" t="n">
+        <v>-97.64</v>
+      </c>
+      <c r="T567" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>2422.48</t>
+        </is>
+      </c>
+      <c r="V567" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W567" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="X567" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y567" t="inlineStr">
+        <is>
+          <t>trending up +26.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:59</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>70</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G568" t="n">
+        <v>77033</v>
+      </c>
+      <c r="H568" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="I568" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K568" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L568" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M568" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N568" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O568" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P568" t="n">
+        <v>1.2725</v>
+      </c>
+      <c r="Q568" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S568" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="T568" t="n">
+        <v>106.69</v>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>77033.0</t>
+        </is>
+      </c>
+      <c r="V568" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="W568" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="X568" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y568" t="inlineStr">
+        <is>
+          <t>IV rank 80% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:59</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>50</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G569" t="n">
+        <v>77033</v>
+      </c>
+      <c r="H569" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="I569" t="n">
+        <v>1</v>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K569" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L569" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M569" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N569" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O569" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P569" t="n">
+        <v>1.6382</v>
+      </c>
+      <c r="Q569" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="S569" t="n">
+        <v>-101.18</v>
+      </c>
+      <c r="T569" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>77033.0</t>
+        </is>
+      </c>
+      <c r="V569" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="W569" t="n">
+        <v>-0.208</v>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y569" t="inlineStr">
+        <is>
+          <t>trending up +19.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:59</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>210</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G570" t="n">
+        <v>2421.6</v>
+      </c>
+      <c r="H570" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I570" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K570" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L570" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M570" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N570" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O570" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P570" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="Q570" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S570" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="T570" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>2421.6</t>
+        </is>
+      </c>
+      <c r="V570" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W570" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="X570" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y570" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:59</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>190</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G571" t="n">
+        <v>2421.6</v>
+      </c>
+      <c r="H571" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I571" t="n">
+        <v>1</v>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K571" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L571" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M571" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N571" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O571" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="P571" t="n">
+        <v>0.5301</v>
+      </c>
+      <c r="Q571" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S571" t="n">
+        <v>-100.07</v>
+      </c>
+      <c r="T571" t="n">
+        <v>100.07</v>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>2421.6</t>
+        </is>
+      </c>
+      <c r="V571" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W571" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="X571" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y571" t="inlineStr">
+        <is>
+          <t>trending up +26.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:29</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>70</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G572" t="n">
+        <v>76924.89999999999</v>
+      </c>
+      <c r="H572" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="I572" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K572" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L572" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M572" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N572" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O572" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P572" t="n">
+        <v>1.7046</v>
+      </c>
+      <c r="Q572" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S572" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="T572" t="n">
+        <v>106.31</v>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>76924.9</t>
+        </is>
+      </c>
+      <c r="V572" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W572" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y572" t="inlineStr">
+        <is>
+          <t>IV rank 60% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:29</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>50</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G573" t="n">
+        <v>76924.89999999999</v>
+      </c>
+      <c r="H573" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="I573" t="n">
+        <v>1</v>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K573" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L573" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M573" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N573" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O573" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P573" t="n">
+        <v>1.7896</v>
+      </c>
+      <c r="Q573" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="S573" t="n">
+        <v>-100.09</v>
+      </c>
+      <c r="T573" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>76924.9</t>
+        </is>
+      </c>
+      <c r="V573" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="W573" t="n">
+        <v>-0.505</v>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y573" t="inlineStr">
+        <is>
+          <t>trending up +19.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:29</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>210</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G574" t="n">
+        <v>2406.82</v>
+      </c>
+      <c r="H574" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="I574" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K574" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L574" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M574" t="n">
+        <v>2370</v>
+      </c>
+      <c r="N574" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O574" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P574" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="Q574" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S574" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="T574" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>2406.82</t>
+        </is>
+      </c>
+      <c r="V574" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="W574" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y574" t="inlineStr">
+        <is>
+          <t>IV rank 70% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:29</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>180</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G575" t="n">
+        <v>2406.82</v>
+      </c>
+      <c r="H575" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="I575" t="n">
+        <v>1</v>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K575" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L575" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M575" t="n">
+        <v>2370</v>
+      </c>
+      <c r="N575" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O575" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="P575" t="n">
+        <v>0.8884</v>
+      </c>
+      <c r="Q575" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S575" t="n">
+        <v>-100.51</v>
+      </c>
+      <c r="T575" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>2406.82</t>
+        </is>
+      </c>
+      <c r="V575" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="W575" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y575" t="inlineStr">
+        <is>
+          <t>trending up +25.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:51</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>60</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G576" t="n">
+        <v>77044.89999999999</v>
+      </c>
+      <c r="H576" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I576" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K576" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L576" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M576" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N576" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O576" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P576" t="n">
+        <v>1.3147</v>
+      </c>
+      <c r="Q576" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S576" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T576" t="n">
+        <v>93.76000000000001</v>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>77044.9</t>
+        </is>
+      </c>
+      <c r="V576" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W576" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y576" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:51</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>50</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G577" t="n">
+        <v>77044.89999999999</v>
+      </c>
+      <c r="H577" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I577" t="n">
+        <v>1</v>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K577" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L577" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M577" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N577" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O577" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P577" t="n">
+        <v>2.2392</v>
+      </c>
+      <c r="Q577" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="S577" t="n">
+        <v>-102.92</v>
+      </c>
+      <c r="T577" t="n">
+        <v>102.92</v>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>77044.9</t>
+        </is>
+      </c>
+      <c r="V577" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="W577" t="n">
+        <v>-0.426</v>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y577" t="inlineStr">
+        <is>
+          <t>trending up +19.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:51</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>210</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G578" t="n">
+        <v>2412.08</v>
+      </c>
+      <c r="H578" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="I578" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K578" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L578" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M578" t="n">
+        <v>2370</v>
+      </c>
+      <c r="N578" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O578" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P578" t="n">
+        <v>0.5797</v>
+      </c>
+      <c r="Q578" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="S578" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="T578" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>2412.08</t>
+        </is>
+      </c>
+      <c r="V578" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W578" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y578" t="inlineStr">
+        <is>
+          <t>IV rank 55% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:51</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>180</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G579" t="n">
+        <v>2412.08</v>
+      </c>
+      <c r="H579" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="I579" t="n">
+        <v>1</v>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K579" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L579" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M579" t="n">
+        <v>2370</v>
+      </c>
+      <c r="N579" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O579" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="P579" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="Q579" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S579" t="n">
+        <v>-99.41</v>
+      </c>
+      <c r="T579" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>2412.08</t>
+        </is>
+      </c>
+      <c r="V579" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="W579" t="n">
+        <v>-0.401</v>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y579" t="inlineStr">
+        <is>
+          <t>trending up +26.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-08-22T11:16</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>60</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G580" t="n">
+        <v>76844.5</v>
+      </c>
+      <c r="H580" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I580" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K580" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L580" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M580" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N580" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O580" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P580" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="Q580" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S580" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T580" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>76844.5</t>
+        </is>
+      </c>
+      <c r="V580" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W580" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y580" t="inlineStr">
+        <is>
+          <t>IV rank 30% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-08-22T11:16</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>50</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G581" t="n">
+        <v>76844.5</v>
+      </c>
+      <c r="H581" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I581" t="n">
+        <v>1</v>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K581" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L581" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M581" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N581" t="n">
+        <v>83200</v>
+      </c>
+      <c r="O581" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P581" t="n">
+        <v>2.7596</v>
+      </c>
+      <c r="Q581" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S581" t="n">
+        <v>-104.33</v>
+      </c>
+      <c r="T581" t="n">
+        <v>104.33</v>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>76844.5</t>
+        </is>
+      </c>
+      <c r="V581" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="W581" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y581" t="inlineStr">
+        <is>
+          <t>trending up +19.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:51</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>70</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G582" t="n">
+        <v>77274.5</v>
+      </c>
+      <c r="H582" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="I582" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K582" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L582" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M582" t="n">
+        <v>72800</v>
+      </c>
+      <c r="N582" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O582" t="n">
+        <v>0</v>
+      </c>
+      <c r="P582" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="Q582" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="S582" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="T582" t="n">
+        <v>97.51000000000001</v>
+      </c>
+      <c r="U582" t="inlineStr"/>
+      <c r="V582" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="W582" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y582" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:51</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>80</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G583" t="n">
+        <v>77274.5</v>
+      </c>
+      <c r="H583" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K583" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L583" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M583" t="n">
+        <v>72800</v>
+      </c>
+      <c r="N583" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O583" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P583" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="Q583" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="S583" t="n">
+        <v>-102.38</v>
+      </c>
+      <c r="T583" t="n">
+        <v>102.38</v>
+      </c>
+      <c r="U583" t="inlineStr"/>
+      <c r="X583" t="inlineStr"/>
+      <c r="Y583" t="inlineStr">
+        <is>
+          <t>trending up +19.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:51</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>300</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G584" t="n">
+        <v>2428.29</v>
+      </c>
+      <c r="H584" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K584" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L584" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M584" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N584" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O584" t="n">
+        <v>0</v>
+      </c>
+      <c r="P584" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="Q584" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S584" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="T584" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="U584" t="inlineStr"/>
+      <c r="V584" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="W584" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Y584" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:51</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>360</v>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G585" t="n">
+        <v>2428.29</v>
+      </c>
+      <c r="H585" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="I585" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K585" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L585" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M585" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N585" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O585" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="P585" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="Q585" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S585" t="n">
+        <v>-101.02</v>
+      </c>
+      <c r="T585" t="n">
+        <v>101.02</v>
+      </c>
+      <c r="U585" t="inlineStr"/>
+      <c r="X585" t="inlineStr"/>
+      <c r="Y585" t="inlineStr">
+        <is>
+          <t>trending up +26.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-08-22T16:52</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>70</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G586" t="n">
+        <v>77332.8</v>
+      </c>
+      <c r="H586" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="I586" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K586" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L586" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M586" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N586" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O586" t="n">
+        <v>0</v>
+      </c>
+      <c r="P586" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="Q586" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="S586" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="T586" t="n">
+        <v>102.18</v>
+      </c>
+      <c r="U586" t="inlineStr"/>
+      <c r="X586" t="inlineStr"/>
+      <c r="Y586" t="inlineStr">
+        <is>
+          <t>IV rank 85% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-08-22T17:16</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>300</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G587" t="n">
+        <v>2425.5</v>
+      </c>
+      <c r="H587" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I587" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K587" t="n">
+        <v>1</v>
+      </c>
+      <c r="L587" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M587" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N587" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O587" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P587" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="Q587" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S587" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="T587" t="n">
+        <v>100.29</v>
+      </c>
+      <c r="U587" t="inlineStr"/>
+      <c r="X587" t="inlineStr"/>
+      <c r="Y587" t="inlineStr">
+        <is>
+          <t>IV rank 85% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -46740,22 +54010,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="C2" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="D2" t="n">
-        <v>3.23</v>
+        <v>3.69</v>
       </c>
       <c r="E2" t="n">
-        <v>841.76</v>
+        <v>1132.07</v>
       </c>
       <c r="F2" t="n">
-        <v>3.57</v>
+        <v>4.1</v>
       </c>
       <c r="G2" t="n">
-        <v>84.18000000000001</v>
+        <v>113.21</v>
       </c>
     </row>
     <row r="3">
@@ -46815,22 +54085,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="E5" t="n">
-        <v>-150.41</v>
+        <v>-181.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.04</v>
+        <v>-15.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-15.04</v>
+        <v>-18.12</v>
       </c>
     </row>
     <row r="6">
@@ -46840,7 +54110,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="C6" t="n">
         <v>69.40000000000001</v>
@@ -46849,13 +54119,13 @@
         <v>0.53</v>
       </c>
       <c r="E6" t="n">
-        <v>-276.31</v>
+        <v>-393.27</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.46</v>
+        <v>-4.01</v>
       </c>
       <c r="G6" t="n">
-        <v>-27.63</v>
+        <v>-39.33</v>
       </c>
     </row>
     <row r="7">
@@ -46865,7 +54135,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -46874,13 +54144,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-355.07</v>
+        <v>-449.86</v>
       </c>
       <c r="F7" t="n">
-        <v>-88.77</v>
+        <v>-89.97</v>
       </c>
       <c r="G7" t="n">
-        <v>-35.51</v>
+        <v>-44.99</v>
       </c>
     </row>
     <row r="8">
@@ -46969,7 +54239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -47285,7 +54555,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21T08:57</t>
+          <t>2026-08-21T22:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -47295,7 +54565,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -47304,7 +54574,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -47312,13 +54582,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2438.71</v>
+        <v>2540.48</v>
       </c>
       <c r="H4" t="n">
-        <v>66.15000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="I4" t="n">
-        <v>0.647</v>
+        <v>0.588</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -47326,63 +54596,63 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.42</v>
+        <v>4.78</v>
       </c>
       <c r="L4" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="M4" t="n">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="N4" t="n">
         <v>2700</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0005</v>
+        <v>-0.001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007</v>
+        <v>-0.0042</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0018</v>
+        <v>0.0007</v>
       </c>
       <c r="S4" t="n">
-        <v>15.09</v>
+        <v>-100.68</v>
       </c>
       <c r="T4" t="n">
-        <v>99.91</v>
+        <v>100.68</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
+          <t>trending up +35.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21T12:37</t>
+          <t>2026-08-21T23:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>XAUTUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>perpetual</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -47390,77 +54660,45 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>76950.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="L5" t="n">
-        <v>76800</v>
-      </c>
-      <c r="M5" t="n">
-        <v>70000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>83200</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.0034</v>
+        <v>4590.36</v>
       </c>
       <c r="S5" t="n">
-        <v>-95.92</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>95.92</v>
+        <v>10</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>trending up +22.4% — skewed fly</t>
+          <t>20/50 EMA 3rd retest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:27</t>
+          <t>2026-08-22T06:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -47468,77 +54706,77 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>77130</v>
+        <v>2443.63</v>
       </c>
       <c r="H6" t="n">
-        <v>36.7</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.676</v>
+        <v>0.678</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.91</v>
+        <v>3.76</v>
       </c>
       <c r="L6" t="n">
-        <v>77000</v>
+        <v>2300</v>
       </c>
       <c r="M6" t="n">
-        <v>72600</v>
+        <v>1700</v>
       </c>
       <c r="N6" t="n">
-        <v>83200</v>
+        <v>2700</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2409</v>
+        <v>0.0132</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0105</v>
+        <v>-0.0026</v>
       </c>
       <c r="S6" t="n">
-        <v>13.4</v>
+        <v>26.95</v>
       </c>
       <c r="T6" t="n">
-        <v>98.59999999999999</v>
+        <v>98.05</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 95% rich — sell premium</t>
+          <t>IV rank 100% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21T16:27</t>
+          <t>2026-08-22T12:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -47546,13 +54784,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2396.15</v>
+        <v>77274.5</v>
       </c>
       <c r="H7" t="n">
-        <v>50.15</v>
+        <v>34.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.646</v>
+        <v>0.91</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -47560,44 +54798,44 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.75</v>
+        <v>1.43</v>
       </c>
       <c r="L7" t="n">
-        <v>2380</v>
+        <v>77000</v>
       </c>
       <c r="M7" t="n">
-        <v>2280</v>
+        <v>72800</v>
       </c>
       <c r="N7" t="n">
-        <v>2600</v>
+        <v>82800</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001</v>
+        <v>-0.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0977</v>
+        <v>0.1535</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0029</v>
+        <v>-0.0102</v>
       </c>
       <c r="S7" t="n">
-        <v>26.62</v>
+        <v>-102.38</v>
       </c>
       <c r="T7" t="n">
-        <v>101.38</v>
+        <v>102.38</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 89% rich — sell premium</t>
+          <t>trending up +19.8% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21T17:01</t>
+          <t>2026-08-22T12:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -47607,16 +54845,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1640</v>
+        <v>360</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -47624,77 +54862,77 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2405.4</v>
+        <v>2428.29</v>
       </c>
       <c r="H8" t="n">
-        <v>58.8</v>
+        <v>51.65</v>
       </c>
       <c r="I8" t="n">
-        <v>0.554</v>
+        <v>0.827</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>1.08</v>
       </c>
       <c r="L8" t="n">
-        <v>2250</v>
+        <v>2420</v>
       </c>
       <c r="M8" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="N8" t="n">
-        <v>2700</v>
+        <v>2640</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0002</v>
+        <v>-0.0028</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001</v>
+        <v>0.0239</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0005</v>
+        <v>-0.001</v>
       </c>
       <c r="S8" t="n">
-        <v>-100.37</v>
+        <v>-101.02</v>
       </c>
       <c r="T8" t="n">
-        <v>100.37</v>
+        <v>101.02</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>trending up +28.2% — skewed fly</t>
+          <t>trending up +26.9% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21T18:04</t>
+          <t>2026-08-22T16:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>340</v>
+        <v>70</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -47702,13 +54940,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2425.53</v>
+        <v>77332.8</v>
       </c>
       <c r="H9" t="n">
-        <v>49.05</v>
+        <v>25.35</v>
       </c>
       <c r="I9" t="n">
-        <v>0.798</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -47716,37 +54954,115 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.77</v>
+        <v>1.37</v>
       </c>
       <c r="L9" t="n">
-        <v>2390</v>
+        <v>77000</v>
       </c>
       <c r="M9" t="n">
-        <v>2300</v>
+        <v>75000</v>
       </c>
       <c r="N9" t="n">
-        <v>2600</v>
+        <v>82800</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0026</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0453</v>
+        <v>0.2024</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0015</v>
+        <v>-0.0124</v>
       </c>
       <c r="S9" t="n">
-        <v>-99.76000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="T9" t="n">
-        <v>99.76000000000001</v>
+        <v>102.18</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>trending up +29.3% — skewed fly</t>
+          <t>IV rank 85% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-22T17:16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>300</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2425.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S10" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="T10" t="n">
+        <v>100.29</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>IV rank 85% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -47767,7 +55083,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21T20:13:32.366391 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-22T20:10:45.283840 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y587"/>
+  <dimension ref="A1:Y643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -53569,7 +53569,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G583" t="n">
@@ -53613,8 +53613,22 @@
       <c r="T583" t="n">
         <v>102.38</v>
       </c>
-      <c r="U583" t="inlineStr"/>
-      <c r="X583" t="inlineStr"/>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>77225.4</t>
+        </is>
+      </c>
+      <c r="V583" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="W583" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="Y583" t="inlineStr">
         <is>
           <t>trending up +19.8% — skewed fly</t>
@@ -53735,7 +53749,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G585" t="n">
@@ -53779,8 +53793,22 @@
       <c r="T585" t="n">
         <v>101.02</v>
       </c>
-      <c r="U585" t="inlineStr"/>
-      <c r="X585" t="inlineStr"/>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>2424.96</t>
+        </is>
+      </c>
+      <c r="V585" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="W585" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="X585" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="Y585" t="inlineStr">
         <is>
           <t>trending up +26.9% — skewed fly</t>
@@ -53813,7 +53841,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G586" t="n">
@@ -53858,7 +53886,17 @@
         <v>102.18</v>
       </c>
       <c r="U586" t="inlineStr"/>
-      <c r="X586" t="inlineStr"/>
+      <c r="V586" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="W586" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="X586" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="Y586" t="inlineStr">
         <is>
           <t>IV rank 85% rich — sell premium</t>
@@ -53891,7 +53929,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G587" t="n">
@@ -53936,10 +53974,5116 @@
         <v>100.29</v>
       </c>
       <c r="U587" t="inlineStr"/>
-      <c r="X587" t="inlineStr"/>
+      <c r="V587" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="W587" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="X587" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
       <c r="Y587" t="inlineStr">
         <is>
           <t>IV rank 85% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-08-22T23:15</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>230</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G588" t="n">
+        <v>2415.18</v>
+      </c>
+      <c r="H588" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="I588" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K588" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L588" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M588" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N588" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O588" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P588" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="Q588" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="S588" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="T588" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>2424.96</t>
+        </is>
+      </c>
+      <c r="V588" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="W588" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="X588" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y588" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-08-23T01:41</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>70</v>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G589" t="n">
+        <v>77225.39999999999</v>
+      </c>
+      <c r="H589" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="I589" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K589" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L589" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M589" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N589" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O589" t="n">
+        <v>0</v>
+      </c>
+      <c r="P589" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="Q589" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="S589" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="T589" t="n">
+        <v>104.17</v>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>77225.4</t>
+        </is>
+      </c>
+      <c r="V589" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="W589" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="X589" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y589" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-08-23T02:49</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>70</v>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G590" t="n">
+        <v>77212.10000000001</v>
+      </c>
+      <c r="H590" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I590" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K590" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L590" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M590" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N590" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O590" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P590" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="Q590" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="S590" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="T590" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>77212.1</t>
+        </is>
+      </c>
+      <c r="V590" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="W590" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y590" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-08-23T02:49</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>50</v>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G591" t="n">
+        <v>77212.10000000001</v>
+      </c>
+      <c r="H591" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I591" t="n">
+        <v>1</v>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K591" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L591" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M591" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N591" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O591" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P591" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="Q591" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="S591" t="n">
+        <v>-91.7</v>
+      </c>
+      <c r="T591" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>77212.1</t>
+        </is>
+      </c>
+      <c r="V591" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="W591" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y591" t="inlineStr">
+        <is>
+          <t>trending up +19.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-08-23T02:49</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>210</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G592" t="n">
+        <v>2422.05</v>
+      </c>
+      <c r="H592" t="n">
+        <v>47</v>
+      </c>
+      <c r="I592" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K592" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L592" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M592" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N592" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O592" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P592" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="Q592" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S592" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="T592" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>2422.05</t>
+        </is>
+      </c>
+      <c r="V592" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="W592" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y592" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-08-23T02:49</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>240</v>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G593" t="n">
+        <v>2422.05</v>
+      </c>
+      <c r="H593" t="n">
+        <v>47</v>
+      </c>
+      <c r="I593" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K593" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L593" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M593" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N593" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O593" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="P593" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="Q593" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S593" t="n">
+        <v>-98.40000000000001</v>
+      </c>
+      <c r="T593" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>2422.05</t>
+        </is>
+      </c>
+      <c r="V593" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="W593" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y593" t="inlineStr">
+        <is>
+          <t>trending up +26.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:45</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>70</v>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G594" t="n">
+        <v>76898.3</v>
+      </c>
+      <c r="H594" t="n">
+        <v>28</v>
+      </c>
+      <c r="I594" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K594" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L594" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M594" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N594" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O594" t="n">
+        <v>0</v>
+      </c>
+      <c r="P594" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="Q594" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="S594" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="T594" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>76898.3</t>
+        </is>
+      </c>
+      <c r="V594" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W594" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="X594" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y594" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:45</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>50</v>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G595" t="n">
+        <v>76898.3</v>
+      </c>
+      <c r="H595" t="n">
+        <v>28</v>
+      </c>
+      <c r="I595" t="n">
+        <v>1</v>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K595" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L595" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M595" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N595" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O595" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P595" t="n">
+        <v>0.5125999999999999</v>
+      </c>
+      <c r="Q595" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="S595" t="n">
+        <v>-95</v>
+      </c>
+      <c r="T595" t="n">
+        <v>95</v>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>76898.3</t>
+        </is>
+      </c>
+      <c r="V595" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="W595" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="X595" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y595" t="inlineStr">
+        <is>
+          <t>trending up +18.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:45</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>220</v>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G596" t="n">
+        <v>2411.62</v>
+      </c>
+      <c r="H596" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I596" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K596" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L596" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M596" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N596" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O596" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P596" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="Q596" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="S596" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="T596" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>2411.62</t>
+        </is>
+      </c>
+      <c r="V596" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="W596" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="X596" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y596" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:45</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>240</v>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G597" t="n">
+        <v>2411.62</v>
+      </c>
+      <c r="H597" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I597" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K597" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L597" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M597" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N597" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O597" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="P597" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="Q597" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S597" t="n">
+        <v>-100.2</v>
+      </c>
+      <c r="T597" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>2411.62</t>
+        </is>
+      </c>
+      <c r="V597" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W597" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="X597" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y597" t="inlineStr">
+        <is>
+          <t>trending up +25.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:31</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>70</v>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G598" t="n">
+        <v>76916.3</v>
+      </c>
+      <c r="H598" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I598" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K598" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L598" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M598" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N598" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O598" t="n">
+        <v>0</v>
+      </c>
+      <c r="P598" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="Q598" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="S598" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="T598" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>76916.3</t>
+        </is>
+      </c>
+      <c r="V598" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="W598" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="X598" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y598" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:31</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>50</v>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G599" t="n">
+        <v>76916.3</v>
+      </c>
+      <c r="H599" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I599" t="n">
+        <v>1</v>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K599" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L599" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M599" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N599" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O599" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P599" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="Q599" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="S599" t="n">
+        <v>-95.36</v>
+      </c>
+      <c r="T599" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>76916.3</t>
+        </is>
+      </c>
+      <c r="V599" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="W599" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="X599" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y599" t="inlineStr">
+        <is>
+          <t>trending up +18.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:31</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>220</v>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G600" t="n">
+        <v>2407.41</v>
+      </c>
+      <c r="H600" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I600" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K600" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L600" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M600" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N600" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O600" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P600" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="Q600" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S600" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="T600" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>2407.41</t>
+        </is>
+      </c>
+      <c r="V600" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="W600" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="X600" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y600" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:31</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>220</v>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G601" t="n">
+        <v>2407.41</v>
+      </c>
+      <c r="H601" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I601" t="n">
+        <v>1</v>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K601" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L601" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M601" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N601" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O601" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="P601" t="n">
+        <v>0.2176</v>
+      </c>
+      <c r="Q601" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S601" t="n">
+        <v>-98.58</v>
+      </c>
+      <c r="T601" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>2407.41</t>
+        </is>
+      </c>
+      <c r="V601" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="W601" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="X601" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y601" t="inlineStr">
+        <is>
+          <t>trending up +25.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:06</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>70</v>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G602" t="n">
+        <v>76486.60000000001</v>
+      </c>
+      <c r="H602" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I602" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K602" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L602" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M602" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N602" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O602" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P602" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="Q602" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="S602" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="T602" t="n">
+        <v>104.06</v>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>76486.6</t>
+        </is>
+      </c>
+      <c r="V602" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="W602" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="X602" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y602" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:06</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>60</v>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G603" t="n">
+        <v>76486.60000000001</v>
+      </c>
+      <c r="H603" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I603" t="n">
+        <v>1</v>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K603" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L603" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M603" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N603" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O603" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P603" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="Q603" t="n">
+        <v>-0.0137</v>
+      </c>
+      <c r="S603" t="n">
+        <v>-102.77</v>
+      </c>
+      <c r="T603" t="n">
+        <v>102.77</v>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>76486.6</t>
+        </is>
+      </c>
+      <c r="V603" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W603" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="X603" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y603" t="inlineStr">
+        <is>
+          <t>trending up +18.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:06</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>210</v>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G604" t="n">
+        <v>2377.37</v>
+      </c>
+      <c r="H604" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="I604" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K604" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L604" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M604" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N604" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O604" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P604" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="Q604" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S604" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="T604" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>2377.37</t>
+        </is>
+      </c>
+      <c r="V604" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="W604" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="X604" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y604" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:06</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>220</v>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G605" t="n">
+        <v>2377.37</v>
+      </c>
+      <c r="H605" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="I605" t="n">
+        <v>1</v>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K605" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L605" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M605" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N605" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O605" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="P605" t="n">
+        <v>0.2228</v>
+      </c>
+      <c r="Q605" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S605" t="n">
+        <v>-98.67</v>
+      </c>
+      <c r="T605" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>2377.37</t>
+        </is>
+      </c>
+      <c r="V605" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="W605" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="X605" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y605" t="inlineStr">
+        <is>
+          <t>trending up +23.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:43</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>70</v>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G606" t="n">
+        <v>76148</v>
+      </c>
+      <c r="H606" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I606" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K606" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L606" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M606" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N606" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O606" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P606" t="n">
+        <v>0.5296999999999999</v>
+      </c>
+      <c r="Q606" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="S606" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T606" t="n">
+        <v>106.74</v>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>76148.0</t>
+        </is>
+      </c>
+      <c r="V606" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="W606" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="X606" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y606" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:43</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>60</v>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G607" t="n">
+        <v>76148</v>
+      </c>
+      <c r="H607" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I607" t="n">
+        <v>1</v>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K607" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L607" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M607" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N607" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O607" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P607" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="Q607" t="n">
+        <v>-0.0113</v>
+      </c>
+      <c r="S607" t="n">
+        <v>-102.1</v>
+      </c>
+      <c r="T607" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>76148.0</t>
+        </is>
+      </c>
+      <c r="V607" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="W607" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="X607" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y607" t="inlineStr">
+        <is>
+          <t>trending up +17.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:43</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>220</v>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G608" t="n">
+        <v>2376.45</v>
+      </c>
+      <c r="H608" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I608" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K608" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L608" t="n">
+        <v>2390</v>
+      </c>
+      <c r="M608" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N608" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O608" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P608" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="Q608" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S608" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="T608" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>2376.45</t>
+        </is>
+      </c>
+      <c r="V608" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="W608" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="X608" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y608" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:43</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>220</v>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G609" t="n">
+        <v>2376.45</v>
+      </c>
+      <c r="H609" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I609" t="n">
+        <v>1</v>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K609" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L609" t="n">
+        <v>2390</v>
+      </c>
+      <c r="M609" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N609" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O609" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="P609" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="Q609" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S609" t="n">
+        <v>-98.25</v>
+      </c>
+      <c r="T609" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>2376.45</t>
+        </is>
+      </c>
+      <c r="V609" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="W609" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="X609" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y609" t="inlineStr">
+        <is>
+          <t>trending up +23.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:03</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>70</v>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G610" t="n">
+        <v>76090</v>
+      </c>
+      <c r="H610" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="I610" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K610" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L610" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M610" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N610" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O610" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P610" t="n">
+        <v>0.4678</v>
+      </c>
+      <c r="Q610" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="S610" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="T610" t="n">
+        <v>105.02</v>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>76090.0</t>
+        </is>
+      </c>
+      <c r="V610" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="W610" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="X610" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y610" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:03</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>60</v>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G611" t="n">
+        <v>76090</v>
+      </c>
+      <c r="H611" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="I611" t="n">
+        <v>1</v>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K611" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L611" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M611" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N611" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O611" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P611" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="Q611" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="S611" t="n">
+        <v>-105.57</v>
+      </c>
+      <c r="T611" t="n">
+        <v>105.57</v>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>76090.0</t>
+        </is>
+      </c>
+      <c r="V611" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="W611" t="n">
+        <v>-0.08799999999999999</v>
+      </c>
+      <c r="X611" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y611" t="inlineStr">
+        <is>
+          <t>trending up +17.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:03</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>220</v>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G612" t="n">
+        <v>2374.26</v>
+      </c>
+      <c r="H612" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I612" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K612" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L612" t="n">
+        <v>2390</v>
+      </c>
+      <c r="M612" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N612" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O612" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P612" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="Q612" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S612" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="T612" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>2374.26</t>
+        </is>
+      </c>
+      <c r="V612" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="W612" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="X612" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y612" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:03</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>220</v>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G613" t="n">
+        <v>2374.26</v>
+      </c>
+      <c r="H613" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I613" t="n">
+        <v>1</v>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K613" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L613" t="n">
+        <v>2390</v>
+      </c>
+      <c r="M613" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N613" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O613" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="P613" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="Q613" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S613" t="n">
+        <v>-101.31</v>
+      </c>
+      <c r="T613" t="n">
+        <v>101.31</v>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>2374.26</t>
+        </is>
+      </c>
+      <c r="V613" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="W613" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="X613" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y613" t="inlineStr">
+        <is>
+          <t>trending up +23.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>70</v>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G614" t="n">
+        <v>76096.5</v>
+      </c>
+      <c r="H614" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I614" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K614" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L614" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M614" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N614" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O614" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P614" t="n">
+        <v>0.4895</v>
+      </c>
+      <c r="Q614" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="S614" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="T614" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>76096.5</t>
+        </is>
+      </c>
+      <c r="V614" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="W614" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="X614" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y614" t="inlineStr">
+        <is>
+          <t>IV rank 76% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>60</v>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G615" t="n">
+        <v>76096.5</v>
+      </c>
+      <c r="H615" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I615" t="n">
+        <v>1</v>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K615" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L615" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M615" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N615" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O615" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P615" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="Q615" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="S615" t="n">
+        <v>-106.27</v>
+      </c>
+      <c r="T615" t="n">
+        <v>106.27</v>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>76096.5</t>
+        </is>
+      </c>
+      <c r="V615" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="W615" t="n">
+        <v>-0.188</v>
+      </c>
+      <c r="X615" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y615" t="inlineStr">
+        <is>
+          <t>trending up +17.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>210</v>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G616" t="n">
+        <v>2389.91</v>
+      </c>
+      <c r="H616" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I616" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K616" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L616" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M616" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N616" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O616" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P616" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="Q616" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S616" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="T616" t="n">
+        <v>100.42</v>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>2389.91</t>
+        </is>
+      </c>
+      <c r="V616" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="W616" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="X616" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y616" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>220</v>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G617" t="n">
+        <v>2389.91</v>
+      </c>
+      <c r="H617" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I617" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K617" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L617" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M617" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N617" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O617" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="P617" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="Q617" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S617" t="n">
+        <v>-98.27</v>
+      </c>
+      <c r="T617" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>2389.91</t>
+        </is>
+      </c>
+      <c r="V617" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W617" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="X617" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y617" t="inlineStr">
+        <is>
+          <t>trending up +24.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:40</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>70</v>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G618" t="n">
+        <v>76116.5</v>
+      </c>
+      <c r="H618" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="I618" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K618" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L618" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M618" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N618" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O618" t="n">
+        <v>0</v>
+      </c>
+      <c r="P618" t="n">
+        <v>0.9403</v>
+      </c>
+      <c r="Q618" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="S618" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="T618" t="n">
+        <v>103.94</v>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>76116.5</t>
+        </is>
+      </c>
+      <c r="V618" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="W618" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="X618" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y618" t="inlineStr">
+        <is>
+          <t>IV rank 81% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:40</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>70</v>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G619" t="n">
+        <v>76116.5</v>
+      </c>
+      <c r="H619" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="I619" t="n">
+        <v>1</v>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K619" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L619" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M619" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N619" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O619" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P619" t="n">
+        <v>1.2337</v>
+      </c>
+      <c r="Q619" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="S619" t="n">
+        <v>-103.1</v>
+      </c>
+      <c r="T619" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>76116.5</t>
+        </is>
+      </c>
+      <c r="V619" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="W619" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="X619" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y619" t="inlineStr">
+        <is>
+          <t>trending up +17.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:40</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>220</v>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G620" t="n">
+        <v>2390.71</v>
+      </c>
+      <c r="H620" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I620" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K620" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L620" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M620" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N620" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O620" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P620" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="Q620" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S620" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="T620" t="n">
+        <v>100.63</v>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>2390.71</t>
+        </is>
+      </c>
+      <c r="V620" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="W620" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="X620" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y620" t="inlineStr">
+        <is>
+          <t>IV rank 81% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:40</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>200</v>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G621" t="n">
+        <v>2390.71</v>
+      </c>
+      <c r="H621" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I621" t="n">
+        <v>1</v>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K621" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L621" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M621" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N621" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O621" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="P621" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="Q621" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S621" t="n">
+        <v>-100.78</v>
+      </c>
+      <c r="T621" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>2390.71</t>
+        </is>
+      </c>
+      <c r="V621" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W621" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="X621" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y621" t="inlineStr">
+        <is>
+          <t>trending up +24.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>70</v>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G622" t="n">
+        <v>75978</v>
+      </c>
+      <c r="H622" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="I622" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K622" t="n">
+        <v>1</v>
+      </c>
+      <c r="L622" t="n">
+        <v>76200</v>
+      </c>
+      <c r="M622" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N622" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O622" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P622" t="n">
+        <v>0.5743</v>
+      </c>
+      <c r="Q622" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="S622" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="T622" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>75978.0</t>
+        </is>
+      </c>
+      <c r="V622" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="W622" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="X622" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y622" t="inlineStr">
+        <is>
+          <t>IV rank 76% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>60</v>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G623" t="n">
+        <v>75978</v>
+      </c>
+      <c r="H623" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="I623" t="n">
+        <v>1</v>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K623" t="n">
+        <v>1</v>
+      </c>
+      <c r="L623" t="n">
+        <v>76200</v>
+      </c>
+      <c r="M623" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N623" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O623" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P623" t="n">
+        <v>0.8086</v>
+      </c>
+      <c r="Q623" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="S623" t="n">
+        <v>-101.25</v>
+      </c>
+      <c r="T623" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>75978.0</t>
+        </is>
+      </c>
+      <c r="V623" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="W623" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="X623" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y623" t="inlineStr">
+        <is>
+          <t>trending up +17.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>210</v>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G624" t="n">
+        <v>2388.34</v>
+      </c>
+      <c r="H624" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="I624" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K624" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L624" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M624" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N624" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O624" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P624" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="Q624" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S624" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="T624" t="n">
+        <v>98.03</v>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>2388.34</t>
+        </is>
+      </c>
+      <c r="V624" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="W624" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="X624" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y624" t="inlineStr">
+        <is>
+          <t>IV rank 76% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>210</v>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G625" t="n">
+        <v>2388.34</v>
+      </c>
+      <c r="H625" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="I625" t="n">
+        <v>1</v>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K625" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L625" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M625" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N625" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O625" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="P625" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="Q625" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S625" t="n">
+        <v>-102.12</v>
+      </c>
+      <c r="T625" t="n">
+        <v>102.12</v>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>2388.34</t>
+        </is>
+      </c>
+      <c r="V625" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="W625" t="n">
+        <v>-0.338</v>
+      </c>
+      <c r="X625" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y625" t="inlineStr">
+        <is>
+          <t>trending up +24.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:47</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>70</v>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G626" t="n">
+        <v>76548.10000000001</v>
+      </c>
+      <c r="H626" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I626" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K626" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L626" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M626" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N626" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O626" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P626" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="Q626" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="S626" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="T626" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>76548.1</t>
+        </is>
+      </c>
+      <c r="V626" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="W626" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="X626" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y626" t="inlineStr">
+        <is>
+          <t>IV rank 62% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:47</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>60</v>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G627" t="n">
+        <v>76548.10000000001</v>
+      </c>
+      <c r="H627" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I627" t="n">
+        <v>1</v>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K627" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L627" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M627" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N627" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O627" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P627" t="n">
+        <v>1.4771</v>
+      </c>
+      <c r="Q627" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="S627" t="n">
+        <v>-105.81</v>
+      </c>
+      <c r="T627" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>76548.1</t>
+        </is>
+      </c>
+      <c r="V627" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="W627" t="n">
+        <v>-0.409</v>
+      </c>
+      <c r="X627" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y627" t="inlineStr">
+        <is>
+          <t>trending up +18.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:47</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>230</v>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G628" t="n">
+        <v>2419.45</v>
+      </c>
+      <c r="H628" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="I628" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K628" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L628" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M628" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N628" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O628" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P628" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="Q628" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S628" t="n">
+        <v>13</v>
+      </c>
+      <c r="T628" t="n">
+        <v>102</v>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>2419.45</t>
+        </is>
+      </c>
+      <c r="V628" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="W628" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="X628" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y628" t="inlineStr">
+        <is>
+          <t>IV rank 71% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:47</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>230</v>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G629" t="n">
+        <v>2419.45</v>
+      </c>
+      <c r="H629" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="I629" t="n">
+        <v>1</v>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K629" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L629" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M629" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N629" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O629" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="P629" t="n">
+        <v>0.5981</v>
+      </c>
+      <c r="Q629" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S629" t="n">
+        <v>-99.25</v>
+      </c>
+      <c r="T629" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>2419.45</t>
+        </is>
+      </c>
+      <c r="V629" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="W629" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="X629" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y629" t="inlineStr">
+        <is>
+          <t>trending up +26.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-08-23T09:23</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>70</v>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G630" t="n">
+        <v>76539.89999999999</v>
+      </c>
+      <c r="H630" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I630" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K630" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L630" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M630" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N630" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O630" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P630" t="n">
+        <v>1.2468</v>
+      </c>
+      <c r="Q630" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="S630" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="T630" t="n">
+        <v>104.92</v>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>76539.9</t>
+        </is>
+      </c>
+      <c r="V630" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="W630" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="X630" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y630" t="inlineStr">
+        <is>
+          <t>IV rank 81% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-08-23T09:23</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>60</v>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G631" t="n">
+        <v>76539.89999999999</v>
+      </c>
+      <c r="H631" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I631" t="n">
+        <v>1</v>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K631" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L631" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M631" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N631" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O631" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P631" t="n">
+        <v>1.5336</v>
+      </c>
+      <c r="Q631" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="S631" t="n">
+        <v>-101.86</v>
+      </c>
+      <c r="T631" t="n">
+        <v>101.86</v>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>76539.9</t>
+        </is>
+      </c>
+      <c r="V631" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W631" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="X631" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y631" t="inlineStr">
+        <is>
+          <t>trending up +18.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-08-23T09:23</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>240</v>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G632" t="n">
+        <v>2411.05</v>
+      </c>
+      <c r="H632" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K632" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L632" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M632" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N632" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O632" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P632" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="Q632" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S632" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="T632" t="n">
+        <v>101.21</v>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>2411.05</t>
+        </is>
+      </c>
+      <c r="V632" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="W632" t="n">
+        <v>1.802</v>
+      </c>
+      <c r="X632" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y632" t="inlineStr">
+        <is>
+          <t>IV rank 57% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-08-23T09:23</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>200</v>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G633" t="n">
+        <v>2411.05</v>
+      </c>
+      <c r="H633" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I633" t="n">
+        <v>1</v>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K633" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L633" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M633" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N633" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O633" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="P633" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="Q633" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S633" t="n">
+        <v>-100.74</v>
+      </c>
+      <c r="T633" t="n">
+        <v>100.74</v>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>2411.05</t>
+        </is>
+      </c>
+      <c r="V633" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W633" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="X633" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y633" t="inlineStr">
+        <is>
+          <t>trending up +25.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-08-23T09:51</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>70</v>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G634" t="n">
+        <v>76618.5</v>
+      </c>
+      <c r="H634" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K634" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L634" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M634" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N634" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O634" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P634" t="n">
+        <v>1.2189</v>
+      </c>
+      <c r="Q634" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="S634" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T634" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="U634" t="inlineStr">
+        <is>
+          <t>76618.5</t>
+        </is>
+      </c>
+      <c r="V634" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="W634" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="X634" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y634" t="inlineStr">
+        <is>
+          <t>IV rank 48% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-08-23T09:51</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>60</v>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G635" t="n">
+        <v>76618.5</v>
+      </c>
+      <c r="H635" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I635" t="n">
+        <v>1</v>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K635" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L635" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M635" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N635" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O635" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P635" t="n">
+        <v>1.8489</v>
+      </c>
+      <c r="Q635" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="S635" t="n">
+        <v>-107.37</v>
+      </c>
+      <c r="T635" t="n">
+        <v>107.37</v>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>76618.5</t>
+        </is>
+      </c>
+      <c r="V635" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W635" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="X635" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y635" t="inlineStr">
+        <is>
+          <t>trending up +18.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-08-23T09:51</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>210</v>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G636" t="n">
+        <v>2415.05</v>
+      </c>
+      <c r="H636" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="I636" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K636" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L636" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M636" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N636" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O636" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P636" t="n">
+        <v>0.2138</v>
+      </c>
+      <c r="Q636" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="S636" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T636" t="n">
+        <v>101.77</v>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>2415.05</t>
+        </is>
+      </c>
+      <c r="V636" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="W636" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="X636" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y636" t="inlineStr">
+        <is>
+          <t>IV rank 43% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-08-23T09:51</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>170</v>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G637" t="n">
+        <v>2415.05</v>
+      </c>
+      <c r="H637" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="I637" t="n">
+        <v>1</v>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K637" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L637" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M637" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N637" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O637" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="P637" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="Q637" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S637" t="n">
+        <v>-101.13</v>
+      </c>
+      <c r="T637" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>2415.05</t>
+        </is>
+      </c>
+      <c r="V637" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="W637" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="X637" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y637" t="inlineStr">
+        <is>
+          <t>trending up +25.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-08-23T10:19</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>60</v>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G638" t="n">
+        <v>76661.10000000001</v>
+      </c>
+      <c r="H638" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K638" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L638" t="n">
+        <v>76600</v>
+      </c>
+      <c r="M638" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N638" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O638" t="n">
+        <v>0</v>
+      </c>
+      <c r="P638" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="Q638" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="S638" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T638" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>76661.1</t>
+        </is>
+      </c>
+      <c r="V638" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="W638" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="X638" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y638" t="inlineStr">
+        <is>
+          <t>IV rank 48% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-08-23T10:19</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>60</v>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G639" t="n">
+        <v>76661.10000000001</v>
+      </c>
+      <c r="H639" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I639" t="n">
+        <v>1</v>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K639" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L639" t="n">
+        <v>76600</v>
+      </c>
+      <c r="M639" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N639" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O639" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P639" t="n">
+        <v>1.8581</v>
+      </c>
+      <c r="Q639" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="S639" t="n">
+        <v>-108.77</v>
+      </c>
+      <c r="T639" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>76661.1</t>
+        </is>
+      </c>
+      <c r="V639" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="W639" t="n">
+        <v>-0.236</v>
+      </c>
+      <c r="X639" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y639" t="inlineStr">
+        <is>
+          <t>trending up +18.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-08-23T12:54</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>70</v>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G640" t="n">
+        <v>77161.60000000001</v>
+      </c>
+      <c r="H640" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="I640" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K640" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L640" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M640" t="n">
+        <v>76800</v>
+      </c>
+      <c r="N640" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O640" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P640" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="Q640" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="S640" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="T640" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="U640" t="inlineStr"/>
+      <c r="X640" t="inlineStr"/>
+      <c r="Y640" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-08-23T12:54</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>90</v>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G641" t="n">
+        <v>77161.60000000001</v>
+      </c>
+      <c r="H641" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="I641" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K641" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L641" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M641" t="n">
+        <v>76800</v>
+      </c>
+      <c r="N641" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O641" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P641" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="Q641" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="S641" t="n">
+        <v>-99.73999999999999</v>
+      </c>
+      <c r="T641" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="U641" t="inlineStr"/>
+      <c r="X641" t="inlineStr"/>
+      <c r="Y641" t="inlineStr">
+        <is>
+          <t>trending up +19.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-23T12:54</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>330</v>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G642" t="n">
+        <v>2424.52</v>
+      </c>
+      <c r="H642" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="I642" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K642" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L642" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M642" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N642" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O642" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P642" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="Q642" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S642" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="T642" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="U642" t="inlineStr"/>
+      <c r="X642" t="inlineStr"/>
+      <c r="Y642" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-08-23T12:54</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>400</v>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G643" t="n">
+        <v>2424.52</v>
+      </c>
+      <c r="H643" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="I643" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K643" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L643" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M643" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N643" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O643" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="P643" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q643" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="S643" t="n">
+        <v>-100.44</v>
+      </c>
+      <c r="T643" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="U643" t="inlineStr"/>
+      <c r="X643" t="inlineStr"/>
+      <c r="Y643" t="inlineStr">
+        <is>
+          <t>trending up +26.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -54010,22 +59154,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="C2" t="n">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="D2" t="n">
-        <v>3.69</v>
+        <v>4.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1132.07</v>
+        <v>1350.28</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1</v>
+        <v>4.43</v>
       </c>
       <c r="G2" t="n">
-        <v>113.21</v>
+        <v>135.03</v>
       </c>
     </row>
     <row r="3">
@@ -54110,22 +59254,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C6" t="n">
-        <v>69.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="E6" t="n">
-        <v>-393.27</v>
+        <v>-302.11</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.01</v>
+        <v>-2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>-39.33</v>
+        <v>-30.21</v>
       </c>
     </row>
     <row r="7">
@@ -54757,7 +59901,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22T12:51</t>
+          <t>2026-08-23T12:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -54767,16 +59911,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -54784,63 +59928,63 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>77274.5</v>
+        <v>77161.60000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>34.3</v>
+        <v>42.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.91</v>
+        <v>0.697</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.43</v>
+        <v>0.41</v>
       </c>
       <c r="L7" t="n">
         <v>77000</v>
       </c>
       <c r="M7" t="n">
-        <v>72800</v>
+        <v>76800</v>
       </c>
       <c r="N7" t="n">
-        <v>82800</v>
+        <v>82000</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0004</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1535</v>
+        <v>0.2015</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0102</v>
+        <v>-0.0097</v>
       </c>
       <c r="S7" t="n">
-        <v>-102.38</v>
+        <v>13.22</v>
       </c>
       <c r="T7" t="n">
-        <v>102.38</v>
+        <v>98.78</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>trending up +19.8% — skewed fly</t>
+          <t>IV rank 95% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-22T12:51</t>
+          <t>2026-08-23T12:54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -54850,11 +59994,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -54862,63 +60006,63 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2428.29</v>
+        <v>77161.60000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>51.65</v>
+        <v>42.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.827</v>
+        <v>0.84</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.08</v>
+        <v>0.41</v>
       </c>
       <c r="L8" t="n">
-        <v>2420</v>
+        <v>77000</v>
       </c>
       <c r="M8" t="n">
-        <v>2300</v>
+        <v>76800</v>
       </c>
       <c r="N8" t="n">
-        <v>2640</v>
+        <v>82000</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0028</v>
+        <v>-0.0004</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0239</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.001</v>
+        <v>-0.0055</v>
       </c>
       <c r="S8" t="n">
-        <v>-101.02</v>
+        <v>-99.73999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>101.02</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>trending up +26.9% — skewed fly</t>
+          <t>trending up +19.1% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-22T16:52</t>
+          <t>2026-08-23T12:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -54928,11 +60072,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -54940,58 +60084,58 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>77332.8</v>
+        <v>2424.52</v>
       </c>
       <c r="H9" t="n">
-        <v>25.35</v>
+        <v>59.8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.627</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.37</v>
+        <v>0.29</v>
       </c>
       <c r="L9" t="n">
-        <v>77000</v>
+        <v>2420</v>
       </c>
       <c r="M9" t="n">
-        <v>75000</v>
+        <v>2340</v>
       </c>
       <c r="N9" t="n">
-        <v>82800</v>
+        <v>2720</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2024</v>
+        <v>0.0859</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0124</v>
+        <v>-0.0028</v>
       </c>
       <c r="S9" t="n">
-        <v>9.82</v>
+        <v>31.35</v>
       </c>
       <c r="T9" t="n">
-        <v>102.18</v>
+        <v>100.65</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>IV rank 85% rich — sell premium</t>
+          <t>IV rank 95% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-22T17:16</t>
+          <t>2026-08-23T12:54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -55001,16 +60145,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -55018,51 +60162,51 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2425.5</v>
+        <v>2424.52</v>
       </c>
       <c r="H10" t="n">
-        <v>38.3</v>
+        <v>59.8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.749</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.29</v>
       </c>
       <c r="L10" t="n">
         <v>2420</v>
       </c>
       <c r="M10" t="n">
-        <v>2300</v>
+        <v>2340</v>
       </c>
       <c r="N10" t="n">
-        <v>2640</v>
+        <v>2720</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0002</v>
+        <v>-0.0021</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0963</v>
+        <v>0.0231</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0035</v>
+        <v>-0.0009</v>
       </c>
       <c r="S10" t="n">
-        <v>19.71</v>
+        <v>-100.44</v>
       </c>
       <c r="T10" t="n">
-        <v>100.29</v>
+        <v>100.44</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>IV rank 85% rich — sell premium</t>
+          <t>trending up +26.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -55083,7 +60227,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-22T20:10:45.283840 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-23T20:10:18.025069 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y643"/>
+  <dimension ref="A1:Y695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -47285,7 +47285,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G514" t="n">
@@ -47297,8 +47297,22 @@
       <c r="T514" t="n">
         <v>10</v>
       </c>
-      <c r="U514" t="inlineStr"/>
-      <c r="X514" t="inlineStr"/>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>4633.88</t>
+        </is>
+      </c>
+      <c r="V514" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="W514" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="Y514" t="inlineStr">
         <is>
           <t>20/50 EMA 3rd retest</t>
@@ -50091,7 +50105,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G545" t="n">
@@ -50136,7 +50150,17 @@
         <v>98.05</v>
       </c>
       <c r="U545" t="inlineStr"/>
-      <c r="X545" t="inlineStr"/>
+      <c r="V545" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W545" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="Y545" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -58801,7 +58825,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G640" t="n">
@@ -58845,8 +58869,22 @@
       <c r="T640" t="n">
         <v>98.78</v>
       </c>
-      <c r="U640" t="inlineStr"/>
-      <c r="X640" t="inlineStr"/>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>77201.0</t>
+        </is>
+      </c>
+      <c r="V640" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="W640" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X640" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="Y640" t="inlineStr">
         <is>
           <t>IV rank 95% rich — sell premium</t>
@@ -58879,7 +58917,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G641" t="n">
@@ -58923,8 +58961,22 @@
       <c r="T641" t="n">
         <v>99.73999999999999</v>
       </c>
-      <c r="U641" t="inlineStr"/>
-      <c r="X641" t="inlineStr"/>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>77201.0</t>
+        </is>
+      </c>
+      <c r="V641" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="W641" t="n">
+        <v>-0.394</v>
+      </c>
+      <c r="X641" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="Y641" t="inlineStr">
         <is>
           <t>trending up +19.1% — skewed fly</t>
@@ -58957,7 +59009,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G642" t="n">
@@ -59001,8 +59053,22 @@
       <c r="T642" t="n">
         <v>100.65</v>
       </c>
-      <c r="U642" t="inlineStr"/>
-      <c r="X642" t="inlineStr"/>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>2438.78</t>
+        </is>
+      </c>
+      <c r="V642" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="W642" t="n">
+        <v>2.828</v>
+      </c>
+      <c r="X642" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="Y642" t="inlineStr">
         <is>
           <t>IV rank 95% rich — sell premium</t>
@@ -59035,7 +59101,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G643" t="n">
@@ -59080,10 +59146,4718 @@
         <v>100.44</v>
       </c>
       <c r="U643" t="inlineStr"/>
-      <c r="X643" t="inlineStr"/>
+      <c r="V643" t="n">
+        <v>-55.6</v>
+      </c>
+      <c r="W643" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="X643" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="Y643" t="inlineStr">
         <is>
           <t>trending up +26.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-08-23T21:44</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>410</v>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G644" t="n">
+        <v>2461.74</v>
+      </c>
+      <c r="H644" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="I644" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K644" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L644" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M644" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N644" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O644" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="P644" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q644" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="S644" t="n">
+        <v>-100.25</v>
+      </c>
+      <c r="T644" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>2438.78</t>
+        </is>
+      </c>
+      <c r="V644" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="W644" t="n">
+        <v>4.904</v>
+      </c>
+      <c r="X644" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y644" t="inlineStr">
+        <is>
+          <t>trending up +28.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-08-24T02:49</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>80</v>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G645" t="n">
+        <v>77301.10000000001</v>
+      </c>
+      <c r="H645" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="I645" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K645" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L645" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M645" t="n">
+        <v>74800</v>
+      </c>
+      <c r="N645" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O645" t="n">
+        <v>0</v>
+      </c>
+      <c r="P645" t="n">
+        <v>0.5518999999999999</v>
+      </c>
+      <c r="Q645" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="S645" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="T645" t="n">
+        <v>97.03</v>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>77301.1</t>
+        </is>
+      </c>
+      <c r="V645" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W645" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X645" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y645" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-08-24T02:49</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>70</v>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G646" t="n">
+        <v>77301.10000000001</v>
+      </c>
+      <c r="H646" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="I646" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K646" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L646" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M646" t="n">
+        <v>74800</v>
+      </c>
+      <c r="N646" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O646" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P646" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="Q646" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="S646" t="n">
+        <v>-100.02</v>
+      </c>
+      <c r="T646" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>77301.1</t>
+        </is>
+      </c>
+      <c r="V646" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="W646" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="X646" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y646" t="inlineStr">
+        <is>
+          <t>trending up +11.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-24T02:49</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>240</v>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G647" t="n">
+        <v>2438.96</v>
+      </c>
+      <c r="H647" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="I647" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K647" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L647" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M647" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N647" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O647" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P647" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="Q647" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S647" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="T647" t="n">
+        <v>101.09</v>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>2438.96</t>
+        </is>
+      </c>
+      <c r="V647" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="W647" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="X647" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y647" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-08-24T02:49</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>360</v>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G648" t="n">
+        <v>2438.96</v>
+      </c>
+      <c r="H648" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="I648" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K648" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L648" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M648" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N648" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O648" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="P648" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="Q648" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S648" t="n">
+        <v>-100.66</v>
+      </c>
+      <c r="T648" t="n">
+        <v>100.66</v>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>2438.96</t>
+        </is>
+      </c>
+      <c r="V648" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="W648" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="X648" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y648" t="inlineStr">
+        <is>
+          <t>trending up +8.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-08-24T03:51</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>70</v>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G649" t="n">
+        <v>77130.8</v>
+      </c>
+      <c r="H649" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="I649" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K649" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L649" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M649" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N649" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O649" t="n">
+        <v>0</v>
+      </c>
+      <c r="P649" t="n">
+        <v>0.6395999999999999</v>
+      </c>
+      <c r="Q649" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="S649" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="T649" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>77130.8</t>
+        </is>
+      </c>
+      <c r="V649" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="W649" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="X649" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y649" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-08-24T03:51</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>70</v>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G650" t="n">
+        <v>77130.8</v>
+      </c>
+      <c r="H650" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="I650" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K650" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L650" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M650" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N650" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O650" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P650" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="Q650" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="S650" t="n">
+        <v>-101.67</v>
+      </c>
+      <c r="T650" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>77130.8</t>
+        </is>
+      </c>
+      <c r="V650" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="W650" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="X650" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y650" t="inlineStr">
+        <is>
+          <t>trending up +11.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-08-24T03:51</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>240</v>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G651" t="n">
+        <v>2440.26</v>
+      </c>
+      <c r="H651" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="I651" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K651" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L651" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M651" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N651" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O651" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P651" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="Q651" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S651" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="T651" t="n">
+        <v>101.66</v>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>2440.26</t>
+        </is>
+      </c>
+      <c r="V651" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="W651" t="n">
+        <v>1.735</v>
+      </c>
+      <c r="X651" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y651" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-08-24T03:51</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>310</v>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G652" t="n">
+        <v>2440.26</v>
+      </c>
+      <c r="H652" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="I652" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K652" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L652" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M652" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N652" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O652" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="P652" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="Q652" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="S652" t="n">
+        <v>-100.41</v>
+      </c>
+      <c r="T652" t="n">
+        <v>100.41</v>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>2440.26</t>
+        </is>
+      </c>
+      <c r="V652" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W652" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X652" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y652" t="inlineStr">
+        <is>
+          <t>trending up +8.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-08-24T04:40</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>70</v>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G653" t="n">
+        <v>77149.10000000001</v>
+      </c>
+      <c r="H653" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="I653" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K653" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L653" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M653" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N653" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O653" t="n">
+        <v>0</v>
+      </c>
+      <c r="P653" t="n">
+        <v>0.6562</v>
+      </c>
+      <c r="Q653" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="S653" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="T653" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>77149.1</t>
+        </is>
+      </c>
+      <c r="V653" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="W653" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="X653" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y653" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-08-24T04:40</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>60</v>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G654" t="n">
+        <v>77149.10000000001</v>
+      </c>
+      <c r="H654" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="I654" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K654" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L654" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M654" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N654" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O654" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P654" t="n">
+        <v>0.7204</v>
+      </c>
+      <c r="Q654" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="S654" t="n">
+        <v>-92.93000000000001</v>
+      </c>
+      <c r="T654" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>77149.1</t>
+        </is>
+      </c>
+      <c r="V654" t="n">
+        <v>8</v>
+      </c>
+      <c r="W654" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X654" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y654" t="inlineStr">
+        <is>
+          <t>trending up +11.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-08-24T04:40</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>240</v>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G655" t="n">
+        <v>2441.88</v>
+      </c>
+      <c r="H655" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="I655" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K655" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L655" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M655" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N655" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O655" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P655" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="Q655" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S655" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="T655" t="n">
+        <v>102.12</v>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>2441.88</t>
+        </is>
+      </c>
+      <c r="V655" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="W655" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X655" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y655" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-08-24T04:40</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>310</v>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G656" t="n">
+        <v>2441.88</v>
+      </c>
+      <c r="H656" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="I656" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K656" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L656" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M656" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N656" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O656" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="P656" t="n">
+        <v>0.1246</v>
+      </c>
+      <c r="Q656" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="S656" t="n">
+        <v>-100.28</v>
+      </c>
+      <c r="T656" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>2441.88</t>
+        </is>
+      </c>
+      <c r="V656" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="W656" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="X656" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y656" t="inlineStr">
+        <is>
+          <t>trending up +8.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:24</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>80</v>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G657" t="n">
+        <v>77108</v>
+      </c>
+      <c r="H657" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="I657" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K657" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L657" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M657" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N657" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O657" t="n">
+        <v>0</v>
+      </c>
+      <c r="P657" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="Q657" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="S657" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="T657" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U657" t="inlineStr">
+        <is>
+          <t>77108.0</t>
+        </is>
+      </c>
+      <c r="V657" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="W657" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="X657" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y657" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:24</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>70</v>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G658" t="n">
+        <v>77108</v>
+      </c>
+      <c r="H658" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="I658" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K658" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L658" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M658" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N658" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O658" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P658" t="n">
+        <v>0.6152</v>
+      </c>
+      <c r="Q658" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="S658" t="n">
+        <v>-105.34</v>
+      </c>
+      <c r="T658" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>77108.0</t>
+        </is>
+      </c>
+      <c r="V658" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W658" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="X658" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y658" t="inlineStr">
+        <is>
+          <t>trending up +11.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:24</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>230</v>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G659" t="n">
+        <v>2451.29</v>
+      </c>
+      <c r="H659" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="I659" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K659" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L659" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M659" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N659" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O659" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P659" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="Q659" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S659" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="T659" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>2451.29</t>
+        </is>
+      </c>
+      <c r="V659" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="W659" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="X659" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y659" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:24</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>310</v>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G660" t="n">
+        <v>2451.29</v>
+      </c>
+      <c r="H660" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="I660" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K660" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L660" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M660" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N660" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O660" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="P660" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="Q660" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S660" t="n">
+        <v>-100.07</v>
+      </c>
+      <c r="T660" t="n">
+        <v>100.07</v>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>2451.29</t>
+        </is>
+      </c>
+      <c r="V660" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="W660" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="X660" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y660" t="inlineStr">
+        <is>
+          <t>trending up +8.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-08-24T06:02</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>80</v>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G661" t="n">
+        <v>77105.10000000001</v>
+      </c>
+      <c r="H661" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="I661" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K661" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L661" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M661" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N661" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O661" t="n">
+        <v>0</v>
+      </c>
+      <c r="P661" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="Q661" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="S661" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="T661" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="U661" t="inlineStr">
+        <is>
+          <t>77105.1</t>
+        </is>
+      </c>
+      <c r="V661" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="W661" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="X661" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y661" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-08-24T06:02</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>60</v>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G662" t="n">
+        <v>77105.10000000001</v>
+      </c>
+      <c r="H662" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="I662" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K662" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L662" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M662" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N662" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O662" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P662" t="n">
+        <v>0.8689</v>
+      </c>
+      <c r="Q662" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="S662" t="n">
+        <v>-97.15000000000001</v>
+      </c>
+      <c r="T662" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>77105.1</t>
+        </is>
+      </c>
+      <c r="V662" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="W662" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="X662" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y662" t="inlineStr">
+        <is>
+          <t>trending up +11.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-08-24T06:02</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>230</v>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G663" t="n">
+        <v>2447.53</v>
+      </c>
+      <c r="H663" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="I663" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K663" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L663" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M663" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N663" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O663" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P663" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="Q663" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S663" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="T663" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>2447.53</t>
+        </is>
+      </c>
+      <c r="V663" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="W663" t="n">
+        <v>1.541</v>
+      </c>
+      <c r="X663" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y663" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-08-24T06:02</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>290</v>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G664" t="n">
+        <v>2447.53</v>
+      </c>
+      <c r="H664" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="I664" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K664" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L664" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M664" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N664" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O664" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="P664" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="Q664" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S664" t="n">
+        <v>-99.81999999999999</v>
+      </c>
+      <c r="T664" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>2447.53</t>
+        </is>
+      </c>
+      <c r="V664" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="W664" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="X664" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y664" t="inlineStr">
+        <is>
+          <t>trending up +8.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-08-24T07:19</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>70</v>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G665" t="n">
+        <v>77630.60000000001</v>
+      </c>
+      <c r="H665" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="I665" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K665" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L665" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M665" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N665" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O665" t="n">
+        <v>0</v>
+      </c>
+      <c r="P665" t="n">
+        <v>0.8722</v>
+      </c>
+      <c r="Q665" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="S665" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="T665" t="n">
+        <v>103.59</v>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>77630.6</t>
+        </is>
+      </c>
+      <c r="V665" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="W665" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="X665" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y665" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-08-24T07:19</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>60</v>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G666" t="n">
+        <v>77630.60000000001</v>
+      </c>
+      <c r="H666" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="I666" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K666" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L666" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M666" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N666" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O666" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P666" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="Q666" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="S666" t="n">
+        <v>-95.75</v>
+      </c>
+      <c r="T666" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>77630.6</t>
+        </is>
+      </c>
+      <c r="V666" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W666" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="X666" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y666" t="inlineStr">
+        <is>
+          <t>trending up +12.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-08-24T07:19</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>230</v>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G667" t="n">
+        <v>2463.88</v>
+      </c>
+      <c r="H667" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="I667" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K667" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L667" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M667" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N667" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O667" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P667" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="Q667" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S667" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="T667" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>2463.88</t>
+        </is>
+      </c>
+      <c r="V667" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W667" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X667" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y667" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-08-24T07:19</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>270</v>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G668" t="n">
+        <v>2463.88</v>
+      </c>
+      <c r="H668" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="I668" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K668" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L668" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M668" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N668" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O668" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="P668" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="Q668" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S668" t="n">
+        <v>-100.2</v>
+      </c>
+      <c r="T668" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>2463.88</t>
+        </is>
+      </c>
+      <c r="V668" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="W668" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="X668" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y668" t="inlineStr">
+        <is>
+          <t>trending up +9.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-08-24T08:10</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>70</v>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G669" t="n">
+        <v>77332.10000000001</v>
+      </c>
+      <c r="H669" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="I669" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K669" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L669" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M669" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N669" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O669" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P669" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="Q669" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="S669" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="T669" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>77332.1</t>
+        </is>
+      </c>
+      <c r="V669" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="W669" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="X669" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y669" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-08-24T08:10</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>60</v>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G670" t="n">
+        <v>77332.10000000001</v>
+      </c>
+      <c r="H670" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="I670" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K670" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L670" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M670" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N670" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O670" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P670" t="n">
+        <v>1.1078</v>
+      </c>
+      <c r="Q670" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="S670" t="n">
+        <v>-102.67</v>
+      </c>
+      <c r="T670" t="n">
+        <v>102.67</v>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>77332.1</t>
+        </is>
+      </c>
+      <c r="V670" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="W670" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="X670" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y670" t="inlineStr">
+        <is>
+          <t>trending up +11.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-08-24T08:10</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>220</v>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G671" t="n">
+        <v>2453.36</v>
+      </c>
+      <c r="H671" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="I671" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K671" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L671" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M671" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N671" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O671" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P671" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="Q671" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S671" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="T671" t="n">
+        <v>100.23</v>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>2453.36</t>
+        </is>
+      </c>
+      <c r="V671" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="W671" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="X671" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y671" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-08-24T08:10</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>250</v>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G672" t="n">
+        <v>2453.36</v>
+      </c>
+      <c r="H672" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="I672" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K672" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L672" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M672" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N672" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O672" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="P672" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="Q672" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S672" t="n">
+        <v>-98.67</v>
+      </c>
+      <c r="T672" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>2453.36</t>
+        </is>
+      </c>
+      <c r="V672" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="W672" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="X672" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y672" t="inlineStr">
+        <is>
+          <t>trending up +8.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-08-24T09:03</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>70</v>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G673" t="n">
+        <v>77109.8</v>
+      </c>
+      <c r="H673" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I673" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K673" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L673" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M673" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N673" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O673" t="n">
+        <v>0</v>
+      </c>
+      <c r="P673" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="Q673" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="S673" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="T673" t="n">
+        <v>106.06</v>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>77109.8</t>
+        </is>
+      </c>
+      <c r="V673" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="W673" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="X673" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y673" t="inlineStr">
+        <is>
+          <t>IV rank 82% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-08-24T09:03</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>50</v>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G674" t="n">
+        <v>77109.8</v>
+      </c>
+      <c r="H674" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I674" t="n">
+        <v>1</v>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K674" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L674" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M674" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N674" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O674" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P674" t="n">
+        <v>1.4414</v>
+      </c>
+      <c r="Q674" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="S674" t="n">
+        <v>-95</v>
+      </c>
+      <c r="T674" t="n">
+        <v>95</v>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>77109.8</t>
+        </is>
+      </c>
+      <c r="V674" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="W674" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="X674" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y674" t="inlineStr">
+        <is>
+          <t>trending up +11.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-08-24T09:03</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>220</v>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G675" t="n">
+        <v>2457.46</v>
+      </c>
+      <c r="H675" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="I675" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K675" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L675" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M675" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N675" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O675" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P675" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="Q675" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S675" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="T675" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>2457.46</t>
+        </is>
+      </c>
+      <c r="V675" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="W675" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="X675" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y675" t="inlineStr">
+        <is>
+          <t>IV rank 82% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-08-24T09:03</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>220</v>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G676" t="n">
+        <v>2457.46</v>
+      </c>
+      <c r="H676" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="I676" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K676" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L676" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M676" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N676" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O676" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="P676" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="Q676" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S676" t="n">
+        <v>-100.39</v>
+      </c>
+      <c r="T676" t="n">
+        <v>100.39</v>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>2457.46</t>
+        </is>
+      </c>
+      <c r="V676" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="W676" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="X676" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y676" t="inlineStr">
+        <is>
+          <t>trending up +9.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:02</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>70</v>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G677" t="n">
+        <v>77552.5</v>
+      </c>
+      <c r="H677" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I677" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K677" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L677" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M677" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N677" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O677" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P677" t="n">
+        <v>1.2983</v>
+      </c>
+      <c r="Q677" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="S677" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="T677" t="n">
+        <v>106.67</v>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>77552.5</t>
+        </is>
+      </c>
+      <c r="V677" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W677" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="X677" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y677" t="inlineStr">
+        <is>
+          <t>IV rank 82% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:02</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>50</v>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G678" t="n">
+        <v>77552.5</v>
+      </c>
+      <c r="H678" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I678" t="n">
+        <v>1</v>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K678" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L678" t="n">
+        <v>77400</v>
+      </c>
+      <c r="M678" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N678" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O678" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P678" t="n">
+        <v>1.6624</v>
+      </c>
+      <c r="Q678" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="S678" t="n">
+        <v>-96.38</v>
+      </c>
+      <c r="T678" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>77552.5</t>
+        </is>
+      </c>
+      <c r="V678" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="W678" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="X678" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y678" t="inlineStr">
+        <is>
+          <t>trending up +11.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:02</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>210</v>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G679" t="n">
+        <v>2464.75</v>
+      </c>
+      <c r="H679" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I679" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K679" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L679" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M679" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N679" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O679" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P679" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="Q679" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S679" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T679" t="n">
+        <v>101.77</v>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>2464.75</t>
+        </is>
+      </c>
+      <c r="V679" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W679" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="X679" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y679" t="inlineStr">
+        <is>
+          <t>IV rank 77% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:02</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>200</v>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G680" t="n">
+        <v>2464.75</v>
+      </c>
+      <c r="H680" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I680" t="n">
+        <v>1</v>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K680" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L680" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M680" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N680" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O680" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="P680" t="n">
+        <v>0.6722</v>
+      </c>
+      <c r="Q680" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S680" t="n">
+        <v>-100.46</v>
+      </c>
+      <c r="T680" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>2464.75</t>
+        </is>
+      </c>
+      <c r="V680" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="W680" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="X680" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y680" t="inlineStr">
+        <is>
+          <t>trending up +9.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:52</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>60</v>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G681" t="n">
+        <v>77606.5</v>
+      </c>
+      <c r="H681" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I681" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K681" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L681" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M681" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N681" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O681" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P681" t="n">
+        <v>1.6548</v>
+      </c>
+      <c r="Q681" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="S681" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T681" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>77606.5</t>
+        </is>
+      </c>
+      <c r="V681" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="W681" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="X681" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y681" t="inlineStr">
+        <is>
+          <t>IV rank 68% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:52</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>50</v>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G682" t="n">
+        <v>77606.5</v>
+      </c>
+      <c r="H682" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I682" t="n">
+        <v>1</v>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K682" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L682" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M682" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N682" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O682" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P682" t="n">
+        <v>2.4671</v>
+      </c>
+      <c r="Q682" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="S682" t="n">
+        <v>-93.48999999999999</v>
+      </c>
+      <c r="T682" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>77606.5</t>
+        </is>
+      </c>
+      <c r="V682" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="W682" t="n">
+        <v>-0.231</v>
+      </c>
+      <c r="X682" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y682" t="inlineStr">
+        <is>
+          <t>trending up +12.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:52</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>210</v>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G683" t="n">
+        <v>2461.79</v>
+      </c>
+      <c r="H683" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I683" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K683" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L683" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M683" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N683" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O683" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P683" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="Q683" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="S683" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T683" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="U683" t="inlineStr">
+        <is>
+          <t>2461.79</t>
+        </is>
+      </c>
+      <c r="V683" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W683" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="X683" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y683" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:52</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>180</v>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G684" t="n">
+        <v>2461.79</v>
+      </c>
+      <c r="H684" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I684" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K684" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L684" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M684" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N684" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O684" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="P684" t="n">
+        <v>0.7033</v>
+      </c>
+      <c r="Q684" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S684" t="n">
+        <v>-98.75</v>
+      </c>
+      <c r="T684" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="U684" t="inlineStr">
+        <is>
+          <t>2461.79</t>
+        </is>
+      </c>
+      <c r="V684" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="W684" t="n">
+        <v>-0.288</v>
+      </c>
+      <c r="X684" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y684" t="inlineStr">
+        <is>
+          <t>trending up +9.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:52</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>240</v>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G685" t="n">
+        <v>2461.79</v>
+      </c>
+      <c r="H685" t="n">
+        <v>65</v>
+      </c>
+      <c r="I685" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K685" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L685" t="n">
+        <v>2350</v>
+      </c>
+      <c r="M685" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N685" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O685" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P685" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="Q685" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S685" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="T685" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="U685" t="inlineStr"/>
+      <c r="X685" t="inlineStr"/>
+      <c r="Y685" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-08-24T11:22</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>60</v>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G686" t="n">
+        <v>77869.89999999999</v>
+      </c>
+      <c r="H686" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I686" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K686" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L686" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M686" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N686" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O686" t="n">
+        <v>0</v>
+      </c>
+      <c r="P686" t="n">
+        <v>1.569</v>
+      </c>
+      <c r="Q686" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S686" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T686" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="U686" t="inlineStr">
+        <is>
+          <t>77869.9</t>
+        </is>
+      </c>
+      <c r="V686" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W686" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="X686" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y686" t="inlineStr">
+        <is>
+          <t>IV rank 27% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-08-24T11:22</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>50</v>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G687" t="n">
+        <v>77869.89999999999</v>
+      </c>
+      <c r="H687" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I687" t="n">
+        <v>1</v>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K687" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L687" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M687" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N687" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O687" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P687" t="n">
+        <v>3.3562</v>
+      </c>
+      <c r="Q687" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="S687" t="n">
+        <v>-100.21</v>
+      </c>
+      <c r="T687" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>77869.9</t>
+        </is>
+      </c>
+      <c r="V687" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="W687" t="n">
+        <v>-0.276</v>
+      </c>
+      <c r="X687" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y687" t="inlineStr">
+        <is>
+          <t>trending up +12.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:39</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>70</v>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G688" t="n">
+        <v>78739.39999999999</v>
+      </c>
+      <c r="H688" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="I688" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K688" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L688" t="n">
+        <v>78200</v>
+      </c>
+      <c r="M688" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N688" t="n">
+        <v>81200</v>
+      </c>
+      <c r="O688" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P688" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="Q688" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="S688" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="T688" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="U688" t="inlineStr"/>
+      <c r="V688" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="W688" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="X688" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y688" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:39</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>100</v>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G689" t="n">
+        <v>78739.39999999999</v>
+      </c>
+      <c r="H689" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="I689" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K689" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L689" t="n">
+        <v>78200</v>
+      </c>
+      <c r="M689" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N689" t="n">
+        <v>81200</v>
+      </c>
+      <c r="O689" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P689" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="Q689" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S689" t="n">
+        <v>-103.16</v>
+      </c>
+      <c r="T689" t="n">
+        <v>103.16</v>
+      </c>
+      <c r="U689" t="inlineStr"/>
+      <c r="X689" t="inlineStr"/>
+      <c r="Y689" t="inlineStr">
+        <is>
+          <t>trending up +13.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:39</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>200</v>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G690" t="n">
+        <v>2500.25</v>
+      </c>
+      <c r="H690" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K690" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L690" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M690" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N690" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O690" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P690" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="Q690" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S690" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="T690" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="U690" t="inlineStr"/>
+      <c r="V690" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="W690" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="X690" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y690" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:39</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>360</v>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G691" t="n">
+        <v>2500.25</v>
+      </c>
+      <c r="H691" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="I691" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K691" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L691" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M691" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N691" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O691" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="P691" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="Q691" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="S691" t="n">
+        <v>-98.68000000000001</v>
+      </c>
+      <c r="T691" t="n">
+        <v>98.68000000000001</v>
+      </c>
+      <c r="U691" t="inlineStr"/>
+      <c r="X691" t="inlineStr"/>
+      <c r="Y691" t="inlineStr">
+        <is>
+          <t>trending up +11.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-08-24T14:25</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>70</v>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G692" t="n">
+        <v>79017.60000000001</v>
+      </c>
+      <c r="H692" t="n">
+        <v>47</v>
+      </c>
+      <c r="I692" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K692" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="L692" t="n">
+        <v>78800</v>
+      </c>
+      <c r="M692" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N692" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O692" t="n">
+        <v>0</v>
+      </c>
+      <c r="P692" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="Q692" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="S692" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="T692" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U692" t="inlineStr"/>
+      <c r="V692" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="W692" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="X692" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y692" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-08-24T16:31</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>190</v>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G693" t="n">
+        <v>2499.42</v>
+      </c>
+      <c r="H693" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="I693" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K693" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L693" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M693" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N693" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O693" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P693" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="Q693" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S693" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="T693" t="n">
+        <v>98.63</v>
+      </c>
+      <c r="U693" t="inlineStr"/>
+      <c r="V693" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="W693" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="X693" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Y693" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-08-24T17:49</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>310</v>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G694" t="n">
+        <v>2464.91</v>
+      </c>
+      <c r="H694" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="I694" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K694" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L694" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M694" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N694" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O694" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P694" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="Q694" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S694" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="T694" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="U694" t="inlineStr"/>
+      <c r="X694" t="inlineStr"/>
+      <c r="Y694" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-08-24T19:17</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>70</v>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G695" t="n">
+        <v>78922.5</v>
+      </c>
+      <c r="H695" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="I695" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K695" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L695" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M695" t="n">
+        <v>75200</v>
+      </c>
+      <c r="N695" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O695" t="n">
+        <v>0</v>
+      </c>
+      <c r="P695" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="Q695" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="S695" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="T695" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="U695" t="inlineStr"/>
+      <c r="X695" t="inlineStr"/>
+      <c r="Y695" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -59154,22 +63928,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="C2" t="n">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2</v>
+        <v>4.87</v>
       </c>
       <c r="E2" t="n">
-        <v>1350.28</v>
+        <v>1629.17</v>
       </c>
       <c r="F2" t="n">
-        <v>4.43</v>
+        <v>4.91</v>
       </c>
       <c r="G2" t="n">
-        <v>135.03</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="3">
@@ -59179,22 +63953,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="E3" t="n">
-        <v>-37.76</v>
+        <v>-15.88</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.55</v>
+        <v>-2.65</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.78</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="4">
@@ -59229,22 +64003,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="E5" t="n">
-        <v>-181.25</v>
+        <v>-170.55</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.1</v>
+        <v>-13.12</v>
       </c>
       <c r="G5" t="n">
-        <v>-18.12</v>
+        <v>-17.05</v>
       </c>
     </row>
     <row r="6">
@@ -59254,22 +64028,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>68.8</v>
+        <v>68.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="E6" t="n">
-        <v>-302.11</v>
+        <v>-236.33</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.42</v>
+        <v>-1.59</v>
       </c>
       <c r="G6" t="n">
-        <v>-30.21</v>
+        <v>-23.63</v>
       </c>
     </row>
     <row r="7">
@@ -59383,7 +64157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -59777,26 +64551,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21T23:20</t>
+          <t>2026-08-24T10:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XAUTUSD</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gold_ema</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>perpetual</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -59804,45 +64578,77 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4590.36</v>
+        <v>2461.79</v>
+      </c>
+      <c r="H5" t="n">
+        <v>65</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2350</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>98.3</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>20/50 EMA 3rd retest</t>
+          <t>IV rank 100% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-22T06:01</t>
+          <t>2026-08-24T12:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -59850,13 +64656,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2443.63</v>
+        <v>78739.39999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>70.65000000000001</v>
+        <v>53.85</v>
       </c>
       <c r="I6" t="n">
-        <v>0.678</v>
+        <v>0.771</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -59864,63 +64670,63 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="L6" t="n">
-        <v>2300</v>
+        <v>78200</v>
       </c>
       <c r="M6" t="n">
-        <v>1700</v>
+        <v>76000</v>
       </c>
       <c r="N6" t="n">
-        <v>2700</v>
+        <v>81200</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0132</v>
+        <v>0.0495</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0026</v>
+        <v>-0.0039</v>
       </c>
       <c r="S6" t="n">
-        <v>26.95</v>
+        <v>-103.16</v>
       </c>
       <c r="T6" t="n">
-        <v>98.05</v>
+        <v>103.16</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
+          <t>trending up +13.6% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23T12:54</t>
+          <t>2026-08-24T12:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>360</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -59928,77 +64734,77 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>77161.60000000001</v>
+        <v>2500.25</v>
       </c>
       <c r="H7" t="n">
-        <v>42.8</v>
+        <v>70.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.697</v>
+        <v>0.701</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.41</v>
+        <v>0.86</v>
       </c>
       <c r="L7" t="n">
-        <v>77000</v>
+        <v>2460</v>
       </c>
       <c r="M7" t="n">
-        <v>76800</v>
+        <v>2300</v>
       </c>
       <c r="N7" t="n">
-        <v>82000</v>
+        <v>2640</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>-0.0022</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2015</v>
+        <v>0.0056</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0097</v>
+        <v>-0.0004</v>
       </c>
       <c r="S7" t="n">
-        <v>13.22</v>
+        <v>-98.68000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>98.78</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 95% rich — sell premium</t>
+          <t>trending up +11.0% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23T12:54</t>
+          <t>2026-08-24T17:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -60006,63 +64812,63 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>77161.60000000001</v>
+        <v>2464.91</v>
       </c>
       <c r="H8" t="n">
-        <v>42.8</v>
+        <v>51.55</v>
       </c>
       <c r="I8" t="n">
-        <v>0.84</v>
+        <v>0.697</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.41</v>
+        <v>0.95</v>
       </c>
       <c r="L8" t="n">
-        <v>77000</v>
+        <v>2460</v>
       </c>
       <c r="M8" t="n">
-        <v>76800</v>
+        <v>2320</v>
       </c>
       <c r="N8" t="n">
-        <v>82000</v>
+        <v>2640</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.1041</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0055</v>
+        <v>-0.0027</v>
       </c>
       <c r="S8" t="n">
-        <v>-99.73999999999999</v>
+        <v>22.47</v>
       </c>
       <c r="T8" t="n">
-        <v>99.73999999999999</v>
+        <v>101.53</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>trending up +19.1% — skewed fly</t>
+          <t>IV rank 91% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23T12:54</t>
+          <t>2026-08-24T19:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -60072,11 +64878,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -60084,129 +64890,51 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2424.52</v>
+        <v>78922.5</v>
       </c>
       <c r="H9" t="n">
-        <v>59.8</v>
+        <v>34.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.627</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.29</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>2420</v>
+        <v>79000</v>
       </c>
       <c r="M9" t="n">
-        <v>2340</v>
+        <v>75200</v>
       </c>
       <c r="N9" t="n">
-        <v>2720</v>
+        <v>82000</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0859</v>
+        <v>0.3032</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0028</v>
+        <v>-0.0107</v>
       </c>
       <c r="S9" t="n">
-        <v>31.35</v>
+        <v>13.22</v>
       </c>
       <c r="T9" t="n">
-        <v>100.65</v>
+        <v>98.78</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>IV rank 95% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-23T12:54</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>broken_wing_butterfly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>400</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2424.52</v>
-      </c>
-      <c r="H10" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2420</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2340</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2720</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.0021</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.0231</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.0009</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-100.44</v>
-      </c>
-      <c r="T10" t="n">
-        <v>100.44</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>trending up +26.3% — skewed fly</t>
+          <t>IV rank 91% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -60227,7 +64955,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-23T20:10:18.025069 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-24T20:18:00.595026 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y695"/>
+  <dimension ref="A1:Y768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -62961,7 +62961,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G685" t="n">
@@ -63006,7 +63006,17 @@
         <v>98.3</v>
       </c>
       <c r="U685" t="inlineStr"/>
-      <c r="X685" t="inlineStr"/>
+      <c r="V685" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="W685" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="X685" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="Y685" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -63311,7 +63321,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -63355,8 +63365,22 @@
       <c r="T689" t="n">
         <v>103.16</v>
       </c>
-      <c r="U689" t="inlineStr"/>
-      <c r="X689" t="inlineStr"/>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>79719.3</t>
+        </is>
+      </c>
+      <c r="V689" t="n">
+        <v>-104.92</v>
+      </c>
+      <c r="W689" t="n">
+        <v>-10.492</v>
+      </c>
+      <c r="X689" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="Y689" t="inlineStr">
         <is>
           <t>trending up +13.6% — skewed fly</t>
@@ -63477,7 +63501,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G691" t="n">
@@ -63521,8 +63545,22 @@
       <c r="T691" t="n">
         <v>98.68000000000001</v>
       </c>
-      <c r="U691" t="inlineStr"/>
-      <c r="X691" t="inlineStr"/>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>2493.71</t>
+        </is>
+      </c>
+      <c r="V691" t="n">
+        <v>-19.66</v>
+      </c>
+      <c r="W691" t="n">
+        <v>-1.966</v>
+      </c>
+      <c r="X691" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="Y691" t="inlineStr">
         <is>
           <t>trending up +11.0% — skewed fly</t>
@@ -63731,7 +63769,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G694" t="n">
@@ -63776,7 +63814,17 @@
         <v>101.53</v>
       </c>
       <c r="U694" t="inlineStr"/>
-      <c r="X694" t="inlineStr"/>
+      <c r="V694" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W694" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X694" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="Y694" t="inlineStr">
         <is>
           <t>IV rank 91% rich — sell premium</t>
@@ -63809,7 +63857,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G695" t="n">
@@ -63854,10 +63902,6634 @@
         <v>98.78</v>
       </c>
       <c r="U695" t="inlineStr"/>
-      <c r="X695" t="inlineStr"/>
+      <c r="V695" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="W695" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="X695" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="Y695" t="inlineStr">
         <is>
           <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-08-24T22:35</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>230</v>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G696" t="n">
+        <v>2482.23</v>
+      </c>
+      <c r="H696" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K696" t="n">
+        <v>1</v>
+      </c>
+      <c r="L696" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M696" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N696" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O696" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P696" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="Q696" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S696" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="T696" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>2493.71</t>
+        </is>
+      </c>
+      <c r="V696" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="W696" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="X696" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y696" t="inlineStr">
+        <is>
+          <t>IV rank 82% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-08-24T23:01</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>70</v>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G697" t="n">
+        <v>78747.7</v>
+      </c>
+      <c r="H697" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="I697" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K697" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="L697" t="n">
+        <v>78800</v>
+      </c>
+      <c r="M697" t="n">
+        <v>75200</v>
+      </c>
+      <c r="N697" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O697" t="n">
+        <v>0</v>
+      </c>
+      <c r="P697" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="Q697" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="S697" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="T697" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>79719.3</t>
+        </is>
+      </c>
+      <c r="V697" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="W697" t="n">
+        <v>1.072</v>
+      </c>
+      <c r="X697" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y697" t="inlineStr">
+        <is>
+          <t>IV rank 82% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:18</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>80</v>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G698" t="n">
+        <v>79719.3</v>
+      </c>
+      <c r="H698" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="I698" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K698" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L698" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M698" t="n">
+        <v>77500</v>
+      </c>
+      <c r="N698" t="n">
+        <v>77500</v>
+      </c>
+      <c r="O698" t="n">
+        <v>0</v>
+      </c>
+      <c r="P698" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="Q698" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="S698" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="T698" t="n">
+        <v>106.42</v>
+      </c>
+      <c r="U698" t="inlineStr"/>
+      <c r="X698" t="inlineStr"/>
+      <c r="Y698" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:18</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>160</v>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G699" t="n">
+        <v>79719.3</v>
+      </c>
+      <c r="H699" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="I699" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K699" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L699" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M699" t="n">
+        <v>77500</v>
+      </c>
+      <c r="N699" t="n">
+        <v>77500</v>
+      </c>
+      <c r="O699" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P699" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="Q699" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="S699" t="n">
+        <v>-103.09</v>
+      </c>
+      <c r="T699" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="U699" t="inlineStr"/>
+      <c r="X699" t="inlineStr"/>
+      <c r="Y699" t="inlineStr">
+        <is>
+          <t>trending up +9.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:18</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>230</v>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G700" t="n">
+        <v>2493.71</v>
+      </c>
+      <c r="H700" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="I700" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K700" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L700" t="n">
+        <v>2350</v>
+      </c>
+      <c r="M700" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N700" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O700" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P700" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="Q700" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S700" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="T700" t="n">
+        <v>101.84</v>
+      </c>
+      <c r="U700" t="inlineStr"/>
+      <c r="X700" t="inlineStr"/>
+      <c r="Y700" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:18</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G701" t="n">
+        <v>2493.71</v>
+      </c>
+      <c r="H701" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="I701" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K701" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L701" t="n">
+        <v>2350</v>
+      </c>
+      <c r="M701" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N701" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O701" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P701" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="Q701" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="S701" t="n">
+        <v>-100.12</v>
+      </c>
+      <c r="T701" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="U701" t="inlineStr"/>
+      <c r="X701" t="inlineStr"/>
+      <c r="Y701" t="inlineStr">
+        <is>
+          <t>trending up +7.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-08-25T02:36</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>70</v>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G702" t="n">
+        <v>80857.8</v>
+      </c>
+      <c r="H702" t="n">
+        <v>62</v>
+      </c>
+      <c r="I702" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K702" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="L702" t="n">
+        <v>79800</v>
+      </c>
+      <c r="M702" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N702" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O702" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P702" t="n">
+        <v>0.2128</v>
+      </c>
+      <c r="Q702" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="S702" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="T702" t="n">
+        <v>106.09</v>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>80857.8</t>
+        </is>
+      </c>
+      <c r="V702" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="W702" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="X702" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y702" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-08-25T02:36</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>70</v>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G703" t="n">
+        <v>80857.8</v>
+      </c>
+      <c r="H703" t="n">
+        <v>62</v>
+      </c>
+      <c r="I703" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K703" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="L703" t="n">
+        <v>79800</v>
+      </c>
+      <c r="M703" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N703" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O703" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P703" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="Q703" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="S703" t="n">
+        <v>-96.68000000000001</v>
+      </c>
+      <c r="T703" t="n">
+        <v>96.68000000000001</v>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>80857.8</t>
+        </is>
+      </c>
+      <c r="V703" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W703" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X703" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y703" t="inlineStr">
+        <is>
+          <t>trending up +10.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-08-25T02:36</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>160</v>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G704" t="n">
+        <v>2516.07</v>
+      </c>
+      <c r="H704" t="n">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="I704" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K704" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L704" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M704" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N704" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O704" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P704" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="Q704" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S704" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="T704" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>2516.07</t>
+        </is>
+      </c>
+      <c r="V704" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="W704" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="X704" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y704" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-08-25T02:36</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>260</v>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G705" t="n">
+        <v>2516.07</v>
+      </c>
+      <c r="H705" t="n">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="I705" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K705" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L705" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M705" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N705" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O705" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="P705" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="Q705" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S705" t="n">
+        <v>-98.33</v>
+      </c>
+      <c r="T705" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>2516.07</t>
+        </is>
+      </c>
+      <c r="V705" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W705" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="X705" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y705" t="inlineStr">
+        <is>
+          <t>trending up +8.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:30</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>70</v>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G706" t="n">
+        <v>80606.10000000001</v>
+      </c>
+      <c r="H706" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I706" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K706" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="L706" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M706" t="n">
+        <v>77400</v>
+      </c>
+      <c r="N706" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O706" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P706" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="Q706" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="S706" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="T706" t="n">
+        <v>105.59</v>
+      </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>80606.1</t>
+        </is>
+      </c>
+      <c r="V706" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W706" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="X706" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y706" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:30</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>70</v>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G707" t="n">
+        <v>80606.10000000001</v>
+      </c>
+      <c r="H707" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I707" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K707" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="L707" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M707" t="n">
+        <v>77400</v>
+      </c>
+      <c r="N707" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O707" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P707" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="Q707" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="S707" t="n">
+        <v>-99.36</v>
+      </c>
+      <c r="T707" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="U707" t="inlineStr">
+        <is>
+          <t>80606.1</t>
+        </is>
+      </c>
+      <c r="V707" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W707" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="X707" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y707" t="inlineStr">
+        <is>
+          <t>trending up +10.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:30</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>180</v>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G708" t="n">
+        <v>2504.07</v>
+      </c>
+      <c r="H708" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="I708" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K708" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L708" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M708" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N708" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O708" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P708" t="n">
+        <v>0.1733</v>
+      </c>
+      <c r="Q708" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S708" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="T708" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="U708" t="inlineStr">
+        <is>
+          <t>2504.07</t>
+        </is>
+      </c>
+      <c r="V708" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="W708" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="X708" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y708" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:30</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>230</v>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G709" t="n">
+        <v>2504.07</v>
+      </c>
+      <c r="H709" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="I709" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K709" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L709" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M709" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N709" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O709" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="P709" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="Q709" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S709" t="n">
+        <v>-101.87</v>
+      </c>
+      <c r="T709" t="n">
+        <v>101.87</v>
+      </c>
+      <c r="U709" t="inlineStr">
+        <is>
+          <t>2504.07</t>
+        </is>
+      </c>
+      <c r="V709" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="W709" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="X709" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y709" t="inlineStr">
+        <is>
+          <t>trending up +7.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-08-25T04:23</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>70</v>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G710" t="n">
+        <v>80335.5</v>
+      </c>
+      <c r="H710" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="I710" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K710" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="L710" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M710" t="n">
+        <v>77400</v>
+      </c>
+      <c r="N710" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O710" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P710" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="Q710" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="S710" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="T710" t="n">
+        <v>102.59</v>
+      </c>
+      <c r="U710" t="inlineStr">
+        <is>
+          <t>80335.5</t>
+        </is>
+      </c>
+      <c r="V710" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="W710" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="X710" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y710" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-08-25T04:23</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>70</v>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G711" t="n">
+        <v>80335.5</v>
+      </c>
+      <c r="H711" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="I711" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K711" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="L711" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M711" t="n">
+        <v>77400</v>
+      </c>
+      <c r="N711" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O711" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P711" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="Q711" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="S711" t="n">
+        <v>-103.02</v>
+      </c>
+      <c r="T711" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>80335.5</t>
+        </is>
+      </c>
+      <c r="V711" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W711" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="X711" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y711" t="inlineStr">
+        <is>
+          <t>trending up +9.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-08-25T04:23</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>190</v>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G712" t="n">
+        <v>2496.86</v>
+      </c>
+      <c r="H712" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="I712" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K712" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L712" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M712" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N712" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O712" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P712" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="Q712" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S712" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="T712" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>2496.86</t>
+        </is>
+      </c>
+      <c r="V712" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="W712" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="X712" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y712" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-08-25T04:23</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>280</v>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G713" t="n">
+        <v>2496.86</v>
+      </c>
+      <c r="H713" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="I713" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K713" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L713" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M713" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N713" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O713" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="P713" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="Q713" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S713" t="n">
+        <v>-100.27</v>
+      </c>
+      <c r="T713" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>2496.86</t>
+        </is>
+      </c>
+      <c r="V713" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W713" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="X713" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y713" t="inlineStr">
+        <is>
+          <t>trending up +7.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:04</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>70</v>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G714" t="n">
+        <v>80442</v>
+      </c>
+      <c r="H714" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="I714" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K714" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L714" t="n">
+        <v>80200</v>
+      </c>
+      <c r="M714" t="n">
+        <v>77200</v>
+      </c>
+      <c r="N714" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O714" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P714" t="n">
+        <v>0.7393</v>
+      </c>
+      <c r="Q714" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="S714" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="T714" t="n">
+        <v>100.91</v>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>80442.0</t>
+        </is>
+      </c>
+      <c r="V714" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="W714" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="X714" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y714" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:04</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>70</v>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G715" t="n">
+        <v>80442</v>
+      </c>
+      <c r="H715" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="I715" t="n">
+        <v>1</v>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K715" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L715" t="n">
+        <v>80200</v>
+      </c>
+      <c r="M715" t="n">
+        <v>77200</v>
+      </c>
+      <c r="N715" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O715" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P715" t="n">
+        <v>0.7246</v>
+      </c>
+      <c r="Q715" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="S715" t="n">
+        <v>-104</v>
+      </c>
+      <c r="T715" t="n">
+        <v>104</v>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>80442.0</t>
+        </is>
+      </c>
+      <c r="V715" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="W715" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="X715" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y715" t="inlineStr">
+        <is>
+          <t>trending up +10.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:04</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>190</v>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G716" t="n">
+        <v>2497.9</v>
+      </c>
+      <c r="H716" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="I716" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K716" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L716" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M716" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N716" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O716" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P716" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="Q716" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S716" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="T716" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>2497.9</t>
+        </is>
+      </c>
+      <c r="V716" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="W716" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="X716" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y716" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:04</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>280</v>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G717" t="n">
+        <v>2497.9</v>
+      </c>
+      <c r="H717" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="I717" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K717" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L717" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M717" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N717" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O717" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="P717" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="Q717" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S717" t="n">
+        <v>-100.44</v>
+      </c>
+      <c r="T717" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="U717" t="inlineStr">
+        <is>
+          <t>2497.9</t>
+        </is>
+      </c>
+      <c r="V717" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="W717" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="X717" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y717" t="inlineStr">
+        <is>
+          <t>trending up +7.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:46</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>70</v>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G718" t="n">
+        <v>80733.89999999999</v>
+      </c>
+      <c r="H718" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="I718" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K718" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="L718" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M718" t="n">
+        <v>77200</v>
+      </c>
+      <c r="N718" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O718" t="n">
+        <v>0</v>
+      </c>
+      <c r="P718" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="Q718" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="S718" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="T718" t="n">
+        <v>100.83</v>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>80733.9</t>
+        </is>
+      </c>
+      <c r="V718" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="W718" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X718" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y718" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:46</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>70</v>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G719" t="n">
+        <v>80733.89999999999</v>
+      </c>
+      <c r="H719" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="I719" t="n">
+        <v>1</v>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K719" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="L719" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M719" t="n">
+        <v>77200</v>
+      </c>
+      <c r="N719" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O719" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P719" t="n">
+        <v>0.8348</v>
+      </c>
+      <c r="Q719" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="S719" t="n">
+        <v>-101.14</v>
+      </c>
+      <c r="T719" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>80733.9</t>
+        </is>
+      </c>
+      <c r="V719" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="W719" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="X719" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y719" t="inlineStr">
+        <is>
+          <t>trending up +10.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:46</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>180</v>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G720" t="n">
+        <v>2508.26</v>
+      </c>
+      <c r="H720" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I720" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K720" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L720" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M720" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N720" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O720" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P720" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="Q720" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S720" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="T720" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="U720" t="inlineStr">
+        <is>
+          <t>2508.26</t>
+        </is>
+      </c>
+      <c r="V720" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="W720" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="X720" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y720" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:46</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>200</v>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G721" t="n">
+        <v>2508.26</v>
+      </c>
+      <c r="H721" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I721" t="n">
+        <v>1</v>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K721" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L721" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M721" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N721" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O721" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="P721" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="Q721" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="S721" t="n">
+        <v>-100.04</v>
+      </c>
+      <c r="T721" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U721" t="inlineStr">
+        <is>
+          <t>2508.26</t>
+        </is>
+      </c>
+      <c r="V721" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="W721" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X721" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y721" t="inlineStr">
+        <is>
+          <t>trending up +7.8% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:38</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>70</v>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G722" t="n">
+        <v>80574.10000000001</v>
+      </c>
+      <c r="H722" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="I722" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K722" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L722" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M722" t="n">
+        <v>77200</v>
+      </c>
+      <c r="N722" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O722" t="n">
+        <v>0</v>
+      </c>
+      <c r="P722" t="n">
+        <v>0.6222</v>
+      </c>
+      <c r="Q722" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="S722" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="T722" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="U722" t="inlineStr">
+        <is>
+          <t>80574.1</t>
+        </is>
+      </c>
+      <c r="V722" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="W722" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="X722" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y722" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:38</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>60</v>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G723" t="n">
+        <v>80574.10000000001</v>
+      </c>
+      <c r="H723" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="I723" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K723" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L723" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M723" t="n">
+        <v>77200</v>
+      </c>
+      <c r="N723" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O723" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P723" t="n">
+        <v>0.7701</v>
+      </c>
+      <c r="Q723" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="S723" t="n">
+        <v>-95.23999999999999</v>
+      </c>
+      <c r="T723" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="U723" t="inlineStr">
+        <is>
+          <t>80574.1</t>
+        </is>
+      </c>
+      <c r="V723" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="W723" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="X723" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y723" t="inlineStr">
+        <is>
+          <t>trending up +10.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:38</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>220</v>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G724" t="n">
+        <v>2500.98</v>
+      </c>
+      <c r="H724" t="n">
+        <v>49</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K724" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L724" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M724" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N724" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O724" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P724" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="Q724" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S724" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="T724" t="n">
+        <v>98.31999999999999</v>
+      </c>
+      <c r="U724" t="inlineStr">
+        <is>
+          <t>2500.98</t>
+        </is>
+      </c>
+      <c r="V724" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="W724" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="X724" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y724" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:38</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>200</v>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G725" t="n">
+        <v>2500.98</v>
+      </c>
+      <c r="H725" t="n">
+        <v>49</v>
+      </c>
+      <c r="I725" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K725" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L725" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M725" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N725" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O725" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="P725" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="Q725" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="S725" t="n">
+        <v>-100.38</v>
+      </c>
+      <c r="T725" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="U725" t="inlineStr">
+        <is>
+          <t>2500.98</t>
+        </is>
+      </c>
+      <c r="V725" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="W725" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="X725" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y725" t="inlineStr">
+        <is>
+          <t>trending up +7.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:30</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>70</v>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G726" t="n">
+        <v>80646.60000000001</v>
+      </c>
+      <c r="H726" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I726" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K726" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="L726" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M726" t="n">
+        <v>77400</v>
+      </c>
+      <c r="N726" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O726" t="n">
+        <v>0</v>
+      </c>
+      <c r="P726" t="n">
+        <v>0.7528</v>
+      </c>
+      <c r="Q726" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="S726" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="T726" t="n">
+        <v>103.44</v>
+      </c>
+      <c r="U726" t="inlineStr">
+        <is>
+          <t>80646.6</t>
+        </is>
+      </c>
+      <c r="V726" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="W726" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="X726" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y726" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:30</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>60</v>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G727" t="n">
+        <v>80646.60000000001</v>
+      </c>
+      <c r="H727" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I727" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K727" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="L727" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M727" t="n">
+        <v>77400</v>
+      </c>
+      <c r="N727" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O727" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P727" t="n">
+        <v>0.8091</v>
+      </c>
+      <c r="Q727" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="S727" t="n">
+        <v>-95</v>
+      </c>
+      <c r="T727" t="n">
+        <v>95</v>
+      </c>
+      <c r="U727" t="inlineStr">
+        <is>
+          <t>80646.6</t>
+        </is>
+      </c>
+      <c r="V727" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="W727" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="X727" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y727" t="inlineStr">
+        <is>
+          <t>trending up +10.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:30</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>220</v>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G728" t="n">
+        <v>2503.98</v>
+      </c>
+      <c r="H728" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="I728" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K728" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L728" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M728" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N728" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O728" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P728" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="Q728" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S728" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="T728" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="U728" t="inlineStr">
+        <is>
+          <t>2503.98</t>
+        </is>
+      </c>
+      <c r="V728" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="W728" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="X728" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y728" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:30</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>200</v>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G729" t="n">
+        <v>2503.98</v>
+      </c>
+      <c r="H729" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="I729" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K729" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L729" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M729" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N729" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O729" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="P729" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="Q729" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S729" t="n">
+        <v>-99.59999999999999</v>
+      </c>
+      <c r="T729" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="U729" t="inlineStr">
+        <is>
+          <t>2503.98</t>
+        </is>
+      </c>
+      <c r="V729" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W729" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X729" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y729" t="inlineStr">
+        <is>
+          <t>trending up +7.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:10</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>70</v>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G730" t="n">
+        <v>79869.60000000001</v>
+      </c>
+      <c r="H730" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="I730" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K730" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L730" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M730" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N730" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O730" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P730" t="n">
+        <v>1.0223</v>
+      </c>
+      <c r="Q730" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="S730" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="T730" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="U730" t="inlineStr">
+        <is>
+          <t>79869.6</t>
+        </is>
+      </c>
+      <c r="V730" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="W730" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="X730" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y730" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:10</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>60</v>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G731" t="n">
+        <v>79869.60000000001</v>
+      </c>
+      <c r="H731" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="I731" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K731" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L731" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M731" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N731" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O731" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P731" t="n">
+        <v>1.2578</v>
+      </c>
+      <c r="Q731" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="S731" t="n">
+        <v>-101.51</v>
+      </c>
+      <c r="T731" t="n">
+        <v>101.51</v>
+      </c>
+      <c r="U731" t="inlineStr">
+        <is>
+          <t>79869.6</t>
+        </is>
+      </c>
+      <c r="V731" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="W731" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="X731" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y731" t="inlineStr">
+        <is>
+          <t>trending up +9.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:10</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>230</v>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G732" t="n">
+        <v>2482.69</v>
+      </c>
+      <c r="H732" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="I732" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K732" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L732" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M732" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N732" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O732" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P732" t="n">
+        <v>0.6302</v>
+      </c>
+      <c r="Q732" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S732" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="T732" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="U732" t="inlineStr">
+        <is>
+          <t>2482.69</t>
+        </is>
+      </c>
+      <c r="V732" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="W732" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="X732" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y732" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:10</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>240</v>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G733" t="n">
+        <v>2482.69</v>
+      </c>
+      <c r="H733" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="I733" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K733" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L733" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M733" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N733" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O733" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="P733" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="Q733" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S733" t="n">
+        <v>-101.45</v>
+      </c>
+      <c r="T733" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="U733" t="inlineStr">
+        <is>
+          <t>2482.69</t>
+        </is>
+      </c>
+      <c r="V733" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W733" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="X733" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y733" t="inlineStr">
+        <is>
+          <t>trending up +6.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:58</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>70</v>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G734" t="n">
+        <v>79928.39999999999</v>
+      </c>
+      <c r="H734" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I734" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K734" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L734" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M734" t="n">
+        <v>79000</v>
+      </c>
+      <c r="N734" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O734" t="n">
+        <v>0</v>
+      </c>
+      <c r="P734" t="n">
+        <v>1.3177</v>
+      </c>
+      <c r="Q734" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="S734" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="T734" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="U734" t="inlineStr">
+        <is>
+          <t>79928.4</t>
+        </is>
+      </c>
+      <c r="V734" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="W734" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="X734" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y734" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:59</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>50</v>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G735" t="n">
+        <v>79928.39999999999</v>
+      </c>
+      <c r="H735" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I735" t="n">
+        <v>1</v>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K735" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L735" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M735" t="n">
+        <v>79000</v>
+      </c>
+      <c r="N735" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O735" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P735" t="n">
+        <v>1.6449</v>
+      </c>
+      <c r="Q735" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="S735" t="n">
+        <v>-91.84999999999999</v>
+      </c>
+      <c r="T735" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="U735" t="inlineStr">
+        <is>
+          <t>79928.4</t>
+        </is>
+      </c>
+      <c r="V735" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W735" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="X735" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y735" t="inlineStr">
+        <is>
+          <t>trending up +9.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:59</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>210</v>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G736" t="n">
+        <v>2484.76</v>
+      </c>
+      <c r="H736" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I736" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K736" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L736" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M736" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N736" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O736" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P736" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="Q736" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S736" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T736" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="U736" t="inlineStr">
+        <is>
+          <t>2484.76</t>
+        </is>
+      </c>
+      <c r="V736" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="W736" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="X736" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y736" t="inlineStr">
+        <is>
+          <t>IV rank 70% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:59</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>200</v>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G737" t="n">
+        <v>2484.76</v>
+      </c>
+      <c r="H737" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I737" t="n">
+        <v>1</v>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K737" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L737" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M737" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N737" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O737" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="P737" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="Q737" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S737" t="n">
+        <v>-98.40000000000001</v>
+      </c>
+      <c r="T737" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="U737" t="inlineStr">
+        <is>
+          <t>2484.76</t>
+        </is>
+      </c>
+      <c r="V737" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W737" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="X737" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y737" t="inlineStr">
+        <is>
+          <t>trending up +6.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:41</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>70</v>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G738" t="n">
+        <v>79873.10000000001</v>
+      </c>
+      <c r="H738" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="I738" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K738" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L738" t="n">
+        <v>79800</v>
+      </c>
+      <c r="M738" t="n">
+        <v>79000</v>
+      </c>
+      <c r="N738" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O738" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P738" t="n">
+        <v>1.4939</v>
+      </c>
+      <c r="Q738" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="S738" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="T738" t="n">
+        <v>103.97</v>
+      </c>
+      <c r="U738" t="inlineStr">
+        <is>
+          <t>79873.1</t>
+        </is>
+      </c>
+      <c r="V738" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="W738" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="X738" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y738" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:41</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>50</v>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G739" t="n">
+        <v>79873.10000000001</v>
+      </c>
+      <c r="H739" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="I739" t="n">
+        <v>1</v>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K739" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L739" t="n">
+        <v>79800</v>
+      </c>
+      <c r="M739" t="n">
+        <v>79000</v>
+      </c>
+      <c r="N739" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O739" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P739" t="n">
+        <v>1.9104</v>
+      </c>
+      <c r="Q739" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="S739" t="n">
+        <v>-95.8</v>
+      </c>
+      <c r="T739" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="U739" t="inlineStr">
+        <is>
+          <t>79873.1</t>
+        </is>
+      </c>
+      <c r="V739" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W739" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="X739" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y739" t="inlineStr">
+        <is>
+          <t>trending up +9.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:41</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>370</v>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G740" t="n">
+        <v>79873.10000000001</v>
+      </c>
+      <c r="H740" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="I740" t="n">
+        <v>1</v>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K740" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L740" t="n">
+        <v>79800</v>
+      </c>
+      <c r="M740" t="n">
+        <v>79000</v>
+      </c>
+      <c r="N740" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O740" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P740" t="n">
+        <v>0.7058</v>
+      </c>
+      <c r="Q740" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="R740" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S740" t="n">
+        <v>-25.97</v>
+      </c>
+      <c r="T740" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="U740" t="inlineStr">
+        <is>
+          <t>79873.1</t>
+        </is>
+      </c>
+      <c r="V740" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="W740" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="X740" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y740" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.2 · 2.3h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:41</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>210</v>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G741" t="n">
+        <v>2489.03</v>
+      </c>
+      <c r="H741" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I741" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K741" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L741" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M741" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N741" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O741" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P741" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="Q741" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S741" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="T741" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="U741" t="inlineStr">
+        <is>
+          <t>2489.03</t>
+        </is>
+      </c>
+      <c r="V741" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="W741" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="X741" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y741" t="inlineStr">
+        <is>
+          <t>IV rank 70% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:41</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>280</v>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G742" t="n">
+        <v>2489.03</v>
+      </c>
+      <c r="H742" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I742" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K742" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L742" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M742" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N742" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O742" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="P742" t="n">
+        <v>0.8806</v>
+      </c>
+      <c r="Q742" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S742" t="n">
+        <v>-99.98999999999999</v>
+      </c>
+      <c r="T742" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="U742" t="inlineStr">
+        <is>
+          <t>2489.03</t>
+        </is>
+      </c>
+      <c r="V742" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="W742" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="X742" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y742" t="inlineStr">
+        <is>
+          <t>trending up +6.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:41</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>620</v>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G743" t="n">
+        <v>2489.03</v>
+      </c>
+      <c r="H743" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I743" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K743" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L743" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M743" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N743" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O743" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="P743" t="n">
+        <v>-0.2222</v>
+      </c>
+      <c r="Q743" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="R743" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S743" t="n">
+        <v>-38.75</v>
+      </c>
+      <c r="T743" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="U743" t="inlineStr">
+        <is>
+          <t>2489.03</t>
+        </is>
+      </c>
+      <c r="V743" t="n">
+        <v>-40.61</v>
+      </c>
+      <c r="W743" t="n">
+        <v>-4.061</v>
+      </c>
+      <c r="X743" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y743" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.7 · 2.3h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:06</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>70</v>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G744" t="n">
+        <v>79228.10000000001</v>
+      </c>
+      <c r="H744" t="n">
+        <v>25</v>
+      </c>
+      <c r="I744" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K744" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L744" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M744" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N744" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O744" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P744" t="n">
+        <v>1.6536</v>
+      </c>
+      <c r="Q744" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S744" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="T744" t="n">
+        <v>105.18</v>
+      </c>
+      <c r="U744" t="inlineStr">
+        <is>
+          <t>79228.1</t>
+        </is>
+      </c>
+      <c r="V744" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="W744" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="X744" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y744" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:06</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>50</v>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G745" t="n">
+        <v>79228.10000000001</v>
+      </c>
+      <c r="H745" t="n">
+        <v>25</v>
+      </c>
+      <c r="I745" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K745" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L745" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M745" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N745" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O745" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P745" t="n">
+        <v>1.5634</v>
+      </c>
+      <c r="Q745" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="S745" t="n">
+        <v>-93.26000000000001</v>
+      </c>
+      <c r="T745" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="U745" t="inlineStr">
+        <is>
+          <t>79228.1</t>
+        </is>
+      </c>
+      <c r="V745" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="W745" t="n">
+        <v>-0.303</v>
+      </c>
+      <c r="X745" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y745" t="inlineStr">
+        <is>
+          <t>trending up +8.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:06</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>750</v>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G746" t="n">
+        <v>79228.10000000001</v>
+      </c>
+      <c r="H746" t="n">
+        <v>25</v>
+      </c>
+      <c r="I746" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K746" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L746" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M746" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N746" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O746" t="n">
+        <v>0</v>
+      </c>
+      <c r="P746" t="n">
+        <v>-1.9366</v>
+      </c>
+      <c r="Q746" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="S746" t="n">
+        <v>-100.58</v>
+      </c>
+      <c r="T746" t="n">
+        <v>100.58</v>
+      </c>
+      <c r="U746" t="inlineStr">
+        <is>
+          <t>79228.1</t>
+        </is>
+      </c>
+      <c r="V746" t="n">
+        <v>-104.77</v>
+      </c>
+      <c r="W746" t="n">
+        <v>-10.477</v>
+      </c>
+      <c r="X746" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y746" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:06</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>390</v>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G747" t="n">
+        <v>79228.10000000001</v>
+      </c>
+      <c r="H747" t="n">
+        <v>25</v>
+      </c>
+      <c r="I747" t="n">
+        <v>1</v>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K747" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L747" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M747" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N747" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O747" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P747" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="Q747" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="R747" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S747" t="n">
+        <v>-22.78</v>
+      </c>
+      <c r="T747" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="U747" t="inlineStr">
+        <is>
+          <t>79228.1</t>
+        </is>
+      </c>
+      <c r="V747" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="W747" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="X747" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y747" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.3 · 1.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:06</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>210</v>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G748" t="n">
+        <v>2477.15</v>
+      </c>
+      <c r="H748" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="I748" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K748" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L748" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M748" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N748" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O748" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P748" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="Q748" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S748" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="T748" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="U748" t="inlineStr">
+        <is>
+          <t>2477.15</t>
+        </is>
+      </c>
+      <c r="V748" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="W748" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="X748" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y748" t="inlineStr">
+        <is>
+          <t>IV rank 57% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:06</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>180</v>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G749" t="n">
+        <v>2477.15</v>
+      </c>
+      <c r="H749" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="I749" t="n">
+        <v>1</v>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K749" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L749" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M749" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N749" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O749" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="P749" t="n">
+        <v>0.6649</v>
+      </c>
+      <c r="Q749" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S749" t="n">
+        <v>-100.71</v>
+      </c>
+      <c r="T749" t="n">
+        <v>100.71</v>
+      </c>
+      <c r="U749" t="inlineStr">
+        <is>
+          <t>2477.15</t>
+        </is>
+      </c>
+      <c r="V749" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W749" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="X749" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y749" t="inlineStr">
+        <is>
+          <t>trending up +6.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:06</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>680</v>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G750" t="n">
+        <v>2477.15</v>
+      </c>
+      <c r="H750" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="I750" t="n">
+        <v>1</v>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K750" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L750" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M750" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N750" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O750" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="P750" t="n">
+        <v>-0.2149</v>
+      </c>
+      <c r="Q750" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="R750" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S750" t="n">
+        <v>-32.16</v>
+      </c>
+      <c r="T750" t="n">
+        <v>100.16</v>
+      </c>
+      <c r="U750" t="inlineStr">
+        <is>
+          <t>2477.15</t>
+        </is>
+      </c>
+      <c r="V750" t="n">
+        <v>-98.45999999999999</v>
+      </c>
+      <c r="W750" t="n">
+        <v>-9.846</v>
+      </c>
+      <c r="X750" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y750" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.4 · 1.9h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:48</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>60</v>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G751" t="n">
+        <v>79355.7</v>
+      </c>
+      <c r="H751" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="I751" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K751" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L751" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M751" t="n">
+        <v>78600</v>
+      </c>
+      <c r="N751" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O751" t="n">
+        <v>0</v>
+      </c>
+      <c r="P751" t="n">
+        <v>1.7021</v>
+      </c>
+      <c r="Q751" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="S751" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T751" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="U751" t="inlineStr">
+        <is>
+          <t>79355.7</t>
+        </is>
+      </c>
+      <c r="V751" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="W751" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="X751" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y751" t="inlineStr">
+        <is>
+          <t>IV rank 65% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:48</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>50</v>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G752" t="n">
+        <v>79355.7</v>
+      </c>
+      <c r="H752" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="I752" t="n">
+        <v>1</v>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K752" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L752" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M752" t="n">
+        <v>78600</v>
+      </c>
+      <c r="N752" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O752" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P752" t="n">
+        <v>2.457</v>
+      </c>
+      <c r="Q752" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S752" t="n">
+        <v>-104.16</v>
+      </c>
+      <c r="T752" t="n">
+        <v>104.16</v>
+      </c>
+      <c r="U752" t="inlineStr">
+        <is>
+          <t>79355.7</t>
+        </is>
+      </c>
+      <c r="V752" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="W752" t="n">
+        <v>-0.156</v>
+      </c>
+      <c r="X752" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y752" t="inlineStr">
+        <is>
+          <t>trending up +8.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:48</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G753" t="n">
+        <v>79355.7</v>
+      </c>
+      <c r="H753" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="I753" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K753" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L753" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M753" t="n">
+        <v>78600</v>
+      </c>
+      <c r="N753" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O753" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P753" t="n">
+        <v>-1.784</v>
+      </c>
+      <c r="Q753" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="S753" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T753" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U753" t="inlineStr">
+        <is>
+          <t>79355.7</t>
+        </is>
+      </c>
+      <c r="V753" t="n">
+        <v>-104.3</v>
+      </c>
+      <c r="W753" t="n">
+        <v>-10.43</v>
+      </c>
+      <c r="X753" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y753" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:48</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>410</v>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G754" t="n">
+        <v>79355.7</v>
+      </c>
+      <c r="H754" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="I754" t="n">
+        <v>1</v>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K754" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L754" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M754" t="n">
+        <v>78600</v>
+      </c>
+      <c r="N754" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O754" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P754" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="Q754" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="R754" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S754" t="n">
+        <v>-18.53</v>
+      </c>
+      <c r="T754" t="n">
+        <v>100.53</v>
+      </c>
+      <c r="U754" t="inlineStr">
+        <is>
+          <t>79355.7</t>
+        </is>
+      </c>
+      <c r="V754" t="n">
+        <v>-52.23</v>
+      </c>
+      <c r="W754" t="n">
+        <v>-5.223</v>
+      </c>
+      <c r="X754" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y754" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.4 · 1.2h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:48</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>210</v>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G755" t="n">
+        <v>2481.29</v>
+      </c>
+      <c r="H755" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I755" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K755" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L755" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M755" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N755" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O755" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P755" t="n">
+        <v>0.6952</v>
+      </c>
+      <c r="Q755" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="S755" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T755" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="U755" t="inlineStr">
+        <is>
+          <t>2481.29</t>
+        </is>
+      </c>
+      <c r="V755" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="W755" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="X755" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y755" t="inlineStr">
+        <is>
+          <t>IV rank 39% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:48</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>190</v>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G756" t="n">
+        <v>2481.29</v>
+      </c>
+      <c r="H756" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I756" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K756" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L756" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M756" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N756" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O756" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="P756" t="n">
+        <v>1.1278</v>
+      </c>
+      <c r="Q756" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S756" t="n">
+        <v>-100.98</v>
+      </c>
+      <c r="T756" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="U756" t="inlineStr">
+        <is>
+          <t>2481.29</t>
+        </is>
+      </c>
+      <c r="V756" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="W756" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="X756" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y756" t="inlineStr">
+        <is>
+          <t>trending up +6.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-08-25T10:48</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>830</v>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G757" t="n">
+        <v>2481.29</v>
+      </c>
+      <c r="H757" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I757" t="n">
+        <v>1</v>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K757" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L757" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M757" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N757" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O757" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="P757" t="n">
+        <v>-0.5507</v>
+      </c>
+      <c r="Q757" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="R757" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="S757" t="n">
+        <v>-17.51</v>
+      </c>
+      <c r="T757" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="U757" t="inlineStr">
+        <is>
+          <t>2481.29</t>
+        </is>
+      </c>
+      <c r="V757" t="n">
+        <v>-141.76</v>
+      </c>
+      <c r="W757" t="n">
+        <v>-14.176</v>
+      </c>
+      <c r="X757" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y757" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 3.1 · 1.2h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-08-25T11:22</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>60</v>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G758" t="n">
+        <v>79261.7</v>
+      </c>
+      <c r="H758" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I758" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K758" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L758" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M758" t="n">
+        <v>78800</v>
+      </c>
+      <c r="N758" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O758" t="n">
+        <v>0</v>
+      </c>
+      <c r="P758" t="n">
+        <v>1.7619</v>
+      </c>
+      <c r="Q758" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S758" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T758" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="U758" t="inlineStr">
+        <is>
+          <t>79261.7</t>
+        </is>
+      </c>
+      <c r="V758" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W758" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="X758" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y758" t="inlineStr">
+        <is>
+          <t>IV rank 26% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-08-25T11:22</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>50</v>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G759" t="n">
+        <v>79261.7</v>
+      </c>
+      <c r="H759" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I759" t="n">
+        <v>1</v>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K759" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L759" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M759" t="n">
+        <v>78800</v>
+      </c>
+      <c r="N759" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O759" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="P759" t="n">
+        <v>1.9024</v>
+      </c>
+      <c r="Q759" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S759" t="n">
+        <v>-105.34</v>
+      </c>
+      <c r="T759" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="U759" t="inlineStr">
+        <is>
+          <t>79261.7</t>
+        </is>
+      </c>
+      <c r="V759" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="W759" t="n">
+        <v>-0.732</v>
+      </c>
+      <c r="X759" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y759" t="inlineStr">
+        <is>
+          <t>trending up +8.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-08-25T11:22</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>7040</v>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G760" t="n">
+        <v>79261.7</v>
+      </c>
+      <c r="H760" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I760" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K760" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L760" t="n">
+        <v>79200</v>
+      </c>
+      <c r="M760" t="n">
+        <v>78800</v>
+      </c>
+      <c r="N760" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O760" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P760" t="n">
+        <v>-1.1974</v>
+      </c>
+      <c r="Q760" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="S760" t="n">
+        <v>-99.97</v>
+      </c>
+      <c r="T760" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="U760" t="inlineStr">
+        <is>
+          <t>79261.7</t>
+        </is>
+      </c>
+      <c r="V760" t="n">
+        <v>-104.19</v>
+      </c>
+      <c r="W760" t="n">
+        <v>-10.419</v>
+      </c>
+      <c r="X760" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y760" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-08-25T11:22</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>3830</v>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G761" t="n">
+        <v>2476.86</v>
+      </c>
+      <c r="H761" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I761" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K761" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L761" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M761" t="n">
+        <v>2440</v>
+      </c>
+      <c r="N761" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O761" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="P761" t="n">
+        <v>-1.5319</v>
+      </c>
+      <c r="Q761" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="S761" t="n">
+        <v>-99.95999999999999</v>
+      </c>
+      <c r="T761" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="U761" t="inlineStr">
+        <is>
+          <t>2476.86</t>
+        </is>
+      </c>
+      <c r="V761" t="n">
+        <v>-104.18</v>
+      </c>
+      <c r="W761" t="n">
+        <v>-10.418</v>
+      </c>
+      <c r="X761" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y761" t="inlineStr">
+        <is>
+          <t>IV rank 13% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-08-25T11:22</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>160</v>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G762" t="n">
+        <v>2476.86</v>
+      </c>
+      <c r="H762" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I762" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K762" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L762" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M762" t="n">
+        <v>2440</v>
+      </c>
+      <c r="N762" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O762" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="P762" t="n">
+        <v>0.7685999999999999</v>
+      </c>
+      <c r="Q762" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="S762" t="n">
+        <v>-98.45999999999999</v>
+      </c>
+      <c r="T762" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="U762" t="inlineStr">
+        <is>
+          <t>2476.86</t>
+        </is>
+      </c>
+      <c r="V762" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="W762" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="X762" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y762" t="inlineStr">
+        <is>
+          <t>trending up +6.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-08-25T13:34</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>70</v>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G763" t="n">
+        <v>78910.39999999999</v>
+      </c>
+      <c r="H763" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="I763" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K763" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L763" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M763" t="n">
+        <v>75200</v>
+      </c>
+      <c r="N763" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O763" t="n">
+        <v>0</v>
+      </c>
+      <c r="P763" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="Q763" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="S763" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="T763" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="U763" t="inlineStr"/>
+      <c r="V763" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="W763" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="X763" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y763" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-08-25T13:34</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>90</v>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G764" t="n">
+        <v>78910.39999999999</v>
+      </c>
+      <c r="H764" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="I764" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K764" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L764" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M764" t="n">
+        <v>75200</v>
+      </c>
+      <c r="N764" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O764" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P764" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="Q764" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S764" t="n">
+        <v>-100.78</v>
+      </c>
+      <c r="T764" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="U764" t="inlineStr"/>
+      <c r="X764" t="inlineStr"/>
+      <c r="Y764" t="inlineStr">
+        <is>
+          <t>trending up +7.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-08-25T13:34</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>310</v>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G765" t="n">
+        <v>2468.42</v>
+      </c>
+      <c r="H765" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="I765" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K765" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L765" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M765" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N765" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O765" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P765" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="Q765" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="S765" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="T765" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="U765" t="inlineStr"/>
+      <c r="V765" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="W765" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="X765" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Y765" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-08-25T13:34</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>420</v>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G766" t="n">
+        <v>2468.42</v>
+      </c>
+      <c r="H766" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="I766" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K766" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L766" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M766" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N766" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O766" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="P766" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="Q766" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="S766" t="n">
+        <v>-100.17</v>
+      </c>
+      <c r="T766" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U766" t="inlineStr"/>
+      <c r="X766" t="inlineStr"/>
+      <c r="Y766" t="inlineStr">
+        <is>
+          <t>trending up +6.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-08-25T17:27</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>70</v>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G767" t="n">
+        <v>78823.89999999999</v>
+      </c>
+      <c r="H767" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I767" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K767" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L767" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M767" t="n">
+        <v>75200</v>
+      </c>
+      <c r="N767" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O767" t="n">
+        <v>0</v>
+      </c>
+      <c r="P767" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="Q767" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="S767" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="T767" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="U767" t="inlineStr"/>
+      <c r="X767" t="inlineStr"/>
+      <c r="Y767" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:37</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>230</v>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G768" t="n">
+        <v>2466.76</v>
+      </c>
+      <c r="H768" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I768" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K768" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L768" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M768" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N768" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O768" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P768" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="Q768" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S768" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="T768" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="U768" t="inlineStr"/>
+      <c r="X768" t="inlineStr"/>
+      <c r="Y768" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -63928,22 +70600,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="C2" t="n">
-        <v>97.3</v>
+        <v>97.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4.87</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1629.17</v>
+        <v>1897.79</v>
       </c>
       <c r="F2" t="n">
-        <v>4.91</v>
+        <v>5.23</v>
       </c>
       <c r="G2" t="n">
-        <v>162.92</v>
+        <v>189.78</v>
       </c>
     </row>
     <row r="3">
@@ -64003,22 +70675,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>53.8</v>
+        <v>57.1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="E5" t="n">
-        <v>-170.55</v>
+        <v>-161.12</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.12</v>
+        <v>-11.51</v>
       </c>
       <c r="G5" t="n">
-        <v>-17.05</v>
+        <v>-16.11</v>
       </c>
     </row>
     <row r="6">
@@ -64028,22 +70700,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="C6" t="n">
-        <v>68.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="E6" t="n">
-        <v>-236.33</v>
+        <v>-278.85</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.59</v>
+        <v>-1.58</v>
       </c>
       <c r="G6" t="n">
-        <v>-23.63</v>
+        <v>-27.89</v>
       </c>
     </row>
     <row r="7">
@@ -64078,22 +70750,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>-1781.69</v>
+        <v>-2041.98</v>
       </c>
       <c r="F8" t="n">
-        <v>-49.49</v>
+        <v>-48.62</v>
       </c>
       <c r="G8" t="n">
-        <v>-178.17</v>
+        <v>-204.2</v>
       </c>
     </row>
     <row r="9">
@@ -64103,7 +70775,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
         <v>1.5</v>
@@ -64112,13 +70784,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-6595.13</v>
+        <v>-6699.31</v>
       </c>
       <c r="F9" t="n">
-        <v>-99.93000000000001</v>
+        <v>-99.98999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-659.51</v>
+        <v>-669.9299999999999</v>
       </c>
     </row>
     <row r="10">
@@ -64128,7 +70800,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -64137,13 +70809,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-8001.99</v>
+        <v>-8315.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-103.92</v>
+        <v>-103.94</v>
       </c>
       <c r="G10" t="n">
-        <v>-800.2</v>
+        <v>-831.52</v>
       </c>
     </row>
   </sheetData>
@@ -64157,7 +70829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -64551,12 +71223,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24T10:52</t>
+          <t>2026-08-25T01:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -64566,11 +71238,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -64578,13 +71250,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2461.79</v>
+        <v>79719.3</v>
       </c>
       <c r="H5" t="n">
-        <v>65</v>
+        <v>45.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.715</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -64592,44 +71264,44 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.71</v>
+        <v>1.85</v>
       </c>
       <c r="L5" t="n">
-        <v>2350</v>
+        <v>77000</v>
       </c>
       <c r="M5" t="n">
-        <v>1700</v>
+        <v>77500</v>
       </c>
       <c r="N5" t="n">
-        <v>2800</v>
+        <v>77500</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0204</v>
+        <v>0.0139</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0074</v>
       </c>
       <c r="S5" t="n">
-        <v>21.7</v>
+        <v>13.58</v>
       </c>
       <c r="T5" t="n">
-        <v>98.3</v>
+        <v>106.42</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24T12:39</t>
+          <t>2026-08-25T01:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -64639,16 +71311,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -64656,13 +71328,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>78739.39999999999</v>
+        <v>79719.3</v>
       </c>
       <c r="H6" t="n">
-        <v>53.85</v>
+        <v>45.15</v>
       </c>
       <c r="I6" t="n">
-        <v>0.771</v>
+        <v>0.598</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -64670,44 +71342,44 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="L6" t="n">
-        <v>78200</v>
+        <v>77000</v>
       </c>
       <c r="M6" t="n">
-        <v>76000</v>
+        <v>77500</v>
       </c>
       <c r="N6" t="n">
-        <v>81200</v>
+        <v>77500</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0495</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0039</v>
+        <v>0.0045</v>
       </c>
       <c r="S6" t="n">
-        <v>-103.16</v>
+        <v>-103.09</v>
       </c>
       <c r="T6" t="n">
-        <v>103.16</v>
+        <v>103.09</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +13.6% — skewed fly</t>
+          <t>trending up +9.0% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24T12:39</t>
+          <t>2026-08-25T01:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -64717,16 +71389,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>360</v>
+        <v>230</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -64734,58 +71406,58 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2500.25</v>
+        <v>2493.71</v>
       </c>
       <c r="H7" t="n">
-        <v>70.2</v>
+        <v>61.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.701</v>
+        <v>0.68</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.86</v>
+        <v>2.22</v>
       </c>
       <c r="L7" t="n">
-        <v>2460</v>
+        <v>2350</v>
       </c>
       <c r="M7" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="N7" t="n">
-        <v>2640</v>
+        <v>2800</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0022</v>
+        <v>0.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0056</v>
+        <v>0.0047</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0004</v>
+        <v>-0.0019</v>
       </c>
       <c r="S7" t="n">
-        <v>-98.68000000000001</v>
+        <v>13.16</v>
       </c>
       <c r="T7" t="n">
-        <v>98.68000000000001</v>
+        <v>101.84</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>trending up +11.0% — skewed fly</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24T17:49</t>
+          <t>2026-08-25T01:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -64795,16 +71467,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>310</v>
+        <v>2260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -64812,58 +71484,58 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2464.91</v>
+        <v>2493.71</v>
       </c>
       <c r="H8" t="n">
-        <v>51.55</v>
+        <v>61.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.697</v>
+        <v>0.526</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.95</v>
+        <v>2.22</v>
       </c>
       <c r="L8" t="n">
-        <v>2460</v>
+        <v>2350</v>
       </c>
       <c r="M8" t="n">
-        <v>2320</v>
+        <v>2200</v>
       </c>
       <c r="N8" t="n">
-        <v>2640</v>
+        <v>2800</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1041</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0027</v>
+        <v>-0.0003</v>
       </c>
       <c r="S8" t="n">
-        <v>22.47</v>
+        <v>-100.12</v>
       </c>
       <c r="T8" t="n">
-        <v>101.53</v>
+        <v>100.12</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>IV rank 91% rich — sell premium</t>
+          <t>trending up +7.1% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24T19:17</t>
+          <t>2026-08-25T13:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -64873,16 +71545,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -64890,13 +71562,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>78922.5</v>
+        <v>78910.39999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>34.05</v>
+        <v>46.4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.831</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -64904,7 +71576,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>2.29</v>
       </c>
       <c r="L9" t="n">
         <v>79000</v>
@@ -64913,28 +71585,262 @@
         <v>75200</v>
       </c>
       <c r="N9" t="n">
-        <v>82000</v>
+        <v>83600</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3032</v>
+        <v>0.0977</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0107</v>
+        <v>-0.0059</v>
       </c>
       <c r="S9" t="n">
-        <v>13.22</v>
+        <v>-100.78</v>
       </c>
       <c r="T9" t="n">
-        <v>98.78</v>
+        <v>100.78</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>trending up +7.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-25T13:34</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>420</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2468.42</v>
+      </c>
+      <c r="H10" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-100.17</v>
+      </c>
+      <c r="T10" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>trending up +6.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-25T17:27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>78823.89999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L11" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>75200</v>
+      </c>
+      <c r="N11" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="T11" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:37</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>230</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2466.76</v>
+      </c>
+      <c r="H12" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="T12" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -64955,7 +71861,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-24T20:18:00.595026 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-25T20:16:32.167814 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y768"/>
+  <dimension ref="A1:Y808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -70159,7 +70159,7 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G764" t="n">
@@ -70203,8 +70203,22 @@
       <c r="T764" t="n">
         <v>100.78</v>
       </c>
-      <c r="U764" t="inlineStr"/>
-      <c r="X764" t="inlineStr"/>
+      <c r="U764" t="inlineStr">
+        <is>
+          <t>79196.4</t>
+        </is>
+      </c>
+      <c r="V764" t="n">
+        <v>-22.86</v>
+      </c>
+      <c r="W764" t="n">
+        <v>-2.286</v>
+      </c>
+      <c r="X764" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="Y764" t="inlineStr">
         <is>
           <t>trending up +7.9% — skewed fly</t>
@@ -70325,7 +70339,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G766" t="n">
@@ -70369,8 +70383,22 @@
       <c r="T766" t="n">
         <v>100.17</v>
       </c>
-      <c r="U766" t="inlineStr"/>
-      <c r="X766" t="inlineStr"/>
+      <c r="U766" t="inlineStr">
+        <is>
+          <t>2468.32</t>
+        </is>
+      </c>
+      <c r="V766" t="n">
+        <v>-25.16</v>
+      </c>
+      <c r="W766" t="n">
+        <v>-2.516</v>
+      </c>
+      <c r="X766" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="Y766" t="inlineStr">
         <is>
           <t>trending up +6.0% — skewed fly</t>
@@ -70403,7 +70431,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G767" t="n">
@@ -70448,7 +70476,17 @@
         <v>99.31</v>
       </c>
       <c r="U767" t="inlineStr"/>
-      <c r="X767" t="inlineStr"/>
+      <c r="V767" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="W767" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="X767" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="Y767" t="inlineStr">
         <is>
           <t>IV rank 91% rich — sell premium</t>
@@ -70481,7 +70519,7 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G768" t="n">
@@ -70526,10 +70564,3640 @@
         <v>98.48999999999999</v>
       </c>
       <c r="U768" t="inlineStr"/>
-      <c r="X768" t="inlineStr"/>
+      <c r="V768" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="W768" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="X768" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="Y768" t="inlineStr">
         <is>
           <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-08-26T02:38</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>70</v>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G769" t="n">
+        <v>79196.39999999999</v>
+      </c>
+      <c r="H769" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="I769" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K769" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L769" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M769" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N769" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O769" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P769" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="Q769" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="S769" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="T769" t="n">
+        <v>102.14</v>
+      </c>
+      <c r="U769" t="inlineStr">
+        <is>
+          <t>79196.4</t>
+        </is>
+      </c>
+      <c r="V769" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="W769" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="X769" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y769" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-08-26T02:39</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>230</v>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G770" t="n">
+        <v>2468.32</v>
+      </c>
+      <c r="H770" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="I770" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K770" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L770" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M770" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N770" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O770" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P770" t="n">
+        <v>0.2046</v>
+      </c>
+      <c r="Q770" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S770" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="T770" t="n">
+        <v>100.72</v>
+      </c>
+      <c r="U770" t="inlineStr">
+        <is>
+          <t>2468.32</t>
+        </is>
+      </c>
+      <c r="V770" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="W770" t="n">
+        <v>1.359</v>
+      </c>
+      <c r="X770" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y770" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-08-26T03:38</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>70</v>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G771" t="n">
+        <v>79044.8</v>
+      </c>
+      <c r="H771" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="I771" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K771" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L771" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M771" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N771" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O771" t="n">
+        <v>0</v>
+      </c>
+      <c r="P771" t="n">
+        <v>0.4628</v>
+      </c>
+      <c r="Q771" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="S771" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="T771" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="U771" t="inlineStr">
+        <is>
+          <t>79044.8</t>
+        </is>
+      </c>
+      <c r="V771" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="W771" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="X771" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y771" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-08-26T03:38</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>220</v>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G772" t="n">
+        <v>2465.13</v>
+      </c>
+      <c r="H772" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="I772" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K772" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L772" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M772" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N772" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O772" t="n">
+        <v>0</v>
+      </c>
+      <c r="P772" t="n">
+        <v>0.1918</v>
+      </c>
+      <c r="Q772" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S772" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="T772" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="U772" t="inlineStr">
+        <is>
+          <t>2465.13</t>
+        </is>
+      </c>
+      <c r="V772" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="W772" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="X772" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y772" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-08-26T04:23</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>70</v>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G773" t="n">
+        <v>79047.8</v>
+      </c>
+      <c r="H773" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="I773" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K773" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L773" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M773" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N773" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O773" t="n">
+        <v>0</v>
+      </c>
+      <c r="P773" t="n">
+        <v>0.4903</v>
+      </c>
+      <c r="Q773" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="S773" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="T773" t="n">
+        <v>104.48</v>
+      </c>
+      <c r="U773" t="inlineStr">
+        <is>
+          <t>79047.8</t>
+        </is>
+      </c>
+      <c r="V773" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="W773" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="X773" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y773" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-08-26T04:23</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>220</v>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G774" t="n">
+        <v>2466.98</v>
+      </c>
+      <c r="H774" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="I774" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K774" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L774" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M774" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N774" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O774" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P774" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="Q774" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S774" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="T774" t="n">
+        <v>100.63</v>
+      </c>
+      <c r="U774" t="inlineStr">
+        <is>
+          <t>2466.98</t>
+        </is>
+      </c>
+      <c r="V774" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="W774" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="X774" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y774" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-08-26T05:04</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>70</v>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G775" t="n">
+        <v>78787</v>
+      </c>
+      <c r="H775" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="I775" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K775" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L775" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M775" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N775" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O775" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P775" t="n">
+        <v>0.5394</v>
+      </c>
+      <c r="Q775" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="S775" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="T775" t="n">
+        <v>104.29</v>
+      </c>
+      <c r="U775" t="inlineStr">
+        <is>
+          <t>78787.0</t>
+        </is>
+      </c>
+      <c r="V775" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="W775" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="X775" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y775" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-08-26T05:04</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E776" t="n">
+        <v>220</v>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G776" t="n">
+        <v>2456.9</v>
+      </c>
+      <c r="H776" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="I776" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K776" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L776" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M776" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N776" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O776" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P776" t="n">
+        <v>0.2218</v>
+      </c>
+      <c r="Q776" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S776" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="T776" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="U776" t="inlineStr">
+        <is>
+          <t>2456.9</t>
+        </is>
+      </c>
+      <c r="V776" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="W776" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="X776" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y776" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-08-26T05:49</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E777" t="n">
+        <v>70</v>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G777" t="n">
+        <v>79040.10000000001</v>
+      </c>
+      <c r="H777" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="I777" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K777" t="n">
+        <v>1</v>
+      </c>
+      <c r="L777" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M777" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N777" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O777" t="n">
+        <v>0</v>
+      </c>
+      <c r="P777" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="Q777" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="S777" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="T777" t="n">
+        <v>104.19</v>
+      </c>
+      <c r="U777" t="inlineStr">
+        <is>
+          <t>79040.1</t>
+        </is>
+      </c>
+      <c r="V777" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="W777" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="X777" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y777" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-08-26T05:49</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E778" t="n">
+        <v>230</v>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G778" t="n">
+        <v>2464.06</v>
+      </c>
+      <c r="H778" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="I778" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K778" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L778" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M778" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N778" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O778" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P778" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="Q778" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S778" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="T778" t="n">
+        <v>102.03</v>
+      </c>
+      <c r="U778" t="inlineStr">
+        <is>
+          <t>2464.06</t>
+        </is>
+      </c>
+      <c r="V778" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W778" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X778" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y778" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-08-26T06:39</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E779" t="n">
+        <v>70</v>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G779" t="n">
+        <v>78861.7</v>
+      </c>
+      <c r="H779" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I779" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K779" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L779" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M779" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N779" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O779" t="n">
+        <v>0</v>
+      </c>
+      <c r="P779" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="Q779" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="S779" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="T779" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="U779" t="inlineStr">
+        <is>
+          <t>78861.7</t>
+        </is>
+      </c>
+      <c r="V779" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="W779" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="X779" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y779" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-08-26T06:39</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E780" t="n">
+        <v>220</v>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G780" t="n">
+        <v>2456.39</v>
+      </c>
+      <c r="H780" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="I780" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K780" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L780" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M780" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N780" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O780" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P780" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="Q780" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S780" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="T780" t="n">
+        <v>100.23</v>
+      </c>
+      <c r="U780" t="inlineStr">
+        <is>
+          <t>2456.39</t>
+        </is>
+      </c>
+      <c r="V780" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="W780" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="X780" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y780" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-08-26T07:32</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E781" t="n">
+        <v>70</v>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G781" t="n">
+        <v>78908</v>
+      </c>
+      <c r="H781" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I781" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K781" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L781" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M781" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N781" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O781" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P781" t="n">
+        <v>0.7299</v>
+      </c>
+      <c r="Q781" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="S781" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="T781" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="U781" t="inlineStr">
+        <is>
+          <t>78908.0</t>
+        </is>
+      </c>
+      <c r="V781" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="W781" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="X781" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y781" t="inlineStr">
+        <is>
+          <t>IV rank 79% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-08-26T07:32</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E782" t="n">
+        <v>650</v>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G782" t="n">
+        <v>78908</v>
+      </c>
+      <c r="H782" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I782" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K782" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L782" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M782" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N782" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O782" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P782" t="n">
+        <v>-0.9074</v>
+      </c>
+      <c r="Q782" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="S782" t="n">
+        <v>-100.23</v>
+      </c>
+      <c r="T782" t="n">
+        <v>100.23</v>
+      </c>
+      <c r="U782" t="inlineStr">
+        <is>
+          <t>78908.0</t>
+        </is>
+      </c>
+      <c r="V782" t="n">
+        <v>-104.39</v>
+      </c>
+      <c r="W782" t="n">
+        <v>-10.439</v>
+      </c>
+      <c r="X782" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y782" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-08-26T07:32</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E783" t="n">
+        <v>210</v>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G783" t="n">
+        <v>2462.05</v>
+      </c>
+      <c r="H783" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I783" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K783" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L783" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M783" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N783" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O783" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P783" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="Q783" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S783" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="T783" t="n">
+        <v>98.09</v>
+      </c>
+      <c r="U783" t="inlineStr">
+        <is>
+          <t>2462.05</t>
+        </is>
+      </c>
+      <c r="V783" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="W783" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="X783" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y783" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-08-26T08:23</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E784" t="n">
+        <v>70</v>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G784" t="n">
+        <v>78961</v>
+      </c>
+      <c r="H784" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I784" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K784" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L784" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M784" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N784" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O784" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P784" t="n">
+        <v>0.6858</v>
+      </c>
+      <c r="Q784" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="S784" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T784" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="U784" t="inlineStr">
+        <is>
+          <t>78961.0</t>
+        </is>
+      </c>
+      <c r="V784" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="W784" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="X784" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y784" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-08-26T08:23</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E785" t="n">
+        <v>930</v>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G785" t="n">
+        <v>78961</v>
+      </c>
+      <c r="H785" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I785" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K785" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L785" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M785" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N785" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O785" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P785" t="n">
+        <v>-0.8851</v>
+      </c>
+      <c r="Q785" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="S785" t="n">
+        <v>-99.88</v>
+      </c>
+      <c r="T785" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="U785" t="inlineStr">
+        <is>
+          <t>78961.0</t>
+        </is>
+      </c>
+      <c r="V785" t="n">
+        <v>-103.97</v>
+      </c>
+      <c r="W785" t="n">
+        <v>-10.397</v>
+      </c>
+      <c r="X785" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y785" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-08-26T08:23</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E786" t="n">
+        <v>210</v>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G786" t="n">
+        <v>2460.35</v>
+      </c>
+      <c r="H786" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I786" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K786" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L786" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M786" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N786" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O786" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P786" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="Q786" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S786" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="T786" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="U786" t="inlineStr">
+        <is>
+          <t>2460.35</t>
+        </is>
+      </c>
+      <c r="V786" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W786" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="X786" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y786" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:10</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>60</v>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G787" t="n">
+        <v>78815.10000000001</v>
+      </c>
+      <c r="H787" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I787" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K787" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L787" t="n">
+        <v>78800</v>
+      </c>
+      <c r="M787" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N787" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O787" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P787" t="n">
+        <v>0.7229</v>
+      </c>
+      <c r="Q787" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="S787" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T787" t="n">
+        <v>92.36</v>
+      </c>
+      <c r="U787" t="inlineStr">
+        <is>
+          <t>78815.1</t>
+        </is>
+      </c>
+      <c r="V787" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W787" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="X787" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y787" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:10</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E788" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G788" t="n">
+        <v>78815.10000000001</v>
+      </c>
+      <c r="H788" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I788" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K788" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L788" t="n">
+        <v>78800</v>
+      </c>
+      <c r="M788" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N788" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O788" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P788" t="n">
+        <v>-0.7714</v>
+      </c>
+      <c r="Q788" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="S788" t="n">
+        <v>-99.95</v>
+      </c>
+      <c r="T788" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="U788" t="inlineStr">
+        <is>
+          <t>78815.1</t>
+        </is>
+      </c>
+      <c r="V788" t="n">
+        <v>-104</v>
+      </c>
+      <c r="W788" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="X788" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y788" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:10</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E789" t="n">
+        <v>460</v>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G789" t="n">
+        <v>78815.10000000001</v>
+      </c>
+      <c r="H789" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I789" t="n">
+        <v>1</v>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K789" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L789" t="n">
+        <v>78800</v>
+      </c>
+      <c r="M789" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N789" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O789" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P789" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="Q789" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="R789" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S789" t="n">
+        <v>-7.54</v>
+      </c>
+      <c r="T789" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="U789" t="inlineStr">
+        <is>
+          <t>78815.1</t>
+        </is>
+      </c>
+      <c r="V789" t="n">
+        <v>-79.67</v>
+      </c>
+      <c r="W789" t="n">
+        <v>-7.967</v>
+      </c>
+      <c r="X789" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y789" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.8 · 2.8h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:10</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>210</v>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G790" t="n">
+        <v>2458.6</v>
+      </c>
+      <c r="H790" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="I790" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K790" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L790" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M790" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N790" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O790" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P790" t="n">
+        <v>0.2209</v>
+      </c>
+      <c r="Q790" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S790" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="T790" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="U790" t="inlineStr">
+        <is>
+          <t>2458.6</t>
+        </is>
+      </c>
+      <c r="V790" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W790" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X790" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y790" t="inlineStr">
+        <is>
+          <t>IV rank 54% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:10</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E791" t="n">
+        <v>740</v>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G791" t="n">
+        <v>2458.6</v>
+      </c>
+      <c r="H791" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="I791" t="n">
+        <v>1</v>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K791" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L791" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M791" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N791" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O791" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="P791" t="n">
+        <v>-0.1797</v>
+      </c>
+      <c r="Q791" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="R791" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S791" t="n">
+        <v>-26.27</v>
+      </c>
+      <c r="T791" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="U791" t="inlineStr">
+        <is>
+          <t>2458.6</t>
+        </is>
+      </c>
+      <c r="V791" t="n">
+        <v>-111.89</v>
+      </c>
+      <c r="W791" t="n">
+        <v>-11.189</v>
+      </c>
+      <c r="X791" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y791" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.7 · 2.8h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:56</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E792" t="n">
+        <v>60</v>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G792" t="n">
+        <v>78426.2</v>
+      </c>
+      <c r="H792" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I792" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K792" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L792" t="n">
+        <v>78400</v>
+      </c>
+      <c r="M792" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N792" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O792" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P792" t="n">
+        <v>0.7224</v>
+      </c>
+      <c r="Q792" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S792" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T792" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="U792" t="inlineStr">
+        <is>
+          <t>78426.2</t>
+        </is>
+      </c>
+      <c r="V792" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W792" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="X792" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y792" t="inlineStr">
+        <is>
+          <t>IV rank 54% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:56</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E793" t="n">
+        <v>2350</v>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G793" t="n">
+        <v>78426.2</v>
+      </c>
+      <c r="H793" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I793" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K793" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L793" t="n">
+        <v>78400</v>
+      </c>
+      <c r="M793" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N793" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O793" t="n">
+        <v>0</v>
+      </c>
+      <c r="P793" t="n">
+        <v>-0.8046</v>
+      </c>
+      <c r="Q793" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="S793" t="n">
+        <v>-100.11</v>
+      </c>
+      <c r="T793" t="n">
+        <v>100.11</v>
+      </c>
+      <c r="U793" t="inlineStr">
+        <is>
+          <t>78426.2</t>
+        </is>
+      </c>
+      <c r="V793" t="n">
+        <v>-104.11</v>
+      </c>
+      <c r="W793" t="n">
+        <v>-10.411</v>
+      </c>
+      <c r="X793" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y793" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:56</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E794" t="n">
+        <v>480</v>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G794" t="n">
+        <v>78426.2</v>
+      </c>
+      <c r="H794" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I794" t="n">
+        <v>1</v>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K794" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L794" t="n">
+        <v>78400</v>
+      </c>
+      <c r="M794" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N794" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O794" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P794" t="n">
+        <v>-0.1245</v>
+      </c>
+      <c r="Q794" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="R794" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S794" t="n">
+        <v>-4.51</v>
+      </c>
+      <c r="T794" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="U794" t="inlineStr">
+        <is>
+          <t>78426.2</t>
+        </is>
+      </c>
+      <c r="V794" t="n">
+        <v>-85.54000000000001</v>
+      </c>
+      <c r="W794" t="n">
+        <v>-8.554</v>
+      </c>
+      <c r="X794" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y794" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.9 · 2.1h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:56</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E795" t="n">
+        <v>210</v>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G795" t="n">
+        <v>2447.61</v>
+      </c>
+      <c r="H795" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I795" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K795" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L795" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M795" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N795" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O795" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P795" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="Q795" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S795" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="T795" t="n">
+        <v>100.97</v>
+      </c>
+      <c r="U795" t="inlineStr">
+        <is>
+          <t>2447.61</t>
+        </is>
+      </c>
+      <c r="V795" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="W795" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="X795" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y795" t="inlineStr">
+        <is>
+          <t>IV rank 42% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:57</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E796" t="n">
+        <v>700</v>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G796" t="n">
+        <v>2447.61</v>
+      </c>
+      <c r="H796" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I796" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K796" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L796" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M796" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N796" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O796" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="P796" t="n">
+        <v>-0.3033</v>
+      </c>
+      <c r="Q796" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="R796" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="S796" t="n">
+        <v>-30.24</v>
+      </c>
+      <c r="T796" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="U796" t="inlineStr">
+        <is>
+          <t>2447.61</t>
+        </is>
+      </c>
+      <c r="V796" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="W796" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="X796" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y796" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 3.2 · 2.1h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-08-26T10:34</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>60</v>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G797" t="n">
+        <v>78640</v>
+      </c>
+      <c r="H797" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="I797" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K797" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L797" t="n">
+        <v>78600</v>
+      </c>
+      <c r="M797" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N797" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O797" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P797" t="n">
+        <v>1.0255</v>
+      </c>
+      <c r="Q797" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S797" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T797" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="U797" t="inlineStr">
+        <is>
+          <t>78640.0</t>
+        </is>
+      </c>
+      <c r="V797" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W797" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="X797" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y797" t="inlineStr">
+        <is>
+          <t>IV rank 29% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-08-26T10:34</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>3960</v>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G798" t="n">
+        <v>78640</v>
+      </c>
+      <c r="H798" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="I798" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K798" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L798" t="n">
+        <v>78600</v>
+      </c>
+      <c r="M798" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N798" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O798" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P798" t="n">
+        <v>-0.7931</v>
+      </c>
+      <c r="Q798" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="S798" t="n">
+        <v>-100.19</v>
+      </c>
+      <c r="T798" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="U798" t="inlineStr">
+        <is>
+          <t>78640.0</t>
+        </is>
+      </c>
+      <c r="V798" t="n">
+        <v>-104.15</v>
+      </c>
+      <c r="W798" t="n">
+        <v>-10.415</v>
+      </c>
+      <c r="X798" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y798" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-08-26T10:34</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>430</v>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G799" t="n">
+        <v>78640</v>
+      </c>
+      <c r="H799" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="I799" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K799" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L799" t="n">
+        <v>78600</v>
+      </c>
+      <c r="M799" t="n">
+        <v>78200</v>
+      </c>
+      <c r="N799" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O799" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P799" t="n">
+        <v>-0.0293</v>
+      </c>
+      <c r="Q799" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R799" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S799" t="n">
+        <v>-13.42</v>
+      </c>
+      <c r="T799" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="U799" t="inlineStr">
+        <is>
+          <t>78640.0</t>
+        </is>
+      </c>
+      <c r="V799" t="n">
+        <v>-14.53</v>
+      </c>
+      <c r="W799" t="n">
+        <v>-1.453</v>
+      </c>
+      <c r="X799" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y799" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.6 · 1.4h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-08-26T10:34</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G800" t="n">
+        <v>2455.92</v>
+      </c>
+      <c r="H800" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="I800" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K800" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L800" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M800" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N800" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O800" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P800" t="n">
+        <v>-0.6622</v>
+      </c>
+      <c r="Q800" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="S800" t="n">
+        <v>-100.32</v>
+      </c>
+      <c r="T800" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="U800" t="inlineStr">
+        <is>
+          <t>2455.92</t>
+        </is>
+      </c>
+      <c r="V800" t="n">
+        <v>-104.37</v>
+      </c>
+      <c r="W800" t="n">
+        <v>-10.437</v>
+      </c>
+      <c r="X800" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y800" t="inlineStr">
+        <is>
+          <t>IV rank 17% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-08-26T10:34</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>680</v>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G801" t="n">
+        <v>2455.92</v>
+      </c>
+      <c r="H801" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="I801" t="n">
+        <v>1</v>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K801" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L801" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M801" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N801" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O801" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="P801" t="n">
+        <v>-0.0809</v>
+      </c>
+      <c r="Q801" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="R801" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S801" t="n">
+        <v>-31.28</v>
+      </c>
+      <c r="T801" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="U801" t="inlineStr">
+        <is>
+          <t>2455.92</t>
+        </is>
+      </c>
+      <c r="V801" t="n">
+        <v>-86.7</v>
+      </c>
+      <c r="W801" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="X801" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y801" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.4 · 1.4h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-08-26T11:06</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E802" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G802" t="n">
+        <v>78748.10000000001</v>
+      </c>
+      <c r="H802" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="I802" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K802" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L802" t="n">
+        <v>78800</v>
+      </c>
+      <c r="M802" t="n">
+        <v>78400</v>
+      </c>
+      <c r="N802" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O802" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P802" t="n">
+        <v>-1.8687</v>
+      </c>
+      <c r="Q802" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="S802" t="n">
+        <v>-99.84</v>
+      </c>
+      <c r="T802" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="U802" t="inlineStr">
+        <is>
+          <t>78748.1</t>
+        </is>
+      </c>
+      <c r="V802" t="n">
+        <v>-104.01</v>
+      </c>
+      <c r="W802" t="n">
+        <v>-10.401</v>
+      </c>
+      <c r="X802" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y802" t="inlineStr">
+        <is>
+          <t>IV rank 17% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-08-26T11:06</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E803" t="n">
+        <v>11650</v>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G803" t="n">
+        <v>78748.10000000001</v>
+      </c>
+      <c r="H803" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="I803" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K803" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L803" t="n">
+        <v>78800</v>
+      </c>
+      <c r="M803" t="n">
+        <v>78400</v>
+      </c>
+      <c r="N803" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O803" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P803" t="n">
+        <v>-0.598</v>
+      </c>
+      <c r="Q803" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="S803" t="n">
+        <v>-100.19</v>
+      </c>
+      <c r="T803" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="U803" t="inlineStr">
+        <is>
+          <t>78748.1</t>
+        </is>
+      </c>
+      <c r="V803" t="n">
+        <v>-103.69</v>
+      </c>
+      <c r="W803" t="n">
+        <v>-10.368</v>
+      </c>
+      <c r="X803" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y803" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-08-26T11:06</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E804" t="n">
+        <v>5460</v>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G804" t="n">
+        <v>2472.16</v>
+      </c>
+      <c r="H804" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I804" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K804" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L804" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M804" t="n">
+        <v>2420</v>
+      </c>
+      <c r="N804" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O804" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="P804" t="n">
+        <v>-0.7591</v>
+      </c>
+      <c r="Q804" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S804" t="n">
+        <v>-99.92</v>
+      </c>
+      <c r="T804" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="U804" t="inlineStr">
+        <is>
+          <t>2472.16</t>
+        </is>
+      </c>
+      <c r="V804" t="n">
+        <v>-104.29</v>
+      </c>
+      <c r="W804" t="n">
+        <v>-10.429</v>
+      </c>
+      <c r="X804" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y804" t="inlineStr">
+        <is>
+          <t>IV rank 12% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-08-26T13:32</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E805" t="n">
+        <v>70</v>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G805" t="n">
+        <v>78098.39999999999</v>
+      </c>
+      <c r="H805" t="n">
+        <v>39</v>
+      </c>
+      <c r="I805" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K805" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L805" t="n">
+        <v>78400</v>
+      </c>
+      <c r="M805" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N805" t="n">
+        <v>84400</v>
+      </c>
+      <c r="O805" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P805" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="Q805" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="S805" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="T805" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="U805" t="inlineStr"/>
+      <c r="V805" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="W805" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="X805" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Y805" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-08-26T13:32</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E806" t="n">
+        <v>300</v>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G806" t="n">
+        <v>2445.99</v>
+      </c>
+      <c r="H806" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="I806" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K806" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L806" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M806" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N806" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O806" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P806" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="Q806" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="S806" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="T806" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="U806" t="inlineStr"/>
+      <c r="X806" t="inlineStr"/>
+      <c r="Y806" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-08-26T16:50</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E807" t="n">
+        <v>70</v>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G807" t="n">
+        <v>78086.2</v>
+      </c>
+      <c r="H807" t="n">
+        <v>28</v>
+      </c>
+      <c r="I807" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K807" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L807" t="n">
+        <v>78200</v>
+      </c>
+      <c r="M807" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N807" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O807" t="n">
+        <v>0</v>
+      </c>
+      <c r="P807" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="Q807" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="S807" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="T807" t="n">
+        <v>100.43</v>
+      </c>
+      <c r="U807" t="inlineStr"/>
+      <c r="X807" t="inlineStr"/>
+      <c r="Y807" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-08-26T21:40</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E808" t="n">
+        <v>1</v>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G808" t="n">
+        <v>4593.6</v>
+      </c>
+      <c r="S808" t="n">
+        <v>0</v>
+      </c>
+      <c r="T808" t="n">
+        <v>10</v>
+      </c>
+      <c r="U808" t="inlineStr"/>
+      <c r="X808" t="inlineStr"/>
+      <c r="Y808" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
         </is>
       </c>
     </row>
@@ -70600,22 +74268,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C2" t="n">
-        <v>97.5</v>
+        <v>97.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>5.91</v>
       </c>
       <c r="E2" t="n">
-        <v>1897.79</v>
+        <v>2070.69</v>
       </c>
       <c r="F2" t="n">
-        <v>5.23</v>
+        <v>5.35</v>
       </c>
       <c r="G2" t="n">
-        <v>189.78</v>
+        <v>207.07</v>
       </c>
     </row>
     <row r="3">
@@ -70700,22 +74368,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
-        <v>70.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="E6" t="n">
-        <v>-278.85</v>
+        <v>-326.87</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.58</v>
+        <v>-1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>-27.89</v>
+        <v>-32.69</v>
       </c>
     </row>
     <row r="7">
@@ -70750,22 +74418,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>-2041.98</v>
+        <v>-2451.81</v>
       </c>
       <c r="F8" t="n">
-        <v>-48.62</v>
+        <v>-51.08</v>
       </c>
       <c r="G8" t="n">
-        <v>-204.2</v>
+        <v>-245.18</v>
       </c>
     </row>
     <row r="9">
@@ -70775,22 +74443,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-6699.31</v>
+        <v>-7011.98</v>
       </c>
       <c r="F9" t="n">
-        <v>-99.98999999999999</v>
+        <v>-100.17</v>
       </c>
       <c r="G9" t="n">
-        <v>-669.9299999999999</v>
+        <v>-701.2</v>
       </c>
     </row>
     <row r="10">
@@ -70800,7 +74468,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -70809,13 +74477,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-8315.25</v>
+        <v>-8939.559999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-103.94</v>
+        <v>-103.95</v>
       </c>
       <c r="G10" t="n">
-        <v>-831.52</v>
+        <v>-893.96</v>
       </c>
     </row>
   </sheetData>
@@ -70829,7 +74497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -71535,26 +75203,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25T13:34</t>
+          <t>2026-08-26T13:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -71562,77 +75230,77 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>78910.39999999999</v>
+        <v>2445.99</v>
       </c>
       <c r="H9" t="n">
-        <v>46.4</v>
+        <v>51.4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.831</v>
+        <v>0.694</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.29</v>
+        <v>0.64</v>
       </c>
       <c r="L9" t="n">
-        <v>79000</v>
+        <v>2450</v>
       </c>
       <c r="M9" t="n">
-        <v>75200</v>
+        <v>2380</v>
       </c>
       <c r="N9" t="n">
-        <v>83600</v>
+        <v>2720</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0977</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0059</v>
+        <v>-0.0028</v>
       </c>
       <c r="S9" t="n">
-        <v>-100.78</v>
+        <v>21.42</v>
       </c>
       <c r="T9" t="n">
-        <v>100.78</v>
+        <v>98.58</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>trending up +7.9% — skewed fly</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25T13:34</t>
+          <t>2026-08-26T16:50</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -71640,13 +75308,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2468.42</v>
+        <v>78086.2</v>
       </c>
       <c r="H10" t="n">
-        <v>59.4</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
-        <v>0.718</v>
+        <v>0.681</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -71654,63 +75322,63 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="L10" t="n">
-        <v>2470</v>
+        <v>78200</v>
       </c>
       <c r="M10" t="n">
-        <v>2400</v>
+        <v>77000</v>
       </c>
       <c r="N10" t="n">
-        <v>2680</v>
+        <v>84000</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0021</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0202</v>
+        <v>0.2361</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="S10" t="n">
-        <v>-100.17</v>
+        <v>11.57</v>
       </c>
       <c r="T10" t="n">
-        <v>100.17</v>
+        <v>100.43</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>trending up +6.0% — skewed fly</t>
+          <t>IV rank 83% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25T17:27</t>
+          <t>2026-08-26T21:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>XAUTUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>perpetual</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -71718,129 +75386,19 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>78823.89999999999</v>
-      </c>
-      <c r="H11" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="L11" t="n">
-        <v>79000</v>
-      </c>
-      <c r="M11" t="n">
-        <v>75200</v>
-      </c>
-      <c r="N11" t="n">
-        <v>83600</v>
-      </c>
-      <c r="O11" t="n">
+        <v>4593.6</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
-        <v>0.2515</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.0115</v>
-      </c>
-      <c r="S11" t="n">
-        <v>12.69</v>
-      </c>
       <c r="T11" t="n">
-        <v>99.31</v>
+        <v>10</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>IV rank 91% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-25T18:37</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>230</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>2466.76</v>
-      </c>
-      <c r="H12" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2470</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2360</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2680</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.1198</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-0.0034</v>
-      </c>
-      <c r="S12" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="T12" t="n">
-        <v>98.48999999999999</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>IV rank 83% rich — sell premium</t>
+          <t>20/50 EMA 3rd retest</t>
         </is>
       </c>
     </row>
@@ -71861,7 +75419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25T20:16:32.167814 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-26T22:34:38.784316 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y808"/>
+  <dimension ref="A1:Y811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -47119,7 +47119,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G512" t="n">
@@ -47164,7 +47164,17 @@
         <v>100.68</v>
       </c>
       <c r="U512" t="inlineStr"/>
-      <c r="X512" t="inlineStr"/>
+      <c r="V512" t="n">
+        <v>-66.95999999999999</v>
+      </c>
+      <c r="W512" t="n">
+        <v>-6.696</v>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="Y512" t="inlineStr">
         <is>
           <t>trending up +35.4% — skewed fly</t>
@@ -64129,7 +64139,7 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G698" t="n">
@@ -64174,7 +64184,17 @@
         <v>106.42</v>
       </c>
       <c r="U698" t="inlineStr"/>
-      <c r="X698" t="inlineStr"/>
+      <c r="V698" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="W698" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="X698" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="Y698" t="inlineStr">
         <is>
           <t>IV rank 96% rich — sell premium</t>
@@ -64285,7 +64305,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G700" t="n">
@@ -64330,7 +64350,17 @@
         <v>101.84</v>
       </c>
       <c r="U700" t="inlineStr"/>
-      <c r="X700" t="inlineStr"/>
+      <c r="V700" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W700" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="X700" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="Y700" t="inlineStr">
         <is>
           <t>IV rank 96% rich — sell premium</t>
@@ -74025,7 +74055,7 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G806" t="n">
@@ -74069,8 +74099,22 @@
       <c r="T806" t="n">
         <v>98.58</v>
       </c>
-      <c r="U806" t="inlineStr"/>
-      <c r="X806" t="inlineStr"/>
+      <c r="U806" t="inlineStr">
+        <is>
+          <t>2489.06</t>
+        </is>
+      </c>
+      <c r="V806" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="W806" t="n">
+        <v>1.959</v>
+      </c>
+      <c r="X806" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="Y806" t="inlineStr">
         <is>
           <t>IV rank 96% rich — sell premium</t>
@@ -74103,7 +74147,7 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G807" t="n">
@@ -74147,8 +74191,22 @@
       <c r="T807" t="n">
         <v>100.43</v>
       </c>
-      <c r="U807" t="inlineStr"/>
-      <c r="X807" t="inlineStr"/>
+      <c r="U807" t="inlineStr">
+        <is>
+          <t>78671.9</t>
+        </is>
+      </c>
+      <c r="V807" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="W807" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="X807" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="Y807" t="inlineStr">
         <is>
           <t>IV rank 83% rich — sell premium</t>
@@ -74181,7 +74239,7 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G808" t="n">
@@ -74193,11 +74251,259 @@
       <c r="T808" t="n">
         <v>10</v>
       </c>
-      <c r="U808" t="inlineStr"/>
-      <c r="X808" t="inlineStr"/>
+      <c r="U808" t="inlineStr">
+        <is>
+          <t>4606.38</t>
+        </is>
+      </c>
+      <c r="V808" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="W808" t="n">
+        <v>-1.424</v>
+      </c>
+      <c r="X808" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="Y808" t="inlineStr">
         <is>
           <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-08-27T21:01</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E809" t="n">
+        <v>60</v>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G809" t="n">
+        <v>80016.2</v>
+      </c>
+      <c r="H809" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I809" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K809" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L809" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M809" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N809" t="n">
+        <v>88000</v>
+      </c>
+      <c r="O809" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P809" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="Q809" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="S809" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="T809" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="U809" t="inlineStr"/>
+      <c r="X809" t="inlineStr"/>
+      <c r="Y809" t="inlineStr">
+        <is>
+          <t>IV rank 64% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-08-27T21:01</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E810" t="n">
+        <v>180</v>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G810" t="n">
+        <v>2503.53</v>
+      </c>
+      <c r="H810" t="n">
+        <v>31</v>
+      </c>
+      <c r="I810" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K810" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L810" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M810" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N810" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O810" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P810" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="Q810" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S810" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="T810" t="n">
+        <v>100.87</v>
+      </c>
+      <c r="U810" t="inlineStr"/>
+      <c r="X810" t="inlineStr"/>
+      <c r="Y810" t="inlineStr">
+        <is>
+          <t>IV rank 64% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-08-27T21:01</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E811" t="n">
+        <v>120</v>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G811" t="n">
+        <v>2503.53</v>
+      </c>
+      <c r="H811" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="I811" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K811" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="L811" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M811" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N811" t="n">
+        <v>2900</v>
+      </c>
+      <c r="O811" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P811" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q811" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="S811" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="T811" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="U811" t="inlineStr"/>
+      <c r="X811" t="inlineStr"/>
+      <c r="Y811" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -74268,22 +74574,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C2" t="n">
         <v>97.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5.91</v>
+        <v>5.99</v>
       </c>
       <c r="E2" t="n">
-        <v>2070.69</v>
+        <v>2101.17</v>
       </c>
       <c r="F2" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="G2" t="n">
-        <v>207.07</v>
+        <v>210.12</v>
       </c>
     </row>
     <row r="3">
@@ -74293,22 +74599,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="E3" t="n">
-        <v>-15.88</v>
+        <v>-30.12</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.65</v>
+        <v>-4.3</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.59</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="4">
@@ -74343,22 +74649,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>57.1</v>
+        <v>62.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>-161.12</v>
+        <v>-153.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.51</v>
+        <v>-9.58</v>
       </c>
       <c r="G5" t="n">
-        <v>-16.11</v>
+        <v>-15.32</v>
       </c>
     </row>
     <row r="6">
@@ -74393,7 +74699,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -74402,13 +74708,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-449.86</v>
+        <v>-516.8200000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-89.97</v>
+        <v>-86.14</v>
       </c>
       <c r="G7" t="n">
-        <v>-44.99</v>
+        <v>-51.68</v>
       </c>
     </row>
     <row r="8">
@@ -74497,7 +74803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -74813,12 +75119,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21T22:18</t>
+          <t>2026-08-25T01:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -74828,11 +75134,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -74840,13 +75146,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2540.48</v>
+        <v>79719.3</v>
       </c>
       <c r="H4" t="n">
-        <v>66.7</v>
+        <v>45.15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.588</v>
+        <v>0.598</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -74854,37 +75160,37 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.78</v>
+        <v>1.85</v>
       </c>
       <c r="L4" t="n">
-        <v>2300</v>
+        <v>77000</v>
       </c>
       <c r="M4" t="n">
-        <v>2200</v>
+        <v>77500</v>
       </c>
       <c r="N4" t="n">
-        <v>2700</v>
+        <v>77500</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.001</v>
+        <v>-0.0001</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0042</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007</v>
+        <v>0.0045</v>
       </c>
       <c r="S4" t="n">
-        <v>-100.68</v>
+        <v>-103.09</v>
       </c>
       <c r="T4" t="n">
-        <v>100.68</v>
+        <v>103.09</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>trending up +35.4% — skewed fly</t>
+          <t>trending up +9.0% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -74896,12 +75202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -74910,7 +75216,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>2260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -74918,13 +75224,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>79719.3</v>
+        <v>2493.71</v>
       </c>
       <c r="H5" t="n">
-        <v>45.15</v>
+        <v>61.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.526</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -74932,44 +75238,44 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="L5" t="n">
-        <v>77000</v>
+        <v>2350</v>
       </c>
       <c r="M5" t="n">
-        <v>77500</v>
+        <v>2200</v>
       </c>
       <c r="N5" t="n">
-        <v>77500</v>
+        <v>2800</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0139</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0003</v>
       </c>
       <c r="S5" t="n">
-        <v>13.58</v>
+        <v>-100.12</v>
       </c>
       <c r="T5" t="n">
-        <v>106.42</v>
+        <v>100.12</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>trending up +7.1% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25T01:18</t>
+          <t>2026-08-27T21:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -74979,16 +75285,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -74996,58 +75302,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>79719.3</v>
+        <v>80016.2</v>
       </c>
       <c r="H6" t="n">
-        <v>45.15</v>
+        <v>23.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.598</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="L6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M6" t="n">
         <v>77000</v>
       </c>
-      <c r="M6" t="n">
-        <v>77500</v>
-      </c>
       <c r="N6" t="n">
-        <v>77500</v>
+        <v>88000</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.2841</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0045</v>
+        <v>-0.012</v>
       </c>
       <c r="S6" t="n">
-        <v>-103.09</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>103.09</v>
+        <v>99.38</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +9.0% — skewed fly</t>
+          <t>IV rank 64% — default sell</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25T01:18</t>
+          <t>2026-08-27T21:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -75057,16 +75363,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -75074,58 +75380,58 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2493.71</v>
+        <v>2503.53</v>
       </c>
       <c r="H7" t="n">
-        <v>61.8</v>
+        <v>31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.68</v>
+        <v>0.719</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.22</v>
+        <v>0.76</v>
       </c>
       <c r="L7" t="n">
-        <v>2350</v>
+        <v>2500</v>
       </c>
       <c r="M7" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="N7" t="n">
         <v>2800</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0047</v>
+        <v>0.0693</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0019</v>
+        <v>-0.0029</v>
       </c>
       <c r="S7" t="n">
-        <v>13.16</v>
+        <v>7.13</v>
       </c>
       <c r="T7" t="n">
-        <v>101.84</v>
+        <v>100.87</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>IV rank 64% — default sell</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25T01:18</t>
+          <t>2026-08-27T21:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -75135,7 +75441,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -75144,7 +75450,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2260</v>
+        <v>120</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -75152,13 +75458,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2493.71</v>
+        <v>2503.53</v>
       </c>
       <c r="H8" t="n">
-        <v>61.8</v>
+        <v>50.7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.526</v>
+        <v>0.622</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -75166,239 +75472,37 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2.22</v>
+        <v>3.22</v>
       </c>
       <c r="L8" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="M8" t="n">
         <v>2200</v>
       </c>
       <c r="N8" t="n">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0165</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0003</v>
+        <v>-0.0053</v>
       </c>
       <c r="S8" t="n">
-        <v>-100.12</v>
+        <v>20.29</v>
       </c>
       <c r="T8" t="n">
-        <v>100.12</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>trending up +7.1% — skewed fly</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-08-26T13:32</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2445.99</v>
-      </c>
-      <c r="H9" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2450</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2380</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2720</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.07920000000000001</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.0028</v>
-      </c>
-      <c r="S9" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="T9" t="n">
-        <v>98.58</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>IV rank 96% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-26T16:50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>70</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>78086.2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>28</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L10" t="n">
-        <v>78200</v>
-      </c>
-      <c r="M10" t="n">
-        <v>77000</v>
-      </c>
-      <c r="N10" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.2361</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.0126</v>
-      </c>
-      <c r="S10" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="T10" t="n">
-        <v>100.43</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>IV rank 83% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-08-26T21:40</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>XAUTUSD</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>gold_ema</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>perpetual</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>4593.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>10</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>20/50 EMA 3rd retest</t>
+          <t>IV rank 92% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -75419,7 +75523,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-26T22:34:38.784316 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-28T03:54:26.433137 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y811"/>
+  <dimension ref="A1:Y815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27905,7 +27905,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -27949,8 +27949,22 @@
       <c r="T301" t="n">
         <v>94.11</v>
       </c>
-      <c r="U301" t="inlineStr"/>
-      <c r="X301" t="inlineStr"/>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>79592.8</t>
+        </is>
+      </c>
+      <c r="V301" t="n">
+        <v>-157.14</v>
+      </c>
+      <c r="W301" t="n">
+        <v>-15.714</v>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="Y301" t="inlineStr">
         <is>
           <t>IV rank 100% rich — sell premium</t>
@@ -34045,7 +34059,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -34089,8 +34103,22 @@
       <c r="T368" t="n">
         <v>97.55</v>
       </c>
-      <c r="U368" t="inlineStr"/>
-      <c r="X368" t="inlineStr"/>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>79592.8</t>
+        </is>
+      </c>
+      <c r="V368" t="n">
+        <v>-113.39</v>
+      </c>
+      <c r="W368" t="n">
+        <v>-11.339</v>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="Y368" t="inlineStr">
         <is>
           <t>trending up +5.5% — skewed fly</t>
@@ -74299,7 +74327,7 @@
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G809" t="n">
@@ -74343,8 +74371,22 @@
       <c r="T809" t="n">
         <v>99.38</v>
       </c>
-      <c r="U809" t="inlineStr"/>
-      <c r="X809" t="inlineStr"/>
+      <c r="U809" t="inlineStr">
+        <is>
+          <t>79592.8</t>
+        </is>
+      </c>
+      <c r="V809" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="W809" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="X809" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="Y809" t="inlineStr">
         <is>
           <t>IV rank 64% — default sell</t>
@@ -74377,7 +74419,7 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G810" t="n">
@@ -74421,8 +74463,22 @@
       <c r="T810" t="n">
         <v>100.87</v>
       </c>
-      <c r="U810" t="inlineStr"/>
-      <c r="X810" t="inlineStr"/>
+      <c r="U810" t="inlineStr">
+        <is>
+          <t>2483.47</t>
+        </is>
+      </c>
+      <c r="V810" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="W810" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="X810" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="Y810" t="inlineStr">
         <is>
           <t>IV rank 64% — default sell</t>
@@ -74504,6 +74560,356 @@
       <c r="Y811" t="inlineStr">
         <is>
           <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-08-28T05:22</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E812" t="n">
+        <v>60</v>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G812" t="n">
+        <v>79592.8</v>
+      </c>
+      <c r="H812" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="I812" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K812" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="L812" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M812" t="n">
+        <v>67000</v>
+      </c>
+      <c r="N812" t="n">
+        <v>88000</v>
+      </c>
+      <c r="O812" t="n">
+        <v>0</v>
+      </c>
+      <c r="P812" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="Q812" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="S812" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="T812" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="U812" t="inlineStr"/>
+      <c r="X812" t="inlineStr"/>
+      <c r="Y812" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-08-28T17:33</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E813" t="n">
+        <v>70</v>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G813" t="n">
+        <v>77995.60000000001</v>
+      </c>
+      <c r="H813" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I813" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K813" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L813" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M813" t="n">
+        <v>76600</v>
+      </c>
+      <c r="N813" t="n">
+        <v>83600</v>
+      </c>
+      <c r="O813" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P813" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="Q813" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="S813" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="T813" t="n">
+        <v>100.82</v>
+      </c>
+      <c r="U813" t="inlineStr">
+        <is>
+          <t>77667.9</t>
+        </is>
+      </c>
+      <c r="V813" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="W813" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="X813" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="Y813" t="inlineStr">
+        <is>
+          <t>IV rank 81% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-08-28T17:33</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E814" t="n">
+        <v>230</v>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G814" t="n">
+        <v>2445.67</v>
+      </c>
+      <c r="H814" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="I814" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K814" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L814" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M814" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N814" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O814" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P814" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="Q814" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="S814" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="T814" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U814" t="inlineStr"/>
+      <c r="V814" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="W814" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="X814" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Y814" t="inlineStr">
+        <is>
+          <t>IV rank 65% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:09</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E815" t="n">
+        <v>210</v>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G815" t="n">
+        <v>2441.19</v>
+      </c>
+      <c r="H815" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="I815" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K815" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L815" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M815" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N815" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O815" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P815" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="Q815" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="S815" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="T815" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="U815" t="inlineStr">
+        <is>
+          <t>2441.19</t>
+        </is>
+      </c>
+      <c r="V815" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="W815" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="X815" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="Y815" t="inlineStr">
+        <is>
+          <t>IV rank 63% — default sell</t>
         </is>
       </c>
     </row>
@@ -74574,22 +74980,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C2" t="n">
         <v>97.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5.99</v>
+        <v>6.08</v>
       </c>
       <c r="E2" t="n">
-        <v>2101.17</v>
+        <v>2142.81</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="G2" t="n">
-        <v>210.12</v>
+        <v>214.28</v>
       </c>
     </row>
     <row r="3">
@@ -74649,22 +75055,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>62.5</v>
+        <v>58.8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="E5" t="n">
-        <v>-153.25</v>
+        <v>-310.39</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.58</v>
+        <v>-18.26</v>
       </c>
       <c r="G5" t="n">
-        <v>-15.32</v>
+        <v>-31.04</v>
       </c>
     </row>
     <row r="6">
@@ -74699,7 +75105,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -74708,13 +75114,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-516.8200000000001</v>
+        <v>-630.21</v>
       </c>
       <c r="F7" t="n">
-        <v>-86.14</v>
+        <v>-90.03</v>
       </c>
       <c r="G7" t="n">
-        <v>-51.68</v>
+        <v>-63.02</v>
       </c>
     </row>
     <row r="8">
@@ -74803,7 +75209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -74963,7 +75369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18T00:57</t>
+          <t>2026-08-25T01:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -74973,16 +75379,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -74990,63 +75396,63 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>64381.7</v>
+        <v>79719.3</v>
       </c>
       <c r="H2" t="n">
-        <v>25.35</v>
+        <v>45.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.522</v>
+        <v>0.598</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.85</v>
+        <v>1.85</v>
       </c>
       <c r="L2" t="n">
-        <v>64000</v>
+        <v>77000</v>
       </c>
       <c r="M2" t="n">
-        <v>58000</v>
+        <v>77500</v>
       </c>
       <c r="N2" t="n">
-        <v>75000</v>
+        <v>77500</v>
       </c>
       <c r="O2" t="n">
         <v>-0.0001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0357</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0316</v>
+        <v>0.0045</v>
       </c>
       <c r="S2" t="n">
-        <v>14.73</v>
+        <v>-103.09</v>
       </c>
       <c r="T2" t="n">
-        <v>94.11</v>
+        <v>103.09</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>IV rank 100% rich — sell premium</t>
+          <t>trending up +9.0% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19T15:06</t>
+          <t>2026-08-25T01:18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -75056,11 +75462,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>190</v>
+        <v>2260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -75068,68 +75474,68 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>66456.7</v>
+        <v>2493.71</v>
       </c>
       <c r="H3" t="n">
-        <v>25.65</v>
+        <v>61.8</v>
       </c>
       <c r="I3" t="n">
-        <v>0.645</v>
+        <v>0.526</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2.22</v>
       </c>
       <c r="L3" t="n">
-        <v>64500</v>
+        <v>2350</v>
       </c>
       <c r="M3" t="n">
-        <v>58000</v>
+        <v>2200</v>
       </c>
       <c r="N3" t="n">
-        <v>75000</v>
+        <v>2800</v>
       </c>
       <c r="O3" t="n">
         <v>-0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0086</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0055</v>
+        <v>-0.0003</v>
       </c>
       <c r="S3" t="n">
-        <v>-97.55</v>
+        <v>-100.12</v>
       </c>
       <c r="T3" t="n">
-        <v>97.55</v>
+        <v>100.12</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>trending up +5.5% — skewed fly</t>
+          <t>trending up +7.1% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25T01:18</t>
+          <t>2026-08-27T21:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -75138,7 +75544,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -75146,13 +75552,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>79719.3</v>
+        <v>2503.53</v>
       </c>
       <c r="H4" t="n">
-        <v>45.15</v>
+        <v>50.7</v>
       </c>
       <c r="I4" t="n">
-        <v>0.598</v>
+        <v>0.622</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -75160,54 +75566,54 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="L4" t="n">
-        <v>77000</v>
+        <v>2400</v>
       </c>
       <c r="M4" t="n">
-        <v>77500</v>
+        <v>2200</v>
       </c>
       <c r="N4" t="n">
-        <v>77500</v>
+        <v>2900</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0045</v>
+        <v>-0.0053</v>
       </c>
       <c r="S4" t="n">
-        <v>-103.09</v>
+        <v>20.29</v>
       </c>
       <c r="T4" t="n">
-        <v>103.09</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>trending up +9.0% — skewed fly</t>
+          <t>IV rank 92% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25T01:18</t>
+          <t>2026-08-28T05:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -75216,7 +75622,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2260</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -75224,13 +75630,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2493.71</v>
+        <v>79592.8</v>
       </c>
       <c r="H5" t="n">
-        <v>61.8</v>
+        <v>40.65</v>
       </c>
       <c r="I5" t="n">
-        <v>0.526</v>
+        <v>0.678</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -75238,271 +75644,37 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.22</v>
+        <v>4.59</v>
       </c>
       <c r="L5" t="n">
-        <v>2350</v>
+        <v>77000</v>
       </c>
       <c r="M5" t="n">
-        <v>2200</v>
+        <v>67000</v>
       </c>
       <c r="N5" t="n">
-        <v>2800</v>
+        <v>88000</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0451</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0168</v>
       </c>
       <c r="S5" t="n">
-        <v>-100.12</v>
+        <v>21.96</v>
       </c>
       <c r="T5" t="n">
-        <v>100.12</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>trending up +7.1% — skewed fly</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-27T21:01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>80016.2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="L6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>77000</v>
-      </c>
-      <c r="N6" t="n">
-        <v>88000</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.2841</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="S6" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="T6" t="n">
-        <v>99.38</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>IV rank 64% — default sell</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-27T21:01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>180</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>2503.53</v>
-      </c>
-      <c r="H7" t="n">
-        <v>31</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2800</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.0693</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.0029</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="T7" t="n">
-        <v>100.87</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>IV rank 64% — default sell</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-08-27T21:01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>iron_condor_wk</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>120</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2503.53</v>
-      </c>
-      <c r="H8" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Bearish</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2900</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.0053</v>
-      </c>
-      <c r="S8" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="T8" t="n">
-        <v>99.70999999999999</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>IV rank 92% rich — sell premium</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -75523,7 +75695,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28T03:54:26.433137 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-29T02:34:52.041360 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y815"/>
+  <dimension ref="A1:Y818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -74913,6 +74913,254 @@
         </is>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-08-29T07:52</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E816" t="n">
+        <v>60</v>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G816" t="n">
+        <v>77631.7</v>
+      </c>
+      <c r="H816" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I816" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K816" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L816" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M816" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N816" t="n">
+        <v>80000</v>
+      </c>
+      <c r="O816" t="n">
+        <v>0</v>
+      </c>
+      <c r="P816" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="Q816" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S816" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T816" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="U816" t="inlineStr">
+        <is>
+          <t>77631.7</t>
+        </is>
+      </c>
+      <c r="V816" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W816" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="X816" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="Y816" t="inlineStr">
+        <is>
+          <t>IV rank 37% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:33</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E817" t="n">
+        <v>70</v>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G817" t="n">
+        <v>77658.60000000001</v>
+      </c>
+      <c r="H817" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I817" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K817" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L817" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M817" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N817" t="n">
+        <v>81000</v>
+      </c>
+      <c r="O817" t="n">
+        <v>0</v>
+      </c>
+      <c r="P817" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="Q817" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="S817" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="T817" t="n">
+        <v>104.72</v>
+      </c>
+      <c r="U817" t="inlineStr"/>
+      <c r="X817" t="inlineStr"/>
+      <c r="Y817" t="inlineStr">
+        <is>
+          <t>IV rank 41% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:33</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E818" t="n">
+        <v>220</v>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G818" t="n">
+        <v>2433.66</v>
+      </c>
+      <c r="H818" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="I818" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K818" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L818" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M818" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N818" t="n">
+        <v>2560</v>
+      </c>
+      <c r="O818" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P818" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="Q818" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S818" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="T818" t="n">
+        <v>101.09</v>
+      </c>
+      <c r="U818" t="inlineStr"/>
+      <c r="X818" t="inlineStr"/>
+      <c r="Y818" t="inlineStr">
+        <is>
+          <t>IV rank 41% — default sell</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -74980,22 +75228,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C2" t="n">
         <v>97.7</v>
       </c>
       <c r="D2" t="n">
-        <v>6.08</v>
+        <v>6.09</v>
       </c>
       <c r="E2" t="n">
-        <v>2142.81</v>
+        <v>2144.63</v>
       </c>
       <c r="F2" t="n">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="G2" t="n">
-        <v>214.28</v>
+        <v>214.46</v>
       </c>
     </row>
     <row r="3">
@@ -75209,7 +75457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -75678,6 +75926,162 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:33</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>77658.60000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M6" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>81000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="T6" t="n">
+        <v>104.72</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>IV rank 41% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:33</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2433.66</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2560</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="T7" t="n">
+        <v>101.09</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>IV rank 41% — default sell</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -75695,7 +76099,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29T02:34:52.041360 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-29T22:06:35.493488 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y818"/>
+  <dimension ref="A1:Y824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -74511,7 +74511,7 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G811" t="n">
@@ -74556,7 +74556,17 @@
         <v>99.70999999999999</v>
       </c>
       <c r="U811" t="inlineStr"/>
-      <c r="X811" t="inlineStr"/>
+      <c r="V811" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="W811" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="X811" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="Y811" t="inlineStr">
         <is>
           <t>IV rank 92% rich — sell premium</t>
@@ -74589,7 +74599,7 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G812" t="n">
@@ -74634,7 +74644,17 @@
         <v>98.04000000000001</v>
       </c>
       <c r="U812" t="inlineStr"/>
-      <c r="X812" t="inlineStr"/>
+      <c r="V812" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="W812" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="X812" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="Y812" t="inlineStr">
         <is>
           <t>IV rank 96% rich — sell premium</t>
@@ -75031,7 +75051,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G817" t="n">
@@ -75075,8 +75095,22 @@
       <c r="T817" t="n">
         <v>104.72</v>
       </c>
-      <c r="U817" t="inlineStr"/>
-      <c r="X817" t="inlineStr"/>
+      <c r="U817" t="inlineStr">
+        <is>
+          <t>78223.1</t>
+        </is>
+      </c>
+      <c r="V817" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="W817" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="X817" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="Y817" t="inlineStr">
         <is>
           <t>IV rank 41% — default sell</t>
@@ -75109,7 +75143,7 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G818" t="n">
@@ -75153,11 +75187,521 @@
       <c r="T818" t="n">
         <v>101.09</v>
       </c>
-      <c r="U818" t="inlineStr"/>
-      <c r="X818" t="inlineStr"/>
+      <c r="U818" t="inlineStr">
+        <is>
+          <t>2462.06</t>
+        </is>
+      </c>
+      <c r="V818" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="W818" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="X818" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="Y818" t="inlineStr">
         <is>
           <t>IV rank 41% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-08-30T05:38</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E819" t="n">
+        <v>60</v>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G819" t="n">
+        <v>78120.60000000001</v>
+      </c>
+      <c r="H819" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I819" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K819" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L819" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M819" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N819" t="n">
+        <v>80000</v>
+      </c>
+      <c r="O819" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P819" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="Q819" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="S819" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T819" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="U819" t="inlineStr">
+        <is>
+          <t>78120.6</t>
+        </is>
+      </c>
+      <c r="V819" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W819" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="X819" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Y819" t="inlineStr">
+        <is>
+          <t>IV rank 39% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-08-30T05:38</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E820" t="n">
+        <v>210</v>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G820" t="n">
+        <v>2455.1</v>
+      </c>
+      <c r="H820" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I820" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K820" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L820" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M820" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N820" t="n">
+        <v>2560</v>
+      </c>
+      <c r="O820" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P820" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="Q820" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S820" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="T820" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="U820" t="inlineStr">
+        <is>
+          <t>2455.1</t>
+        </is>
+      </c>
+      <c r="V820" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W820" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="X820" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Y820" t="inlineStr">
+        <is>
+          <t>IV rank 54% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-08-30T15:01</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E821" t="n">
+        <v>70</v>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G821" t="n">
+        <v>78778.7</v>
+      </c>
+      <c r="H821" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I821" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K821" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L821" t="n">
+        <v>78800</v>
+      </c>
+      <c r="M821" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N821" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O821" t="n">
+        <v>0</v>
+      </c>
+      <c r="P821" t="n">
+        <v>0.1948</v>
+      </c>
+      <c r="Q821" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="S821" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="T821" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="U821" t="inlineStr"/>
+      <c r="X821" t="inlineStr"/>
+      <c r="Y821" t="inlineStr">
+        <is>
+          <t>IV rank 79% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-08-30T15:01</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E822" t="n">
+        <v>230</v>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G822" t="n">
+        <v>2477.06</v>
+      </c>
+      <c r="H822" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="I822" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K822" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L822" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M822" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N822" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O822" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P822" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="Q822" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="S822" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="T822" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="U822" t="inlineStr"/>
+      <c r="X822" t="inlineStr"/>
+      <c r="Y822" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-08-30T18:38</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E823" t="n">
+        <v>60</v>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G823" t="n">
+        <v>79168.39999999999</v>
+      </c>
+      <c r="H823" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I823" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K823" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="L823" t="n">
+        <v>77500</v>
+      </c>
+      <c r="M823" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N823" t="n">
+        <v>88000</v>
+      </c>
+      <c r="O823" t="n">
+        <v>0</v>
+      </c>
+      <c r="P823" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="Q823" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="S823" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="T823" t="n">
+        <v>101.69</v>
+      </c>
+      <c r="U823" t="inlineStr"/>
+      <c r="X823" t="inlineStr"/>
+      <c r="Y823" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-08-30T18:38</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E824" t="n">
+        <v>250</v>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G824" t="n">
+        <v>2516.46</v>
+      </c>
+      <c r="H824" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="I824" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K824" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L824" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M824" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N824" t="n">
+        <v>2900</v>
+      </c>
+      <c r="O824" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P824" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="Q824" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S824" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T824" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="U824" t="inlineStr"/>
+      <c r="X824" t="inlineStr"/>
+      <c r="Y824" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -75228,22 +75772,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C2" t="n">
         <v>97.7</v>
       </c>
       <c r="D2" t="n">
-        <v>6.09</v>
+        <v>6.15</v>
       </c>
       <c r="E2" t="n">
-        <v>2144.63</v>
+        <v>2169.3</v>
       </c>
       <c r="F2" t="n">
-        <v>5.43</v>
+        <v>5.44</v>
       </c>
       <c r="G2" t="n">
-        <v>214.46</v>
+        <v>216.93</v>
       </c>
     </row>
     <row r="3">
@@ -75303,22 +75847,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>58.8</v>
+        <v>63.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="E5" t="n">
-        <v>-310.39</v>
+        <v>-290.32</v>
       </c>
       <c r="F5" t="n">
-        <v>-18.26</v>
+        <v>-15.28</v>
       </c>
       <c r="G5" t="n">
-        <v>-31.04</v>
+        <v>-29.03</v>
       </c>
     </row>
     <row r="6">
@@ -75773,26 +76317,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27T21:01</t>
+          <t>2026-08-30T15:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -75800,77 +76344,77 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2503.53</v>
+        <v>78778.7</v>
       </c>
       <c r="H4" t="n">
-        <v>50.7</v>
+        <v>25.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.622</v>
+        <v>0.66</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.22</v>
+        <v>1.32</v>
       </c>
       <c r="L4" t="n">
-        <v>2400</v>
+        <v>78800</v>
       </c>
       <c r="M4" t="n">
-        <v>2200</v>
+        <v>76400</v>
       </c>
       <c r="N4" t="n">
-        <v>2900</v>
+        <v>82000</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0165</v>
+        <v>0.1948</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0053</v>
+        <v>-0.0132</v>
       </c>
       <c r="S4" t="n">
-        <v>20.29</v>
+        <v>11.56</v>
       </c>
       <c r="T4" t="n">
-        <v>99.70999999999999</v>
+        <v>100.44</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 92% rich — sell premium</t>
+          <t>IV rank 79% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28T05:22</t>
+          <t>2026-08-30T15:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -75878,58 +76422,58 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>79592.8</v>
+        <v>2477.06</v>
       </c>
       <c r="H5" t="n">
-        <v>40.65</v>
+        <v>37.95</v>
       </c>
       <c r="I5" t="n">
-        <v>0.678</v>
+        <v>0.712</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4.59</v>
+        <v>0.57</v>
       </c>
       <c r="L5" t="n">
-        <v>77000</v>
+        <v>2460</v>
       </c>
       <c r="M5" t="n">
-        <v>67000</v>
+        <v>2380</v>
       </c>
       <c r="N5" t="n">
-        <v>88000</v>
+        <v>2640</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0451</v>
+        <v>0.0815</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0168</v>
+        <v>-0.0036</v>
       </c>
       <c r="S5" t="n">
-        <v>21.96</v>
+        <v>13.73</v>
       </c>
       <c r="T5" t="n">
-        <v>98.04000000000001</v>
+        <v>101.27</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>IV rank 86% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-29T13:33</t>
+          <t>2026-08-30T18:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -75939,16 +76483,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -75956,58 +76500,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>77658.60000000001</v>
+        <v>79168.39999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>15.8</v>
+        <v>32.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.45</v>
+        <v>5.16</v>
       </c>
       <c r="L6" t="n">
-        <v>77600</v>
+        <v>77500</v>
       </c>
       <c r="M6" t="n">
-        <v>76000</v>
+        <v>60000</v>
       </c>
       <c r="N6" t="n">
-        <v>81000</v>
+        <v>88000</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1435</v>
+        <v>0.0605</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0163</v>
+        <v>-0.0179</v>
       </c>
       <c r="S6" t="n">
-        <v>7.28</v>
+        <v>18.31</v>
       </c>
       <c r="T6" t="n">
-        <v>104.72</v>
+        <v>101.69</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 41% — default sell</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-29T13:33</t>
+          <t>2026-08-30T18:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -76017,16 +76561,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -76034,51 +76578,51 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2433.66</v>
+        <v>2516.46</v>
       </c>
       <c r="H7" t="n">
-        <v>23.75</v>
+        <v>46.45</v>
       </c>
       <c r="I7" t="n">
-        <v>0.728</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.84</v>
+        <v>1.97</v>
       </c>
       <c r="L7" t="n">
-        <v>2440</v>
+        <v>2500</v>
       </c>
       <c r="M7" t="n">
-        <v>2360</v>
+        <v>1800</v>
       </c>
       <c r="N7" t="n">
-        <v>2560</v>
+        <v>2900</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0624</v>
+        <v>0.0188</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0046</v>
+        <v>-0.0039</v>
       </c>
       <c r="S7" t="n">
-        <v>8.91</v>
+        <v>25.8</v>
       </c>
       <c r="T7" t="n">
-        <v>101.09</v>
+        <v>99.2</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 41% — default sell</t>
+          <t>IV rank 89% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -76099,7 +76643,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29T22:06:35.493488 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-30T22:12:49.711296 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y824"/>
+  <dimension ref="A1:Y832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -75419,7 +75419,7 @@
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G821" t="n">
@@ -75464,7 +75464,17 @@
         <v>100.44</v>
       </c>
       <c r="U821" t="inlineStr"/>
-      <c r="X821" t="inlineStr"/>
+      <c r="V821" t="n">
+        <v>-29.46</v>
+      </c>
+      <c r="W821" t="n">
+        <v>-2.946</v>
+      </c>
+      <c r="X821" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="Y821" t="inlineStr">
         <is>
           <t>IV rank 79% rich — sell premium</t>
@@ -75497,7 +75507,7 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G822" t="n">
@@ -75542,7 +75552,17 @@
         <v>101.27</v>
       </c>
       <c r="U822" t="inlineStr"/>
-      <c r="X822" t="inlineStr"/>
+      <c r="V822" t="n">
+        <v>-39.03</v>
+      </c>
+      <c r="W822" t="n">
+        <v>-3.903</v>
+      </c>
+      <c r="X822" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="Y822" t="inlineStr">
         <is>
           <t>IV rank 86% rich — sell premium</t>
@@ -75653,7 +75673,7 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G824" t="n">
@@ -75698,10 +75718,710 @@
         <v>99.2</v>
       </c>
       <c r="U824" t="inlineStr"/>
-      <c r="X824" t="inlineStr"/>
+      <c r="V824" t="n">
+        <v>-39.27</v>
+      </c>
+      <c r="W824" t="n">
+        <v>-3.928</v>
+      </c>
+      <c r="X824" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="Y824" t="inlineStr">
         <is>
           <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-08-30T23:52</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E825" t="n">
+        <v>70</v>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G825" t="n">
+        <v>77553.3</v>
+      </c>
+      <c r="H825" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="I825" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K825" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L825" t="n">
+        <v>78200</v>
+      </c>
+      <c r="M825" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N825" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O825" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P825" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="Q825" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="S825" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="T825" t="n">
+        <v>100.43</v>
+      </c>
+      <c r="U825" t="inlineStr">
+        <is>
+          <t>77651.9</t>
+        </is>
+      </c>
+      <c r="V825" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="W825" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="X825" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Y825" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-08-30T23:52</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E826" t="n">
+        <v>240</v>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G826" t="n">
+        <v>2411.34</v>
+      </c>
+      <c r="H826" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="I826" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="K826" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L826" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M826" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N826" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O826" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P826" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="Q826" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S826" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="T826" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="U826" t="inlineStr"/>
+      <c r="V826" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="W826" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="X826" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Y826" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-08-30T23:52</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E827" t="n">
+        <v>270</v>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G827" t="n">
+        <v>2411.34</v>
+      </c>
+      <c r="H827" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="I827" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K827" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L827" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M827" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N827" t="n">
+        <v>2900</v>
+      </c>
+      <c r="O827" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P827" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="Q827" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S827" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="T827" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="U827" t="inlineStr"/>
+      <c r="X827" t="inlineStr"/>
+      <c r="Y827" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-08-31T03:13</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E828" t="n">
+        <v>210</v>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G828" t="n">
+        <v>2416.03</v>
+      </c>
+      <c r="H828" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I828" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="K828" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L828" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M828" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N828" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O828" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="P828" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="Q828" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S828" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="T828" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="U828" t="inlineStr">
+        <is>
+          <t>2416.03</t>
+        </is>
+      </c>
+      <c r="V828" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="W828" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="X828" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Y828" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-08-31T09:47</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E829" t="n">
+        <v>60</v>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G829" t="n">
+        <v>78725.8</v>
+      </c>
+      <c r="H829" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="I829" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K829" t="n">
+        <v>1</v>
+      </c>
+      <c r="L829" t="n">
+        <v>78600</v>
+      </c>
+      <c r="M829" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N829" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O829" t="n">
+        <v>0</v>
+      </c>
+      <c r="P829" t="n">
+        <v>0.9603</v>
+      </c>
+      <c r="Q829" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="S829" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T829" t="n">
+        <v>93.04000000000001</v>
+      </c>
+      <c r="U829" t="inlineStr">
+        <is>
+          <t>78725.8</t>
+        </is>
+      </c>
+      <c r="V829" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="W829" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="X829" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Y829" t="inlineStr">
+        <is>
+          <t>IV rank 45% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-08-31T09:47</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E830" t="n">
+        <v>210</v>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G830" t="n">
+        <v>2453.15</v>
+      </c>
+      <c r="H830" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I830" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K830" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L830" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M830" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N830" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O830" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="P830" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="Q830" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S830" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="T830" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="U830" t="inlineStr">
+        <is>
+          <t>2453.15</t>
+        </is>
+      </c>
+      <c r="V830" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="W830" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="X830" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Y830" t="inlineStr">
+        <is>
+          <t>IV rank 34% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-08-31T17:21</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E831" t="n">
+        <v>70</v>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G831" t="n">
+        <v>78606.60000000001</v>
+      </c>
+      <c r="H831" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I831" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K831" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L831" t="n">
+        <v>78600</v>
+      </c>
+      <c r="M831" t="n">
+        <v>76400</v>
+      </c>
+      <c r="N831" t="n">
+        <v>81200</v>
+      </c>
+      <c r="O831" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P831" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="Q831" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="S831" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="T831" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="U831" t="inlineStr"/>
+      <c r="X831" t="inlineStr"/>
+      <c r="Y831" t="inlineStr">
+        <is>
+          <t>IV rank 66% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-08-31T17:21</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E832" t="n">
+        <v>290</v>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G832" t="n">
+        <v>2468.51</v>
+      </c>
+      <c r="H832" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="I832" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K832" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L832" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M832" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N832" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O832" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P832" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="Q832" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S832" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="T832" t="n">
+        <v>99.01000000000001</v>
+      </c>
+      <c r="U832" t="inlineStr"/>
+      <c r="X832" t="inlineStr"/>
+      <c r="Y832" t="inlineStr">
+        <is>
+          <t>IV rank 76% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -75772,22 +76492,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C2" t="n">
-        <v>97.7</v>
+        <v>97.3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.15</v>
+        <v>5.36</v>
       </c>
       <c r="E2" t="n">
-        <v>2169.3</v>
+        <v>2137.5</v>
       </c>
       <c r="F2" t="n">
-        <v>5.44</v>
+        <v>5.26</v>
       </c>
       <c r="G2" t="n">
-        <v>216.93</v>
+        <v>213.75</v>
       </c>
     </row>
     <row r="3">
@@ -75843,51 +76563,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="C5" t="n">
-        <v>63.2</v>
+        <v>69.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="E5" t="n">
-        <v>-290.32</v>
+        <v>-326.87</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.28</v>
+        <v>-1.83</v>
       </c>
       <c r="G5" t="n">
-        <v>-29.03</v>
+        <v>-32.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>69.3</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>0.71</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>-326.87</v>
+        <v>-329.59</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.83</v>
+        <v>-16.48</v>
       </c>
       <c r="G6" t="n">
-        <v>-32.69</v>
+        <v>-32.96</v>
       </c>
     </row>
     <row r="7">
@@ -76317,7 +77037,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30T15:01</t>
+          <t>2026-08-30T18:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -76327,16 +77047,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -76344,58 +77064,58 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>78778.7</v>
+        <v>79168.39999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>25.6</v>
+        <v>32.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66</v>
+        <v>0.679</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.32</v>
+        <v>5.16</v>
       </c>
       <c r="L4" t="n">
-        <v>78800</v>
+        <v>77500</v>
       </c>
       <c r="M4" t="n">
-        <v>76400</v>
+        <v>60000</v>
       </c>
       <c r="N4" t="n">
-        <v>82000</v>
+        <v>88000</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1948</v>
+        <v>0.0605</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0132</v>
+        <v>-0.0179</v>
       </c>
       <c r="S4" t="n">
-        <v>11.56</v>
+        <v>18.31</v>
       </c>
       <c r="T4" t="n">
-        <v>100.44</v>
+        <v>101.69</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 79% rich — sell premium</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30T15:01</t>
+          <t>2026-08-30T23:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -76405,16 +77125,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -76422,13 +77142,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2477.06</v>
+        <v>2411.34</v>
       </c>
       <c r="H5" t="n">
-        <v>37.95</v>
+        <v>47.85</v>
       </c>
       <c r="I5" t="n">
-        <v>0.712</v>
+        <v>0.621</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -76436,44 +77156,44 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.57</v>
+        <v>2.03</v>
       </c>
       <c r="L5" t="n">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="M5" t="n">
-        <v>2380</v>
+        <v>1800</v>
       </c>
       <c r="N5" t="n">
-        <v>2640</v>
+        <v>2900</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0005</v>
+        <v>0.0002</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0815</v>
+        <v>0.0199</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0039</v>
       </c>
       <c r="S5" t="n">
-        <v>13.73</v>
+        <v>33.75</v>
       </c>
       <c r="T5" t="n">
-        <v>101.27</v>
+        <v>101.25</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 86% rich — sell premium</t>
+          <t>IV rank 89% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30T18:38</t>
+          <t>2026-08-31T17:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -76483,16 +77203,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -76500,58 +77220,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>79168.39999999999</v>
+        <v>78606.60000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>32.5</v>
+        <v>23.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.679</v>
+        <v>0.666</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.16</v>
+        <v>1.18</v>
       </c>
       <c r="L6" t="n">
-        <v>77500</v>
+        <v>78600</v>
       </c>
       <c r="M6" t="n">
-        <v>60000</v>
+        <v>76400</v>
       </c>
       <c r="N6" t="n">
-        <v>88000</v>
+        <v>81200</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0605</v>
+        <v>0.2291</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0179</v>
+        <v>-0.0138</v>
       </c>
       <c r="S6" t="n">
-        <v>18.31</v>
+        <v>10.96</v>
       </c>
       <c r="T6" t="n">
-        <v>101.69</v>
+        <v>101.05</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>IV rank 66% — default sell</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30T18:38</t>
+          <t>2026-08-31T17:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -76561,16 +77281,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -76578,51 +77298,51 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2516.46</v>
+        <v>2468.51</v>
       </c>
       <c r="H7" t="n">
-        <v>46.45</v>
+        <v>36.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.97</v>
+        <v>0.99</v>
       </c>
       <c r="L7" t="n">
-        <v>2500</v>
+        <v>2460</v>
       </c>
       <c r="M7" t="n">
-        <v>1800</v>
+        <v>2360</v>
       </c>
       <c r="N7" t="n">
-        <v>2900</v>
+        <v>2640</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0188</v>
+        <v>0.0882</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0039</v>
+        <v>-0.0034</v>
       </c>
       <c r="S7" t="n">
-        <v>25.8</v>
+        <v>16.99</v>
       </c>
       <c r="T7" t="n">
-        <v>99.2</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 89% rich — sell premium</t>
+          <t>IV rank 76% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -76643,7 +77363,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-30T22:12:49.711296 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-08-31T23:28:58.550211 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y832"/>
+  <dimension ref="A1:Y845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -75941,7 +75941,7 @@
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G827" t="n">
@@ -75986,7 +75986,17 @@
         <v>101.25</v>
       </c>
       <c r="U827" t="inlineStr"/>
-      <c r="X827" t="inlineStr"/>
+      <c r="V827" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="W827" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="X827" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="Y827" t="inlineStr">
         <is>
           <t>IV rank 89% rich — sell premium</t>
@@ -76295,7 +76305,7 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G831" t="n">
@@ -76339,8 +76349,22 @@
       <c r="T831" t="n">
         <v>101.05</v>
       </c>
-      <c r="U831" t="inlineStr"/>
-      <c r="X831" t="inlineStr"/>
+      <c r="U831" t="inlineStr">
+        <is>
+          <t>78701.6</t>
+        </is>
+      </c>
+      <c r="V831" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="W831" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="X831" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="Y831" t="inlineStr">
         <is>
           <t>IV rank 66% — default sell</t>
@@ -76373,7 +76397,7 @@
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G832" t="n">
@@ -76418,10 +76442,1132 @@
         <v>99.01000000000001</v>
       </c>
       <c r="U832" t="inlineStr"/>
-      <c r="X832" t="inlineStr"/>
+      <c r="V832" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="W832" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="X832" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="Y832" t="inlineStr">
         <is>
           <t>IV rank 76% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-09-01T01:09</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E833" t="n">
+        <v>60</v>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G833" t="n">
+        <v>78701.60000000001</v>
+      </c>
+      <c r="H833" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="I833" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K833" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L833" t="n">
+        <v>78500</v>
+      </c>
+      <c r="M833" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N833" t="n">
+        <v>90000</v>
+      </c>
+      <c r="O833" t="n">
+        <v>0</v>
+      </c>
+      <c r="P833" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="Q833" t="n">
+        <v>-0.0208</v>
+      </c>
+      <c r="S833" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="T833" t="n">
+        <v>98.09</v>
+      </c>
+      <c r="U833" t="inlineStr"/>
+      <c r="X833" t="inlineStr"/>
+      <c r="Y833" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-09-01T01:09</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E834" t="n">
+        <v>220</v>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G834" t="n">
+        <v>2472.49</v>
+      </c>
+      <c r="H834" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="I834" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K834" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L834" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M834" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N834" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O834" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P834" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="Q834" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S834" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="T834" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="U834" t="inlineStr">
+        <is>
+          <t>2472.49</t>
+        </is>
+      </c>
+      <c r="V834" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="W834" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="X834" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Y834" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-09-01T01:09</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E835" t="n">
+        <v>10</v>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G835" t="n">
+        <v>2472.49</v>
+      </c>
+      <c r="H835" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="I835" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K835" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L835" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M835" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N835" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O835" t="n">
+        <v>0</v>
+      </c>
+      <c r="P835" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q835" t="n">
+        <v>0</v>
+      </c>
+      <c r="S835" t="n">
+        <v>0</v>
+      </c>
+      <c r="T835" t="n">
+        <v>0</v>
+      </c>
+      <c r="U835" t="inlineStr"/>
+      <c r="X835" t="inlineStr"/>
+      <c r="Y835" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-09-01T06:14</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E836" t="n">
+        <v>70</v>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G836" t="n">
+        <v>79020.39999999999</v>
+      </c>
+      <c r="H836" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="I836" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K836" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L836" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M836" t="n">
+        <v>78800</v>
+      </c>
+      <c r="N836" t="n">
+        <v>81200</v>
+      </c>
+      <c r="O836" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P836" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="Q836" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="S836" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="T836" t="n">
+        <v>106.52</v>
+      </c>
+      <c r="U836" t="inlineStr">
+        <is>
+          <t>79020.4</t>
+        </is>
+      </c>
+      <c r="V836" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="W836" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="X836" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Y836" t="inlineStr">
+        <is>
+          <t>IV rank 77% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-09-01T06:14</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E837" t="n">
+        <v>690</v>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G837" t="n">
+        <v>79020.39999999999</v>
+      </c>
+      <c r="H837" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="I837" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K837" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L837" t="n">
+        <v>79000</v>
+      </c>
+      <c r="M837" t="n">
+        <v>78800</v>
+      </c>
+      <c r="N837" t="n">
+        <v>81200</v>
+      </c>
+      <c r="O837" t="n">
+        <v>0</v>
+      </c>
+      <c r="P837" t="n">
+        <v>-0.6873</v>
+      </c>
+      <c r="Q837" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="S837" t="n">
+        <v>-100.46</v>
+      </c>
+      <c r="T837" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="U837" t="inlineStr">
+        <is>
+          <t>79020.4</t>
+        </is>
+      </c>
+      <c r="V837" t="n">
+        <v>-104.6</v>
+      </c>
+      <c r="W837" t="n">
+        <v>-10.46</v>
+      </c>
+      <c r="X837" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Y837" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-09-01T06:14</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E838" t="n">
+        <v>220</v>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G838" t="n">
+        <v>2479.16</v>
+      </c>
+      <c r="H838" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I838" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K838" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L838" t="n">
+        <v>2470</v>
+      </c>
+      <c r="M838" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N838" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O838" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P838" t="n">
+        <v>0.2052</v>
+      </c>
+      <c r="Q838" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S838" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="T838" t="n">
+        <v>101.42</v>
+      </c>
+      <c r="U838" t="inlineStr">
+        <is>
+          <t>2479.16</t>
+        </is>
+      </c>
+      <c r="V838" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="W838" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="X838" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Y838" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-09-01T11:42</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E839" t="n">
+        <v>12620</v>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G839" t="n">
+        <v>78162.60000000001</v>
+      </c>
+      <c r="H839" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I839" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K839" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L839" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M839" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N839" t="n">
+        <v>78600</v>
+      </c>
+      <c r="O839" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P839" t="n">
+        <v>-0.4538</v>
+      </c>
+      <c r="Q839" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="S839" t="n">
+        <v>-99.7</v>
+      </c>
+      <c r="T839" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="U839" t="inlineStr">
+        <is>
+          <t>78162.6</t>
+        </is>
+      </c>
+      <c r="V839" t="n">
+        <v>-104.75</v>
+      </c>
+      <c r="W839" t="n">
+        <v>-10.475</v>
+      </c>
+      <c r="X839" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Y839" t="inlineStr">
+        <is>
+          <t>IV rank 0% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-09-01T11:42</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E840" t="n">
+        <v>57970</v>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G840" t="n">
+        <v>78162.60000000001</v>
+      </c>
+      <c r="H840" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K840" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L840" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M840" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N840" t="n">
+        <v>78600</v>
+      </c>
+      <c r="O840" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P840" t="n">
+        <v>-0.1827</v>
+      </c>
+      <c r="Q840" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S840" t="n">
+        <v>-98.55</v>
+      </c>
+      <c r="T840" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="U840" t="inlineStr">
+        <is>
+          <t>78162.6</t>
+        </is>
+      </c>
+      <c r="V840" t="n">
+        <v>-104.35</v>
+      </c>
+      <c r="W840" t="n">
+        <v>-10.435</v>
+      </c>
+      <c r="X840" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Y840" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-09-01T11:42</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E841" t="n">
+        <v>18510</v>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G841" t="n">
+        <v>2462.96</v>
+      </c>
+      <c r="H841" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I841" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K841" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L841" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M841" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N841" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O841" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P841" t="n">
+        <v>-0.3675</v>
+      </c>
+      <c r="Q841" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="S841" t="n">
+        <v>-99.95</v>
+      </c>
+      <c r="T841" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="U841" t="inlineStr">
+        <is>
+          <t>2462.96</t>
+        </is>
+      </c>
+      <c r="V841" t="n">
+        <v>-103.66</v>
+      </c>
+      <c r="W841" t="n">
+        <v>-10.366</v>
+      </c>
+      <c r="X841" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Y841" t="inlineStr">
+        <is>
+          <t>IV rank 7% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-09-01T15:33</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E842" t="n">
+        <v>70</v>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G842" t="n">
+        <v>77863.3</v>
+      </c>
+      <c r="H842" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I842" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K842" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L842" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M842" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N842" t="n">
+        <v>81600</v>
+      </c>
+      <c r="O842" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P842" t="n">
+        <v>0.2052</v>
+      </c>
+      <c r="Q842" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="S842" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="T842" t="n">
+        <v>101.32</v>
+      </c>
+      <c r="U842" t="inlineStr"/>
+      <c r="X842" t="inlineStr"/>
+      <c r="Y842" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-09-01T15:33</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E843" t="n">
+        <v>230</v>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G843" t="n">
+        <v>2444.15</v>
+      </c>
+      <c r="H843" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="I843" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K843" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L843" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M843" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N843" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O843" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P843" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="Q843" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S843" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="T843" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="U843" t="inlineStr"/>
+      <c r="X843" t="inlineStr"/>
+      <c r="Y843" t="inlineStr">
+        <is>
+          <t>IV rank 70% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-09-01T18:50</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E844" t="n">
+        <v>310</v>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G844" t="n">
+        <v>2399.95</v>
+      </c>
+      <c r="H844" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="I844" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="K844" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L844" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M844" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N844" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O844" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="P844" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="Q844" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S844" t="n">
+        <v>-101.56</v>
+      </c>
+      <c r="T844" t="n">
+        <v>101.56</v>
+      </c>
+      <c r="U844" t="inlineStr"/>
+      <c r="X844" t="inlineStr"/>
+      <c r="Y844" t="inlineStr">
+        <is>
+          <t>trending down -4.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-09-01T18:50</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E845" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G845" t="n">
+        <v>2399.95</v>
+      </c>
+      <c r="H845" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="I845" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K845" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L845" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M845" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N845" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O845" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P845" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Q845" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="S845" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T845" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U845" t="inlineStr"/>
+      <c r="X845" t="inlineStr"/>
+      <c r="Y845" t="inlineStr">
+        <is>
+          <t>trending down -4.1% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -76492,22 +77638,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C2" t="n">
         <v>97.3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.36</v>
+        <v>5.45</v>
       </c>
       <c r="E2" t="n">
-        <v>2137.5</v>
+        <v>2180.3</v>
       </c>
       <c r="F2" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="G2" t="n">
-        <v>213.75</v>
+        <v>218.03</v>
       </c>
     </row>
     <row r="3">
@@ -76563,51 +77709,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>69.3</v>
+        <v>61.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.71</v>
+        <v>0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>-326.87</v>
+        <v>-312.28</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.83</v>
+        <v>-14.87</v>
       </c>
       <c r="G5" t="n">
-        <v>-32.69</v>
+        <v>-31.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>69.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.21</v>
+        <v>0.71</v>
       </c>
       <c r="E6" t="n">
-        <v>-329.59</v>
+        <v>-326.87</v>
       </c>
       <c r="F6" t="n">
-        <v>-16.48</v>
+        <v>-1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>-32.96</v>
+        <v>-32.69</v>
       </c>
     </row>
     <row r="7">
@@ -76667,7 +77813,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
         <v>1.4</v>
@@ -76676,13 +77822,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-7011.98</v>
+        <v>-7220.39</v>
       </c>
       <c r="F9" t="n">
-        <v>-100.17</v>
+        <v>-100.28</v>
       </c>
       <c r="G9" t="n">
-        <v>-701.2</v>
+        <v>-722.04</v>
       </c>
     </row>
     <row r="10">
@@ -76692,7 +77838,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -76701,13 +77847,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-8939.559999999999</v>
+        <v>-9148.51</v>
       </c>
       <c r="F10" t="n">
-        <v>-103.95</v>
+        <v>-103.96</v>
       </c>
       <c r="G10" t="n">
-        <v>-893.96</v>
+        <v>-914.85</v>
       </c>
     </row>
   </sheetData>
@@ -76721,7 +77867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -77115,12 +78261,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30T23:52</t>
+          <t>2026-09-01T01:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -77130,11 +78276,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -77142,13 +78288,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2411.34</v>
+        <v>78701.60000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>47.85</v>
+        <v>34.95</v>
       </c>
       <c r="I5" t="n">
-        <v>0.621</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -77156,63 +78302,63 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.03</v>
+        <v>1.06</v>
       </c>
       <c r="L5" t="n">
-        <v>2450</v>
+        <v>78500</v>
       </c>
       <c r="M5" t="n">
-        <v>1800</v>
+        <v>75000</v>
       </c>
       <c r="N5" t="n">
-        <v>2900</v>
+        <v>90000</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0199</v>
+        <v>0.0324</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0208</v>
       </c>
       <c r="S5" t="n">
-        <v>33.75</v>
+        <v>21.91</v>
       </c>
       <c r="T5" t="n">
-        <v>101.25</v>
+        <v>98.09</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 89% rich — sell premium</t>
+          <t>IV rank 93% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31T17:21</t>
+          <t>2026-09-01T01:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -77220,13 +78366,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>78606.60000000001</v>
+        <v>2472.49</v>
       </c>
       <c r="H6" t="n">
-        <v>23.7</v>
+        <v>47.45</v>
       </c>
       <c r="I6" t="n">
-        <v>0.666</v>
+        <v>0.339</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -77234,49 +78380,49 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.18</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>78600</v>
+        <v>2450</v>
       </c>
       <c r="M6" t="n">
-        <v>76400</v>
+        <v>2300</v>
       </c>
       <c r="N6" t="n">
-        <v>81200</v>
+        <v>3000</v>
       </c>
       <c r="O6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2291</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0138</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>10.96</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>101.05</v>
+        <v>0</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 66% — default sell</t>
+          <t>IV rank 87% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31T17:21</t>
+          <t>2026-09-01T15:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -77286,11 +78432,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -77298,51 +78444,285 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2468.51</v>
+        <v>77863.3</v>
       </c>
       <c r="H7" t="n">
-        <v>36.25</v>
+        <v>28.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.698</v>
+        <v>0.702</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.99</v>
+        <v>0.57</v>
       </c>
       <c r="L7" t="n">
-        <v>2460</v>
+        <v>78000</v>
       </c>
       <c r="M7" t="n">
-        <v>2360</v>
+        <v>78000</v>
       </c>
       <c r="N7" t="n">
-        <v>2640</v>
+        <v>81600</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0882</v>
+        <v>0.2052</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0034</v>
+        <v>-0.0118</v>
       </c>
       <c r="S7" t="n">
-        <v>16.99</v>
+        <v>10.68</v>
       </c>
       <c r="T7" t="n">
-        <v>99.01000000000001</v>
+        <v>101.32</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 76% rich — sell premium</t>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-01T15:33</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>230</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2444.15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2440</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S8" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>IV rank 70% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-01T18:50</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>310</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2399.95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-101.56</v>
+      </c>
+      <c r="T9" t="n">
+        <v>101.56</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>trending down -4.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-01T18:50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2399.95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-100.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>trending down -4.1% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -77363,7 +78743,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-08-31T23:28:58.550211 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-01T22:10:17.143186 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y845"/>
+  <dimension ref="A1:Y850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -64421,7 +64421,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G701" t="n">
@@ -64466,7 +64466,17 @@
         <v>100.12</v>
       </c>
       <c r="U701" t="inlineStr"/>
-      <c r="X701" t="inlineStr"/>
+      <c r="V701" t="n">
+        <v>80.23</v>
+      </c>
+      <c r="W701" t="n">
+        <v>8.023</v>
+      </c>
+      <c r="X701" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="Y701" t="inlineStr">
         <is>
           <t>trending up +7.1% — skewed fly</t>
@@ -77285,7 +77295,7 @@
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G842" t="n">
@@ -77329,8 +77339,22 @@
       <c r="T842" t="n">
         <v>101.32</v>
       </c>
-      <c r="U842" t="inlineStr"/>
-      <c r="X842" t="inlineStr"/>
+      <c r="U842" t="inlineStr">
+        <is>
+          <t>77324.0</t>
+        </is>
+      </c>
+      <c r="V842" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="W842" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="X842" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="Y842" t="inlineStr">
         <is>
           <t>IV rank 87% rich — sell premium</t>
@@ -77363,7 +77387,7 @@
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G843" t="n">
@@ -77407,8 +77431,22 @@
       <c r="T843" t="n">
         <v>98.58</v>
       </c>
-      <c r="U843" t="inlineStr"/>
-      <c r="X843" t="inlineStr"/>
+      <c r="U843" t="inlineStr">
+        <is>
+          <t>2413.49</t>
+        </is>
+      </c>
+      <c r="V843" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="W843" t="n">
+        <v>1.541</v>
+      </c>
+      <c r="X843" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="Y843" t="inlineStr">
         <is>
           <t>IV rank 70% rich — sell premium</t>
@@ -77441,7 +77479,7 @@
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G844" t="n">
@@ -77485,8 +77523,22 @@
       <c r="T844" t="n">
         <v>101.56</v>
       </c>
-      <c r="U844" t="inlineStr"/>
-      <c r="X844" t="inlineStr"/>
+      <c r="U844" t="inlineStr">
+        <is>
+          <t>2413.49</t>
+        </is>
+      </c>
+      <c r="V844" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="W844" t="n">
+        <v>4.976</v>
+      </c>
+      <c r="X844" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="Y844" t="inlineStr">
         <is>
           <t>trending down -4.1% — skewed fly</t>
@@ -77568,6 +77620,434 @@
       <c r="Y845" t="inlineStr">
         <is>
           <t>trending down -4.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-09-02T06:08</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E846" t="n">
+        <v>70</v>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G846" t="n">
+        <v>77687.2</v>
+      </c>
+      <c r="H846" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="I846" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K846" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L846" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M846" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N846" t="n">
+        <v>79000</v>
+      </c>
+      <c r="O846" t="n">
+        <v>0</v>
+      </c>
+      <c r="P846" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="Q846" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="S846" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="T846" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="U846" t="inlineStr">
+        <is>
+          <t>77687.2</t>
+        </is>
+      </c>
+      <c r="V846" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="W846" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="X846" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Y846" t="inlineStr">
+        <is>
+          <t>IV rank 81% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-09-02T06:08</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E847" t="n">
+        <v>220</v>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G847" t="n">
+        <v>2419.72</v>
+      </c>
+      <c r="H847" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="I847" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K847" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L847" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M847" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N847" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O847" t="n">
+        <v>0</v>
+      </c>
+      <c r="P847" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="Q847" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S847" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="T847" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="U847" t="inlineStr">
+        <is>
+          <t>2419.72</t>
+        </is>
+      </c>
+      <c r="V847" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="W847" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="X847" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Y847" t="inlineStr">
+        <is>
+          <t>IV rank 68% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-09-02T15:11</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E848" t="n">
+        <v>70</v>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G848" t="n">
+        <v>76800.89999999999</v>
+      </c>
+      <c r="H848" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="I848" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K848" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L848" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M848" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N848" t="n">
+        <v>81600</v>
+      </c>
+      <c r="O848" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P848" t="n">
+        <v>0.1428</v>
+      </c>
+      <c r="Q848" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="S848" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="T848" t="n">
+        <v>102.19</v>
+      </c>
+      <c r="U848" t="inlineStr"/>
+      <c r="X848" t="inlineStr"/>
+      <c r="Y848" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-09-02T15:11</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E849" t="n">
+        <v>230</v>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G849" t="n">
+        <v>2382.09</v>
+      </c>
+      <c r="H849" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="I849" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="K849" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L849" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M849" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N849" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O849" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P849" t="n">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="Q849" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S849" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="T849" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="U849" t="inlineStr"/>
+      <c r="V849" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="W849" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="X849" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Y849" t="inlineStr">
+        <is>
+          <t>IV rank 84% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09-02T21:19</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E850" t="n">
+        <v>220</v>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G850" t="n">
+        <v>2391.13</v>
+      </c>
+      <c r="H850" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="I850" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K850" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L850" t="n">
+        <v>2390</v>
+      </c>
+      <c r="M850" t="n">
+        <v>2320</v>
+      </c>
+      <c r="N850" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O850" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P850" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="Q850" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="S850" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="T850" t="n">
+        <v>98.01000000000001</v>
+      </c>
+      <c r="U850" t="inlineStr"/>
+      <c r="X850" t="inlineStr"/>
+      <c r="Y850" t="inlineStr">
+        <is>
+          <t>IV rank 52% — default sell</t>
         </is>
       </c>
     </row>
@@ -77638,22 +78118,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C2" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="E2" t="n">
-        <v>2180.3</v>
+        <v>2229.47</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="G2" t="n">
-        <v>218.03</v>
+        <v>222.95</v>
       </c>
     </row>
     <row r="3">
@@ -77709,51 +78189,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="C5" t="n">
-        <v>61.9</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>-312.28</v>
+        <v>-277.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-14.87</v>
+        <v>-1.54</v>
       </c>
       <c r="G5" t="n">
-        <v>-31.23</v>
+        <v>-27.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>69.3</v>
+        <v>61.9</v>
       </c>
       <c r="D6" t="n">
-        <v>0.71</v>
+        <v>0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>-326.87</v>
+        <v>-312.28</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.83</v>
+        <v>-14.87</v>
       </c>
       <c r="G6" t="n">
-        <v>-32.69</v>
+        <v>-31.23</v>
       </c>
     </row>
     <row r="7">
@@ -77763,22 +78243,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>-630.21</v>
+        <v>-549.98</v>
       </c>
       <c r="F7" t="n">
-        <v>-90.03</v>
+        <v>-68.75</v>
       </c>
       <c r="G7" t="n">
-        <v>-63.02</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="8">
@@ -77867,7 +78347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -78105,17 +78585,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25T01:18</t>
+          <t>2026-08-30T18:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -78124,7 +78604,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2260</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -78132,13 +78612,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2493.71</v>
+        <v>79168.39999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>61.8</v>
+        <v>32.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.526</v>
+        <v>0.679</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -78146,44 +78626,44 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.22</v>
+        <v>5.16</v>
       </c>
       <c r="L3" t="n">
-        <v>2350</v>
+        <v>77500</v>
       </c>
       <c r="M3" t="n">
-        <v>2200</v>
+        <v>60000</v>
       </c>
       <c r="N3" t="n">
-        <v>2800</v>
+        <v>88000</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0605</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0003</v>
+        <v>-0.0179</v>
       </c>
       <c r="S3" t="n">
-        <v>-100.12</v>
+        <v>18.31</v>
       </c>
       <c r="T3" t="n">
-        <v>100.12</v>
+        <v>101.69</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>trending up +7.1% — skewed fly</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30T18:38</t>
+          <t>2026-09-01T01:09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -78198,7 +78678,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -78210,51 +78690,51 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>79168.39999999999</v>
+        <v>78701.60000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>32.5</v>
+        <v>34.95</v>
       </c>
       <c r="I4" t="n">
-        <v>0.679</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.16</v>
+        <v>1.06</v>
       </c>
       <c r="L4" t="n">
-        <v>77500</v>
+        <v>78500</v>
       </c>
       <c r="M4" t="n">
-        <v>60000</v>
+        <v>75000</v>
       </c>
       <c r="N4" t="n">
-        <v>88000</v>
+        <v>90000</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0605</v>
+        <v>0.0324</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0179</v>
+        <v>-0.0208</v>
       </c>
       <c r="S4" t="n">
-        <v>18.31</v>
+        <v>21.91</v>
       </c>
       <c r="T4" t="n">
-        <v>101.69</v>
+        <v>98.09</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>IV rank 93% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -78266,7 +78746,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -78280,7 +78760,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -78288,13 +78768,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>78701.60000000001</v>
+        <v>2472.49</v>
       </c>
       <c r="H5" t="n">
-        <v>34.95</v>
+        <v>47.45</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.339</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -78302,44 +78782,44 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.06</v>
+        <v>0.51</v>
       </c>
       <c r="L5" t="n">
-        <v>78500</v>
+        <v>2450</v>
       </c>
       <c r="M5" t="n">
-        <v>75000</v>
+        <v>2300</v>
       </c>
       <c r="N5" t="n">
-        <v>90000</v>
+        <v>3000</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0324</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0208</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>21.91</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>98.09</v>
+        <v>0</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 93% rich — sell premium</t>
+          <t>IV rank 87% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01T01:09</t>
+          <t>2026-09-01T18:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -78349,7 +78829,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -78358,7 +78838,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>2860</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -78366,58 +78846,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2472.49</v>
+        <v>2399.95</v>
       </c>
       <c r="H6" t="n">
-        <v>47.45</v>
+        <v>44.85</v>
       </c>
       <c r="I6" t="n">
-        <v>0.339</v>
+        <v>0.475</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0.82</v>
       </c>
       <c r="L6" t="n">
         <v>2450</v>
       </c>
       <c r="M6" t="n">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="N6" t="n">
         <v>3000</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-100.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>100.1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 87% rich — sell premium</t>
+          <t>trending down -4.1% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01T15:33</t>
+          <t>2026-09-02T15:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -78432,7 +78912,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -78444,13 +78924,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>77863.3</v>
+        <v>76800.89999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>28.5</v>
+        <v>28.45</v>
       </c>
       <c r="I7" t="n">
-        <v>0.702</v>
+        <v>0.66</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -78458,13 +78938,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="L7" t="n">
-        <v>78000</v>
+        <v>77000</v>
       </c>
       <c r="M7" t="n">
-        <v>78000</v>
+        <v>77000</v>
       </c>
       <c r="N7" t="n">
         <v>81600</v>
@@ -78473,16 +78953,16 @@
         <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2052</v>
+        <v>0.1428</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0118</v>
+        <v>-0.0095</v>
       </c>
       <c r="S7" t="n">
-        <v>10.68</v>
+        <v>9.81</v>
       </c>
       <c r="T7" t="n">
-        <v>101.32</v>
+        <v>102.19</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -78495,7 +78975,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01T15:33</t>
+          <t>2026-09-02T21:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -78510,11 +78990,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -78522,207 +79002,51 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2444.15</v>
+        <v>2391.13</v>
       </c>
       <c r="H8" t="n">
-        <v>35.85</v>
+        <v>27.1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.657</v>
+        <v>0.675</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="L8" t="n">
-        <v>2440</v>
+        <v>2390</v>
       </c>
       <c r="M8" t="n">
-        <v>2360</v>
+        <v>2320</v>
       </c>
       <c r="N8" t="n">
-        <v>2640</v>
+        <v>2600</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0898</v>
+        <v>0.1081</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.004</v>
+        <v>-0.0038</v>
       </c>
       <c r="S8" t="n">
-        <v>16.42</v>
+        <v>11.99</v>
       </c>
       <c r="T8" t="n">
-        <v>98.58</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>IV rank 70% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-01T18:50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>broken_wing_butterfly</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>310</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2399.95</v>
-      </c>
-      <c r="H9" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2420</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2360</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2640</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.0693</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-101.56</v>
-      </c>
-      <c r="T9" t="n">
-        <v>101.56</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>trending down -4.1% — skewed fly</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-01T18:50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>broken_wing_butterfly_wk</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2860</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2399.95</v>
-      </c>
-      <c r="H10" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2450</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2400</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3000</v>
-      </c>
-      